--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-04-17</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-04-17</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-04-17</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-04-17</t>
+    <t>Price_2026-04-24</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-04-24</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-04-24</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-04-24</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-04-24</t>
   </si>
   <si>
     <t>RS_Score_2026-04-17</t>
@@ -43,159 +46,156 @@
     <t>RS_Score_2026-04-03</t>
   </si>
   <si>
-    <t>RS_Score_2026-03-27</t>
-  </si>
-  <si>
     <t>HINDALCO</t>
   </si>
   <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>ADANIENT</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
     <t>TATASTEEL</t>
   </si>
   <si>
     <t>TITAN</t>
   </si>
   <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
     <t>POWERGRID</t>
   </si>
   <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>ADANIPORTS</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
     <t>SHRIRAMFIN</t>
   </si>
   <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
     <t>LT</t>
   </si>
   <si>
-    <t>ADANIENT</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>BEL</t>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
   </si>
   <si>
     <t>TMPV</t>
   </si>
   <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>NESTLEIND</t>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
   </si>
   <si>
     <t>EICHERMOT</t>
   </si>
   <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>ETERNAL</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
   </si>
   <si>
     <t>TECHM</t>
   </si>
   <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>ETERNAL</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>INFY</t>
   </si>
   <si>
     <t>HCLTECH</t>
   </si>
   <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
     <t>2026-04-17</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
   </si>
 </sst>
 </file>
@@ -722,28 +722,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>1039</v>
+        <v>1048.35</v>
       </c>
       <c r="C2" s="2">
-        <v>28.15</v>
+        <v>27.17</v>
       </c>
       <c r="D2" s="2">
-        <v>11.66</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="E2" s="2">
-        <v>10.93</v>
+        <v>22.66</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H2" s="2">
         <v>92</v>
       </c>
       <c r="I2" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>60</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>212.12</v>
+        <v>1421.3</v>
       </c>
       <c r="C3" s="2">
-        <v>27.19</v>
+        <v>17.61</v>
       </c>
       <c r="D3" s="2">
-        <v>12.52</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E3" s="2">
-        <v>8.539999999999999</v>
+        <v>20.12</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="H3" s="2">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="I3" s="2">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>4525.9</v>
+        <v>4297.3</v>
       </c>
       <c r="C4" s="2">
-        <v>19.09</v>
+        <v>6.17</v>
       </c>
       <c r="D4" s="2">
-        <v>14.49</v>
+        <v>3.02</v>
       </c>
       <c r="E4" s="2">
-        <v>10.64</v>
+        <v>27.68</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="H4" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I4" s="2">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>318.1</v>
+        <v>2287.6</v>
       </c>
       <c r="C5" s="2">
-        <v>19.54</v>
+        <v>0.43</v>
       </c>
       <c r="D5" s="2">
-        <v>18.96</v>
+        <v>1.67</v>
       </c>
       <c r="E5" s="2">
-        <v>6.57</v>
+        <v>25.84</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H5" s="2">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="I5" s="2">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>284.05</v>
+        <v>401.85</v>
       </c>
       <c r="C6" s="2">
-        <v>20.02</v>
+        <v>25.51</v>
       </c>
       <c r="D6" s="2">
-        <v>14.48</v>
+        <v>11.04</v>
       </c>
       <c r="E6" s="2">
-        <v>7.29</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H6" s="2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I6" s="2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>1573.4</v>
+        <v>210.07</v>
       </c>
       <c r="C7" s="2">
-        <v>4.5</v>
+        <v>26.26</v>
       </c>
       <c r="D7" s="2">
-        <v>12.14</v>
+        <v>4</v>
       </c>
       <c r="E7" s="2">
-        <v>15.23</v>
+        <v>10.11</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="H7" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="I7" s="2">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>393.6</v>
+        <v>4410</v>
       </c>
       <c r="C8" s="2">
-        <v>22.8</v>
+        <v>14.7</v>
       </c>
       <c r="D8" s="2">
-        <v>13.19</v>
+        <v>3.57</v>
       </c>
       <c r="E8" s="2">
-        <v>2.67</v>
+        <v>13.09</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H8" s="2">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="I8" s="2">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>1036.95</v>
+        <v>284.8</v>
       </c>
       <c r="C9" s="2">
-        <v>25.21</v>
+        <v>22.27</v>
       </c>
       <c r="D9" s="2">
-        <v>7.78</v>
+        <v>9.34</v>
       </c>
       <c r="E9" s="2">
-        <v>3.22</v>
+        <v>6.25</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H9" s="2">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I9" s="2">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>4096.1</v>
+        <v>1585.1</v>
       </c>
       <c r="C10" s="2">
-        <v>2.82</v>
+        <v>5.39</v>
       </c>
       <c r="D10" s="2">
-        <v>4.46</v>
+        <v>1.5</v>
       </c>
       <c r="E10" s="2">
-        <v>15.62</v>
+        <v>17.92</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H10" s="2">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="I10" s="2">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>2218.3</v>
+        <v>316.4</v>
       </c>
       <c r="C11" s="2">
-        <v>0.02</v>
+        <v>20.83</v>
       </c>
       <c r="D11" s="2">
-        <v>11.17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E11" s="2">
-        <v>12.3</v>
+        <v>5.82</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="H11" s="2">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="I11" s="2">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>4107.7</v>
+        <v>1011.3</v>
       </c>
       <c r="C12" s="2">
-        <v>-2.56</v>
+        <v>19.38</v>
       </c>
       <c r="D12" s="2">
-        <v>10.4</v>
+        <v>-4.84</v>
       </c>
       <c r="E12" s="2">
-        <v>13.02</v>
+        <v>11.92</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="H12" s="2">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="I12" s="2">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,25 +1074,25 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>1359.1</v>
+        <v>1365.9</v>
       </c>
       <c r="C13" s="2">
-        <v>6.18</v>
+        <v>7.32</v>
       </c>
       <c r="D13" s="2">
-        <v>3.63</v>
+        <v>1.83</v>
       </c>
       <c r="E13" s="2">
-        <v>10.67</v>
+        <v>14.52</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
+        <v>78</v>
+      </c>
+      <c r="H13" s="2">
         <v>88</v>
-      </c>
-      <c r="H13" s="2">
-        <v>54</v>
       </c>
       <c r="I13" s="2">
         <v>54</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>462.75</v>
+        <v>1255.7</v>
       </c>
       <c r="C14" s="2">
-        <v>14.14</v>
+        <v>13.6</v>
       </c>
       <c r="D14" s="2">
-        <v>5.83</v>
+        <v>0.86</v>
       </c>
       <c r="E14" s="2">
-        <v>5.33</v>
+        <v>10.76</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H14" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I14" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>360.1</v>
+        <v>456</v>
       </c>
       <c r="C15" s="2">
-        <v>1.02</v>
+        <v>20.32</v>
       </c>
       <c r="D15" s="2">
-        <v>-0.77</v>
+        <v>7.03</v>
       </c>
       <c r="E15" s="2">
-        <v>12.81</v>
+        <v>3.14</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H15" s="2">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="I15" s="2">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>9773.5</v>
+        <v>444.45</v>
       </c>
       <c r="C16" s="2">
-        <v>7.58</v>
+        <v>15.19</v>
       </c>
       <c r="D16" s="2">
-        <v>2.92</v>
+        <v>2.07</v>
       </c>
       <c r="E16" s="2">
-        <v>7.28</v>
+        <v>7.24</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
+        <v>76</v>
+      </c>
+      <c r="H16" s="2">
+        <v>72</v>
+      </c>
+      <c r="I16" s="2">
         <v>84</v>
-      </c>
-      <c r="H16" s="2">
-        <v>60</v>
-      </c>
-      <c r="I16" s="2">
-        <v>68</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>1240.3</v>
+        <v>7732.5</v>
       </c>
       <c r="C17" s="2">
-        <v>7.8</v>
+        <v>10.46</v>
       </c>
       <c r="D17" s="2">
-        <v>3.43</v>
+        <v>7.37</v>
       </c>
       <c r="E17" s="2">
-        <v>6.26</v>
+        <v>4.31</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H17" s="2">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I17" s="2">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>7699</v>
+        <v>1174</v>
       </c>
       <c r="C18" s="2">
-        <v>7.06</v>
+        <v>2.79</v>
       </c>
       <c r="D18" s="2">
-        <v>11.19</v>
+        <v>0.58</v>
       </c>
       <c r="E18" s="2">
-        <v>2.65</v>
+        <v>11.48</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="H18" s="2">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="I18" s="2">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1080.25</v>
+        <v>4014.3</v>
       </c>
       <c r="C19" s="2">
-        <v>13.94</v>
+        <v>0.26</v>
       </c>
       <c r="D19" s="2">
-        <v>5.01</v>
+        <v>-2.41</v>
       </c>
       <c r="E19" s="2">
-        <v>1.46</v>
+        <v>14.15</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="H19" s="2">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I19" s="2">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>1285.6</v>
+        <v>1101.1</v>
       </c>
       <c r="C20" s="2">
-        <v>4.04</v>
+        <v>14.31</v>
       </c>
       <c r="D20" s="2">
-        <v>-1.2</v>
+        <v>-3.92</v>
       </c>
       <c r="E20" s="2">
-        <v>6.52</v>
+        <v>6.82</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H20" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I20" s="2">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>7189.5</v>
+        <v>9576</v>
       </c>
       <c r="C21" s="2">
-        <v>1.26</v>
+        <v>5.77</v>
       </c>
       <c r="D21" s="2">
-        <v>2.92</v>
+        <v>-0.15</v>
       </c>
       <c r="E21" s="2">
-        <v>4.04</v>
+        <v>7.62</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H21" s="2">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="I21" s="2">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>438.75</v>
+        <v>2327.3</v>
       </c>
       <c r="C22" s="2">
-        <v>17.28</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D22" s="2">
-        <v>4.97</v>
+        <v>-4.42</v>
       </c>
       <c r="E22" s="2">
-        <v>-5.08</v>
+        <v>11.62</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="H22" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="I22" s="2">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>11886</v>
+        <v>11998</v>
       </c>
       <c r="C23" s="2">
-        <v>2.39</v>
+        <v>4.59</v>
       </c>
       <c r="D23" s="2">
-        <v>-5.18</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="E23" s="2">
-        <v>6.93</v>
+        <v>11.46</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
+        <v>58</v>
+      </c>
+      <c r="H23" s="2">
         <v>52</v>
       </c>
-      <c r="H23" s="2">
+      <c r="I23" s="2">
         <v>34</v>
-      </c>
-      <c r="I23" s="2">
-        <v>44</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>1511.4</v>
+        <v>350.5</v>
       </c>
       <c r="C24" s="2">
-        <v>-3.26</v>
+        <v>1.11</v>
       </c>
       <c r="D24" s="2">
-        <v>-12.33</v>
+        <v>-7.13</v>
       </c>
       <c r="E24" s="2">
-        <v>12.64</v>
+        <v>12.63</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="H24" s="2">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="I24" s="2">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>2464</v>
+        <v>2485.1</v>
       </c>
       <c r="C25" s="2">
-        <v>-16.68</v>
+        <v>-10.59</v>
       </c>
       <c r="D25" s="2">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="E25" s="2">
-        <v>10.09</v>
+        <v>12.08</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
+        <v>54</v>
+      </c>
+      <c r="H25" s="2">
         <v>36</v>
       </c>
-      <c r="H25" s="2">
+      <c r="I25" s="2">
         <v>14</v>
-      </c>
-      <c r="I25" s="2">
-        <v>20</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>1346.8</v>
+        <v>1317.1</v>
       </c>
       <c r="C26" s="2">
-        <v>-2.88</v>
+        <v>3.42</v>
       </c>
       <c r="D26" s="2">
-        <v>-0.44</v>
+        <v>3.26</v>
       </c>
       <c r="E26" s="2">
-        <v>4.51</v>
+        <v>4.56</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="H26" s="2">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="I26" s="2">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>1007.65</v>
+        <v>2739.3</v>
       </c>
       <c r="C27" s="2">
-        <v>-7.03</v>
+        <v>-2.09</v>
       </c>
       <c r="D27" s="2">
-        <v>5.17</v>
+        <v>-6.39</v>
       </c>
       <c r="E27" s="2">
-        <v>3.2</v>
+        <v>7.45</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="H27" s="2">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="I27" s="2">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>1113.2</v>
+        <v>1326.2</v>
       </c>
       <c r="C28" s="2">
-        <v>-3.07</v>
+        <v>-2.49</v>
       </c>
       <c r="D28" s="2">
-        <v>-1.08</v>
+        <v>-5.02</v>
       </c>
       <c r="E28" s="2">
-        <v>3.27</v>
+        <v>5.99</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
+        <v>52</v>
+      </c>
+      <c r="H28" s="2">
+        <v>54</v>
+      </c>
+      <c r="I28" s="2">
         <v>40</v>
-      </c>
-      <c r="H28" s="2">
-        <v>56</v>
-      </c>
-      <c r="I28" s="2">
-        <v>56</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>1970.9</v>
+        <v>7111.5</v>
       </c>
       <c r="C29" s="2">
-        <v>-1.46</v>
+        <v>-1.99</v>
       </c>
       <c r="D29" s="2">
-        <v>-1.37</v>
+        <v>-1.17</v>
       </c>
       <c r="E29" s="2">
-        <v>2.01</v>
+        <v>3.5</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H29" s="2">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="I29" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>4638.4</v>
+        <v>4523.1</v>
       </c>
       <c r="C30" s="2">
-        <v>-14.68</v>
+        <v>-6.14</v>
       </c>
       <c r="D30" s="2">
-        <v>-1.04</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="E30" s="2">
-        <v>8.17</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
+        <v>44</v>
+      </c>
+      <c r="H30" s="2">
         <v>30</v>
       </c>
-      <c r="H30" s="2">
+      <c r="I30" s="2">
         <v>26</v>
-      </c>
-      <c r="I30" s="2">
-        <v>8</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>2720.5</v>
+        <v>921.55</v>
       </c>
       <c r="C31" s="2">
-        <v>-0.36</v>
+        <v>-8.43</v>
       </c>
       <c r="D31" s="2">
-        <v>-1.95</v>
+        <v>-6.27</v>
       </c>
       <c r="E31" s="2">
-        <v>1.39</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="H31" s="2">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="I31" s="2">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>908.25</v>
+        <v>999.4</v>
       </c>
       <c r="C32" s="2">
-        <v>-11.74</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="D32" s="2">
-        <v>0.5</v>
+        <v>-1.05</v>
       </c>
       <c r="E32" s="2">
-        <v>4.56</v>
+        <v>3.12</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H32" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I32" s="2">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>1235.7</v>
+        <v>1295</v>
       </c>
       <c r="C33" s="2">
-        <v>-3.28</v>
+        <v>-14.37</v>
       </c>
       <c r="D33" s="2">
-        <v>4.5</v>
+        <v>-3.54</v>
       </c>
       <c r="E33" s="2">
-        <v>-3.75</v>
+        <v>6.2</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H33" s="2">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="I33" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>2240.8</v>
+        <v>256.79</v>
       </c>
       <c r="C34" s="2">
-        <v>-8.99</v>
+        <v>-11.74</v>
       </c>
       <c r="D34" s="2">
-        <v>-4.94</v>
+        <v>-11.1</v>
       </c>
       <c r="E34" s="2">
-        <v>3.83</v>
+        <v>7.92</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="H34" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I34" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,25 +1778,25 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>252.61</v>
+        <v>245.73</v>
       </c>
       <c r="C35" s="2">
-        <v>-14.59</v>
+        <v>-17.66</v>
       </c>
       <c r="D35" s="2">
-        <v>-7.35</v>
+        <v>-8.74</v>
       </c>
       <c r="E35" s="2">
-        <v>7.66</v>
+        <v>5.6</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H35" s="2">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I35" s="2">
         <v>28</v>
@@ -1810,16 +1810,16 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>1838.9</v>
+        <v>1770.7</v>
       </c>
       <c r="C36" s="2">
-        <v>-10.26</v>
+        <v>-14.29</v>
       </c>
       <c r="D36" s="2">
-        <v>-4.73</v>
+        <v>-12.54</v>
       </c>
       <c r="E36" s="2">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
@@ -1828,10 +1828,10 @@
         <v>32</v>
       </c>
       <c r="H36" s="2">
+        <v>32</v>
+      </c>
+      <c r="I36" s="2">
         <v>6</v>
-      </c>
-      <c r="I36" s="2">
-        <v>14</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>1442.3</v>
+        <v>1814.5</v>
       </c>
       <c r="C37" s="2">
-        <v>-12.2</v>
+        <v>-11.63</v>
       </c>
       <c r="D37" s="2">
-        <v>-13.98</v>
+        <v>-10.98</v>
       </c>
       <c r="E37" s="2">
-        <v>9.17</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H37" s="2">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="I37" s="2">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,25 +1874,25 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>383.6</v>
+        <v>301.6</v>
       </c>
       <c r="C38" s="2">
-        <v>-10.18</v>
+        <v>-23.57</v>
       </c>
       <c r="D38" s="2">
-        <v>-6.03</v>
+        <v>-6.57</v>
       </c>
       <c r="E38" s="2">
-        <v>2.51</v>
+        <v>3.55</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H38" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I38" s="2">
         <v>30</v>
@@ -1906,16 +1906,16 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>243.86</v>
+        <v>13048</v>
       </c>
       <c r="C39" s="2">
-        <v>-19.32</v>
+        <v>-19.69</v>
       </c>
       <c r="D39" s="2">
-        <v>-0.1</v>
+        <v>-12.89</v>
       </c>
       <c r="E39" s="2">
-        <v>2.63</v>
+        <v>4.69</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
@@ -1927,7 +1927,7 @@
         <v>28</v>
       </c>
       <c r="I39" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>13453</v>
+        <v>199.36</v>
       </c>
       <c r="C40" s="2">
-        <v>-15.89</v>
+        <v>-21.12</v>
       </c>
       <c r="D40" s="2">
-        <v>-6.47</v>
+        <v>-13.35</v>
       </c>
       <c r="E40" s="2">
-        <v>3.71</v>
+        <v>5.63</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H40" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I40" s="2">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1970,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>3200.2</v>
+        <v>370.85</v>
       </c>
       <c r="C41" s="2">
-        <v>-12.84</v>
+        <v>-14.95</v>
       </c>
       <c r="D41" s="2">
-        <v>-7.59</v>
+        <v>-13.51</v>
       </c>
       <c r="E41" s="2">
-        <v>2.28</v>
+        <v>1.09</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H41" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I41" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>1846.9</v>
+        <v>1620.4</v>
       </c>
       <c r="C42" s="2">
-        <v>-12.21</v>
+        <v>-9.75</v>
       </c>
       <c r="D42" s="2">
-        <v>-6.03</v>
+        <v>-4.94</v>
       </c>
       <c r="E42" s="2">
-        <v>1.09</v>
+        <v>-7.58</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="H42" s="2">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="I42" s="2">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>1675.5</v>
+        <v>1768.9</v>
       </c>
       <c r="C43" s="2">
-        <v>-7.25</v>
+        <v>-11.74</v>
       </c>
       <c r="D43" s="2">
-        <v>3.59</v>
+        <v>-12.48</v>
       </c>
       <c r="E43" s="2">
-        <v>-6.63</v>
+        <v>-3.65</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="H43" s="2">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="I43" s="2">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>1365</v>
+        <v>3038.4</v>
       </c>
       <c r="C44" s="2">
-        <v>-11.11</v>
+        <v>-17.1</v>
       </c>
       <c r="D44" s="2">
-        <v>-1.83</v>
+        <v>-15.82</v>
       </c>
       <c r="E44" s="2">
-        <v>-2.33</v>
+        <v>0.23</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H44" s="2">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="I44" s="2">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2098,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>204.32</v>
+        <v>784.85</v>
       </c>
       <c r="C45" s="2">
-        <v>-18.42</v>
+        <v>-21.54</v>
       </c>
       <c r="D45" s="2">
-        <v>-15.67</v>
+        <v>-16.26</v>
       </c>
       <c r="E45" s="2">
-        <v>6.79</v>
+        <v>2.61</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H45" s="2">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="I45" s="2">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,28 +2130,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>2581.5</v>
+        <v>1327.8</v>
       </c>
       <c r="C46" s="2">
-        <v>-18.6</v>
+        <v>-14.06</v>
       </c>
       <c r="D46" s="2">
-        <v>-18.55</v>
+        <v>-9.15</v>
       </c>
       <c r="E46" s="2">
-        <v>7.94</v>
+        <v>-5.95</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H46" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I46" s="2">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>306.8</v>
+        <v>1358.5</v>
       </c>
       <c r="C47" s="2">
-        <v>-22.29</v>
+        <v>-13.37</v>
       </c>
       <c r="D47" s="2">
-        <v>-0.47</v>
+        <v>-16.23</v>
       </c>
       <c r="E47" s="2">
-        <v>0.64</v>
+        <v>-5.18</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="H47" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I47" s="2">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,28 +2194,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>1318.7</v>
+        <v>2396.9</v>
       </c>
       <c r="C48" s="2">
-        <v>-17.46</v>
+        <v>-23.54</v>
       </c>
       <c r="D48" s="2">
-        <v>-19.07</v>
+        <v>-18.7</v>
       </c>
       <c r="E48" s="2">
-        <v>6.96</v>
+        <v>-0.08</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H48" s="2">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="I48" s="2">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,16 +2226,16 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>1240.8</v>
+        <v>588.2</v>
       </c>
       <c r="C49" s="2">
-        <v>-18.42</v>
+        <v>-24.12</v>
       </c>
       <c r="D49" s="2">
-        <v>-5.4</v>
+        <v>-16.91</v>
       </c>
       <c r="E49" s="2">
-        <v>-3.21</v>
+        <v>-2.45</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
@@ -2244,10 +2244,10 @@
         <v>4</v>
       </c>
       <c r="H49" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I49" s="2">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,28 +2258,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>616.45</v>
+        <v>1154.6</v>
       </c>
       <c r="C50" s="2">
-        <v>-18.97</v>
+        <v>-27.75</v>
       </c>
       <c r="D50" s="2">
-        <v>-14.08</v>
+        <v>-22.88</v>
       </c>
       <c r="E50" s="2">
-        <v>-4.02</v>
+        <v>-9.68</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H50" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I50" s="2">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2290,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>799.9</v>
+        <v>1203.2</v>
       </c>
       <c r="C51" s="2">
-        <v>-19.79</v>
+        <v>-26.15</v>
       </c>
       <c r="D51" s="2">
-        <v>-13.81</v>
+        <v>-23.46</v>
       </c>
       <c r="E51" s="2">
-        <v>-5.38</v>
+        <v>-10.71</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H51" s="2">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="I51" s="2">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2462,138 +2462,138 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>1039</v>
+        <v>1048.35</v>
       </c>
       <c r="C2" s="2">
-        <v>28.15</v>
+        <v>27.17</v>
       </c>
       <c r="D2" s="2">
-        <v>11.66</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="E2" s="2">
-        <v>10.93</v>
+        <v>22.66</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H2" s="2">
         <v>92</v>
       </c>
       <c r="I2" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1">
-        <v>212.12</v>
+        <v>401.85</v>
       </c>
       <c r="C3" s="2">
-        <v>27.19</v>
+        <v>25.51</v>
       </c>
       <c r="D3" s="2">
-        <v>12.52</v>
+        <v>11.04</v>
       </c>
       <c r="E3" s="2">
-        <v>8.539999999999999</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G3" s="2">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H3" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I3" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1">
-        <v>4525.9</v>
+        <v>210.07</v>
       </c>
       <c r="C4" s="2">
-        <v>19.09</v>
+        <v>26.26</v>
       </c>
       <c r="D4" s="2">
-        <v>14.49</v>
+        <v>4</v>
       </c>
       <c r="E4" s="2">
-        <v>10.64</v>
+        <v>10.11</v>
       </c>
       <c r="F4" s="2">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G4" s="2">
         <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="I4" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1">
-        <v>318.1</v>
+        <v>4410</v>
       </c>
       <c r="C5" s="2">
-        <v>19.54</v>
+        <v>14.7</v>
       </c>
       <c r="D5" s="2">
-        <v>18.96</v>
+        <v>3.57</v>
       </c>
       <c r="E5" s="2">
-        <v>6.57</v>
+        <v>13.09</v>
       </c>
       <c r="F5" s="2">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G5" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H5" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I5" s="2">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1">
-        <v>284.05</v>
+        <v>284.8</v>
       </c>
       <c r="C6" s="2">
-        <v>20.02</v>
+        <v>22.27</v>
       </c>
       <c r="D6" s="2">
-        <v>14.48</v>
+        <v>9.34</v>
       </c>
       <c r="E6" s="2">
-        <v>7.29</v>
+        <v>6.25</v>
       </c>
       <c r="F6" s="2">
+        <v>86</v>
+      </c>
+      <c r="G6" s="2">
         <v>92</v>
-      </c>
-      <c r="G6" s="2">
-        <v>100</v>
       </c>
       <c r="H6" s="2">
         <v>100</v>
@@ -2604,28 +2604,28 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1">
-        <v>393.6</v>
+        <v>316.4</v>
       </c>
       <c r="C7" s="2">
-        <v>22.8</v>
+        <v>20.83</v>
       </c>
       <c r="D7" s="2">
-        <v>13.19</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E7" s="2">
-        <v>2.67</v>
+        <v>5.82</v>
       </c>
       <c r="F7" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G7" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I7" s="2">
         <v>96</v>
@@ -2682,7 +2682,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2724,235 +2724,293 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>1039</v>
+        <v>1048.35</v>
       </c>
       <c r="C2" s="2">
-        <v>28.15</v>
+        <v>27.17</v>
       </c>
       <c r="D2" s="2">
-        <v>11.66</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="E2" s="2">
-        <v>10.93</v>
+        <v>22.66</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H2" s="2">
         <v>92</v>
       </c>
       <c r="I2" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1">
-        <v>212.12</v>
+        <v>4297.3</v>
       </c>
       <c r="C3" s="2">
-        <v>27.19</v>
+        <v>6.17</v>
       </c>
       <c r="D3" s="2">
-        <v>12.52</v>
+        <v>3.02</v>
       </c>
       <c r="E3" s="2">
-        <v>8.539999999999999</v>
+        <v>27.68</v>
       </c>
       <c r="F3" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G3" s="2">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="H3" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="I3" s="2">
-        <v>86</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>4525.9</v>
+        <v>2287.6</v>
       </c>
       <c r="C4" s="2">
-        <v>19.09</v>
+        <v>0.43</v>
       </c>
       <c r="D4" s="2">
-        <v>14.49</v>
+        <v>1.67</v>
       </c>
       <c r="E4" s="2">
-        <v>10.64</v>
+        <v>25.84</v>
       </c>
       <c r="F4" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G4" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="H4" s="2">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="I4" s="2">
-        <v>80</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>318.1</v>
+        <v>401.85</v>
       </c>
       <c r="C5" s="2">
-        <v>19.54</v>
+        <v>25.51</v>
       </c>
       <c r="D5" s="2">
-        <v>18.96</v>
+        <v>11.04</v>
       </c>
       <c r="E5" s="2">
-        <v>6.57</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G5" s="2">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I5" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>284.05</v>
+        <v>210.07</v>
       </c>
       <c r="C6" s="2">
-        <v>20.02</v>
+        <v>26.26</v>
       </c>
       <c r="D6" s="2">
-        <v>14.48</v>
+        <v>4</v>
       </c>
       <c r="E6" s="2">
-        <v>7.29</v>
+        <v>10.11</v>
       </c>
       <c r="F6" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G6" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H6" s="2">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I6" s="2">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>1573.4</v>
+        <v>4410</v>
       </c>
       <c r="C7" s="2">
-        <v>4.5</v>
+        <v>14.7</v>
       </c>
       <c r="D7" s="2">
-        <v>12.14</v>
+        <v>3.57</v>
       </c>
       <c r="E7" s="2">
-        <v>15.23</v>
+        <v>13.09</v>
       </c>
       <c r="F7" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G7" s="2">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="H7" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="I7" s="2">
-        <v>46</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1">
-        <v>393.6</v>
+        <v>284.8</v>
       </c>
       <c r="C8" s="2">
-        <v>22.8</v>
+        <v>22.27</v>
       </c>
       <c r="D8" s="2">
-        <v>13.19</v>
+        <v>9.34</v>
       </c>
       <c r="E8" s="2">
-        <v>2.67</v>
+        <v>6.25</v>
       </c>
       <c r="F8" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G8" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H8" s="2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I8" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1">
-        <v>1036.95</v>
+        <v>1585.1</v>
       </c>
       <c r="C9" s="2">
-        <v>25.21</v>
+        <v>5.39</v>
       </c>
       <c r="D9" s="2">
-        <v>7.78</v>
+        <v>1.5</v>
       </c>
       <c r="E9" s="2">
-        <v>3.22</v>
+        <v>17.92</v>
       </c>
       <c r="F9" s="2">
+        <v>84</v>
+      </c>
+      <c r="G9" s="2">
+        <v>90</v>
+      </c>
+      <c r="H9" s="2">
+        <v>80</v>
+      </c>
+      <c r="I9" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1">
+        <v>316.4</v>
+      </c>
+      <c r="C10" s="2">
+        <v>20.83</v>
+      </c>
+      <c r="D10" s="2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E10" s="2">
+        <v>5.82</v>
+      </c>
+      <c r="F10" s="2">
+        <v>82</v>
+      </c>
+      <c r="G10" s="2">
+        <v>94</v>
+      </c>
+      <c r="H10" s="2">
+        <v>94</v>
+      </c>
+      <c r="I10" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1011.3</v>
+      </c>
+      <c r="C11" s="2">
+        <v>19.38</v>
+      </c>
+      <c r="D11" s="2">
+        <v>-4.84</v>
+      </c>
+      <c r="E11" s="2">
+        <v>11.92</v>
+      </c>
+      <c r="F11" s="2">
+        <v>80</v>
+      </c>
+      <c r="G11" s="2">
         <v>86</v>
       </c>
-      <c r="G9" s="2">
+      <c r="H11" s="2">
         <v>86</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I11" s="2">
         <v>62</v>
       </c>
-      <c r="I9" s="2">
-        <v>60</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C2:C11">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2960,7 +3018,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D11">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2968,7 +3026,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2976,22 +3034,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F11">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G11">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H11">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
+  <conditionalFormatting sqref="I2:I11">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -3027,13 +3085,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D2" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3041,13 +3099,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D3" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3055,13 +3113,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="C4" s="2">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3069,13 +3127,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-04-24</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-04-24</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-04-24</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-04-24</t>
+    <t>Price_2026-05-01</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-05-01</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-05-01</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-05-01</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-05-01</t>
   </si>
   <si>
     <t>RS_Score_2026-04-24</t>
@@ -43,150 +46,147 @@
     <t>RS_Score_2026-04-10</t>
   </si>
   <si>
-    <t>RS_Score_2026-04-03</t>
+    <t>ADANIENT</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
   </si>
   <si>
     <t>HINDALCO</t>
   </si>
   <si>
-    <t>NESTLEIND</t>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO</t>
   </si>
   <si>
     <t>TRENT</t>
   </si>
   <si>
-    <t>ADANIENT</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
     <t>TITAN</t>
   </si>
   <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>ADANIPORTS</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>TMPV</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
   </si>
   <si>
     <t>SHRIRAMFIN</t>
   </si>
   <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>TMPV</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
   </si>
   <si>
     <t>ICICIBANK</t>
   </si>
   <si>
-    <t>EICHERMOT</t>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>ETERNAL</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
   </si>
   <si>
     <t>INDIGO</t>
   </si>
   <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>ETERNAL</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
     <t>M&amp;M</t>
   </si>
   <si>
+    <t>TCS</t>
+  </si>
+  <si>
     <t>HDFCBANK</t>
   </si>
   <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
     <t>HDFCLIFE</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
     <t>2026-04-24</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
   </si>
 </sst>
 </file>
@@ -722,28 +722,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>1048.35</v>
+        <v>2408.4</v>
       </c>
       <c r="C2" s="2">
-        <v>27.17</v>
+        <v>7.88</v>
       </c>
       <c r="D2" s="2">
-        <v>8.720000000000001</v>
+        <v>12.72</v>
       </c>
       <c r="E2" s="2">
-        <v>22.66</v>
+        <v>30.71</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H2" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I2" s="2">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>60</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1421.3</v>
+        <v>1458.6</v>
       </c>
       <c r="C3" s="2">
-        <v>17.61</v>
+        <v>18.78</v>
       </c>
       <c r="D3" s="2">
-        <v>9.699999999999999</v>
+        <v>13.72</v>
       </c>
       <c r="E3" s="2">
-        <v>20.12</v>
+        <v>23.53</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
+        <v>98</v>
+      </c>
+      <c r="H3" s="2">
         <v>64</v>
       </c>
-      <c r="H3" s="2">
-        <v>60</v>
-      </c>
       <c r="I3" s="2">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>4297.3</v>
+        <v>1038</v>
       </c>
       <c r="C4" s="2">
-        <v>6.17</v>
+        <v>22.29</v>
       </c>
       <c r="D4" s="2">
-        <v>3.02</v>
+        <v>14.19</v>
       </c>
       <c r="E4" s="2">
-        <v>27.68</v>
+        <v>14.75</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H4" s="2">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="I4" s="2">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>2287.6</v>
+        <v>481.45</v>
       </c>
       <c r="C5" s="2">
-        <v>0.43</v>
+        <v>26.79</v>
       </c>
       <c r="D5" s="2">
-        <v>1.67</v>
+        <v>19.28</v>
       </c>
       <c r="E5" s="2">
-        <v>25.84</v>
+        <v>7.13</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
+        <v>74</v>
+      </c>
+      <c r="H5" s="2">
+        <v>60</v>
+      </c>
+      <c r="I5" s="2">
         <v>82</v>
-      </c>
-      <c r="H5" s="2">
-        <v>70</v>
-      </c>
-      <c r="I5" s="2">
-        <v>10</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>401.85</v>
+        <v>1657.3</v>
       </c>
       <c r="C6" s="2">
-        <v>25.51</v>
+        <v>11.51</v>
       </c>
       <c r="D6" s="2">
-        <v>11.04</v>
+        <v>9.1</v>
       </c>
       <c r="E6" s="2">
-        <v>7</v>
+        <v>19.63</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H6" s="2">
         <v>90</v>
       </c>
       <c r="I6" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>210.07</v>
+        <v>299.55</v>
       </c>
       <c r="C7" s="2">
-        <v>26.26</v>
+        <v>31.64</v>
       </c>
       <c r="D7" s="2">
-        <v>4</v>
+        <v>14.66</v>
       </c>
       <c r="E7" s="2">
-        <v>10.11</v>
+        <v>3.99</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H7" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I7" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>4410</v>
+        <v>399.15</v>
       </c>
       <c r="C8" s="2">
-        <v>14.7</v>
+        <v>25.19</v>
       </c>
       <c r="D8" s="2">
-        <v>3.57</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E8" s="2">
-        <v>13.09</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H8" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="I8" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>284.8</v>
+        <v>318.35</v>
       </c>
       <c r="C9" s="2">
-        <v>22.27</v>
+        <v>23.3</v>
       </c>
       <c r="D9" s="2">
-        <v>9.34</v>
+        <v>10.85</v>
       </c>
       <c r="E9" s="2">
-        <v>6.25</v>
+        <v>8.73</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H9" s="2">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I9" s="2">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,16 +978,16 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>1585.1</v>
+        <v>211.36</v>
       </c>
       <c r="C10" s="2">
-        <v>5.39</v>
+        <v>24.08</v>
       </c>
       <c r="D10" s="2">
-        <v>1.5</v>
+        <v>4.03</v>
       </c>
       <c r="E10" s="2">
-        <v>17.92</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
@@ -996,10 +996,10 @@
         <v>90</v>
       </c>
       <c r="H10" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="I10" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>316.4</v>
+        <v>1264.5</v>
       </c>
       <c r="C11" s="2">
-        <v>20.83</v>
+        <v>17.16</v>
       </c>
       <c r="D11" s="2">
-        <v>9.199999999999999</v>
+        <v>2.64</v>
       </c>
       <c r="E11" s="2">
-        <v>5.82</v>
+        <v>10.88</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="H11" s="2">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="I11" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1011.3</v>
+        <v>9994</v>
       </c>
       <c r="C12" s="2">
-        <v>19.38</v>
+        <v>12.36</v>
       </c>
       <c r="D12" s="2">
-        <v>-4.84</v>
+        <v>2.4</v>
       </c>
       <c r="E12" s="2">
-        <v>11.92</v>
+        <v>12.35</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="H12" s="2">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="I12" s="2">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>1365.9</v>
+        <v>4144.6</v>
       </c>
       <c r="C13" s="2">
-        <v>7.32</v>
+        <v>2.46</v>
       </c>
       <c r="D13" s="2">
-        <v>1.83</v>
+        <v>-2.53</v>
       </c>
       <c r="E13" s="2">
-        <v>14.52</v>
+        <v>17.53</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="H13" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I13" s="2">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>1255.7</v>
+        <v>4385.2</v>
       </c>
       <c r="C14" s="2">
-        <v>13.6</v>
+        <v>12.21</v>
       </c>
       <c r="D14" s="2">
-        <v>0.86</v>
+        <v>4.93</v>
       </c>
       <c r="E14" s="2">
-        <v>10.76</v>
+        <v>7.86</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="H14" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="I14" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>456</v>
+        <v>1322.9</v>
       </c>
       <c r="C15" s="2">
-        <v>20.32</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2">
-        <v>7.03</v>
+        <v>4.32</v>
       </c>
       <c r="E15" s="2">
-        <v>3.14</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H15" s="2">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="I15" s="2">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>444.45</v>
+        <v>1144.6</v>
       </c>
       <c r="C16" s="2">
-        <v>15.19</v>
+        <v>-2.98</v>
       </c>
       <c r="D16" s="2">
-        <v>2.07</v>
+        <v>1.1</v>
       </c>
       <c r="E16" s="2">
-        <v>7.24</v>
+        <v>11.8</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H16" s="2">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="I16" s="2">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>7732.5</v>
+        <v>7636.5</v>
       </c>
       <c r="C17" s="2">
-        <v>10.46</v>
+        <v>10.48</v>
       </c>
       <c r="D17" s="2">
-        <v>7.37</v>
+        <v>1.38</v>
       </c>
       <c r="E17" s="2">
-        <v>4.31</v>
+        <v>4.53</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H17" s="2">
         <v>68</v>
       </c>
       <c r="I17" s="2">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>1174</v>
+        <v>431.3</v>
       </c>
       <c r="C18" s="2">
-        <v>2.79</v>
+        <v>12.33</v>
       </c>
       <c r="D18" s="2">
-        <v>0.58</v>
+        <v>-0.55</v>
       </c>
       <c r="E18" s="2">
-        <v>11.48</v>
+        <v>3.01</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="H18" s="2">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="I18" s="2">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>4014.3</v>
+        <v>4014</v>
       </c>
       <c r="C19" s="2">
-        <v>0.26</v>
+        <v>-1.19</v>
       </c>
       <c r="D19" s="2">
-        <v>-2.41</v>
+        <v>-3.83</v>
       </c>
       <c r="E19" s="2">
-        <v>14.15</v>
+        <v>11.27</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
+        <v>66</v>
+      </c>
+      <c r="H19" s="2">
         <v>84</v>
       </c>
-      <c r="H19" s="2">
+      <c r="I19" s="2">
         <v>66</v>
-      </c>
-      <c r="I19" s="2">
-        <v>58</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>1101.1</v>
+        <v>1808.3</v>
       </c>
       <c r="C20" s="2">
-        <v>14.31</v>
+        <v>1.51</v>
       </c>
       <c r="D20" s="2">
-        <v>-3.92</v>
+        <v>6.53</v>
       </c>
       <c r="E20" s="2">
-        <v>6.82</v>
+        <v>4.62</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="H20" s="2">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="I20" s="2">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>9576</v>
+        <v>2250.9</v>
       </c>
       <c r="C21" s="2">
-        <v>5.77</v>
+        <v>-1.09</v>
       </c>
       <c r="D21" s="2">
-        <v>-0.15</v>
+        <v>-2.36</v>
       </c>
       <c r="E21" s="2">
-        <v>7.62</v>
+        <v>9.02</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H21" s="2">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="I21" s="2">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>2327.3</v>
+        <v>937</v>
       </c>
       <c r="C22" s="2">
-        <v>0.9399999999999999</v>
+        <v>-6.26</v>
       </c>
       <c r="D22" s="2">
-        <v>-4.42</v>
+        <v>-8.56</v>
       </c>
       <c r="E22" s="2">
-        <v>11.62</v>
+        <v>14.65</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H22" s="2">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I22" s="2">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>11998</v>
+        <v>341.55</v>
       </c>
       <c r="C23" s="2">
-        <v>4.59</v>
+        <v>-1.39</v>
       </c>
       <c r="D23" s="2">
-        <v>-8.050000000000001</v>
+        <v>-10.18</v>
       </c>
       <c r="E23" s="2">
-        <v>11.46</v>
+        <v>12.74</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H23" s="2">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="I23" s="2">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>350.5</v>
+        <v>2794.5</v>
       </c>
       <c r="C24" s="2">
-        <v>1.11</v>
+        <v>-0.43</v>
       </c>
       <c r="D24" s="2">
-        <v>-7.13</v>
+        <v>-3.24</v>
       </c>
       <c r="E24" s="2">
-        <v>12.63</v>
+        <v>7.78</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="H24" s="2">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I24" s="2">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>2485.1</v>
+        <v>1268.3</v>
       </c>
       <c r="C25" s="2">
-        <v>-10.59</v>
+        <v>3.56</v>
       </c>
       <c r="D25" s="2">
-        <v>2.8</v>
+        <v>-4.8</v>
       </c>
       <c r="E25" s="2">
-        <v>12.08</v>
+        <v>6.3</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="I25" s="2">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>1317.1</v>
+        <v>2444.5</v>
       </c>
       <c r="C26" s="2">
-        <v>3.42</v>
+        <v>-12.25</v>
       </c>
       <c r="D26" s="2">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="E26" s="2">
-        <v>4.56</v>
+        <v>9.83</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="H26" s="2">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="I26" s="2">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>2739.3</v>
+        <v>1068.45</v>
       </c>
       <c r="C27" s="2">
-        <v>-2.09</v>
+        <v>9.49</v>
       </c>
       <c r="D27" s="2">
-        <v>-6.39</v>
+        <v>-10.86</v>
       </c>
       <c r="E27" s="2">
-        <v>7.45</v>
+        <v>4.98</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="H27" s="2">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I27" s="2">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>1326.2</v>
+        <v>11586</v>
       </c>
       <c r="C28" s="2">
-        <v>-2.49</v>
+        <v>0.4</v>
       </c>
       <c r="D28" s="2">
-        <v>-5.02</v>
+        <v>-10.62</v>
       </c>
       <c r="E28" s="2">
-        <v>5.99</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
+        <v>58</v>
+      </c>
+      <c r="H28" s="2">
+        <v>58</v>
+      </c>
+      <c r="I28" s="2">
         <v>52</v>
-      </c>
-      <c r="H28" s="2">
-        <v>54</v>
-      </c>
-      <c r="I28" s="2">
-        <v>40</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>7111.5</v>
+        <v>1309.6</v>
       </c>
       <c r="C29" s="2">
-        <v>-1.99</v>
+        <v>-12.51</v>
       </c>
       <c r="D29" s="2">
-        <v>-1.17</v>
+        <v>-1.64</v>
       </c>
       <c r="E29" s="2">
-        <v>3.5</v>
+        <v>9.51</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="H29" s="2">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="I29" s="2">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>4523.1</v>
+        <v>937.35</v>
       </c>
       <c r="C30" s="2">
-        <v>-6.14</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="D30" s="2">
-        <v>-8.880000000000001</v>
+        <v>-12.05</v>
       </c>
       <c r="E30" s="2">
-        <v>8.970000000000001</v>
+        <v>4.09</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="H30" s="2">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="I30" s="2">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>921.55</v>
+        <v>1430.8</v>
       </c>
       <c r="C31" s="2">
-        <v>-8.43</v>
+        <v>-7.36</v>
       </c>
       <c r="D31" s="2">
-        <v>-6.27</v>
+        <v>0.79</v>
       </c>
       <c r="E31" s="2">
-        <v>8.550000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H31" s="2">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="I31" s="2">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>999.4</v>
+        <v>1473.5</v>
       </c>
       <c r="C32" s="2">
-        <v>-8.130000000000001</v>
+        <v>-6.71</v>
       </c>
       <c r="D32" s="2">
-        <v>-1.05</v>
+        <v>-3.97</v>
       </c>
       <c r="E32" s="2">
-        <v>3.12</v>
+        <v>4.91</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
+        <v>10</v>
+      </c>
+      <c r="H32" s="2">
+        <v>56</v>
+      </c>
+      <c r="I32" s="2">
         <v>50</v>
-      </c>
-      <c r="H32" s="2">
-        <v>10</v>
-      </c>
-      <c r="I32" s="2">
-        <v>36</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>1295</v>
+        <v>993.05</v>
       </c>
       <c r="C33" s="2">
-        <v>-14.37</v>
+        <v>-3.69</v>
       </c>
       <c r="D33" s="2">
-        <v>-3.54</v>
+        <v>-5.75</v>
       </c>
       <c r="E33" s="2">
-        <v>6.2</v>
+        <v>3.56</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H33" s="2">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="I33" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>256.79</v>
+        <v>314.9</v>
       </c>
       <c r="C34" s="2">
-        <v>-11.74</v>
+        <v>-19.58</v>
       </c>
       <c r="D34" s="2">
-        <v>-11.1</v>
+        <v>0.37</v>
       </c>
       <c r="E34" s="2">
-        <v>7.92</v>
+        <v>7.95</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H34" s="2">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="I34" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>245.73</v>
+        <v>7109</v>
       </c>
       <c r="C35" s="2">
-        <v>-17.66</v>
+        <v>-0.36</v>
       </c>
       <c r="D35" s="2">
-        <v>-8.74</v>
+        <v>-11.85</v>
       </c>
       <c r="E35" s="2">
-        <v>5.6</v>
+        <v>4.15</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="I35" s="2">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>1770.7</v>
+        <v>1886.8</v>
       </c>
       <c r="C36" s="2">
-        <v>-14.29</v>
+        <v>-10.49</v>
       </c>
       <c r="D36" s="2">
-        <v>-12.54</v>
+        <v>-5.88</v>
       </c>
       <c r="E36" s="2">
-        <v>3.89</v>
+        <v>5.89</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="I36" s="2">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>1814.5</v>
+        <v>383.3</v>
       </c>
       <c r="C37" s="2">
-        <v>-11.63</v>
+        <v>-11.81</v>
       </c>
       <c r="D37" s="2">
-        <v>-10.98</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="E37" s="2">
-        <v>0.6899999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
+        <v>22</v>
+      </c>
+      <c r="H37" s="2">
+        <v>28</v>
+      </c>
+      <c r="I37" s="2">
         <v>20</v>
-      </c>
-      <c r="H37" s="2">
-        <v>46</v>
-      </c>
-      <c r="I37" s="2">
-        <v>46</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>301.6</v>
+        <v>1263.4</v>
       </c>
       <c r="C38" s="2">
-        <v>-23.57</v>
+        <v>-6.58</v>
       </c>
       <c r="D38" s="2">
-        <v>-6.57</v>
+        <v>-10.69</v>
       </c>
       <c r="E38" s="2">
-        <v>3.55</v>
+        <v>4.18</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="H38" s="2">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="I38" s="2">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>13048</v>
+        <v>246.37</v>
       </c>
       <c r="C39" s="2">
-        <v>-19.69</v>
+        <v>-15.96</v>
       </c>
       <c r="D39" s="2">
-        <v>-12.89</v>
+        <v>-6.66</v>
       </c>
       <c r="E39" s="2">
-        <v>4.69</v>
+        <v>6.23</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
+        <v>34</v>
+      </c>
+      <c r="H39" s="2">
+        <v>26</v>
+      </c>
+      <c r="I39" s="2">
         <v>24</v>
-      </c>
-      <c r="H39" s="2">
-        <v>28</v>
-      </c>
-      <c r="I39" s="2">
-        <v>8</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>199.36</v>
+        <v>1747.2</v>
       </c>
       <c r="C40" s="2">
-        <v>-21.12</v>
+        <v>-13.56</v>
       </c>
       <c r="D40" s="2">
-        <v>-13.35</v>
+        <v>-13.64</v>
       </c>
       <c r="E40" s="2">
-        <v>5.63</v>
+        <v>6.08</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H40" s="2">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I40" s="2">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1970,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>370.85</v>
+        <v>1819</v>
       </c>
       <c r="C41" s="2">
-        <v>-14.95</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="D41" s="2">
-        <v>-13.51</v>
+        <v>-10.45</v>
       </c>
       <c r="E41" s="2">
-        <v>1.09</v>
+        <v>1.59</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H41" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="I41" s="2">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>1620.4</v>
+        <v>200.65</v>
       </c>
       <c r="C42" s="2">
-        <v>-9.75</v>
+        <v>-21.18</v>
       </c>
       <c r="D42" s="2">
-        <v>-4.94</v>
+        <v>-6.28</v>
       </c>
       <c r="E42" s="2">
-        <v>-7.58</v>
+        <v>4.95</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
+        <v>24</v>
+      </c>
+      <c r="H42" s="2">
+        <v>14</v>
+      </c>
+      <c r="I42" s="2">
         <v>18</v>
-      </c>
-      <c r="H42" s="2">
-        <v>16</v>
-      </c>
-      <c r="I42" s="2">
-        <v>80</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>1768.9</v>
+        <v>247.03</v>
       </c>
       <c r="C43" s="2">
-        <v>-11.74</v>
+        <v>-13.16</v>
       </c>
       <c r="D43" s="2">
-        <v>-12.48</v>
+        <v>-13.38</v>
       </c>
       <c r="E43" s="2">
-        <v>-3.65</v>
+        <v>4.44</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H43" s="2">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I43" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>3038.4</v>
+        <v>13314</v>
       </c>
       <c r="C44" s="2">
-        <v>-17.1</v>
+        <v>-18.81</v>
       </c>
       <c r="D44" s="2">
-        <v>-15.82</v>
+        <v>-12.62</v>
       </c>
       <c r="E44" s="2">
-        <v>0.23</v>
+        <v>6.44</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H44" s="2">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="I44" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2098,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>784.85</v>
+        <v>4295.3</v>
       </c>
       <c r="C45" s="2">
-        <v>-21.54</v>
+        <v>-13.76</v>
       </c>
       <c r="D45" s="2">
-        <v>-16.26</v>
+        <v>-12.86</v>
       </c>
       <c r="E45" s="2">
-        <v>2.61</v>
+        <v>2.74</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="H45" s="2">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="I45" s="2">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,16 +2130,16 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>1327.8</v>
+        <v>3097.5</v>
       </c>
       <c r="C46" s="2">
-        <v>-14.06</v>
+        <v>-14.26</v>
       </c>
       <c r="D46" s="2">
-        <v>-9.15</v>
+        <v>-12.34</v>
       </c>
       <c r="E46" s="2">
-        <v>-5.95</v>
+        <v>2.18</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
@@ -2148,10 +2148,10 @@
         <v>16</v>
       </c>
       <c r="H46" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I46" s="2">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>1358.5</v>
+        <v>2473.9</v>
       </c>
       <c r="C47" s="2">
-        <v>-13.37</v>
+        <v>-21.72</v>
       </c>
       <c r="D47" s="2">
-        <v>-16.23</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="E47" s="2">
-        <v>-5.18</v>
+        <v>2.73</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="H47" s="2">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="I47" s="2">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,28 +2194,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>2396.9</v>
+        <v>771.7</v>
       </c>
       <c r="C48" s="2">
-        <v>-23.54</v>
+        <v>-21.58</v>
       </c>
       <c r="D48" s="2">
-        <v>-18.7</v>
+        <v>-14.63</v>
       </c>
       <c r="E48" s="2">
-        <v>-0.08</v>
+        <v>3.97</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H48" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I48" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,25 +2226,25 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>588.2</v>
+        <v>586.9</v>
       </c>
       <c r="C49" s="2">
-        <v>-24.12</v>
+        <v>-22.11</v>
       </c>
       <c r="D49" s="2">
-        <v>-16.91</v>
+        <v>-15.77</v>
       </c>
       <c r="E49" s="2">
-        <v>-2.45</v>
+        <v>2.43</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
+        <v>6</v>
+      </c>
+      <c r="H49" s="2">
         <v>4</v>
-      </c>
-      <c r="H49" s="2">
-        <v>2</v>
       </c>
       <c r="I49" s="2">
         <v>2</v>
@@ -2258,28 +2258,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>1154.6</v>
+        <v>1181.8</v>
       </c>
       <c r="C50" s="2">
-        <v>-27.75</v>
+        <v>-26.23</v>
       </c>
       <c r="D50" s="2">
-        <v>-22.88</v>
+        <v>-13.68</v>
       </c>
       <c r="E50" s="2">
-        <v>-9.68</v>
+        <v>-7.36</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
+        <v>4</v>
+      </c>
+      <c r="H50" s="2">
         <v>8</v>
       </c>
-      <c r="H50" s="2">
+      <c r="I50" s="2">
         <v>6</v>
-      </c>
-      <c r="I50" s="2">
-        <v>50</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2290,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>1203.2</v>
+        <v>1199.1</v>
       </c>
       <c r="C51" s="2">
-        <v>-26.15</v>
+        <v>-25.62</v>
       </c>
       <c r="D51" s="2">
-        <v>-23.46</v>
+        <v>-16.02</v>
       </c>
       <c r="E51" s="2">
-        <v>-10.71</v>
+        <v>-9.77</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
+        <v>2</v>
+      </c>
+      <c r="H51" s="2">
         <v>30</v>
       </c>
-      <c r="H51" s="2">
+      <c r="I51" s="2">
         <v>42</v>
-      </c>
-      <c r="I51" s="2">
-        <v>64</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2459,28 +2459,28 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1">
-        <v>1048.35</v>
+        <v>1038</v>
       </c>
       <c r="C2" s="2">
-        <v>27.17</v>
+        <v>22.29</v>
       </c>
       <c r="D2" s="2">
-        <v>8.720000000000001</v>
+        <v>14.19</v>
       </c>
       <c r="E2" s="2">
-        <v>22.66</v>
+        <v>14.75</v>
       </c>
       <c r="F2" s="2">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G2" s="2">
         <v>100</v>
       </c>
       <c r="H2" s="2">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2">
         <v>92</v>
@@ -2491,28 +2491,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="1">
-        <v>401.85</v>
+        <v>1657.3</v>
       </c>
       <c r="C3" s="2">
-        <v>25.51</v>
+        <v>11.51</v>
       </c>
       <c r="D3" s="2">
-        <v>11.04</v>
+        <v>9.1</v>
       </c>
       <c r="E3" s="2">
-        <v>7</v>
+        <v>19.63</v>
       </c>
       <c r="F3" s="2">
         <v>92</v>
       </c>
       <c r="G3" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H3" s="2">
         <v>90</v>
       </c>
       <c r="I3" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2520,28 +2520,28 @@
         <v>14</v>
       </c>
       <c r="B4" s="1">
-        <v>210.07</v>
+        <v>299.55</v>
       </c>
       <c r="C4" s="2">
-        <v>26.26</v>
+        <v>31.64</v>
       </c>
       <c r="D4" s="2">
-        <v>4</v>
+        <v>14.66</v>
       </c>
       <c r="E4" s="2">
-        <v>10.11</v>
+        <v>3.99</v>
       </c>
       <c r="F4" s="2">
         <v>90</v>
       </c>
       <c r="G4" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H4" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I4" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2549,28 +2549,28 @@
         <v>15</v>
       </c>
       <c r="B5" s="1">
-        <v>4410</v>
+        <v>399.15</v>
       </c>
       <c r="C5" s="2">
-        <v>14.7</v>
+        <v>25.19</v>
       </c>
       <c r="D5" s="2">
-        <v>3.57</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E5" s="2">
-        <v>13.09</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="F5" s="2">
         <v>88</v>
       </c>
       <c r="G5" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H5" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="I5" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2578,54 +2578,54 @@
         <v>16</v>
       </c>
       <c r="B6" s="1">
-        <v>284.8</v>
+        <v>318.35</v>
       </c>
       <c r="C6" s="2">
-        <v>22.27</v>
+        <v>23.3</v>
       </c>
       <c r="D6" s="2">
-        <v>9.34</v>
+        <v>10.85</v>
       </c>
       <c r="E6" s="2">
-        <v>6.25</v>
+        <v>8.73</v>
       </c>
       <c r="F6" s="2">
         <v>86</v>
       </c>
       <c r="G6" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H6" s="2">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I6" s="2">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1">
-        <v>316.4</v>
+        <v>211.36</v>
       </c>
       <c r="C7" s="2">
-        <v>20.83</v>
+        <v>24.08</v>
       </c>
       <c r="D7" s="2">
-        <v>9.199999999999999</v>
+        <v>4.03</v>
       </c>
       <c r="E7" s="2">
-        <v>5.82</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="F7" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G7" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H7" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I7" s="2">
         <v>96</v>
@@ -2682,7 +2682,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2724,86 +2724,86 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>1048.35</v>
+        <v>2408.4</v>
       </c>
       <c r="C2" s="2">
-        <v>27.17</v>
+        <v>7.88</v>
       </c>
       <c r="D2" s="2">
-        <v>8.720000000000001</v>
+        <v>12.72</v>
       </c>
       <c r="E2" s="2">
-        <v>22.66</v>
+        <v>30.71</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H2" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I2" s="2">
-        <v>92</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>4297.3</v>
+        <v>1458.6</v>
       </c>
       <c r="C3" s="2">
-        <v>6.17</v>
+        <v>18.78</v>
       </c>
       <c r="D3" s="2">
-        <v>3.02</v>
+        <v>13.72</v>
       </c>
       <c r="E3" s="2">
-        <v>27.68</v>
+        <v>23.53</v>
       </c>
       <c r="F3" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="H3" s="2">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I3" s="2">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>2287.6</v>
+        <v>1038</v>
       </c>
       <c r="C4" s="2">
-        <v>0.43</v>
+        <v>22.29</v>
       </c>
       <c r="D4" s="2">
-        <v>1.67</v>
+        <v>14.19</v>
       </c>
       <c r="E4" s="2">
-        <v>25.84</v>
+        <v>14.75</v>
       </c>
       <c r="F4" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H4" s="2">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="I4" s="2">
-        <v>10</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2811,28 +2811,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>401.85</v>
+        <v>1657.3</v>
       </c>
       <c r="C5" s="2">
-        <v>25.51</v>
+        <v>11.51</v>
       </c>
       <c r="D5" s="2">
-        <v>11.04</v>
+        <v>9.1</v>
       </c>
       <c r="E5" s="2">
-        <v>7</v>
+        <v>19.63</v>
       </c>
       <c r="F5" s="2">
         <v>92</v>
       </c>
       <c r="G5" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H5" s="2">
         <v>90</v>
       </c>
       <c r="I5" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2840,28 +2840,28 @@
         <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>210.07</v>
+        <v>299.55</v>
       </c>
       <c r="C6" s="2">
-        <v>26.26</v>
+        <v>31.64</v>
       </c>
       <c r="D6" s="2">
-        <v>4</v>
+        <v>14.66</v>
       </c>
       <c r="E6" s="2">
-        <v>10.11</v>
+        <v>3.99</v>
       </c>
       <c r="F6" s="2">
         <v>90</v>
       </c>
       <c r="G6" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H6" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I6" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2869,28 +2869,28 @@
         <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>4410</v>
+        <v>399.15</v>
       </c>
       <c r="C7" s="2">
-        <v>14.7</v>
+        <v>25.19</v>
       </c>
       <c r="D7" s="2">
-        <v>3.57</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E7" s="2">
-        <v>13.09</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="F7" s="2">
         <v>88</v>
       </c>
       <c r="G7" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H7" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="I7" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2898,28 +2898,28 @@
         <v>16</v>
       </c>
       <c r="B8" s="1">
-        <v>284.8</v>
+        <v>318.35</v>
       </c>
       <c r="C8" s="2">
-        <v>22.27</v>
+        <v>23.3</v>
       </c>
       <c r="D8" s="2">
-        <v>9.34</v>
+        <v>10.85</v>
       </c>
       <c r="E8" s="2">
-        <v>6.25</v>
+        <v>8.73</v>
       </c>
       <c r="F8" s="2">
         <v>86</v>
       </c>
       <c r="G8" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H8" s="2">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I8" s="2">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2927,16 +2927,16 @@
         <v>17</v>
       </c>
       <c r="B9" s="1">
-        <v>1585.1</v>
+        <v>211.36</v>
       </c>
       <c r="C9" s="2">
-        <v>5.39</v>
+        <v>24.08</v>
       </c>
       <c r="D9" s="2">
-        <v>1.5</v>
+        <v>4.03</v>
       </c>
       <c r="E9" s="2">
-        <v>17.92</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="F9" s="2">
         <v>84</v>
@@ -2945,72 +2945,14 @@
         <v>90</v>
       </c>
       <c r="H9" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="I9" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1">
-        <v>316.4</v>
-      </c>
-      <c r="C10" s="2">
-        <v>20.83</v>
-      </c>
-      <c r="D10" s="2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E10" s="2">
-        <v>5.82</v>
-      </c>
-      <c r="F10" s="2">
-        <v>82</v>
-      </c>
-      <c r="G10" s="2">
-        <v>94</v>
-      </c>
-      <c r="H10" s="2">
-        <v>94</v>
-      </c>
-      <c r="I10" s="2">
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1">
-        <v>1011.3</v>
-      </c>
-      <c r="C11" s="2">
-        <v>19.38</v>
-      </c>
-      <c r="D11" s="2">
-        <v>-4.84</v>
-      </c>
-      <c r="E11" s="2">
-        <v>11.92</v>
-      </c>
-      <c r="F11" s="2">
-        <v>80</v>
-      </c>
-      <c r="G11" s="2">
-        <v>86</v>
-      </c>
-      <c r="H11" s="2">
-        <v>86</v>
-      </c>
-      <c r="I11" s="2">
-        <v>62</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C11">
+  <conditionalFormatting sqref="C2:C9">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3018,7 +2960,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D11">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3026,7 +2968,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E11">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3034,22 +2976,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
+  <conditionalFormatting sqref="F2:F9">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G11">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H11">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I11">
+  <conditionalFormatting sqref="I2:I9">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -3085,13 +3027,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C2" s="2">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D2" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3099,13 +3041,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C3" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D3" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3113,13 +3055,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D4" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3127,13 +3069,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-05-01</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-05-01</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-05-01</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-05-01</t>
+    <t>Price_2026-05-08</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-05-08</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-05-08</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-05-08</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-05-08</t>
   </si>
   <si>
     <t>RS_Score_2026-05-01</t>
@@ -43,153 +46,150 @@
     <t>RS_Score_2026-04-17</t>
   </si>
   <si>
-    <t>RS_Score_2026-04-10</t>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
   </si>
   <si>
     <t>ADANIENT</t>
   </si>
   <si>
-    <t>NESTLEIND</t>
+    <t>BAJAJ-AUTO</t>
   </si>
   <si>
     <t>HINDALCO</t>
   </si>
   <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
     <t>COALINDIA</t>
   </si>
   <si>
-    <t>ADANIPORTS</t>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>TITAN</t>
   </si>
   <si>
     <t>ONGC</t>
   </si>
   <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>TITAN</t>
+    <t>TATACONSUM</t>
   </si>
   <si>
     <t>DRREDDY</t>
   </si>
   <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
+    <t>CIPLA</t>
   </si>
   <si>
     <t>BEL</t>
   </si>
   <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>ETERNAL</t>
+  </si>
+  <si>
+    <t>TMPV</t>
+  </si>
+  <si>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
     <t>LT</t>
   </si>
   <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>TMPV</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
   </si>
   <si>
     <t>AXISBANK</t>
   </si>
   <si>
-    <t>ASIANPAINT</t>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
   </si>
   <si>
     <t>SBIN</t>
   </si>
   <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>MAXHEALTH</t>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
   </si>
   <si>
     <t>ITC</t>
   </si>
   <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
   </si>
   <si>
     <t>WIPRO</t>
   </si>
   <si>
-    <t>ETERNAL</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
+    <t>HDFCBANK</t>
   </si>
   <si>
     <t>TCS</t>
   </si>
   <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
     <t>INFY</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
     <t>2026-05-01</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-04-17</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
   </si>
 </sst>
 </file>
@@ -722,28 +722,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>2408.4</v>
+        <v>1760.4</v>
       </c>
       <c r="C2" s="2">
-        <v>7.88</v>
+        <v>18.38</v>
       </c>
       <c r="D2" s="2">
-        <v>12.72</v>
+        <v>13.15</v>
       </c>
       <c r="E2" s="2">
-        <v>30.71</v>
+        <v>19.32</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>94</v>
+        <v>93.48</v>
       </c>
       <c r="H2" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I2" s="2">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>60</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1458.6</v>
+        <v>1482.4</v>
       </c>
       <c r="C3" s="2">
-        <v>18.78</v>
+        <v>17.11</v>
       </c>
       <c r="D3" s="2">
-        <v>13.72</v>
+        <v>12.72</v>
       </c>
       <c r="E3" s="2">
-        <v>23.53</v>
+        <v>18.66</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
+        <v>97.83</v>
+      </c>
+      <c r="H3" s="2">
         <v>98</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>64</v>
-      </c>
-      <c r="I3" s="2">
-        <v>60</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,16 +786,16 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>1038</v>
+        <v>2505.9</v>
       </c>
       <c r="C4" s="2">
-        <v>22.29</v>
+        <v>12.38</v>
       </c>
       <c r="D4" s="2">
-        <v>14.19</v>
+        <v>14.37</v>
       </c>
       <c r="E4" s="2">
-        <v>14.75</v>
+        <v>20.08</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
@@ -804,10 +804,10 @@
         <v>100</v>
       </c>
       <c r="H4" s="2">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I4" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>481.45</v>
+        <v>10711.5</v>
       </c>
       <c r="C5" s="2">
-        <v>26.79</v>
+        <v>18.17</v>
       </c>
       <c r="D5" s="2">
-        <v>19.28</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E5" s="2">
-        <v>7.13</v>
+        <v>9.15</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>74</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="H5" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I5" s="2">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>1657.3</v>
+        <v>1044.4</v>
       </c>
       <c r="C6" s="2">
-        <v>11.51</v>
+        <v>19.65</v>
       </c>
       <c r="D6" s="2">
-        <v>9.1</v>
+        <v>13.99</v>
       </c>
       <c r="E6" s="2">
-        <v>19.63</v>
+        <v>5.27</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>84</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H6" s="2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I6" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>299.55</v>
+        <v>402.15</v>
       </c>
       <c r="C7" s="2">
-        <v>31.64</v>
+        <v>25.02</v>
       </c>
       <c r="D7" s="2">
-        <v>14.66</v>
+        <v>7.11</v>
       </c>
       <c r="E7" s="2">
-        <v>3.99</v>
+        <v>5.79</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>86</v>
+        <v>91.3</v>
       </c>
       <c r="H7" s="2">
         <v>92</v>
       </c>
       <c r="I7" s="2">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>399.15</v>
+        <v>1847.9</v>
       </c>
       <c r="C8" s="2">
-        <v>25.19</v>
+        <v>8.17</v>
       </c>
       <c r="D8" s="2">
-        <v>9.960000000000001</v>
+        <v>6.67</v>
       </c>
       <c r="E8" s="2">
-        <v>9.460000000000001</v>
+        <v>11.66</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>92</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="H8" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I8" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>318.35</v>
+        <v>214.49</v>
       </c>
       <c r="C9" s="2">
-        <v>23.3</v>
+        <v>26.83</v>
       </c>
       <c r="D9" s="2">
-        <v>10.85</v>
+        <v>3.05</v>
       </c>
       <c r="E9" s="2">
-        <v>8.73</v>
+        <v>3.81</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>82</v>
+        <v>82.61</v>
       </c>
       <c r="H9" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>211.36</v>
+        <v>8097</v>
       </c>
       <c r="C10" s="2">
-        <v>24.08</v>
+        <v>13.3</v>
       </c>
       <c r="D10" s="2">
-        <v>4.03</v>
+        <v>5.25</v>
       </c>
       <c r="E10" s="2">
-        <v>8.609999999999999</v>
+        <v>7.79</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>90</v>
+        <v>67.39</v>
       </c>
       <c r="H10" s="2">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="I10" s="2">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>1264.5</v>
+        <v>456.4</v>
       </c>
       <c r="C11" s="2">
-        <v>17.16</v>
+        <v>14.99</v>
       </c>
       <c r="D11" s="2">
-        <v>2.64</v>
+        <v>7.14</v>
       </c>
       <c r="E11" s="2">
-        <v>10.88</v>
+        <v>5.14</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>76</v>
+        <v>89.13</v>
       </c>
       <c r="H11" s="2">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I11" s="2">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>9994</v>
+        <v>313.95</v>
       </c>
       <c r="C12" s="2">
-        <v>12.36</v>
+        <v>19.6</v>
       </c>
       <c r="D12" s="2">
-        <v>2.4</v>
+        <v>3.49</v>
       </c>
       <c r="E12" s="2">
-        <v>12.35</v>
+        <v>3.7</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>62</v>
+        <v>84.78</v>
       </c>
       <c r="H12" s="2">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="I12" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>4144.6</v>
+        <v>1277.8</v>
       </c>
       <c r="C13" s="2">
-        <v>2.46</v>
+        <v>16.76</v>
       </c>
       <c r="D13" s="2">
-        <v>-2.53</v>
+        <v>3.01</v>
       </c>
       <c r="E13" s="2">
-        <v>17.53</v>
+        <v>5.19</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>96</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="H13" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I13" s="2">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>4385.2</v>
+        <v>2968.6</v>
       </c>
       <c r="C14" s="2">
-        <v>12.21</v>
+        <v>5.36</v>
       </c>
       <c r="D14" s="2">
-        <v>4.93</v>
+        <v>3.31</v>
       </c>
       <c r="E14" s="2">
-        <v>7.86</v>
+        <v>8.24</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>88</v>
+        <v>54.35</v>
       </c>
       <c r="H14" s="2">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="I14" s="2">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>1322.9</v>
+        <v>2599.9</v>
       </c>
       <c r="C15" s="2">
-        <v>4</v>
+        <v>-5.34</v>
       </c>
       <c r="D15" s="2">
-        <v>4.32</v>
+        <v>7</v>
       </c>
       <c r="E15" s="2">
-        <v>9.369999999999999</v>
+        <v>10.13</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>52</v>
+        <v>58.7</v>
       </c>
       <c r="H15" s="2">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="I15" s="2">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>1144.6</v>
+        <v>4242.3</v>
       </c>
       <c r="C16" s="2">
-        <v>-2.98</v>
+        <v>-1</v>
       </c>
       <c r="D16" s="2">
-        <v>1.1</v>
+        <v>4.62</v>
       </c>
       <c r="E16" s="2">
-        <v>11.8</v>
+        <v>8.32</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>68</v>
+        <v>76.09</v>
       </c>
       <c r="H16" s="2">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="I16" s="2">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>7636.5</v>
+        <v>4509</v>
       </c>
       <c r="C17" s="2">
-        <v>10.48</v>
+        <v>12.95</v>
       </c>
       <c r="D17" s="2">
-        <v>1.38</v>
+        <v>5.53</v>
       </c>
       <c r="E17" s="2">
-        <v>4.53</v>
+        <v>0.09</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>70</v>
+        <v>73.91</v>
       </c>
       <c r="H17" s="2">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="I17" s="2">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>431.3</v>
+        <v>279.2</v>
       </c>
       <c r="C18" s="2">
-        <v>12.33</v>
+        <v>21.85</v>
       </c>
       <c r="D18" s="2">
-        <v>-0.55</v>
+        <v>1.29</v>
       </c>
       <c r="E18" s="2">
-        <v>3.01</v>
+        <v>-2.55</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>72</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H18" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I18" s="2">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>4014</v>
+        <v>1176.2</v>
       </c>
       <c r="C19" s="2">
-        <v>-1.19</v>
+        <v>0.04</v>
       </c>
       <c r="D19" s="2">
-        <v>-3.83</v>
+        <v>0.38</v>
       </c>
       <c r="E19" s="2">
-        <v>11.27</v>
+        <v>7.54</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>66</v>
+        <v>65.22</v>
       </c>
       <c r="H19" s="2">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="I19" s="2">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>1808.3</v>
+        <v>1293.9</v>
       </c>
       <c r="C20" s="2">
-        <v>1.51</v>
+        <v>1.94</v>
       </c>
       <c r="D20" s="2">
-        <v>6.53</v>
+        <v>-1.03</v>
       </c>
       <c r="E20" s="2">
-        <v>4.62</v>
+        <v>5.01</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>20</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="H20" s="2">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="I20" s="2">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>2250.9</v>
+        <v>1347</v>
       </c>
       <c r="C21" s="2">
-        <v>-1.09</v>
+        <v>-10.56</v>
       </c>
       <c r="D21" s="2">
-        <v>-2.36</v>
+        <v>1.55</v>
       </c>
       <c r="E21" s="2">
-        <v>9.02</v>
+        <v>9.56</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>60</v>
+        <v>39.13</v>
       </c>
       <c r="H21" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I21" s="2">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>937</v>
+        <v>439.7</v>
       </c>
       <c r="C22" s="2">
-        <v>-6.26</v>
+        <v>10.82</v>
       </c>
       <c r="D22" s="2">
-        <v>-8.56</v>
+        <v>0.41</v>
       </c>
       <c r="E22" s="2">
-        <v>14.65</v>
+        <v>-0.62</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>42</v>
+        <v>60.87</v>
       </c>
       <c r="H22" s="2">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="I22" s="2">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>341.55</v>
+        <v>2287.7</v>
       </c>
       <c r="C23" s="2">
-        <v>-1.39</v>
+        <v>0.1</v>
       </c>
       <c r="D23" s="2">
-        <v>-10.18</v>
+        <v>-2.46</v>
       </c>
       <c r="E23" s="2">
-        <v>12.74</v>
+        <v>6.14</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>56</v>
+        <v>56.52</v>
       </c>
       <c r="H23" s="2">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="I23" s="2">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>2794.5</v>
+        <v>1435.2</v>
       </c>
       <c r="C24" s="2">
-        <v>-0.43</v>
+        <v>-7.95</v>
       </c>
       <c r="D24" s="2">
-        <v>-3.24</v>
+        <v>0.5</v>
       </c>
       <c r="E24" s="2">
-        <v>7.78</v>
+        <v>6.3</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>50</v>
+        <v>41.3</v>
       </c>
       <c r="H24" s="2">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="I24" s="2">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,25 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>1268.3</v>
+        <v>256.39</v>
       </c>
       <c r="C25" s="2">
-        <v>3.56</v>
+        <v>-9</v>
       </c>
       <c r="D25" s="2">
-        <v>-4.8</v>
+        <v>-4.33</v>
       </c>
       <c r="E25" s="2">
-        <v>6.3</v>
+        <v>6.73</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
-      <c r="G25" s="2">
-        <v>78</v>
-      </c>
       <c r="H25" s="2">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="I25" s="2">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1487,25 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>2444.5</v>
+        <v>355.45</v>
       </c>
       <c r="C26" s="2">
-        <v>-12.25</v>
+        <v>-0.93</v>
       </c>
       <c r="D26" s="2">
-        <v>3.3</v>
+        <v>-6.45</v>
       </c>
       <c r="E26" s="2">
-        <v>9.83</v>
+        <v>3.75</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
-      <c r="G26" s="2">
-        <v>54</v>
-      </c>
       <c r="H26" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I26" s="2">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1516,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>1068.45</v>
+        <v>1012.5</v>
       </c>
       <c r="C27" s="2">
-        <v>9.49</v>
+        <v>-5.75</v>
       </c>
       <c r="D27" s="2">
-        <v>-10.86</v>
+        <v>-6.56</v>
       </c>
       <c r="E27" s="2">
-        <v>4.98</v>
+        <v>6.2</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>64</v>
+        <v>34.78</v>
       </c>
       <c r="H27" s="2">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="I27" s="2">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1548,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>11586</v>
+        <v>11950</v>
       </c>
       <c r="C28" s="2">
-        <v>0.4</v>
+        <v>1.32</v>
       </c>
       <c r="D28" s="2">
-        <v>-10.62</v>
+        <v>-7.91</v>
       </c>
       <c r="E28" s="2">
-        <v>8.140000000000001</v>
+        <v>3.12</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H28" s="2">
         <v>58</v>
       </c>
       <c r="I28" s="2">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1580,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>1309.6</v>
+        <v>1007.75</v>
       </c>
       <c r="C29" s="2">
-        <v>-12.51</v>
+        <v>4.95</v>
       </c>
       <c r="D29" s="2">
-        <v>-1.64</v>
+        <v>-5.35</v>
       </c>
       <c r="E29" s="2">
-        <v>9.51</v>
+        <v>-1.93</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>38</v>
+        <v>43.48</v>
       </c>
       <c r="H29" s="2">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="I29" s="2">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1612,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>937.35</v>
+        <v>1463</v>
       </c>
       <c r="C30" s="2">
-        <v>8.460000000000001</v>
+        <v>-9.26</v>
       </c>
       <c r="D30" s="2">
-        <v>-12.05</v>
+        <v>1.53</v>
       </c>
       <c r="E30" s="2">
-        <v>4.09</v>
+        <v>1.58</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>80</v>
+        <v>28.26</v>
       </c>
       <c r="H30" s="2">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="I30" s="2">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1644,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>1430.8</v>
+        <v>955.35</v>
       </c>
       <c r="C31" s="2">
-        <v>-7.36</v>
+        <v>-4.47</v>
       </c>
       <c r="D31" s="2">
-        <v>0.79</v>
+        <v>-7.34</v>
       </c>
       <c r="E31" s="2">
-        <v>4.5</v>
+        <v>3.33</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>12</v>
+        <v>52.17</v>
       </c>
       <c r="H31" s="2">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="I31" s="2">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1676,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>1473.5</v>
+        <v>3330.4</v>
       </c>
       <c r="C32" s="2">
-        <v>-6.71</v>
+        <v>-8.08</v>
       </c>
       <c r="D32" s="2">
-        <v>-3.97</v>
+        <v>-3.39</v>
       </c>
       <c r="E32" s="2">
-        <v>4.91</v>
+        <v>2.17</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>10</v>
+        <v>15.22</v>
       </c>
       <c r="H32" s="2">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="I32" s="2">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1708,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>993.05</v>
+        <v>3974.5</v>
       </c>
       <c r="C33" s="2">
-        <v>-3.69</v>
+        <v>-1.8</v>
       </c>
       <c r="D33" s="2">
-        <v>-5.75</v>
+        <v>-10.04</v>
       </c>
       <c r="E33" s="2">
-        <v>3.56</v>
+        <v>0.37</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>40</v>
+        <v>63.04</v>
       </c>
       <c r="H33" s="2">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I33" s="2">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1740,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>314.9</v>
+        <v>7302.5</v>
       </c>
       <c r="C34" s="2">
-        <v>-19.58</v>
+        <v>-0.29</v>
       </c>
       <c r="D34" s="2">
-        <v>0.37</v>
+        <v>-9.16</v>
       </c>
       <c r="E34" s="2">
-        <v>7.95</v>
+        <v>-1.64</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>28</v>
+        <v>36.96</v>
       </c>
       <c r="H34" s="2">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="I34" s="2">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1772,25 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>7109</v>
+        <v>249.34</v>
       </c>
       <c r="C35" s="2">
-        <v>-0.36</v>
+        <v>-16.03</v>
       </c>
       <c r="D35" s="2">
-        <v>-11.85</v>
+        <v>-3.28</v>
       </c>
       <c r="E35" s="2">
-        <v>4.15</v>
+        <v>2.52</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
-      <c r="G35" s="2">
-        <v>46</v>
-      </c>
       <c r="H35" s="2">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="I35" s="2">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1801,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>1886.8</v>
+        <v>1268.3</v>
       </c>
       <c r="C36" s="2">
-        <v>-10.49</v>
+        <v>3.26</v>
       </c>
       <c r="D36" s="2">
-        <v>-5.88</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="E36" s="2">
-        <v>5.89</v>
+        <v>-6.11</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>30</v>
+        <v>47.83</v>
       </c>
       <c r="H36" s="2">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="I36" s="2">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1833,25 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>383.3</v>
+        <v>4522.7</v>
       </c>
       <c r="C37" s="2">
-        <v>-11.81</v>
+        <v>-10.87</v>
       </c>
       <c r="D37" s="2">
-        <v>-8.880000000000001</v>
+        <v>-6.98</v>
       </c>
       <c r="E37" s="2">
-        <v>7.65</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
-      <c r="G37" s="2">
-        <v>22</v>
-      </c>
       <c r="H37" s="2">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="I37" s="2">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1862,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>1263.4</v>
+        <v>1818.3</v>
       </c>
       <c r="C38" s="2">
-        <v>-6.58</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="D38" s="2">
-        <v>-10.69</v>
+        <v>-11.37</v>
       </c>
       <c r="E38" s="2">
-        <v>4.18</v>
+        <v>0.5</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>48</v>
+        <v>19.57</v>
       </c>
       <c r="H38" s="2">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="I38" s="2">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1894,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>246.37</v>
+        <v>380.8</v>
       </c>
       <c r="C39" s="2">
-        <v>-15.96</v>
+        <v>-12.02</v>
       </c>
       <c r="D39" s="2">
-        <v>-6.66</v>
+        <v>-11.59</v>
       </c>
       <c r="E39" s="2">
-        <v>6.23</v>
+        <v>1.67</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>34</v>
+        <v>26.09</v>
       </c>
       <c r="H39" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I39" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1926,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>1747.2</v>
+        <v>1019.3</v>
       </c>
       <c r="C40" s="2">
-        <v>-13.56</v>
+        <v>5.48</v>
       </c>
       <c r="D40" s="2">
-        <v>-13.64</v>
+        <v>-16.98</v>
       </c>
       <c r="E40" s="2">
-        <v>6.08</v>
+        <v>-4.44</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>32</v>
+        <v>45.65</v>
       </c>
       <c r="H40" s="2">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="I40" s="2">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1958,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>1819</v>
+        <v>1872.1</v>
       </c>
       <c r="C41" s="2">
-        <v>-9.390000000000001</v>
+        <v>-7.15</v>
       </c>
       <c r="D41" s="2">
-        <v>-10.45</v>
+        <v>-11.13</v>
       </c>
       <c r="E41" s="2">
-        <v>1.59</v>
+        <v>-2.66</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
+        <v>21.74</v>
+      </c>
+      <c r="H41" s="2">
         <v>18</v>
       </c>
-      <c r="H41" s="2">
+      <c r="I41" s="2">
         <v>46</v>
-      </c>
-      <c r="I41" s="2">
-        <v>48</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +1990,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>200.65</v>
+        <v>1264.8</v>
       </c>
       <c r="C42" s="2">
-        <v>-21.18</v>
+        <v>-6.34</v>
       </c>
       <c r="D42" s="2">
-        <v>-6.28</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="E42" s="2">
-        <v>4.95</v>
+        <v>-4.32</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>24</v>
+        <v>23.91</v>
       </c>
       <c r="H42" s="2">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="I42" s="2">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2022,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>247.03</v>
+        <v>1834.5</v>
       </c>
       <c r="C43" s="2">
-        <v>-13.16</v>
+        <v>-12.87</v>
       </c>
       <c r="D43" s="2">
-        <v>-13.38</v>
+        <v>-8.15</v>
       </c>
       <c r="E43" s="2">
-        <v>4.44</v>
+        <v>-1.9</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>36</v>
+        <v>30.43</v>
       </c>
       <c r="H43" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I43" s="2">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2054,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>13314</v>
+        <v>307.45</v>
       </c>
       <c r="C44" s="2">
-        <v>-18.81</v>
+        <v>-22.33</v>
       </c>
       <c r="D44" s="2">
-        <v>-12.62</v>
+        <v>-5.52</v>
       </c>
       <c r="E44" s="2">
-        <v>6.44</v>
+        <v>1.05</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>26</v>
+        <v>32.61</v>
       </c>
       <c r="H44" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I44" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2086,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>4295.3</v>
+        <v>13726</v>
       </c>
       <c r="C45" s="2">
-        <v>-13.76</v>
+        <v>-17.29</v>
       </c>
       <c r="D45" s="2">
-        <v>-12.86</v>
+        <v>-8.93</v>
       </c>
       <c r="E45" s="2">
-        <v>2.74</v>
+        <v>0.12</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>44</v>
+        <v>17.39</v>
       </c>
       <c r="H45" s="2">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="I45" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,28 +2118,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>3097.5</v>
+        <v>621.7</v>
       </c>
       <c r="C46" s="2">
-        <v>-14.26</v>
+        <v>-16.93</v>
       </c>
       <c r="D46" s="2">
-        <v>-12.34</v>
+        <v>-16.26</v>
       </c>
       <c r="E46" s="2">
-        <v>2.18</v>
+        <v>2.9</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>16</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H46" s="2">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I46" s="2">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2150,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>2473.9</v>
+        <v>197.91</v>
       </c>
       <c r="C47" s="2">
-        <v>-21.72</v>
+        <v>-23.76</v>
       </c>
       <c r="D47" s="2">
-        <v>-8.109999999999999</v>
+        <v>-3.88</v>
       </c>
       <c r="E47" s="2">
-        <v>2.73</v>
+        <v>-3.4</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>8</v>
+        <v>13.04</v>
       </c>
       <c r="H47" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I47" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,28 +2182,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>771.7</v>
+        <v>780.85</v>
       </c>
       <c r="C48" s="2">
-        <v>-21.58</v>
+        <v>-21.29</v>
       </c>
       <c r="D48" s="2">
-        <v>-14.63</v>
+        <v>-15.46</v>
       </c>
       <c r="E48" s="2">
-        <v>3.97</v>
+        <v>-3.63</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
+        <v>6.52</v>
+      </c>
+      <c r="H48" s="2">
         <v>14</v>
       </c>
-      <c r="H48" s="2">
+      <c r="I48" s="2">
         <v>2</v>
-      </c>
-      <c r="I48" s="2">
-        <v>8</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,28 +2214,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>586.9</v>
+        <v>2394.4</v>
       </c>
       <c r="C49" s="2">
-        <v>-22.11</v>
+        <v>-25.67</v>
       </c>
       <c r="D49" s="2">
-        <v>-15.77</v>
+        <v>-10.53</v>
       </c>
       <c r="E49" s="2">
-        <v>2.43</v>
+        <v>-5.15</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>6</v>
+        <v>10.87</v>
       </c>
       <c r="H49" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I49" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,28 +2246,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>1181.8</v>
+        <v>1179.2</v>
       </c>
       <c r="C50" s="2">
-        <v>-26.23</v>
+        <v>-28.8</v>
       </c>
       <c r="D50" s="2">
-        <v>-13.68</v>
+        <v>-11.17</v>
       </c>
       <c r="E50" s="2">
-        <v>-7.36</v>
+        <v>-8.77</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
+        <v>4.35</v>
+      </c>
+      <c r="H50" s="2">
         <v>4</v>
       </c>
-      <c r="H50" s="2">
+      <c r="I50" s="2">
         <v>8</v>
-      </c>
-      <c r="I50" s="2">
-        <v>6</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2278,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>1199.1</v>
+        <v>1198.4</v>
       </c>
       <c r="C51" s="2">
-        <v>-25.62</v>
+        <v>-25.93</v>
       </c>
       <c r="D51" s="2">
-        <v>-16.02</v>
+        <v>-14.36</v>
       </c>
       <c r="E51" s="2">
-        <v>-9.77</v>
+        <v>-15.84</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
+        <v>2.17</v>
+      </c>
+      <c r="H51" s="2">
         <v>2</v>
       </c>
-      <c r="H51" s="2">
+      <c r="I51" s="2">
         <v>30</v>
-      </c>
-      <c r="I51" s="2">
-        <v>42</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2459,86 +2447,86 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>1038</v>
+        <v>1760.4</v>
       </c>
       <c r="C2" s="2">
-        <v>22.29</v>
+        <v>18.38</v>
       </c>
       <c r="D2" s="2">
-        <v>14.19</v>
+        <v>13.15</v>
       </c>
       <c r="E2" s="2">
-        <v>14.75</v>
+        <v>19.32</v>
       </c>
       <c r="F2" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>100</v>
+        <v>93.48</v>
       </c>
       <c r="H2" s="2">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="I2" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1">
-        <v>1657.3</v>
+        <v>2505.9</v>
       </c>
       <c r="C3" s="2">
-        <v>11.51</v>
+        <v>12.38</v>
       </c>
       <c r="D3" s="2">
-        <v>9.1</v>
+        <v>14.37</v>
       </c>
       <c r="E3" s="2">
-        <v>19.63</v>
+        <v>20.08</v>
       </c>
       <c r="F3" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G3" s="2">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H3" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I3" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
-        <v>299.55</v>
+        <v>1044.4</v>
       </c>
       <c r="C4" s="2">
-        <v>31.64</v>
+        <v>19.65</v>
       </c>
       <c r="D4" s="2">
-        <v>14.66</v>
+        <v>13.99</v>
       </c>
       <c r="E4" s="2">
-        <v>3.99</v>
+        <v>5.27</v>
       </c>
       <c r="F4" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G4" s="2">
-        <v>86</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H4" s="2">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="I4" s="2">
         <v>100</v>
@@ -2546,31 +2534,31 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>399.15</v>
+        <v>402.15</v>
       </c>
       <c r="C5" s="2">
-        <v>25.19</v>
+        <v>25.02</v>
       </c>
       <c r="D5" s="2">
-        <v>9.960000000000001</v>
+        <v>7.11</v>
       </c>
       <c r="E5" s="2">
-        <v>9.460000000000001</v>
+        <v>5.79</v>
       </c>
       <c r="F5" s="2">
+        <v>90</v>
+      </c>
+      <c r="G5" s="2">
+        <v>91.3</v>
+      </c>
+      <c r="H5" s="2">
+        <v>92</v>
+      </c>
+      <c r="I5" s="2">
         <v>88</v>
-      </c>
-      <c r="G5" s="2">
-        <v>92</v>
-      </c>
-      <c r="H5" s="2">
-        <v>88</v>
-      </c>
-      <c r="I5" s="2">
-        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2578,57 +2566,57 @@
         <v>16</v>
       </c>
       <c r="B6" s="1">
-        <v>318.35</v>
+        <v>214.49</v>
       </c>
       <c r="C6" s="2">
-        <v>23.3</v>
+        <v>26.83</v>
       </c>
       <c r="D6" s="2">
-        <v>10.85</v>
+        <v>3.05</v>
       </c>
       <c r="E6" s="2">
-        <v>8.73</v>
+        <v>3.81</v>
       </c>
       <c r="F6" s="2">
         <v>86</v>
       </c>
       <c r="G6" s="2">
-        <v>82</v>
+        <v>82.61</v>
       </c>
       <c r="H6" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I6" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1">
-        <v>211.36</v>
+        <v>313.95</v>
       </c>
       <c r="C7" s="2">
-        <v>24.08</v>
+        <v>19.6</v>
       </c>
       <c r="D7" s="2">
-        <v>4.03</v>
+        <v>3.49</v>
       </c>
       <c r="E7" s="2">
-        <v>8.609999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="F7" s="2">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G7" s="2">
-        <v>90</v>
+        <v>84.78</v>
       </c>
       <c r="H7" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I7" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2682,7 +2670,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2724,28 +2712,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>2408.4</v>
+        <v>1760.4</v>
       </c>
       <c r="C2" s="2">
-        <v>7.88</v>
+        <v>18.38</v>
       </c>
       <c r="D2" s="2">
-        <v>12.72</v>
+        <v>13.15</v>
       </c>
       <c r="E2" s="2">
-        <v>30.71</v>
+        <v>19.32</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>94</v>
+        <v>93.48</v>
       </c>
       <c r="H2" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I2" s="2">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2753,28 +2741,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1458.6</v>
+        <v>1482.4</v>
       </c>
       <c r="C3" s="2">
-        <v>18.78</v>
+        <v>17.11</v>
       </c>
       <c r="D3" s="2">
-        <v>13.72</v>
+        <v>12.72</v>
       </c>
       <c r="E3" s="2">
-        <v>23.53</v>
+        <v>18.66</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
+        <v>97.83</v>
+      </c>
+      <c r="H3" s="2">
         <v>98</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>64</v>
-      </c>
-      <c r="I3" s="2">
-        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2782,16 +2770,16 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>1038</v>
+        <v>2505.9</v>
       </c>
       <c r="C4" s="2">
-        <v>22.29</v>
+        <v>12.38</v>
       </c>
       <c r="D4" s="2">
-        <v>14.19</v>
+        <v>14.37</v>
       </c>
       <c r="E4" s="2">
-        <v>14.75</v>
+        <v>20.08</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
@@ -2800,65 +2788,65 @@
         <v>100</v>
       </c>
       <c r="H4" s="2">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I4" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1657.3</v>
+        <v>10711.5</v>
       </c>
       <c r="C5" s="2">
-        <v>11.51</v>
+        <v>18.17</v>
       </c>
       <c r="D5" s="2">
-        <v>9.1</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E5" s="2">
-        <v>19.63</v>
+        <v>9.15</v>
       </c>
       <c r="F5" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>84</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="H5" s="2">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="I5" s="2">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>299.55</v>
+        <v>1044.4</v>
       </c>
       <c r="C6" s="2">
-        <v>31.64</v>
+        <v>19.65</v>
       </c>
       <c r="D6" s="2">
-        <v>14.66</v>
+        <v>13.99</v>
       </c>
       <c r="E6" s="2">
-        <v>3.99</v>
+        <v>5.27</v>
       </c>
       <c r="F6" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>86</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H6" s="2">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="I6" s="2">
         <v>100</v>
@@ -2866,31 +2854,31 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>399.15</v>
+        <v>402.15</v>
       </c>
       <c r="C7" s="2">
-        <v>25.19</v>
+        <v>25.02</v>
       </c>
       <c r="D7" s="2">
-        <v>9.960000000000001</v>
+        <v>7.11</v>
       </c>
       <c r="E7" s="2">
-        <v>9.460000000000001</v>
+        <v>5.79</v>
       </c>
       <c r="F7" s="2">
+        <v>90</v>
+      </c>
+      <c r="G7" s="2">
+        <v>91.3</v>
+      </c>
+      <c r="H7" s="2">
+        <v>92</v>
+      </c>
+      <c r="I7" s="2">
         <v>88</v>
-      </c>
-      <c r="G7" s="2">
-        <v>92</v>
-      </c>
-      <c r="H7" s="2">
-        <v>88</v>
-      </c>
-      <c r="I7" s="2">
-        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2898,61 +2886,90 @@
         <v>16</v>
       </c>
       <c r="B8" s="1">
-        <v>318.35</v>
+        <v>214.49</v>
       </c>
       <c r="C8" s="2">
-        <v>23.3</v>
+        <v>26.83</v>
       </c>
       <c r="D8" s="2">
-        <v>10.85</v>
+        <v>3.05</v>
       </c>
       <c r="E8" s="2">
-        <v>8.73</v>
+        <v>3.81</v>
       </c>
       <c r="F8" s="2">
         <v>86</v>
       </c>
       <c r="G8" s="2">
-        <v>82</v>
+        <v>82.61</v>
       </c>
       <c r="H8" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I8" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1">
-        <v>211.36</v>
+        <v>456.4</v>
       </c>
       <c r="C9" s="2">
-        <v>24.08</v>
+        <v>14.99</v>
       </c>
       <c r="D9" s="2">
-        <v>4.03</v>
+        <v>7.14</v>
       </c>
       <c r="E9" s="2">
-        <v>8.609999999999999</v>
+        <v>5.14</v>
       </c>
       <c r="F9" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G9" s="2">
-        <v>90</v>
+        <v>89.13</v>
       </c>
       <c r="H9" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="I9" s="2">
-        <v>96</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1">
+        <v>313.95</v>
+      </c>
+      <c r="C10" s="2">
+        <v>19.6</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3.49</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="F10" s="2">
+        <v>80</v>
+      </c>
+      <c r="G10" s="2">
+        <v>84.78</v>
+      </c>
+      <c r="H10" s="2">
+        <v>82</v>
+      </c>
+      <c r="I10" s="2">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C2:C10">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2960,7 +2977,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D10">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2968,7 +2985,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E10">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2976,22 +2993,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F10">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G10">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H10">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
+  <conditionalFormatting sqref="I2:I10">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -3027,13 +3044,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C2" s="2">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D2" s="2">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3041,13 +3058,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C3" s="2">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D3" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3055,13 +3072,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C4" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D4" s="2">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3069,13 +3086,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C5" s="2">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D5" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-05-08</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-05-08</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-05-08</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-05-08</t>
+    <t>Price_2026-05-15</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-05-15</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-05-15</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-05-15</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-05-15</t>
   </si>
   <si>
     <t>RS_Score_2026-05-08</t>
@@ -43,7 +46,7 @@
     <t>RS_Score_2026-04-24</t>
   </si>
   <si>
-    <t>RS_Score_2026-04-17</t>
+    <t>ADANIENT</t>
   </si>
   <si>
     <t>ADANIPORTS</t>
@@ -52,64 +55,88 @@
     <t>NESTLEIND</t>
   </si>
   <si>
-    <t>ADANIENT</t>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
   </si>
   <si>
     <t>BAJAJ-AUTO</t>
   </si>
   <si>
-    <t>HINDALCO</t>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
   </si>
   <si>
     <t>NTPC</t>
   </si>
   <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
   </si>
   <si>
     <t>POWERGRID</t>
   </si>
   <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>TMPV</t>
   </si>
   <si>
     <t>TRENT</t>
   </si>
   <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
     <t>TITAN</t>
   </si>
   <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
     <t>BEL</t>
   </si>
   <si>
-    <t>HINDUNILVR</t>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
   </si>
   <si>
     <t>RELIANCE</t>
@@ -118,75 +145,48 @@
     <t>ETERNAL</t>
   </si>
   <si>
-    <t>TMPV</t>
-  </si>
-  <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
   </si>
   <si>
     <t>SHRIRAMFIN</t>
   </si>
   <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
     <t>SBIN</t>
   </si>
   <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
+    <t>HDFCBANK</t>
   </si>
   <si>
     <t>WIPRO</t>
   </si>
   <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
     <t>TCS</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
     <t>2026-05-08</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-17</t>
   </si>
 </sst>
 </file>
@@ -722,28 +722,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>1760.4</v>
+        <v>2716</v>
       </c>
       <c r="C2" s="2">
-        <v>18.38</v>
+        <v>19.13</v>
       </c>
       <c r="D2" s="2">
-        <v>13.15</v>
+        <v>27.84</v>
       </c>
       <c r="E2" s="2">
-        <v>19.32</v>
+        <v>21.82</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>93.48</v>
+        <v>96</v>
       </c>
       <c r="H2" s="2">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>60</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1482.4</v>
+        <v>1795.1</v>
       </c>
       <c r="C3" s="2">
-        <v>17.11</v>
+        <v>20.52</v>
       </c>
       <c r="D3" s="2">
-        <v>12.72</v>
+        <v>22.09</v>
       </c>
       <c r="E3" s="2">
-        <v>18.66</v>
+        <v>13.73</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>97.83</v>
+        <v>100</v>
       </c>
       <c r="H3" s="2">
-        <v>98</v>
+        <v>93.48</v>
       </c>
       <c r="I3" s="2">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>2505.9</v>
+        <v>1430.5</v>
       </c>
       <c r="C4" s="2">
-        <v>12.38</v>
+        <v>12.39</v>
       </c>
       <c r="D4" s="2">
-        <v>14.37</v>
+        <v>11.78</v>
       </c>
       <c r="E4" s="2">
-        <v>20.08</v>
+        <v>11.2</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>94</v>
+        <v>97.83</v>
       </c>
       <c r="I4" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>10711.5</v>
+        <v>299.35</v>
       </c>
       <c r="C5" s="2">
-        <v>18.17</v>
+        <v>26.89</v>
       </c>
       <c r="D5" s="2">
-        <v>8.140000000000001</v>
+        <v>6.08</v>
       </c>
       <c r="E5" s="2">
-        <v>9.15</v>
+        <v>5.65</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>80.43000000000001</v>
+        <v>68</v>
       </c>
       <c r="H5" s="2">
-        <v>62</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="I5" s="2">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>1044.4</v>
+        <v>1878.2</v>
       </c>
       <c r="C6" s="2">
-        <v>19.65</v>
+        <v>9.4</v>
       </c>
       <c r="D6" s="2">
-        <v>13.99</v>
+        <v>7.17</v>
       </c>
       <c r="E6" s="2">
-        <v>5.27</v>
+        <v>12.56</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>95.65000000000001</v>
+        <v>88</v>
       </c>
       <c r="H6" s="2">
-        <v>100</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="I6" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>402.15</v>
+        <v>1067.5</v>
       </c>
       <c r="C7" s="2">
-        <v>25.02</v>
+        <v>15.32</v>
       </c>
       <c r="D7" s="2">
-        <v>7.11</v>
+        <v>13.56</v>
       </c>
       <c r="E7" s="2">
-        <v>5.79</v>
+        <v>5.15</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>91.3</v>
+        <v>92</v>
       </c>
       <c r="H7" s="2">
-        <v>92</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="I7" s="2">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>1847.9</v>
+        <v>1234</v>
       </c>
       <c r="C8" s="2">
-        <v>8.17</v>
+        <v>5.41</v>
       </c>
       <c r="D8" s="2">
-        <v>6.67</v>
+        <v>9.67</v>
       </c>
       <c r="E8" s="2">
-        <v>11.66</v>
+        <v>10.14</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>69.56999999999999</v>
+        <v>66</v>
       </c>
       <c r="H8" s="2">
-        <v>20</v>
+        <v>65.22</v>
       </c>
       <c r="I8" s="2">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>214.49</v>
+        <v>1432.1</v>
       </c>
       <c r="C9" s="2">
-        <v>26.83</v>
+        <v>-5.26</v>
       </c>
       <c r="D9" s="2">
-        <v>3.05</v>
+        <v>5.96</v>
       </c>
       <c r="E9" s="2">
-        <v>3.81</v>
+        <v>16.48</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>82.61</v>
+        <v>62</v>
       </c>
       <c r="H9" s="2">
-        <v>90</v>
+        <v>39.13</v>
       </c>
       <c r="I9" s="2">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>8097</v>
+        <v>8082.5</v>
       </c>
       <c r="C10" s="2">
-        <v>13.3</v>
+        <v>13.52</v>
       </c>
       <c r="D10" s="2">
-        <v>5.25</v>
+        <v>3.73</v>
       </c>
       <c r="E10" s="2">
-        <v>7.79</v>
+        <v>5.56</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
+        <v>84</v>
+      </c>
+      <c r="H10" s="2">
         <v>67.39</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <v>70</v>
-      </c>
-      <c r="I10" s="2">
-        <v>68</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>456.4</v>
+        <v>462.2</v>
       </c>
       <c r="C11" s="2">
-        <v>14.99</v>
+        <v>9.44</v>
       </c>
       <c r="D11" s="2">
-        <v>7.14</v>
+        <v>8.43</v>
       </c>
       <c r="E11" s="2">
-        <v>5.14</v>
+        <v>4.63</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
+        <v>82</v>
+      </c>
+      <c r="H11" s="2">
         <v>89.13</v>
       </c>
-      <c r="H11" s="2">
+      <c r="I11" s="2">
         <v>74</v>
-      </c>
-      <c r="I11" s="2">
-        <v>60</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>313.95</v>
+        <v>10377.5</v>
       </c>
       <c r="C12" s="2">
-        <v>19.6</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="D12" s="2">
-        <v>3.49</v>
+        <v>6.15</v>
       </c>
       <c r="E12" s="2">
-        <v>3.7</v>
+        <v>5.86</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>84.78</v>
+        <v>94</v>
       </c>
       <c r="H12" s="2">
-        <v>82</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="I12" s="2">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>1277.8</v>
+        <v>1336.7</v>
       </c>
       <c r="C13" s="2">
-        <v>16.76</v>
+        <v>6.42</v>
       </c>
       <c r="D13" s="2">
-        <v>3.01</v>
+        <v>3.27</v>
       </c>
       <c r="E13" s="2">
-        <v>5.19</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>78.26000000000001</v>
+        <v>64</v>
       </c>
       <c r="H13" s="2">
-        <v>76</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I13" s="2">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>2968.6</v>
+        <v>216.84</v>
       </c>
       <c r="C14" s="2">
-        <v>5.36</v>
+        <v>18.57</v>
       </c>
       <c r="D14" s="2">
-        <v>3.31</v>
+        <v>2.76</v>
       </c>
       <c r="E14" s="2">
-        <v>8.24</v>
+        <v>2.42</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>54.35</v>
+        <v>86</v>
       </c>
       <c r="H14" s="2">
-        <v>50</v>
+        <v>82.61</v>
       </c>
       <c r="I14" s="2">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>2599.9</v>
+        <v>2933.8</v>
       </c>
       <c r="C15" s="2">
-        <v>-5.34</v>
+        <v>2.71</v>
       </c>
       <c r="D15" s="2">
-        <v>7</v>
+        <v>5.63</v>
       </c>
       <c r="E15" s="2">
-        <v>10.13</v>
+        <v>6.29</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>58.7</v>
+        <v>76</v>
       </c>
       <c r="H15" s="2">
-        <v>54</v>
+        <v>54.35</v>
       </c>
       <c r="I15" s="2">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>4242.3</v>
+        <v>395.25</v>
       </c>
       <c r="C16" s="2">
-        <v>-1</v>
+        <v>13.1</v>
       </c>
       <c r="D16" s="2">
-        <v>4.62</v>
+        <v>4.69</v>
       </c>
       <c r="E16" s="2">
-        <v>8.32</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>76.09</v>
+        <v>90</v>
       </c>
       <c r="H16" s="2">
-        <v>96</v>
+        <v>91.3</v>
       </c>
       <c r="I16" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>4509</v>
+        <v>2605.6</v>
       </c>
       <c r="C17" s="2">
-        <v>12.95</v>
+        <v>-6.02</v>
       </c>
       <c r="D17" s="2">
-        <v>5.53</v>
+        <v>12.94</v>
       </c>
       <c r="E17" s="2">
-        <v>0.09</v>
+        <v>3.53</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>73.91</v>
+        <v>74</v>
       </c>
       <c r="H17" s="2">
-        <v>88</v>
+        <v>58.7</v>
       </c>
       <c r="I17" s="2">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>279.2</v>
+        <v>1278.8</v>
       </c>
       <c r="C18" s="2">
-        <v>21.85</v>
+        <v>8.31</v>
       </c>
       <c r="D18" s="2">
-        <v>1.29</v>
+        <v>0.91</v>
       </c>
       <c r="E18" s="2">
-        <v>-2.55</v>
+        <v>0.34</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>86.95999999999999</v>
+        <v>78</v>
       </c>
       <c r="H18" s="2">
-        <v>86</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="I18" s="2">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1176.2</v>
+        <v>305.85</v>
       </c>
       <c r="C19" s="2">
-        <v>0.04</v>
+        <v>14.15</v>
       </c>
       <c r="D19" s="2">
-        <v>0.38</v>
+        <v>3.05</v>
       </c>
       <c r="E19" s="2">
-        <v>7.54</v>
+        <v>-4.33</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>65.22</v>
+        <v>80</v>
       </c>
       <c r="H19" s="2">
-        <v>68</v>
+        <v>84.78</v>
       </c>
       <c r="I19" s="2">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>1293.9</v>
+        <v>1050.1</v>
       </c>
       <c r="C20" s="2">
-        <v>1.94</v>
+        <v>-1.18</v>
       </c>
       <c r="D20" s="2">
-        <v>-1.03</v>
+        <v>-3.09</v>
       </c>
       <c r="E20" s="2">
-        <v>5.01</v>
+        <v>3.83</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>71.73999999999999</v>
+        <v>50</v>
       </c>
       <c r="H20" s="2">
-        <v>52</v>
+        <v>34.78</v>
       </c>
       <c r="I20" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>1347</v>
+        <v>1905.4</v>
       </c>
       <c r="C21" s="2">
-        <v>-10.56</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="D21" s="2">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="E21" s="2">
-        <v>9.56</v>
+        <v>3.21</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>39.13</v>
+        <v>18</v>
       </c>
       <c r="H21" s="2">
-        <v>38</v>
+        <v>30.43</v>
       </c>
       <c r="I21" s="2">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>439.7</v>
+        <v>2272.2</v>
       </c>
       <c r="C22" s="2">
-        <v>10.82</v>
+        <v>-3.23</v>
       </c>
       <c r="D22" s="2">
-        <v>0.41</v>
+        <v>-2.09</v>
       </c>
       <c r="E22" s="2">
-        <v>-0.62</v>
+        <v>1.82</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>60.87</v>
+        <v>58</v>
       </c>
       <c r="H22" s="2">
-        <v>72</v>
+        <v>56.52</v>
       </c>
       <c r="I22" s="2">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,25 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>2287.7</v>
+        <v>356.55</v>
       </c>
       <c r="C23" s="2">
-        <v>0.1</v>
+        <v>-3.73</v>
       </c>
       <c r="D23" s="2">
-        <v>-2.46</v>
+        <v>-3.79</v>
       </c>
       <c r="E23" s="2">
-        <v>6.14</v>
+        <v>0.24</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>56.52</v>
-      </c>
-      <c r="H23" s="2">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I23" s="2">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1423,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>1435.2</v>
+        <v>4101.3</v>
       </c>
       <c r="C24" s="2">
-        <v>-7.95</v>
+        <v>-6.99</v>
       </c>
       <c r="D24" s="2">
-        <v>0.5</v>
+        <v>6.57</v>
       </c>
       <c r="E24" s="2">
-        <v>6.3</v>
+        <v>-3.34</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>41.3</v>
+        <v>72</v>
       </c>
       <c r="H24" s="2">
-        <v>12</v>
+        <v>76.09</v>
       </c>
       <c r="I24" s="2">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,25 +1455,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>256.39</v>
+        <v>309.45</v>
       </c>
       <c r="C25" s="2">
-        <v>-9</v>
+        <v>-9.75</v>
       </c>
       <c r="D25" s="2">
-        <v>-4.33</v>
+        <v>-1.73</v>
       </c>
       <c r="E25" s="2">
-        <v>6.73</v>
+        <v>1.46</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
+      <c r="G25" s="2">
+        <v>16</v>
+      </c>
       <c r="H25" s="2">
-        <v>36</v>
+        <v>32.61</v>
       </c>
       <c r="I25" s="2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1487,25 +1487,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>355.45</v>
+        <v>387.05</v>
       </c>
       <c r="C26" s="2">
-        <v>-0.93</v>
+        <v>-11.84</v>
       </c>
       <c r="D26" s="2">
-        <v>-6.45</v>
+        <v>-6.31</v>
       </c>
       <c r="E26" s="2">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
+      <c r="G26" s="2">
+        <v>26</v>
+      </c>
       <c r="H26" s="2">
-        <v>56</v>
+        <v>26.09</v>
       </c>
       <c r="I26" s="2">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1516,28 +1519,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>1012.5</v>
+        <v>4169.1</v>
       </c>
       <c r="C27" s="2">
-        <v>-5.75</v>
+        <v>2.9</v>
       </c>
       <c r="D27" s="2">
-        <v>-6.56</v>
+        <v>-2.37</v>
       </c>
       <c r="E27" s="2">
-        <v>6.2</v>
+        <v>-7.62</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>34.78</v>
+        <v>70</v>
       </c>
       <c r="H27" s="2">
-        <v>40</v>
+        <v>73.91</v>
       </c>
       <c r="I27" s="2">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1548,28 +1551,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>11950</v>
+        <v>423.65</v>
       </c>
       <c r="C28" s="2">
-        <v>1.32</v>
+        <v>5.53</v>
       </c>
       <c r="D28" s="2">
-        <v>-7.91</v>
+        <v>-6.28</v>
       </c>
       <c r="E28" s="2">
-        <v>3.12</v>
+        <v>-7.41</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H28" s="2">
-        <v>58</v>
+        <v>60.87</v>
       </c>
       <c r="I28" s="2">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1580,28 +1583,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>1007.75</v>
+        <v>910.45</v>
       </c>
       <c r="C29" s="2">
-        <v>4.95</v>
+        <v>-8.08</v>
       </c>
       <c r="D29" s="2">
-        <v>-5.35</v>
+        <v>-6.93</v>
       </c>
       <c r="E29" s="2">
-        <v>-1.93</v>
+        <v>-0.8</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>43.48</v>
+        <v>42</v>
       </c>
       <c r="H29" s="2">
-        <v>80</v>
+        <v>52.17</v>
       </c>
       <c r="I29" s="2">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1612,28 +1615,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>1463</v>
+        <v>3909</v>
       </c>
       <c r="C30" s="2">
-        <v>-9.26</v>
+        <v>-6.11</v>
       </c>
       <c r="D30" s="2">
-        <v>1.53</v>
+        <v>-3.88</v>
       </c>
       <c r="E30" s="2">
-        <v>1.58</v>
+        <v>-3.51</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>28.26</v>
+        <v>38</v>
       </c>
       <c r="H30" s="2">
-        <v>10</v>
+        <v>63.04</v>
       </c>
       <c r="I30" s="2">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1644,28 +1647,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>955.35</v>
+        <v>11487</v>
       </c>
       <c r="C31" s="2">
-        <v>-4.47</v>
+        <v>-3.46</v>
       </c>
       <c r="D31" s="2">
-        <v>-7.34</v>
+        <v>-8.26</v>
       </c>
       <c r="E31" s="2">
-        <v>3.33</v>
+        <v>-3.61</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>52.17</v>
+        <v>48</v>
       </c>
       <c r="H31" s="2">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I31" s="2">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1676,28 +1679,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>3330.4</v>
+        <v>7014.5</v>
       </c>
       <c r="C32" s="2">
-        <v>-8.08</v>
+        <v>-4.36</v>
       </c>
       <c r="D32" s="2">
-        <v>-3.39</v>
+        <v>-10.37</v>
       </c>
       <c r="E32" s="2">
-        <v>2.17</v>
+        <v>-3.15</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>15.22</v>
+        <v>36</v>
       </c>
       <c r="H32" s="2">
-        <v>16</v>
+        <v>36.96</v>
       </c>
       <c r="I32" s="2">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1708,28 +1711,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>3974.5</v>
+        <v>1336.4</v>
       </c>
       <c r="C33" s="2">
-        <v>-1.8</v>
+        <v>-16.07</v>
       </c>
       <c r="D33" s="2">
-        <v>-10.04</v>
+        <v>-1.59</v>
       </c>
       <c r="E33" s="2">
-        <v>0.37</v>
+        <v>-1.97</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>63.04</v>
+        <v>56</v>
       </c>
       <c r="H33" s="2">
-        <v>66</v>
+        <v>41.3</v>
       </c>
       <c r="I33" s="2">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1740,28 +1743,25 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>7302.5</v>
+        <v>241.18</v>
       </c>
       <c r="C34" s="2">
-        <v>-0.29</v>
+        <v>-15.12</v>
       </c>
       <c r="D34" s="2">
-        <v>-9.16</v>
+        <v>-0.7</v>
       </c>
       <c r="E34" s="2">
-        <v>-1.64</v>
+        <v>-5.38</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>36.96</v>
-      </c>
-      <c r="H34" s="2">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I34" s="2">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1772,25 +1772,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>249.34</v>
+        <v>1244.8</v>
       </c>
       <c r="C35" s="2">
-        <v>-16.03</v>
+        <v>-1.74</v>
       </c>
       <c r="D35" s="2">
-        <v>-3.28</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="E35" s="2">
-        <v>2.52</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
+      <c r="G35" s="2">
+        <v>32</v>
+      </c>
       <c r="H35" s="2">
-        <v>34</v>
+        <v>47.83</v>
       </c>
       <c r="I35" s="2">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1801,28 +1804,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>1268.3</v>
+        <v>1864.5</v>
       </c>
       <c r="C36" s="2">
-        <v>3.26</v>
+        <v>-9.69</v>
       </c>
       <c r="D36" s="2">
-        <v>-8.539999999999999</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="E36" s="2">
-        <v>-6.11</v>
+        <v>-5.95</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>47.83</v>
+        <v>22</v>
       </c>
       <c r="H36" s="2">
-        <v>78</v>
+        <v>21.74</v>
       </c>
       <c r="I36" s="2">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1833,25 +1836,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>4522.7</v>
+        <v>3123.1</v>
       </c>
       <c r="C37" s="2">
-        <v>-10.87</v>
+        <v>-17.87</v>
       </c>
       <c r="D37" s="2">
-        <v>-6.98</v>
+        <v>-6.33</v>
       </c>
       <c r="E37" s="2">
-        <v>-0.6899999999999999</v>
+        <v>-3.06</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
+      <c r="G37" s="2">
+        <v>40</v>
+      </c>
       <c r="H37" s="2">
-        <v>44</v>
+        <v>15.22</v>
       </c>
       <c r="I37" s="2">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1862,28 +1868,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>1818.3</v>
+        <v>1370.5</v>
       </c>
       <c r="C38" s="2">
-        <v>-9.880000000000001</v>
+        <v>-14.98</v>
       </c>
       <c r="D38" s="2">
-        <v>-11.37</v>
+        <v>1.87</v>
       </c>
       <c r="E38" s="2">
-        <v>0.5</v>
+        <v>-8.9</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>19.57</v>
+        <v>44</v>
       </c>
       <c r="H38" s="2">
-        <v>32</v>
+        <v>28.26</v>
       </c>
       <c r="I38" s="2">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1894,28 +1900,25 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>380.8</v>
+        <v>233.06</v>
       </c>
       <c r="C39" s="2">
-        <v>-12.02</v>
+        <v>-22.75</v>
       </c>
       <c r="D39" s="2">
-        <v>-11.59</v>
+        <v>-6.4</v>
       </c>
       <c r="E39" s="2">
-        <v>1.67</v>
+        <v>-1.72</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>26.09</v>
-      </c>
-      <c r="H39" s="2">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I39" s="2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1926,28 +1929,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>1019.3</v>
+        <v>13221</v>
       </c>
       <c r="C40" s="2">
-        <v>5.48</v>
+        <v>-22.05</v>
       </c>
       <c r="D40" s="2">
-        <v>-16.98</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="E40" s="2">
-        <v>-4.44</v>
+        <v>-1.7</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>45.65</v>
+        <v>14</v>
       </c>
       <c r="H40" s="2">
-        <v>64</v>
+        <v>17.39</v>
       </c>
       <c r="I40" s="2">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1958,28 +1961,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>1872.1</v>
+        <v>608.7</v>
       </c>
       <c r="C41" s="2">
-        <v>-7.15</v>
+        <v>-19.36</v>
       </c>
       <c r="D41" s="2">
-        <v>-11.13</v>
+        <v>-13.94</v>
       </c>
       <c r="E41" s="2">
-        <v>-2.66</v>
+        <v>-0.17</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>21.74</v>
+        <v>12</v>
       </c>
       <c r="H41" s="2">
-        <v>18</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I41" s="2">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -1990,28 +1993,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>1264.8</v>
+        <v>1244.5</v>
       </c>
       <c r="C42" s="2">
-        <v>-6.34</v>
+        <v>-8.18</v>
       </c>
       <c r="D42" s="2">
-        <v>-9.619999999999999</v>
+        <v>-9.43</v>
       </c>
       <c r="E42" s="2">
-        <v>-4.32</v>
+        <v>-8.24</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
+        <v>20</v>
+      </c>
+      <c r="H42" s="2">
         <v>23.91</v>
       </c>
-      <c r="H42" s="2">
+      <c r="I42" s="2">
         <v>48</v>
-      </c>
-      <c r="I42" s="2">
-        <v>52</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2022,28 +2025,25 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>1834.5</v>
+        <v>4314.9</v>
       </c>
       <c r="C43" s="2">
-        <v>-12.87</v>
+        <v>-15.49</v>
       </c>
       <c r="D43" s="2">
-        <v>-8.15</v>
+        <v>-4.55</v>
       </c>
       <c r="E43" s="2">
-        <v>-1.9</v>
+        <v>-7.77</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>30.43</v>
-      </c>
-      <c r="H43" s="2">
         <v>30</v>
       </c>
       <c r="I43" s="2">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2054,28 +2054,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>307.45</v>
+        <v>1728.1</v>
       </c>
       <c r="C44" s="2">
-        <v>-22.33</v>
+        <v>-15.22</v>
       </c>
       <c r="D44" s="2">
-        <v>-5.52</v>
+        <v>-11.01</v>
       </c>
       <c r="E44" s="2">
-        <v>1.05</v>
+        <v>-5.6</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>32.61</v>
+        <v>28</v>
       </c>
       <c r="H44" s="2">
-        <v>28</v>
+        <v>19.57</v>
       </c>
       <c r="I44" s="2">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2086,28 +2086,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>13726</v>
+        <v>937.9</v>
       </c>
       <c r="C45" s="2">
-        <v>-17.29</v>
+        <v>-7.17</v>
       </c>
       <c r="D45" s="2">
-        <v>-8.93</v>
+        <v>-10.89</v>
       </c>
       <c r="E45" s="2">
-        <v>0.12</v>
+        <v>-10.26</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>17.39</v>
+        <v>46</v>
       </c>
       <c r="H45" s="2">
-        <v>26</v>
+        <v>43.48</v>
       </c>
       <c r="I45" s="2">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2118,28 +2118,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>621.7</v>
+        <v>963.2</v>
       </c>
       <c r="C46" s="2">
-        <v>-16.93</v>
+        <v>-1.84</v>
       </c>
       <c r="D46" s="2">
-        <v>-16.26</v>
+        <v>-17.59</v>
       </c>
       <c r="E46" s="2">
-        <v>2.9</v>
+        <v>-11.49</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>8.699999999999999</v>
+        <v>24</v>
       </c>
       <c r="H46" s="2">
-        <v>6</v>
+        <v>45.65</v>
       </c>
       <c r="I46" s="2">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2150,25 +2150,25 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>197.91</v>
+        <v>767.5</v>
       </c>
       <c r="C47" s="2">
-        <v>-23.76</v>
+        <v>-23.37</v>
       </c>
       <c r="D47" s="2">
-        <v>-3.88</v>
+        <v>-12.72</v>
       </c>
       <c r="E47" s="2">
-        <v>-3.4</v>
+        <v>-3.51</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>13.04</v>
+        <v>8</v>
       </c>
       <c r="H47" s="2">
-        <v>24</v>
+        <v>6.52</v>
       </c>
       <c r="I47" s="2">
         <v>14</v>
@@ -2182,28 +2182,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>780.85</v>
+        <v>190</v>
       </c>
       <c r="C48" s="2">
-        <v>-21.29</v>
+        <v>-27.54</v>
       </c>
       <c r="D48" s="2">
-        <v>-15.46</v>
+        <v>-4.32</v>
       </c>
       <c r="E48" s="2">
-        <v>-3.63</v>
+        <v>-6.16</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>6.52</v>
+        <v>10</v>
       </c>
       <c r="H48" s="2">
-        <v>14</v>
+        <v>13.04</v>
       </c>
       <c r="I48" s="2">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2214,28 +2214,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>2394.4</v>
+        <v>2264</v>
       </c>
       <c r="C49" s="2">
-        <v>-25.67</v>
+        <v>-29.09</v>
       </c>
       <c r="D49" s="2">
-        <v>-10.53</v>
+        <v>-13.37</v>
       </c>
       <c r="E49" s="2">
-        <v>-5.15</v>
+        <v>-12.23</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
+        <v>6</v>
+      </c>
+      <c r="H49" s="2">
         <v>10.87</v>
       </c>
-      <c r="H49" s="2">
+      <c r="I49" s="2">
         <v>8</v>
-      </c>
-      <c r="I49" s="2">
-        <v>12</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2246,28 +2246,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>1179.2</v>
+        <v>1119</v>
       </c>
       <c r="C50" s="2">
-        <v>-28.8</v>
+        <v>-31.78</v>
       </c>
       <c r="D50" s="2">
-        <v>-11.17</v>
+        <v>-13.18</v>
       </c>
       <c r="E50" s="2">
-        <v>-8.77</v>
+        <v>-14.75</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
+        <v>4</v>
+      </c>
+      <c r="H50" s="2">
         <v>4.35</v>
       </c>
-      <c r="H50" s="2">
+      <c r="I50" s="2">
         <v>4</v>
-      </c>
-      <c r="I50" s="2">
-        <v>8</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2278,28 +2278,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>1198.4</v>
+        <v>1132.6</v>
       </c>
       <c r="C51" s="2">
-        <v>-25.93</v>
+        <v>-29.12</v>
       </c>
       <c r="D51" s="2">
-        <v>-14.36</v>
+        <v>-15.81</v>
       </c>
       <c r="E51" s="2">
-        <v>-15.84</v>
+        <v>-19.18</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
+        <v>2</v>
+      </c>
+      <c r="H51" s="2">
         <v>2.17</v>
       </c>
-      <c r="H51" s="2">
+      <c r="I51" s="2">
         <v>2</v>
-      </c>
-      <c r="I51" s="2">
-        <v>30</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2408,7 +2408,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2450,86 +2450,86 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>1760.4</v>
+        <v>2716</v>
       </c>
       <c r="C2" s="2">
-        <v>18.38</v>
+        <v>19.13</v>
       </c>
       <c r="D2" s="2">
-        <v>13.15</v>
+        <v>27.84</v>
       </c>
       <c r="E2" s="2">
-        <v>19.32</v>
+        <v>21.82</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>93.48</v>
+        <v>96</v>
       </c>
       <c r="H2" s="2">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>2505.9</v>
+        <v>1795.1</v>
       </c>
       <c r="C3" s="2">
-        <v>12.38</v>
+        <v>20.52</v>
       </c>
       <c r="D3" s="2">
-        <v>14.37</v>
+        <v>22.09</v>
       </c>
       <c r="E3" s="2">
-        <v>20.08</v>
+        <v>13.73</v>
       </c>
       <c r="F3" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G3" s="2">
         <v>100</v>
       </c>
       <c r="H3" s="2">
-        <v>94</v>
+        <v>93.48</v>
       </c>
       <c r="I3" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>1044.4</v>
+        <v>1430.5</v>
       </c>
       <c r="C4" s="2">
-        <v>19.65</v>
+        <v>12.39</v>
       </c>
       <c r="D4" s="2">
-        <v>13.99</v>
+        <v>11.78</v>
       </c>
       <c r="E4" s="2">
-        <v>5.27</v>
+        <v>11.2</v>
       </c>
       <c r="F4" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>95.65000000000001</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>100</v>
+        <v>97.83</v>
       </c>
       <c r="I4" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2537,90 +2537,32 @@
         <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>402.15</v>
+        <v>1067.5</v>
       </c>
       <c r="C5" s="2">
-        <v>25.02</v>
+        <v>15.32</v>
       </c>
       <c r="D5" s="2">
-        <v>7.11</v>
+        <v>13.56</v>
       </c>
       <c r="E5" s="2">
-        <v>5.79</v>
+        <v>5.15</v>
       </c>
       <c r="F5" s="2">
         <v>90</v>
       </c>
       <c r="G5" s="2">
-        <v>91.3</v>
+        <v>92</v>
       </c>
       <c r="H5" s="2">
-        <v>92</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1">
-        <v>214.49</v>
-      </c>
-      <c r="C6" s="2">
-        <v>26.83</v>
-      </c>
-      <c r="D6" s="2">
-        <v>3.05</v>
-      </c>
-      <c r="E6" s="2">
-        <v>3.81</v>
-      </c>
-      <c r="F6" s="2">
-        <v>86</v>
-      </c>
-      <c r="G6" s="2">
-        <v>82.61</v>
-      </c>
-      <c r="H6" s="2">
-        <v>90</v>
-      </c>
-      <c r="I6" s="2">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="1">
-        <v>313.95</v>
-      </c>
-      <c r="C7" s="2">
-        <v>19.6</v>
-      </c>
-      <c r="D7" s="2">
-        <v>3.49</v>
-      </c>
-      <c r="E7" s="2">
-        <v>3.7</v>
-      </c>
-      <c r="F7" s="2">
-        <v>80</v>
-      </c>
-      <c r="G7" s="2">
-        <v>84.78</v>
-      </c>
-      <c r="H7" s="2">
-        <v>82</v>
-      </c>
-      <c r="I7" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C5">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2628,7 +2570,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D5">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2636,7 +2578,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E5">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2644,22 +2586,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F5">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G5">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H5">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I5">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2670,7 +2612,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2712,28 +2654,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>1760.4</v>
+        <v>2716</v>
       </c>
       <c r="C2" s="2">
-        <v>18.38</v>
+        <v>19.13</v>
       </c>
       <c r="D2" s="2">
-        <v>13.15</v>
+        <v>27.84</v>
       </c>
       <c r="E2" s="2">
-        <v>19.32</v>
+        <v>21.82</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>93.48</v>
+        <v>96</v>
       </c>
       <c r="H2" s="2">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2741,28 +2683,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1482.4</v>
+        <v>1795.1</v>
       </c>
       <c r="C3" s="2">
-        <v>17.11</v>
+        <v>20.52</v>
       </c>
       <c r="D3" s="2">
-        <v>12.72</v>
+        <v>22.09</v>
       </c>
       <c r="E3" s="2">
-        <v>18.66</v>
+        <v>13.73</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>97.83</v>
+        <v>100</v>
       </c>
       <c r="H3" s="2">
-        <v>98</v>
+        <v>93.48</v>
       </c>
       <c r="I3" s="2">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2770,83 +2712,83 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>2505.9</v>
+        <v>1430.5</v>
       </c>
       <c r="C4" s="2">
-        <v>12.38</v>
+        <v>12.39</v>
       </c>
       <c r="D4" s="2">
-        <v>14.37</v>
+        <v>11.78</v>
       </c>
       <c r="E4" s="2">
-        <v>20.08</v>
+        <v>11.2</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>94</v>
+        <v>97.83</v>
       </c>
       <c r="I4" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>10711.5</v>
+        <v>1878.2</v>
       </c>
       <c r="C5" s="2">
-        <v>18.17</v>
+        <v>9.4</v>
       </c>
       <c r="D5" s="2">
-        <v>8.140000000000001</v>
+        <v>7.17</v>
       </c>
       <c r="E5" s="2">
-        <v>9.15</v>
+        <v>12.56</v>
       </c>
       <c r="F5" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G5" s="2">
-        <v>80.43000000000001</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2">
-        <v>62</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="I5" s="2">
-        <v>72</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>1044.4</v>
+        <v>1067.5</v>
       </c>
       <c r="C6" s="2">
-        <v>19.65</v>
+        <v>15.32</v>
       </c>
       <c r="D6" s="2">
-        <v>13.99</v>
+        <v>13.56</v>
       </c>
       <c r="E6" s="2">
-        <v>5.27</v>
+        <v>5.15</v>
       </c>
       <c r="F6" s="2">
+        <v>90</v>
+      </c>
+      <c r="G6" s="2">
         <v>92</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <v>95.65000000000001</v>
-      </c>
-      <c r="H6" s="2">
-        <v>100</v>
       </c>
       <c r="I6" s="2">
         <v>100</v>
@@ -2854,122 +2796,93 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1">
-        <v>402.15</v>
+        <v>8082.5</v>
       </c>
       <c r="C7" s="2">
-        <v>25.02</v>
+        <v>13.52</v>
       </c>
       <c r="D7" s="2">
-        <v>7.11</v>
+        <v>3.73</v>
       </c>
       <c r="E7" s="2">
-        <v>5.79</v>
+        <v>5.56</v>
       </c>
       <c r="F7" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G7" s="2">
-        <v>91.3</v>
+        <v>84</v>
       </c>
       <c r="H7" s="2">
-        <v>92</v>
+        <v>67.39</v>
       </c>
       <c r="I7" s="2">
-        <v>88</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1">
-        <v>214.49</v>
+        <v>462.2</v>
       </c>
       <c r="C8" s="2">
-        <v>26.83</v>
+        <v>9.44</v>
       </c>
       <c r="D8" s="2">
-        <v>3.05</v>
+        <v>8.43</v>
       </c>
       <c r="E8" s="2">
-        <v>3.81</v>
+        <v>4.63</v>
       </c>
       <c r="F8" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G8" s="2">
-        <v>82.61</v>
+        <v>82</v>
       </c>
       <c r="H8" s="2">
-        <v>90</v>
+        <v>89.13</v>
       </c>
       <c r="I8" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1">
-        <v>456.4</v>
+        <v>10377.5</v>
       </c>
       <c r="C9" s="2">
-        <v>14.99</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="D9" s="2">
-        <v>7.14</v>
+        <v>6.15</v>
       </c>
       <c r="E9" s="2">
-        <v>5.14</v>
+        <v>5.86</v>
       </c>
       <c r="F9" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G9" s="2">
-        <v>89.13</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2">
-        <v>74</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="I9" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1">
-        <v>313.95</v>
-      </c>
-      <c r="C10" s="2">
-        <v>19.6</v>
-      </c>
-      <c r="D10" s="2">
-        <v>3.49</v>
-      </c>
-      <c r="E10" s="2">
-        <v>3.7</v>
-      </c>
-      <c r="F10" s="2">
-        <v>80</v>
-      </c>
-      <c r="G10" s="2">
-        <v>84.78</v>
-      </c>
-      <c r="H10" s="2">
-        <v>82</v>
-      </c>
-      <c r="I10" s="2">
-        <v>94</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C10">
+  <conditionalFormatting sqref="C2:C9">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2977,7 +2890,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D10">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2985,7 +2898,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E10">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2993,22 +2906,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F10">
+  <conditionalFormatting sqref="F2:F9">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G10">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H10">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I10">
+  <conditionalFormatting sqref="I2:I9">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -3044,13 +2957,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C2" s="2">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3058,13 +2971,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D3" s="2">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3072,10 +2985,10 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C4" s="2">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D4" s="2">
         <v>48</v>
@@ -3086,13 +2999,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C5" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-05-15</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-05-15</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-05-15</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-05-15</t>
+    <t>Price_2026-05-22</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-05-22</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-05-22</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-05-22</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-05-22</t>
   </si>
   <si>
     <t>RS_Score_2026-05-15</t>
@@ -43,156 +46,153 @@
     <t>RS_Score_2026-05-01</t>
   </si>
   <si>
-    <t>RS_Score_2026-04-24</t>
-  </si>
-  <si>
     <t>ADANIENT</t>
   </si>
   <si>
     <t>ADANIPORTS</t>
   </si>
   <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
     <t>NESTLEIND</t>
   </si>
   <si>
-    <t>ONGC</t>
+    <t>TRENT</t>
   </si>
   <si>
     <t>SUNPHARMA</t>
   </si>
   <si>
-    <t>HINDALCO</t>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
   </si>
   <si>
     <t>TATACONSUM</t>
   </si>
   <si>
+    <t>TMPV</t>
+  </si>
+  <si>
     <t>CIPLA</t>
   </si>
   <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO</t>
+    <t>NTPC</t>
   </si>
   <si>
     <t>DRREDDY</t>
   </si>
   <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
   </si>
   <si>
     <t>POWERGRID</t>
   </si>
   <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
   </si>
   <si>
     <t>HINDUNILVR</t>
   </si>
   <si>
-    <t>TMPV</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>ETERNAL</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
   </si>
   <si>
     <t>TITAN</t>
   </si>
   <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>ETERNAL</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
     <t>M&amp;M</t>
   </si>
   <si>
-    <t>TECHM</t>
-  </si>
-  <si>
     <t>JIOFIN</t>
   </si>
   <si>
     <t>MARUTI</t>
   </si>
   <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>INFY</t>
   </si>
   <si>
     <t>SBIN</t>
   </si>
   <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
     <t>TCS</t>
   </si>
   <si>
-    <t>INFY</t>
-  </si>
-  <si>
     <t>HCLTECH</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
     <t>2026-05-15</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
   </si>
 </sst>
 </file>
@@ -722,28 +722,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>2716</v>
+        <v>2717.3</v>
       </c>
       <c r="C2" s="2">
-        <v>19.13</v>
+        <v>26.17</v>
       </c>
       <c r="D2" s="2">
-        <v>27.84</v>
+        <v>36.1</v>
       </c>
       <c r="E2" s="2">
-        <v>21.82</v>
+        <v>17.03</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2">
         <v>96</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>100</v>
-      </c>
-      <c r="I2" s="2">
-        <v>94</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>60</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1795.1</v>
+        <v>1786.9</v>
       </c>
       <c r="C3" s="2">
-        <v>20.52</v>
+        <v>24.44</v>
       </c>
       <c r="D3" s="2">
-        <v>22.09</v>
+        <v>25.48</v>
       </c>
       <c r="E3" s="2">
-        <v>13.73</v>
+        <v>9.73</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
+        <v>98</v>
+      </c>
+      <c r="H3" s="2">
         <v>100</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>93.48</v>
-      </c>
-      <c r="I3" s="2">
-        <v>84</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>1430.5</v>
+        <v>3155.3</v>
       </c>
       <c r="C4" s="2">
-        <v>12.39</v>
+        <v>13.63</v>
       </c>
       <c r="D4" s="2">
-        <v>11.78</v>
+        <v>14.99</v>
       </c>
       <c r="E4" s="2">
-        <v>11.2</v>
+        <v>13.57</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="H4" s="2">
-        <v>97.83</v>
+        <v>76</v>
       </c>
       <c r="I4" s="2">
-        <v>98</v>
+        <v>54.35</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>299.35</v>
+        <v>1109.2</v>
       </c>
       <c r="C5" s="2">
-        <v>26.89</v>
+        <v>23.11</v>
       </c>
       <c r="D5" s="2">
-        <v>6.08</v>
+        <v>15.95</v>
       </c>
       <c r="E5" s="2">
-        <v>5.65</v>
+        <v>4.46</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="H5" s="2">
-        <v>86.95999999999999</v>
+        <v>92</v>
       </c>
       <c r="I5" s="2">
-        <v>86</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>1878.2</v>
+        <v>10549.5</v>
       </c>
       <c r="C6" s="2">
-        <v>9.4</v>
+        <v>10.32</v>
       </c>
       <c r="D6" s="2">
-        <v>7.17</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="E6" s="2">
-        <v>12.56</v>
+        <v>9.19</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H6" s="2">
-        <v>69.56999999999999</v>
+        <v>94</v>
       </c>
       <c r="I6" s="2">
-        <v>20</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>1067.5</v>
+        <v>290</v>
       </c>
       <c r="C7" s="2">
-        <v>15.32</v>
+        <v>26.8</v>
       </c>
       <c r="D7" s="2">
-        <v>13.56</v>
+        <v>7.73</v>
       </c>
       <c r="E7" s="2">
-        <v>5.15</v>
+        <v>1.43</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2">
-        <v>95.65000000000001</v>
+        <v>68</v>
       </c>
       <c r="I7" s="2">
-        <v>100</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>1234</v>
+        <v>8362.5</v>
       </c>
       <c r="C8" s="2">
-        <v>5.41</v>
+        <v>15.39</v>
       </c>
       <c r="D8" s="2">
-        <v>9.67</v>
+        <v>7.17</v>
       </c>
       <c r="E8" s="2">
-        <v>10.14</v>
+        <v>6.87</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="H8" s="2">
-        <v>65.22</v>
+        <v>84</v>
       </c>
       <c r="I8" s="2">
-        <v>68</v>
+        <v>67.39</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>1432.1</v>
+        <v>1423.1</v>
       </c>
       <c r="C9" s="2">
-        <v>-5.26</v>
+        <v>10.14</v>
       </c>
       <c r="D9" s="2">
-        <v>5.96</v>
+        <v>14.66</v>
       </c>
       <c r="E9" s="2">
-        <v>16.48</v>
+        <v>0.41</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="H9" s="2">
-        <v>39.13</v>
+        <v>98</v>
       </c>
       <c r="I9" s="2">
-        <v>38</v>
+        <v>97.83</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>8082.5</v>
+        <v>4296.5</v>
       </c>
       <c r="C10" s="2">
-        <v>13.52</v>
+        <v>8.15</v>
       </c>
       <c r="D10" s="2">
-        <v>3.73</v>
+        <v>15.64</v>
       </c>
       <c r="E10" s="2">
-        <v>5.56</v>
+        <v>0.84</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="H10" s="2">
-        <v>67.39</v>
+        <v>72</v>
       </c>
       <c r="I10" s="2">
-        <v>70</v>
+        <v>76.09</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>462.2</v>
+        <v>1844.6</v>
       </c>
       <c r="C11" s="2">
-        <v>9.44</v>
+        <v>7.32</v>
       </c>
       <c r="D11" s="2">
-        <v>8.43</v>
+        <v>1.75</v>
       </c>
       <c r="E11" s="2">
-        <v>4.63</v>
+        <v>6.41</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H11" s="2">
-        <v>89.13</v>
+        <v>88</v>
       </c>
       <c r="I11" s="2">
-        <v>74</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>10377.5</v>
+        <v>2639.8</v>
       </c>
       <c r="C12" s="2">
-        <v>9.210000000000001</v>
+        <v>-6.57</v>
       </c>
       <c r="D12" s="2">
-        <v>6.15</v>
+        <v>15.76</v>
       </c>
       <c r="E12" s="2">
-        <v>5.86</v>
+        <v>6.22</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H12" s="2">
-        <v>80.43000000000001</v>
+        <v>74</v>
       </c>
       <c r="I12" s="2">
-        <v>62</v>
+        <v>58.7</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>1336.7</v>
+        <v>209.19</v>
       </c>
       <c r="C13" s="2">
-        <v>6.42</v>
+        <v>17.26</v>
       </c>
       <c r="D13" s="2">
-        <v>3.27</v>
+        <v>7.28</v>
       </c>
       <c r="E13" s="2">
-        <v>8.449999999999999</v>
+        <v>-1.91</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="H13" s="2">
-        <v>71.73999999999999</v>
+        <v>86</v>
       </c>
       <c r="I13" s="2">
-        <v>52</v>
+        <v>82.61</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>216.84</v>
+        <v>1285.5</v>
       </c>
       <c r="C14" s="2">
-        <v>18.57</v>
+        <v>10.93</v>
       </c>
       <c r="D14" s="2">
-        <v>2.76</v>
+        <v>5.86</v>
       </c>
       <c r="E14" s="2">
-        <v>2.42</v>
+        <v>0.22</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="H14" s="2">
-        <v>82.61</v>
+        <v>78</v>
       </c>
       <c r="I14" s="2">
-        <v>90</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>2933.8</v>
+        <v>456.55</v>
       </c>
       <c r="C15" s="2">
-        <v>2.71</v>
+        <v>10.57</v>
       </c>
       <c r="D15" s="2">
-        <v>5.63</v>
+        <v>2.93</v>
       </c>
       <c r="E15" s="2">
-        <v>6.29</v>
+        <v>0.9</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H15" s="2">
-        <v>54.35</v>
+        <v>82</v>
       </c>
       <c r="I15" s="2">
-        <v>50</v>
+        <v>89.13</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>395.25</v>
+        <v>1191.8</v>
       </c>
       <c r="C16" s="2">
-        <v>13.1</v>
+        <v>1.35</v>
       </c>
       <c r="D16" s="2">
-        <v>4.69</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="E16" s="2">
-        <v>-0.6899999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H16" s="2">
-        <v>91.3</v>
+        <v>66</v>
       </c>
       <c r="I16" s="2">
-        <v>92</v>
+        <v>65.22</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,25 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>2605.6</v>
+        <v>363.35</v>
       </c>
       <c r="C17" s="2">
-        <v>-6.02</v>
+        <v>2.6</v>
       </c>
       <c r="D17" s="2">
-        <v>12.94</v>
+        <v>5.26</v>
       </c>
       <c r="E17" s="2">
-        <v>3.53</v>
+        <v>2.54</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="H17" s="2">
-        <v>58.7</v>
-      </c>
-      <c r="I17" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1231,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>1278.8</v>
+        <v>1399.2</v>
       </c>
       <c r="C18" s="2">
-        <v>8.31</v>
+        <v>-4.54</v>
       </c>
       <c r="D18" s="2">
-        <v>0.91</v>
+        <v>4.93</v>
       </c>
       <c r="E18" s="2">
-        <v>0.34</v>
+        <v>6.23</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H18" s="2">
-        <v>78.26000000000001</v>
+        <v>62</v>
       </c>
       <c r="I18" s="2">
-        <v>76</v>
+        <v>39.13</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1263,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>305.85</v>
+        <v>388.65</v>
       </c>
       <c r="C19" s="2">
-        <v>14.15</v>
+        <v>16.54</v>
       </c>
       <c r="D19" s="2">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="E19" s="2">
-        <v>-4.33</v>
+        <v>-5.25</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H19" s="2">
-        <v>84.78</v>
+        <v>90</v>
       </c>
       <c r="I19" s="2">
-        <v>82</v>
+        <v>91.3</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1295,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>1050.1</v>
+        <v>1307.2</v>
       </c>
       <c r="C20" s="2">
-        <v>-1.18</v>
+        <v>8.02</v>
       </c>
       <c r="D20" s="2">
-        <v>-3.09</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E20" s="2">
-        <v>3.83</v>
+        <v>-2.05</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="H20" s="2">
-        <v>34.78</v>
+        <v>64</v>
       </c>
       <c r="I20" s="2">
-        <v>40</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1327,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>1905.4</v>
+        <v>1023.25</v>
       </c>
       <c r="C21" s="2">
-        <v>-9.539999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="D21" s="2">
-        <v>1.72</v>
+        <v>-1.9</v>
       </c>
       <c r="E21" s="2">
-        <v>3.21</v>
+        <v>1.33</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="H21" s="2">
-        <v>30.43</v>
+        <v>50</v>
       </c>
       <c r="I21" s="2">
-        <v>30</v>
+        <v>34.78</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1359,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>2272.2</v>
+        <v>1422.2</v>
       </c>
       <c r="C22" s="2">
-        <v>-3.23</v>
+        <v>-10.11</v>
       </c>
       <c r="D22" s="2">
-        <v>-2.09</v>
+        <v>6.4</v>
       </c>
       <c r="E22" s="2">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="H22" s="2">
-        <v>56.52</v>
+        <v>44</v>
       </c>
       <c r="I22" s="2">
-        <v>60</v>
+        <v>28.26</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,25 +1391,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>356.55</v>
+        <v>1871.4</v>
       </c>
       <c r="C23" s="2">
-        <v>-3.73</v>
+        <v>-7.68</v>
       </c>
       <c r="D23" s="2">
-        <v>-3.79</v>
+        <v>1.13</v>
       </c>
       <c r="E23" s="2">
-        <v>0.24</v>
+        <v>2.82</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>52</v>
+        <v>62</v>
+      </c>
+      <c r="H23" s="2">
+        <v>18</v>
       </c>
       <c r="I23" s="2">
-        <v>56</v>
+        <v>30.43</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1423,28 +1423,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>4101.3</v>
+        <v>294.3</v>
       </c>
       <c r="C24" s="2">
-        <v>-6.99</v>
+        <v>15.35</v>
       </c>
       <c r="D24" s="2">
-        <v>6.57</v>
+        <v>-1.46</v>
       </c>
       <c r="E24" s="2">
-        <v>-3.34</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H24" s="2">
-        <v>76.09</v>
+        <v>80</v>
       </c>
       <c r="I24" s="2">
-        <v>96</v>
+        <v>84.78</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1455,28 +1455,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>309.45</v>
+        <v>3926.6</v>
       </c>
       <c r="C25" s="2">
-        <v>-9.75</v>
+        <v>-1.5</v>
       </c>
       <c r="D25" s="2">
-        <v>-1.73</v>
+        <v>2.29</v>
       </c>
       <c r="E25" s="2">
-        <v>1.46</v>
+        <v>-2.19</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="H25" s="2">
-        <v>32.61</v>
+        <v>38</v>
       </c>
       <c r="I25" s="2">
-        <v>28</v>
+        <v>63.04</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1487,28 +1487,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>387.05</v>
+        <v>1285.4</v>
       </c>
       <c r="C26" s="2">
-        <v>-11.84</v>
+        <v>1.05</v>
       </c>
       <c r="D26" s="2">
-        <v>-6.31</v>
+        <v>-2.23</v>
       </c>
       <c r="E26" s="2">
-        <v>2.07</v>
+        <v>-2.93</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H26" s="2">
-        <v>26.09</v>
+        <v>32</v>
       </c>
       <c r="I26" s="2">
-        <v>22</v>
+        <v>47.83</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1519,28 +1519,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>4169.1</v>
+        <v>384.15</v>
       </c>
       <c r="C27" s="2">
-        <v>2.9</v>
+        <v>-9.69</v>
       </c>
       <c r="D27" s="2">
-        <v>-2.37</v>
+        <v>-1.97</v>
       </c>
       <c r="E27" s="2">
-        <v>-7.62</v>
+        <v>1.95</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="H27" s="2">
-        <v>73.91</v>
+        <v>26</v>
       </c>
       <c r="I27" s="2">
-        <v>88</v>
+        <v>26.09</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1551,28 +1551,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>423.65</v>
+        <v>916.55</v>
       </c>
       <c r="C28" s="2">
-        <v>5.53</v>
+        <v>-4.49</v>
       </c>
       <c r="D28" s="2">
-        <v>-6.28</v>
+        <v>-2.47</v>
       </c>
       <c r="E28" s="2">
-        <v>-7.41</v>
+        <v>-0.57</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2">
-        <v>60.87</v>
+        <v>42</v>
       </c>
       <c r="I28" s="2">
-        <v>72</v>
+        <v>52.17</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1583,28 +1583,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>910.45</v>
+        <v>1870.7</v>
       </c>
       <c r="C29" s="2">
-        <v>-8.08</v>
+        <v>-9.5</v>
       </c>
       <c r="D29" s="2">
-        <v>-6.93</v>
+        <v>-4.74</v>
       </c>
       <c r="E29" s="2">
-        <v>-0.8</v>
+        <v>3.05</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H29" s="2">
-        <v>52.17</v>
+        <v>22</v>
       </c>
       <c r="I29" s="2">
-        <v>42</v>
+        <v>21.74</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1615,28 +1615,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>3909</v>
+        <v>11569</v>
       </c>
       <c r="C30" s="2">
-        <v>-6.11</v>
+        <v>-3.08</v>
       </c>
       <c r="D30" s="2">
-        <v>-3.88</v>
+        <v>-0.73</v>
       </c>
       <c r="E30" s="2">
-        <v>-3.51</v>
+        <v>-3.67</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H30" s="2">
-        <v>63.04</v>
+        <v>48</v>
       </c>
       <c r="I30" s="2">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1647,28 +1647,25 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>11487</v>
+        <v>4438.6</v>
       </c>
       <c r="C31" s="2">
-        <v>-3.46</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="D31" s="2">
-        <v>-8.26</v>
+        <v>1.33</v>
       </c>
       <c r="E31" s="2">
-        <v>-3.61</v>
+        <v>-2.69</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="H31" s="2">
-        <v>50</v>
-      </c>
-      <c r="I31" s="2">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1679,28 +1676,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>7014.5</v>
+        <v>301.7</v>
       </c>
       <c r="C32" s="2">
-        <v>-4.36</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="D32" s="2">
-        <v>-10.37</v>
+        <v>-2.38</v>
       </c>
       <c r="E32" s="2">
-        <v>-3.15</v>
+        <v>-0.71</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="H32" s="2">
-        <v>36.96</v>
+        <v>16</v>
       </c>
       <c r="I32" s="2">
-        <v>46</v>
+        <v>32.61</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1711,28 +1708,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>1336.4</v>
+        <v>1354.5</v>
       </c>
       <c r="C33" s="2">
-        <v>-16.07</v>
+        <v>-8.19</v>
       </c>
       <c r="D33" s="2">
-        <v>-1.59</v>
+        <v>-3.85</v>
       </c>
       <c r="E33" s="2">
-        <v>-1.97</v>
+        <v>-0.83</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
+        <v>38</v>
+      </c>
+      <c r="H33" s="2">
         <v>56</v>
       </c>
-      <c r="H33" s="2">
+      <c r="I33" s="2">
         <v>41.3</v>
-      </c>
-      <c r="I33" s="2">
-        <v>12</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1743,25 +1740,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>241.18</v>
+        <v>2203.6</v>
       </c>
       <c r="C34" s="2">
-        <v>-15.12</v>
+        <v>-7.12</v>
       </c>
       <c r="D34" s="2">
-        <v>-0.7</v>
+        <v>0.61</v>
       </c>
       <c r="E34" s="2">
-        <v>-5.38</v>
+        <v>-5.36</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>54</v>
+        <v>60</v>
+      </c>
+      <c r="H34" s="2">
+        <v>58</v>
       </c>
       <c r="I34" s="2">
-        <v>36</v>
+        <v>56.52</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1772,28 +1772,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>1244.8</v>
+        <v>616.6</v>
       </c>
       <c r="C35" s="2">
-        <v>-1.74</v>
+        <v>-17.78</v>
       </c>
       <c r="D35" s="2">
-        <v>-9.289999999999999</v>
+        <v>-6.02</v>
       </c>
       <c r="E35" s="2">
-        <v>-8.109999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H35" s="2">
-        <v>47.83</v>
+        <v>12</v>
       </c>
       <c r="I35" s="2">
-        <v>78</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1804,28 +1804,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>1864.5</v>
+        <v>1766</v>
       </c>
       <c r="C36" s="2">
-        <v>-9.69</v>
+        <v>-11.36</v>
       </c>
       <c r="D36" s="2">
-        <v>-8.119999999999999</v>
+        <v>-5.45</v>
       </c>
       <c r="E36" s="2">
-        <v>-5.95</v>
+        <v>-0.35</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H36" s="2">
-        <v>21.74</v>
+        <v>28</v>
       </c>
       <c r="I36" s="2">
-        <v>18</v>
+        <v>19.57</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1836,28 +1836,25 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>3123.1</v>
+        <v>241.95</v>
       </c>
       <c r="C37" s="2">
-        <v>-17.87</v>
+        <v>-14.91</v>
       </c>
       <c r="D37" s="2">
-        <v>-6.33</v>
+        <v>6.76</v>
       </c>
       <c r="E37" s="2">
-        <v>-3.06</v>
+        <v>-5.3</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H37" s="2">
-        <v>15.22</v>
-      </c>
-      <c r="I37" s="2">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1868,28 +1865,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>1370.5</v>
+        <v>416.55</v>
       </c>
       <c r="C38" s="2">
-        <v>-14.98</v>
+        <v>-0.08</v>
       </c>
       <c r="D38" s="2">
-        <v>1.87</v>
+        <v>-10.1</v>
       </c>
       <c r="E38" s="2">
-        <v>-8.9</v>
+        <v>-4.37</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H38" s="2">
-        <v>28.26</v>
+        <v>60</v>
       </c>
       <c r="I38" s="2">
-        <v>10</v>
+        <v>60.87</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1900,25 +1897,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>233.06</v>
+        <v>6981.5</v>
       </c>
       <c r="C39" s="2">
-        <v>-22.75</v>
+        <v>-7</v>
       </c>
       <c r="D39" s="2">
-        <v>-6.4</v>
+        <v>-7.36</v>
       </c>
       <c r="E39" s="2">
-        <v>-1.72</v>
+        <v>-2.68</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="H39" s="2">
+        <v>36</v>
       </c>
       <c r="I39" s="2">
-        <v>34</v>
+        <v>36.96</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1929,28 +1929,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>13221</v>
+        <v>1264.3</v>
       </c>
       <c r="C40" s="2">
-        <v>-22.05</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="D40" s="2">
-        <v>-8.109999999999999</v>
+        <v>-3.63</v>
       </c>
       <c r="E40" s="2">
-        <v>-1.7</v>
+        <v>-3.79</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H40" s="2">
-        <v>17.39</v>
+        <v>20</v>
       </c>
       <c r="I40" s="2">
-        <v>26</v>
+        <v>23.91</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1961,28 +1961,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>608.7</v>
+        <v>203.11</v>
       </c>
       <c r="C41" s="2">
-        <v>-19.36</v>
+        <v>-20.46</v>
       </c>
       <c r="D41" s="2">
-        <v>-13.94</v>
+        <v>1.08</v>
       </c>
       <c r="E41" s="2">
-        <v>-0.17</v>
+        <v>-0.95</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H41" s="2">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="I41" s="2">
-        <v>6</v>
+        <v>13.04</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -1993,28 +1993,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>1244.5</v>
+        <v>941</v>
       </c>
       <c r="C42" s="2">
-        <v>-8.18</v>
+        <v>-3.53</v>
       </c>
       <c r="D42" s="2">
-        <v>-9.43</v>
+        <v>-11.47</v>
       </c>
       <c r="E42" s="2">
-        <v>-8.24</v>
+        <v>-3.45</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H42" s="2">
-        <v>23.91</v>
+        <v>46</v>
       </c>
       <c r="I42" s="2">
-        <v>48</v>
+        <v>43.48</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2025,25 +2025,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>4314.9</v>
+        <v>4079.8</v>
       </c>
       <c r="C43" s="2">
-        <v>-15.49</v>
+        <v>-2.9</v>
       </c>
       <c r="D43" s="2">
-        <v>-4.55</v>
+        <v>-3.32</v>
       </c>
       <c r="E43" s="2">
-        <v>-7.77</v>
+        <v>-8.15</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>30</v>
+        <v>50</v>
+      </c>
+      <c r="H43" s="2">
+        <v>70</v>
       </c>
       <c r="I43" s="2">
-        <v>44</v>
+        <v>73.91</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2054,28 +2057,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>1728.1</v>
+        <v>3081.3</v>
       </c>
       <c r="C44" s="2">
-        <v>-15.22</v>
+        <v>-16.21</v>
       </c>
       <c r="D44" s="2">
-        <v>-11.01</v>
+        <v>-6.45</v>
       </c>
       <c r="E44" s="2">
-        <v>-5.6</v>
+        <v>-0.68</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H44" s="2">
-        <v>19.57</v>
+        <v>40</v>
       </c>
       <c r="I44" s="2">
-        <v>32</v>
+        <v>15.22</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2086,28 +2089,25 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>937.9</v>
+        <v>238.19</v>
       </c>
       <c r="C45" s="2">
-        <v>-7.17</v>
+        <v>-17.08</v>
       </c>
       <c r="D45" s="2">
-        <v>-10.89</v>
+        <v>0.93</v>
       </c>
       <c r="E45" s="2">
-        <v>-10.26</v>
+        <v>-6.09</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="H45" s="2">
-        <v>43.48</v>
-      </c>
-      <c r="I45" s="2">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2118,16 +2118,16 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>963.2</v>
+        <v>12987</v>
       </c>
       <c r="C46" s="2">
-        <v>-1.84</v>
+        <v>-21.3</v>
       </c>
       <c r="D46" s="2">
-        <v>-17.59</v>
+        <v>-6.35</v>
       </c>
       <c r="E46" s="2">
-        <v>-11.49</v>
+        <v>-1.78</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
@@ -2136,10 +2136,10 @@
         <v>24</v>
       </c>
       <c r="H46" s="2">
-        <v>45.65</v>
+        <v>14</v>
       </c>
       <c r="I46" s="2">
-        <v>64</v>
+        <v>17.39</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2150,28 +2150,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>767.5</v>
+        <v>766.8</v>
       </c>
       <c r="C47" s="2">
-        <v>-23.37</v>
+        <v>-18.34</v>
       </c>
       <c r="D47" s="2">
-        <v>-12.72</v>
+        <v>-9.73</v>
       </c>
       <c r="E47" s="2">
-        <v>-3.51</v>
+        <v>-2.91</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
+        <v>10</v>
+      </c>
+      <c r="H47" s="2">
         <v>8</v>
       </c>
-      <c r="H47" s="2">
+      <c r="I47" s="2">
         <v>6.52</v>
-      </c>
-      <c r="I47" s="2">
-        <v>14</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2182,28 +2182,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>190</v>
+        <v>1174.5</v>
       </c>
       <c r="C48" s="2">
-        <v>-27.54</v>
+        <v>-27.23</v>
       </c>
       <c r="D48" s="2">
-        <v>-4.32</v>
+        <v>-9.35</v>
       </c>
       <c r="E48" s="2">
-        <v>-6.16</v>
+        <v>0.36</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H48" s="2">
-        <v>13.04</v>
+        <v>4</v>
       </c>
       <c r="I48" s="2">
-        <v>24</v>
+        <v>4.35</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2214,28 +2214,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>2264</v>
+        <v>949.2</v>
       </c>
       <c r="C49" s="2">
-        <v>-29.09</v>
+        <v>-3.42</v>
       </c>
       <c r="D49" s="2">
-        <v>-13.37</v>
+        <v>-13.12</v>
       </c>
       <c r="E49" s="2">
-        <v>-12.23</v>
+        <v>-13.09</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H49" s="2">
-        <v>10.87</v>
+        <v>24</v>
       </c>
       <c r="I49" s="2">
-        <v>8</v>
+        <v>45.65</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2246,28 +2246,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>1119</v>
+        <v>2317.3</v>
       </c>
       <c r="C50" s="2">
-        <v>-31.78</v>
+        <v>-26.45</v>
       </c>
       <c r="D50" s="2">
-        <v>-13.18</v>
+        <v>-7.79</v>
       </c>
       <c r="E50" s="2">
-        <v>-14.75</v>
+        <v>-5.32</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H50" s="2">
-        <v>4.35</v>
+        <v>6</v>
       </c>
       <c r="I50" s="2">
-        <v>4</v>
+        <v>10.87</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2278,16 +2278,16 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>1132.6</v>
+        <v>1164</v>
       </c>
       <c r="C51" s="2">
-        <v>-29.12</v>
+        <v>-28.08</v>
       </c>
       <c r="D51" s="2">
-        <v>-15.81</v>
+        <v>-12.87</v>
       </c>
       <c r="E51" s="2">
-        <v>-19.18</v>
+        <v>-5.23</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
@@ -2296,10 +2296,10 @@
         <v>2</v>
       </c>
       <c r="H51" s="2">
+        <v>2</v>
+      </c>
+      <c r="I51" s="2">
         <v>2.17</v>
-      </c>
-      <c r="I51" s="2">
-        <v>2</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2408,7 +2408,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2450,28 +2450,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>2716</v>
+        <v>2717.3</v>
       </c>
       <c r="C2" s="2">
-        <v>19.13</v>
+        <v>26.17</v>
       </c>
       <c r="D2" s="2">
-        <v>27.84</v>
+        <v>36.1</v>
       </c>
       <c r="E2" s="2">
-        <v>21.82</v>
+        <v>17.03</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2">
         <v>96</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>100</v>
-      </c>
-      <c r="I2" s="2">
-        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2479,90 +2479,119 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1795.1</v>
+        <v>1786.9</v>
       </c>
       <c r="C3" s="2">
-        <v>20.52</v>
+        <v>24.44</v>
       </c>
       <c r="D3" s="2">
-        <v>22.09</v>
+        <v>25.48</v>
       </c>
       <c r="E3" s="2">
-        <v>13.73</v>
+        <v>9.73</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
+        <v>98</v>
+      </c>
+      <c r="H3" s="2">
         <v>100</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>93.48</v>
-      </c>
-      <c r="I3" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>1430.5</v>
+        <v>1109.2</v>
       </c>
       <c r="C4" s="2">
-        <v>12.39</v>
+        <v>23.11</v>
       </c>
       <c r="D4" s="2">
-        <v>11.78</v>
+        <v>15.95</v>
       </c>
       <c r="E4" s="2">
-        <v>11.2</v>
+        <v>4.46</v>
       </c>
       <c r="F4" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G4" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H4" s="2">
-        <v>97.83</v>
+        <v>92</v>
       </c>
       <c r="I4" s="2">
-        <v>98</v>
+        <v>95.65000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>1067.5</v>
+        <v>10549.5</v>
       </c>
       <c r="C5" s="2">
-        <v>15.32</v>
+        <v>10.32</v>
       </c>
       <c r="D5" s="2">
-        <v>13.56</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="E5" s="2">
-        <v>5.15</v>
+        <v>9.19</v>
       </c>
       <c r="F5" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G5" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H5" s="2">
-        <v>95.65000000000001</v>
+        <v>94</v>
       </c>
       <c r="I5" s="2">
-        <v>100</v>
+        <v>80.43000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1423.1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>10.14</v>
+      </c>
+      <c r="D6" s="2">
+        <v>14.66</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.41</v>
+      </c>
+      <c r="F6" s="2">
+        <v>86</v>
+      </c>
+      <c r="G6" s="2">
+        <v>96</v>
+      </c>
+      <c r="H6" s="2">
+        <v>98</v>
+      </c>
+      <c r="I6" s="2">
+        <v>97.83</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C5">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2570,7 +2599,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D5">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2578,7 +2607,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E5">
+  <conditionalFormatting sqref="E2:E6">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2586,22 +2615,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F5">
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G5">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H5">
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5">
+  <conditionalFormatting sqref="I2:I6">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2654,28 +2683,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>2716</v>
+        <v>2717.3</v>
       </c>
       <c r="C2" s="2">
-        <v>19.13</v>
+        <v>26.17</v>
       </c>
       <c r="D2" s="2">
-        <v>27.84</v>
+        <v>36.1</v>
       </c>
       <c r="E2" s="2">
-        <v>21.82</v>
+        <v>17.03</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2">
         <v>96</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>100</v>
-      </c>
-      <c r="I2" s="2">
-        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2683,57 +2712,57 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1795.1</v>
+        <v>1786.9</v>
       </c>
       <c r="C3" s="2">
-        <v>20.52</v>
+        <v>24.44</v>
       </c>
       <c r="D3" s="2">
-        <v>22.09</v>
+        <v>25.48</v>
       </c>
       <c r="E3" s="2">
-        <v>13.73</v>
+        <v>9.73</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
+        <v>98</v>
+      </c>
+      <c r="H3" s="2">
         <v>100</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>93.48</v>
-      </c>
-      <c r="I3" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>1430.5</v>
+        <v>1109.2</v>
       </c>
       <c r="C4" s="2">
-        <v>12.39</v>
+        <v>23.11</v>
       </c>
       <c r="D4" s="2">
-        <v>11.78</v>
+        <v>15.95</v>
       </c>
       <c r="E4" s="2">
-        <v>11.2</v>
+        <v>4.46</v>
       </c>
       <c r="F4" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G4" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H4" s="2">
-        <v>97.83</v>
+        <v>92</v>
       </c>
       <c r="I4" s="2">
-        <v>98</v>
+        <v>95.65000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2741,28 +2770,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>1878.2</v>
+        <v>10549.5</v>
       </c>
       <c r="C5" s="2">
-        <v>9.4</v>
+        <v>10.32</v>
       </c>
       <c r="D5" s="2">
-        <v>7.17</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="E5" s="2">
-        <v>12.56</v>
+        <v>9.19</v>
       </c>
       <c r="F5" s="2">
         <v>92</v>
       </c>
       <c r="G5" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H5" s="2">
-        <v>69.56999999999999</v>
+        <v>94</v>
       </c>
       <c r="I5" s="2">
-        <v>20</v>
+        <v>80.43000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2770,115 +2799,115 @@
         <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>1067.5</v>
+        <v>290</v>
       </c>
       <c r="C6" s="2">
-        <v>15.32</v>
+        <v>26.8</v>
       </c>
       <c r="D6" s="2">
-        <v>13.56</v>
+        <v>7.73</v>
       </c>
       <c r="E6" s="2">
-        <v>5.15</v>
+        <v>1.43</v>
       </c>
       <c r="F6" s="2">
         <v>90</v>
       </c>
       <c r="G6" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2">
-        <v>95.65000000000001</v>
+        <v>68</v>
       </c>
       <c r="I6" s="2">
-        <v>100</v>
+        <v>86.95999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>8082.5</v>
+        <v>8362.5</v>
       </c>
       <c r="C7" s="2">
-        <v>13.52</v>
+        <v>15.39</v>
       </c>
       <c r="D7" s="2">
-        <v>3.73</v>
+        <v>7.17</v>
       </c>
       <c r="E7" s="2">
-        <v>5.56</v>
+        <v>6.87</v>
       </c>
       <c r="F7" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G7" s="2">
         <v>84</v>
       </c>
       <c r="H7" s="2">
+        <v>84</v>
+      </c>
+      <c r="I7" s="2">
         <v>67.39</v>
-      </c>
-      <c r="I7" s="2">
-        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1">
-        <v>462.2</v>
+        <v>1423.1</v>
       </c>
       <c r="C8" s="2">
-        <v>9.44</v>
+        <v>10.14</v>
       </c>
       <c r="D8" s="2">
-        <v>8.43</v>
+        <v>14.66</v>
       </c>
       <c r="E8" s="2">
-        <v>4.63</v>
+        <v>0.41</v>
       </c>
       <c r="F8" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G8" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="H8" s="2">
-        <v>89.13</v>
+        <v>98</v>
       </c>
       <c r="I8" s="2">
-        <v>74</v>
+        <v>97.83</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1">
-        <v>10377.5</v>
+        <v>1844.6</v>
       </c>
       <c r="C9" s="2">
-        <v>9.210000000000001</v>
+        <v>7.32</v>
       </c>
       <c r="D9" s="2">
-        <v>6.15</v>
+        <v>1.75</v>
       </c>
       <c r="E9" s="2">
-        <v>5.86</v>
+        <v>6.41</v>
       </c>
       <c r="F9" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G9" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H9" s="2">
-        <v>80.43000000000001</v>
+        <v>88</v>
       </c>
       <c r="I9" s="2">
-        <v>62</v>
+        <v>69.56999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2957,13 +2986,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2">
         <v>50</v>
       </c>
       <c r="D2" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2971,13 +3000,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C3" s="2">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2985,13 +3014,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C4" s="2">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D4" s="2">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2999,10 +3028,10 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C5" s="2">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D5" s="2">
         <v>48</v>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-05-22</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-05-22</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-05-22</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-05-22</t>
+    <t>Price_2026-05-29</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-05-29</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-05-29</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-05-29</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-05-29</t>
   </si>
   <si>
     <t>RS_Score_2026-05-22</t>
@@ -43,159 +46,156 @@
     <t>RS_Score_2026-05-08</t>
   </si>
   <si>
-    <t>RS_Score_2026-05-01</t>
-  </si>
-  <si>
     <t>ADANIENT</t>
   </si>
   <si>
     <t>ADANIPORTS</t>
   </si>
   <si>
+    <t>TMPV</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
     <t>GRASIM</t>
   </si>
   <si>
-    <t>HINDALCO</t>
-  </si>
-  <si>
     <t>BAJAJ-AUTO</t>
   </si>
   <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>ETERNAL</t>
+  </si>
+  <si>
     <t>ONGC</t>
   </si>
   <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>TMPV</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>TITAN</t>
   </si>
   <si>
     <t>MAXHEALTH</t>
   </si>
   <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
     <t>ITC</t>
   </si>
   <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
     <t>RELIANCE</t>
   </si>
   <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>ETERNAL</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>TITAN</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>HCLTECH</t>
   </si>
   <si>
     <t>HDFCBANK</t>
   </si>
   <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
     <t>TCS</t>
   </si>
   <si>
-    <t>HCLTECH</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
     <t>2026-05-22</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>2717.3</v>
+        <v>2937.4</v>
       </c>
       <c r="C2" s="2">
-        <v>26.17</v>
+        <v>36.16</v>
       </c>
       <c r="D2" s="2">
-        <v>36.1</v>
+        <v>48.7</v>
       </c>
       <c r="E2" s="2">
-        <v>17.03</v>
+        <v>18.17</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -740,10 +740,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="2">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
         <v>96</v>
-      </c>
-      <c r="I2" s="2">
-        <v>100</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>60</v>
@@ -754,16 +754,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1786.9</v>
+        <v>1804.6</v>
       </c>
       <c r="C3" s="2">
-        <v>24.44</v>
+        <v>26.91</v>
       </c>
       <c r="D3" s="2">
-        <v>25.48</v>
+        <v>32.16</v>
       </c>
       <c r="E3" s="2">
-        <v>9.73</v>
+        <v>3.56</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
@@ -772,10 +772,10 @@
         <v>98</v>
       </c>
       <c r="H3" s="2">
+        <v>98</v>
+      </c>
+      <c r="I3" s="2">
         <v>100</v>
-      </c>
-      <c r="I3" s="2">
-        <v>93.48</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>3155.3</v>
+        <v>393.9</v>
       </c>
       <c r="C4" s="2">
-        <v>13.63</v>
+        <v>11.4</v>
       </c>
       <c r="D4" s="2">
-        <v>14.99</v>
+        <v>23.4</v>
       </c>
       <c r="E4" s="2">
-        <v>13.57</v>
+        <v>14.82</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H4" s="2">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="I4" s="2">
-        <v>54.35</v>
+        <v>52</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1109.2</v>
+        <v>1126.7</v>
       </c>
       <c r="C5" s="2">
-        <v>23.11</v>
+        <v>20.55</v>
       </c>
       <c r="D5" s="2">
-        <v>15.95</v>
+        <v>20.29</v>
       </c>
       <c r="E5" s="2">
-        <v>4.46</v>
+        <v>8.06</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
+        <v>94</v>
+      </c>
+      <c r="H5" s="2">
         <v>90</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>92</v>
-      </c>
-      <c r="I5" s="2">
-        <v>95.65000000000001</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>10549.5</v>
+        <v>3122.4</v>
       </c>
       <c r="C6" s="2">
-        <v>10.32</v>
+        <v>11.13</v>
       </c>
       <c r="D6" s="2">
-        <v>9.779999999999999</v>
+        <v>16.36</v>
       </c>
       <c r="E6" s="2">
-        <v>9.19</v>
+        <v>9.33</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="H6" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="I6" s="2">
-        <v>80.43000000000001</v>
+        <v>76</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>290</v>
+        <v>10460</v>
       </c>
       <c r="C7" s="2">
-        <v>26.8</v>
+        <v>11.78</v>
       </c>
       <c r="D7" s="2">
-        <v>7.73</v>
+        <v>16.43</v>
       </c>
       <c r="E7" s="2">
-        <v>1.43</v>
+        <v>4.69</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
+        <v>92</v>
+      </c>
+      <c r="H7" s="2">
+        <v>80</v>
+      </c>
+      <c r="I7" s="2">
         <v>94</v>
-      </c>
-      <c r="H7" s="2">
-        <v>68</v>
-      </c>
-      <c r="I7" s="2">
-        <v>86.95999999999999</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>8362.5</v>
+        <v>2671.6</v>
       </c>
       <c r="C8" s="2">
-        <v>15.39</v>
+        <v>-3.09</v>
       </c>
       <c r="D8" s="2">
-        <v>7.17</v>
+        <v>19.36</v>
       </c>
       <c r="E8" s="2">
-        <v>6.87</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H8" s="2">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="I8" s="2">
-        <v>67.39</v>
+        <v>74</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>1423.1</v>
+        <v>8176.5</v>
       </c>
       <c r="C9" s="2">
-        <v>10.14</v>
+        <v>13.16</v>
       </c>
       <c r="D9" s="2">
-        <v>14.66</v>
+        <v>9.02</v>
       </c>
       <c r="E9" s="2">
-        <v>0.41</v>
+        <v>5.67</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H9" s="2">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I9" s="2">
-        <v>97.83</v>
+        <v>84</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>4296.5</v>
+        <v>4224</v>
       </c>
       <c r="C10" s="2">
-        <v>8.15</v>
+        <v>8.32</v>
       </c>
       <c r="D10" s="2">
-        <v>15.64</v>
+        <v>16.22</v>
       </c>
       <c r="E10" s="2">
-        <v>0.84</v>
+        <v>1.58</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
+        <v>84</v>
+      </c>
+      <c r="H10" s="2">
         <v>56</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <v>72</v>
-      </c>
-      <c r="I10" s="2">
-        <v>76.09</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>1844.6</v>
+        <v>4076.5</v>
       </c>
       <c r="C11" s="2">
-        <v>7.32</v>
+        <v>6.74</v>
       </c>
       <c r="D11" s="2">
-        <v>1.75</v>
+        <v>16.19</v>
       </c>
       <c r="E11" s="2">
-        <v>6.41</v>
+        <v>0.38</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="H11" s="2">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="I11" s="2">
-        <v>69.56999999999999</v>
+        <v>38</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>2639.8</v>
+        <v>1421.5</v>
       </c>
       <c r="C12" s="2">
-        <v>-6.57</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D12" s="2">
-        <v>15.76</v>
+        <v>17.78</v>
       </c>
       <c r="E12" s="2">
-        <v>6.22</v>
+        <v>-2.44</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="H12" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="I12" s="2">
-        <v>58.7</v>
+        <v>98</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>209.19</v>
+        <v>1401</v>
       </c>
       <c r="C13" s="2">
-        <v>17.26</v>
+        <v>0.25</v>
       </c>
       <c r="D13" s="2">
-        <v>7.28</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="E13" s="2">
-        <v>-1.91</v>
+        <v>4.94</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H13" s="2">
         <v>86</v>
       </c>
       <c r="I13" s="2">
-        <v>82.61</v>
+        <v>62</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>1285.5</v>
+        <v>1278</v>
       </c>
       <c r="C14" s="2">
-        <v>10.93</v>
+        <v>7.64</v>
       </c>
       <c r="D14" s="2">
-        <v>5.86</v>
+        <v>9.49</v>
       </c>
       <c r="E14" s="2">
-        <v>0.22</v>
+        <v>0.9</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
+        <v>76</v>
+      </c>
+      <c r="H14" s="2">
         <v>68</v>
       </c>
-      <c r="H14" s="2">
+      <c r="I14" s="2">
         <v>78</v>
-      </c>
-      <c r="I14" s="2">
-        <v>78.26000000000001</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>456.55</v>
+        <v>1178.4</v>
       </c>
       <c r="C15" s="2">
-        <v>10.57</v>
+        <v>-0.06</v>
       </c>
       <c r="D15" s="2">
-        <v>2.93</v>
+        <v>10.24</v>
       </c>
       <c r="E15" s="2">
-        <v>0.9</v>
+        <v>2.41</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="H15" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I15" s="2">
-        <v>89.13</v>
+        <v>66</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>1191.8</v>
+        <v>1303.5</v>
       </c>
       <c r="C16" s="2">
-        <v>1.35</v>
+        <v>10.89</v>
       </c>
       <c r="D16" s="2">
-        <v>8.390000000000001</v>
+        <v>1.53</v>
       </c>
       <c r="E16" s="2">
-        <v>2.7</v>
+        <v>1.27</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="H16" s="2">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="I16" s="2">
-        <v>65.22</v>
+        <v>64</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,25 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>363.35</v>
+        <v>208.02</v>
       </c>
       <c r="C17" s="2">
-        <v>2.6</v>
+        <v>10.53</v>
       </c>
       <c r="D17" s="2">
-        <v>5.26</v>
+        <v>6.44</v>
       </c>
       <c r="E17" s="2">
-        <v>2.54</v>
+        <v>-1.99</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="H17" s="2">
-        <v>52</v>
+        <v>76</v>
+      </c>
+      <c r="I17" s="2">
+        <v>86</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1231,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>1399.2</v>
+        <v>386.9</v>
       </c>
       <c r="C18" s="2">
-        <v>-4.54</v>
+        <v>12.55</v>
       </c>
       <c r="D18" s="2">
-        <v>4.93</v>
+        <v>0.93</v>
       </c>
       <c r="E18" s="2">
-        <v>6.23</v>
+        <v>-3.29</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="H18" s="2">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="I18" s="2">
-        <v>39.13</v>
+        <v>90</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1263,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>388.65</v>
+        <v>1799.2</v>
       </c>
       <c r="C19" s="2">
-        <v>16.54</v>
+        <v>8.51</v>
       </c>
       <c r="D19" s="2">
-        <v>3.01</v>
+        <v>0.27</v>
       </c>
       <c r="E19" s="2">
-        <v>-5.25</v>
+        <v>-1.33</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H19" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I19" s="2">
-        <v>91.3</v>
+        <v>88</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1295,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>1307.2</v>
+        <v>1286.6</v>
       </c>
       <c r="C20" s="2">
-        <v>8.02</v>
+        <v>-0.59</v>
       </c>
       <c r="D20" s="2">
-        <v>-0.5600000000000001</v>
+        <v>4.76</v>
       </c>
       <c r="E20" s="2">
-        <v>-2.05</v>
+        <v>0.9</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="H20" s="2">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="I20" s="2">
-        <v>71.73999999999999</v>
+        <v>32</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1327,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>1023.25</v>
+        <v>4405</v>
       </c>
       <c r="C21" s="2">
-        <v>0.59</v>
+        <v>-7.07</v>
       </c>
       <c r="D21" s="2">
-        <v>-1.9</v>
+        <v>2.73</v>
       </c>
       <c r="E21" s="2">
-        <v>1.33</v>
+        <v>3.35</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="H21" s="2">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="I21" s="2">
-        <v>34.78</v>
+        <v>30</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1359,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>1422.2</v>
+        <v>384.2</v>
       </c>
       <c r="C22" s="2">
-        <v>-10.11</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="D22" s="2">
-        <v>6.4</v>
+        <v>2.67</v>
       </c>
       <c r="E22" s="2">
-        <v>1.87</v>
+        <v>3.38</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="H22" s="2">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I22" s="2">
-        <v>28.26</v>
+        <v>26</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1391,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>1871.4</v>
+        <v>1483.9</v>
       </c>
       <c r="C23" s="2">
-        <v>-7.68</v>
+        <v>-11.17</v>
       </c>
       <c r="D23" s="2">
-        <v>1.13</v>
+        <v>10.59</v>
       </c>
       <c r="E23" s="2">
-        <v>2.82</v>
+        <v>0.84</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H23" s="2">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I23" s="2">
-        <v>30.43</v>
+        <v>44</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1423,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>294.3</v>
+        <v>7177</v>
       </c>
       <c r="C24" s="2">
-        <v>15.35</v>
+        <v>-1.89</v>
       </c>
       <c r="D24" s="2">
-        <v>-1.46</v>
+        <v>3.86</v>
       </c>
       <c r="E24" s="2">
-        <v>-8.289999999999999</v>
+        <v>-2.07</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="H24" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I24" s="2">
-        <v>84.78</v>
+        <v>36</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1455,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>3926.6</v>
+        <v>457.9</v>
       </c>
       <c r="C25" s="2">
-        <v>-1.5</v>
+        <v>7.65</v>
       </c>
       <c r="D25" s="2">
-        <v>2.29</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E25" s="2">
-        <v>-2.19</v>
+        <v>-4.59</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="H25" s="2">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="I25" s="2">
-        <v>63.04</v>
+        <v>82</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1487,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>1285.4</v>
+        <v>290.55</v>
       </c>
       <c r="C26" s="2">
-        <v>1.05</v>
+        <v>14.19</v>
       </c>
       <c r="D26" s="2">
-        <v>-2.23</v>
+        <v>-2.66</v>
       </c>
       <c r="E26" s="2">
-        <v>-2.93</v>
+        <v>-8.93</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="H26" s="2">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="I26" s="2">
-        <v>47.83</v>
+        <v>80</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1519,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>384.15</v>
+        <v>250.58</v>
       </c>
       <c r="C27" s="2">
-        <v>-9.69</v>
+        <v>-12.9</v>
       </c>
       <c r="D27" s="2">
-        <v>-1.97</v>
+        <v>6.8</v>
       </c>
       <c r="E27" s="2">
-        <v>1.95</v>
+        <v>-0.52</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="H27" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I27" s="2">
-        <v>26.09</v>
+        <v>54</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1551,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>916.55</v>
+        <v>265.4</v>
       </c>
       <c r="C28" s="2">
-        <v>-4.49</v>
+        <v>9.9</v>
       </c>
       <c r="D28" s="2">
-        <v>-2.47</v>
+        <v>0.25</v>
       </c>
       <c r="E28" s="2">
-        <v>-0.57</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="H28" s="2">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="I28" s="2">
-        <v>52.17</v>
+        <v>68</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1583,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>1870.7</v>
+        <v>11482</v>
       </c>
       <c r="C29" s="2">
-        <v>-9.5</v>
+        <v>-7.24</v>
       </c>
       <c r="D29" s="2">
-        <v>-4.74</v>
+        <v>3.29</v>
       </c>
       <c r="E29" s="2">
-        <v>3.05</v>
+        <v>-2.35</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H29" s="2">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="I29" s="2">
-        <v>21.74</v>
+        <v>48</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1615,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>11569</v>
+        <v>908.25</v>
       </c>
       <c r="C30" s="2">
-        <v>-3.08</v>
+        <v>-4.42</v>
       </c>
       <c r="D30" s="2">
-        <v>-0.73</v>
+        <v>4.56</v>
       </c>
       <c r="E30" s="2">
-        <v>-3.67</v>
+        <v>-4.41</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
+        <v>48</v>
+      </c>
+      <c r="H30" s="2">
+        <v>46</v>
+      </c>
+      <c r="I30" s="2">
         <v>42</v>
-      </c>
-      <c r="H30" s="2">
-        <v>48</v>
-      </c>
-      <c r="I30" s="2">
-        <v>50</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1647,25 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>4438.6</v>
+        <v>1783.6</v>
       </c>
       <c r="C31" s="2">
-        <v>-8.369999999999999</v>
+        <v>-10.93</v>
       </c>
       <c r="D31" s="2">
-        <v>1.33</v>
+        <v>0.5</v>
       </c>
       <c r="E31" s="2">
-        <v>-2.69</v>
+        <v>0.75</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H31" s="2">
-        <v>30</v>
+        <v>16</v>
+      </c>
+      <c r="I31" s="2">
+        <v>28</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1676,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>301.7</v>
+        <v>1829</v>
       </c>
       <c r="C32" s="2">
-        <v>-8.640000000000001</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="D32" s="2">
-        <v>-2.38</v>
+        <v>0.11</v>
       </c>
       <c r="E32" s="2">
-        <v>-0.71</v>
+        <v>0.1</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H32" s="2">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="I32" s="2">
-        <v>32.61</v>
+        <v>18</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1708,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>1354.5</v>
+        <v>204.25</v>
       </c>
       <c r="C33" s="2">
-        <v>-8.19</v>
+        <v>-21.66</v>
       </c>
       <c r="D33" s="2">
-        <v>-3.85</v>
+        <v>6.76</v>
       </c>
       <c r="E33" s="2">
-        <v>-0.83</v>
+        <v>1.74</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="H33" s="2">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="I33" s="2">
-        <v>41.3</v>
+        <v>10</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1740,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>2203.6</v>
+        <v>947.15</v>
       </c>
       <c r="C34" s="2">
-        <v>-7.12</v>
+        <v>-4.85</v>
       </c>
       <c r="D34" s="2">
-        <v>0.61</v>
+        <v>-5.72</v>
       </c>
       <c r="E34" s="2">
-        <v>-5.36</v>
+        <v>-1.38</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="I34" s="2">
-        <v>56.52</v>
+        <v>46</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1772,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>616.6</v>
+        <v>1256.4</v>
       </c>
       <c r="C35" s="2">
-        <v>-17.78</v>
+        <v>-10.94</v>
       </c>
       <c r="D35" s="2">
-        <v>-6.02</v>
+        <v>-2.51</v>
       </c>
       <c r="E35" s="2">
-        <v>3.23</v>
+        <v>-1.13</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H35" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I35" s="2">
-        <v>8.699999999999999</v>
+        <v>20</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1804,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>1766</v>
+        <v>1830.1</v>
       </c>
       <c r="C36" s="2">
-        <v>-11.36</v>
+        <v>-11.93</v>
       </c>
       <c r="D36" s="2">
-        <v>-5.45</v>
+        <v>-5.28</v>
       </c>
       <c r="E36" s="2">
-        <v>-0.35</v>
+        <v>0.55</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I36" s="2">
-        <v>19.57</v>
+        <v>22</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1836,25 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>241.95</v>
+        <v>410.75</v>
       </c>
       <c r="C37" s="2">
-        <v>-14.91</v>
+        <v>0.55</v>
       </c>
       <c r="D37" s="2">
-        <v>6.76</v>
+        <v>-6.51</v>
       </c>
       <c r="E37" s="2">
-        <v>-5.3</v>
+        <v>-5.26</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H37" s="2">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="I37" s="2">
+        <v>60</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1865,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>416.55</v>
+        <v>4074.9</v>
       </c>
       <c r="C38" s="2">
-        <v>-0.08</v>
+        <v>-2.91</v>
       </c>
       <c r="D38" s="2">
-        <v>-10.1</v>
+        <v>-0.38</v>
       </c>
       <c r="E38" s="2">
-        <v>-4.37</v>
+        <v>-6.6</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="H38" s="2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I38" s="2">
-        <v>60.87</v>
+        <v>70</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1897,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>6981.5</v>
+        <v>965.1</v>
       </c>
       <c r="C39" s="2">
-        <v>-7</v>
+        <v>-6.93</v>
       </c>
       <c r="D39" s="2">
-        <v>-7.36</v>
+        <v>-1.16</v>
       </c>
       <c r="E39" s="2">
-        <v>-2.68</v>
+        <v>-4.59</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="H39" s="2">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="I39" s="2">
-        <v>36.96</v>
+        <v>50</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1929,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>1264.3</v>
+        <v>286.9</v>
       </c>
       <c r="C40" s="2">
-        <v>-9.970000000000001</v>
+        <v>-8.6</v>
       </c>
       <c r="D40" s="2">
-        <v>-3.63</v>
+        <v>-3.32</v>
       </c>
       <c r="E40" s="2">
-        <v>-3.79</v>
+        <v>-5.27</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H40" s="2">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="I40" s="2">
-        <v>23.91</v>
+        <v>16</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1961,28 +1970,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>203.11</v>
+        <v>2153.5</v>
       </c>
       <c r="C41" s="2">
-        <v>-20.46</v>
+        <v>-8.77</v>
       </c>
       <c r="D41" s="2">
-        <v>1.08</v>
+        <v>-0.22</v>
       </c>
       <c r="E41" s="2">
-        <v>-0.95</v>
+        <v>-6.75</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="H41" s="2">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="I41" s="2">
-        <v>13.04</v>
+        <v>58</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -1993,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>941</v>
+        <v>13127</v>
       </c>
       <c r="C42" s="2">
-        <v>-3.53</v>
+        <v>-17.23</v>
       </c>
       <c r="D42" s="2">
-        <v>-11.47</v>
+        <v>1.19</v>
       </c>
       <c r="E42" s="2">
-        <v>-3.45</v>
+        <v>-3.34</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
+        <v>12</v>
+      </c>
+      <c r="H42" s="2">
+        <v>24</v>
+      </c>
+      <c r="I42" s="2">
         <v>14</v>
-      </c>
-      <c r="H42" s="2">
-        <v>46</v>
-      </c>
-      <c r="I42" s="2">
-        <v>43.48</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2025,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>4079.8</v>
+        <v>3045.6</v>
       </c>
       <c r="C43" s="2">
-        <v>-2.9</v>
+        <v>-16.75</v>
       </c>
       <c r="D43" s="2">
-        <v>-3.32</v>
+        <v>-2.66</v>
       </c>
       <c r="E43" s="2">
-        <v>-8.15</v>
+        <v>-1.96</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="H43" s="2">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="I43" s="2">
-        <v>73.91</v>
+        <v>40</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2057,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>3081.3</v>
+        <v>594.8</v>
       </c>
       <c r="C44" s="2">
-        <v>-16.21</v>
+        <v>-18.8</v>
       </c>
       <c r="D44" s="2">
-        <v>-6.45</v>
+        <v>-7.4</v>
       </c>
       <c r="E44" s="2">
-        <v>-0.68</v>
+        <v>1.1</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H44" s="2">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="I44" s="2">
-        <v>15.22</v>
+        <v>12</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2089,24 +2098,27 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>238.19</v>
+        <v>238.95</v>
       </c>
       <c r="C45" s="2">
-        <v>-17.08</v>
+        <v>-14.29</v>
       </c>
       <c r="D45" s="2">
-        <v>0.93</v>
+        <v>0.57</v>
       </c>
       <c r="E45" s="2">
-        <v>-6.09</v>
+        <v>-5.46</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
+        <v>14</v>
+      </c>
+      <c r="H45" s="2">
         <v>26</v>
       </c>
-      <c r="H45" s="2">
+      <c r="I45" s="2">
         <v>34</v>
       </c>
       <c r="J45" s="4" t="s">
@@ -2118,28 +2130,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>12987</v>
+        <v>964.4</v>
       </c>
       <c r="C46" s="2">
-        <v>-21.3</v>
+        <v>-5.81</v>
       </c>
       <c r="D46" s="2">
-        <v>-6.35</v>
+        <v>-7.79</v>
       </c>
       <c r="E46" s="2">
-        <v>-1.78</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
+        <v>6</v>
+      </c>
+      <c r="H46" s="2">
+        <v>12</v>
+      </c>
+      <c r="I46" s="2">
         <v>24</v>
-      </c>
-      <c r="H46" s="2">
-        <v>14</v>
-      </c>
-      <c r="I46" s="2">
-        <v>17.39</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2150,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>766.8</v>
+        <v>1321.2</v>
       </c>
       <c r="C47" s="2">
-        <v>-18.34</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="D47" s="2">
-        <v>-9.73</v>
+        <v>-5.47</v>
       </c>
       <c r="E47" s="2">
-        <v>-2.91</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H47" s="2">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="I47" s="2">
-        <v>6.52</v>
+        <v>56</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2182,28 +2194,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>1174.5</v>
+        <v>1160.9</v>
       </c>
       <c r="C48" s="2">
-        <v>-27.23</v>
+        <v>-31.3</v>
       </c>
       <c r="D48" s="2">
-        <v>-9.35</v>
+        <v>-5.84</v>
       </c>
       <c r="E48" s="2">
-        <v>0.36</v>
+        <v>-0.64</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H48" s="2">
         <v>4</v>
       </c>
       <c r="I48" s="2">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2214,28 +2226,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>949.2</v>
+        <v>1183.8</v>
       </c>
       <c r="C49" s="2">
-        <v>-3.42</v>
+        <v>-28.95</v>
       </c>
       <c r="D49" s="2">
-        <v>-13.12</v>
+        <v>-8.68</v>
       </c>
       <c r="E49" s="2">
-        <v>-13.09</v>
+        <v>-1.39</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H49" s="2">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I49" s="2">
-        <v>45.65</v>
+        <v>2</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2246,28 +2258,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>2317.3</v>
+        <v>744.55</v>
       </c>
       <c r="C50" s="2">
-        <v>-26.45</v>
+        <v>-20.04</v>
       </c>
       <c r="D50" s="2">
-        <v>-7.79</v>
+        <v>-11.92</v>
       </c>
       <c r="E50" s="2">
-        <v>-5.32</v>
+        <v>-4.47</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H50" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I50" s="2">
-        <v>10.87</v>
+        <v>8</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2278,28 +2290,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>1164</v>
+        <v>2258.9</v>
       </c>
       <c r="C51" s="2">
-        <v>-28.08</v>
+        <v>-28.6</v>
       </c>
       <c r="D51" s="2">
-        <v>-12.87</v>
+        <v>-4.27</v>
       </c>
       <c r="E51" s="2">
-        <v>-5.23</v>
+        <v>-5.83</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H51" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I51" s="2">
-        <v>2.17</v>
+        <v>6</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2408,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2450,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>2717.3</v>
+        <v>2937.4</v>
       </c>
       <c r="C2" s="2">
-        <v>26.17</v>
+        <v>36.16</v>
       </c>
       <c r="D2" s="2">
-        <v>36.1</v>
+        <v>48.7</v>
       </c>
       <c r="E2" s="2">
-        <v>17.03</v>
+        <v>18.17</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2468,10 +2480,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="2">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
         <v>96</v>
-      </c>
-      <c r="I2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2479,16 +2491,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1786.9</v>
+        <v>1804.6</v>
       </c>
       <c r="C3" s="2">
-        <v>24.44</v>
+        <v>26.91</v>
       </c>
       <c r="D3" s="2">
-        <v>25.48</v>
+        <v>32.16</v>
       </c>
       <c r="E3" s="2">
-        <v>9.73</v>
+        <v>3.56</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
@@ -2497,10 +2509,10 @@
         <v>98</v>
       </c>
       <c r="H3" s="2">
+        <v>98</v>
+      </c>
+      <c r="I3" s="2">
         <v>100</v>
-      </c>
-      <c r="I3" s="2">
-        <v>93.48</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2508,57 +2520,57 @@
         <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>1109.2</v>
+        <v>1126.7</v>
       </c>
       <c r="C4" s="2">
-        <v>23.11</v>
+        <v>20.55</v>
       </c>
       <c r="D4" s="2">
-        <v>15.95</v>
+        <v>20.29</v>
       </c>
       <c r="E4" s="2">
-        <v>4.46</v>
+        <v>8.06</v>
       </c>
       <c r="F4" s="2">
         <v>94</v>
       </c>
       <c r="G4" s="2">
+        <v>94</v>
+      </c>
+      <c r="H4" s="2">
         <v>90</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>92</v>
-      </c>
-      <c r="I4" s="2">
-        <v>95.65000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>10549.5</v>
+        <v>10460</v>
       </c>
       <c r="C5" s="2">
-        <v>10.32</v>
+        <v>11.78</v>
       </c>
       <c r="D5" s="2">
-        <v>9.779999999999999</v>
+        <v>16.43</v>
       </c>
       <c r="E5" s="2">
-        <v>9.19</v>
+        <v>4.69</v>
       </c>
       <c r="F5" s="2">
+        <v>90</v>
+      </c>
+      <c r="G5" s="2">
         <v>92</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <v>80</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>94</v>
-      </c>
-      <c r="I5" s="2">
-        <v>80.43000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2566,32 +2578,61 @@
         <v>16</v>
       </c>
       <c r="B6" s="1">
-        <v>1423.1</v>
+        <v>8176.5</v>
       </c>
       <c r="C6" s="2">
-        <v>10.14</v>
+        <v>13.16</v>
       </c>
       <c r="D6" s="2">
-        <v>14.66</v>
+        <v>9.02</v>
       </c>
       <c r="E6" s="2">
-        <v>0.41</v>
+        <v>5.67</v>
       </c>
       <c r="F6" s="2">
         <v>86</v>
       </c>
       <c r="G6" s="2">
+        <v>88</v>
+      </c>
+      <c r="H6" s="2">
+        <v>84</v>
+      </c>
+      <c r="I6" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1421.5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="D7" s="2">
+        <v>17.78</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-2.44</v>
+      </c>
+      <c r="F7" s="2">
+        <v>80</v>
+      </c>
+      <c r="G7" s="2">
+        <v>86</v>
+      </c>
+      <c r="H7" s="2">
         <v>96</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I7" s="2">
         <v>98</v>
       </c>
-      <c r="I6" s="2">
-        <v>97.83</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2599,7 +2640,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2607,7 +2648,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E6">
+  <conditionalFormatting sqref="E2:E7">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2615,22 +2656,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
+  <conditionalFormatting sqref="F2:F7">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G6">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H6">
+  <conditionalFormatting sqref="H2:H7">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
+  <conditionalFormatting sqref="I2:I7">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2641,7 +2682,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2683,16 +2724,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>2717.3</v>
+        <v>2937.4</v>
       </c>
       <c r="C2" s="2">
-        <v>26.17</v>
+        <v>36.16</v>
       </c>
       <c r="D2" s="2">
-        <v>36.1</v>
+        <v>48.7</v>
       </c>
       <c r="E2" s="2">
-        <v>17.03</v>
+        <v>18.17</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2701,10 +2742,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="2">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
         <v>96</v>
-      </c>
-      <c r="I2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2712,16 +2753,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1786.9</v>
+        <v>1804.6</v>
       </c>
       <c r="C3" s="2">
-        <v>24.44</v>
+        <v>26.91</v>
       </c>
       <c r="D3" s="2">
-        <v>25.48</v>
+        <v>32.16</v>
       </c>
       <c r="E3" s="2">
-        <v>9.73</v>
+        <v>3.56</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
@@ -2730,10 +2771,10 @@
         <v>98</v>
       </c>
       <c r="H3" s="2">
+        <v>98</v>
+      </c>
+      <c r="I3" s="2">
         <v>100</v>
-      </c>
-      <c r="I3" s="2">
-        <v>93.48</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2741,28 +2782,28 @@
         <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>1109.2</v>
+        <v>1126.7</v>
       </c>
       <c r="C4" s="2">
-        <v>23.11</v>
+        <v>20.55</v>
       </c>
       <c r="D4" s="2">
-        <v>15.95</v>
+        <v>20.29</v>
       </c>
       <c r="E4" s="2">
-        <v>4.46</v>
+        <v>8.06</v>
       </c>
       <c r="F4" s="2">
         <v>94</v>
       </c>
       <c r="G4" s="2">
+        <v>94</v>
+      </c>
+      <c r="H4" s="2">
         <v>90</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>92</v>
-      </c>
-      <c r="I4" s="2">
-        <v>95.65000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2770,28 +2811,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>10549.5</v>
+        <v>3122.4</v>
       </c>
       <c r="C5" s="2">
-        <v>10.32</v>
+        <v>11.13</v>
       </c>
       <c r="D5" s="2">
-        <v>9.779999999999999</v>
+        <v>16.36</v>
       </c>
       <c r="E5" s="2">
-        <v>9.19</v>
+        <v>9.33</v>
       </c>
       <c r="F5" s="2">
         <v>92</v>
       </c>
       <c r="G5" s="2">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="H5" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="I5" s="2">
-        <v>80.43000000000001</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2799,28 +2840,28 @@
         <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>290</v>
+        <v>10460</v>
       </c>
       <c r="C6" s="2">
-        <v>26.8</v>
+        <v>11.78</v>
       </c>
       <c r="D6" s="2">
-        <v>7.73</v>
+        <v>16.43</v>
       </c>
       <c r="E6" s="2">
-        <v>1.43</v>
+        <v>4.69</v>
       </c>
       <c r="F6" s="2">
         <v>90</v>
       </c>
       <c r="G6" s="2">
+        <v>92</v>
+      </c>
+      <c r="H6" s="2">
+        <v>80</v>
+      </c>
+      <c r="I6" s="2">
         <v>94</v>
-      </c>
-      <c r="H6" s="2">
-        <v>68</v>
-      </c>
-      <c r="I6" s="2">
-        <v>86.95999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2828,28 +2869,28 @@
         <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>8362.5</v>
+        <v>2671.6</v>
       </c>
       <c r="C7" s="2">
-        <v>15.39</v>
+        <v>-3.09</v>
       </c>
       <c r="D7" s="2">
-        <v>7.17</v>
+        <v>19.36</v>
       </c>
       <c r="E7" s="2">
-        <v>6.87</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="F7" s="2">
         <v>88</v>
       </c>
       <c r="G7" s="2">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H7" s="2">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="I7" s="2">
-        <v>67.39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2857,61 +2898,90 @@
         <v>16</v>
       </c>
       <c r="B8" s="1">
-        <v>1423.1</v>
+        <v>8176.5</v>
       </c>
       <c r="C8" s="2">
-        <v>10.14</v>
+        <v>13.16</v>
       </c>
       <c r="D8" s="2">
-        <v>14.66</v>
+        <v>9.02</v>
       </c>
       <c r="E8" s="2">
-        <v>0.41</v>
+        <v>5.67</v>
       </c>
       <c r="F8" s="2">
         <v>86</v>
       </c>
       <c r="G8" s="2">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H8" s="2">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I8" s="2">
-        <v>97.83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1">
-        <v>1844.6</v>
+        <v>4224</v>
       </c>
       <c r="C9" s="2">
-        <v>7.32</v>
+        <v>8.32</v>
       </c>
       <c r="D9" s="2">
-        <v>1.75</v>
+        <v>16.22</v>
       </c>
       <c r="E9" s="2">
-        <v>6.41</v>
+        <v>1.58</v>
       </c>
       <c r="F9" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G9" s="2">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H9" s="2">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="I9" s="2">
-        <v>69.56999999999999</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1421.5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="D10" s="2">
+        <v>17.78</v>
+      </c>
+      <c r="E10" s="2">
+        <v>-2.44</v>
+      </c>
+      <c r="F10" s="2">
+        <v>80</v>
+      </c>
+      <c r="G10" s="2">
+        <v>86</v>
+      </c>
+      <c r="H10" s="2">
+        <v>96</v>
+      </c>
+      <c r="I10" s="2">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C2:C10">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2919,7 +2989,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D10">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2927,7 +2997,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E10">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2935,22 +3005,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F10">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G10">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H10">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
+  <conditionalFormatting sqref="I2:I10">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2986,13 +3056,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
+        <v>38</v>
+      </c>
+      <c r="C2" s="2">
         <v>46</v>
       </c>
-      <c r="C2" s="2">
-        <v>50</v>
-      </c>
       <c r="D2" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3000,7 +3070,7 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C3" s="2">
         <v>50</v>
@@ -3014,13 +3084,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3028,13 +3098,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D5" s="2">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-05-29</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-05-29</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-05-29</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-05-29</t>
+    <t>Price_2026-06-05</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-06-05</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-06-05</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-06-05</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-06-05</t>
   </si>
   <si>
     <t>RS_Score_2026-05-29</t>
@@ -43,9 +46,6 @@
     <t>RS_Score_2026-05-15</t>
   </si>
   <si>
-    <t>RS_Score_2026-05-08</t>
-  </si>
-  <si>
     <t>ADANIENT</t>
   </si>
   <si>
@@ -58,144 +58,144 @@
     <t>HINDALCO</t>
   </si>
   <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
     <t>GRASIM</t>
   </si>
   <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
     <t>BAJAJ-AUTO</t>
   </si>
   <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>TRENT</t>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
   </si>
   <si>
     <t>LT</t>
   </si>
   <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>ETERNAL</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
     <t>NESTLEIND</t>
   </si>
   <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>BEL</t>
   </si>
   <si>
     <t>TATACONSUM</t>
   </si>
   <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>ETERNAL</t>
-  </si>
-  <si>
-    <t>ONGC</t>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>HINDUNILVR</t>
   </si>
   <si>
     <t>ULTRACEMCO</t>
   </si>
   <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>TITAN</t>
-  </si>
-  <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
     <t>M&amp;M</t>
   </si>
   <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
     <t>HDFCLIFE</t>
   </si>
   <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>INFY</t>
+    <t>TCS</t>
   </si>
   <si>
     <t>HCLTECH</t>
   </si>
   <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
     <t>2026-05-29</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>2937.4</v>
+        <v>3048.2</v>
       </c>
       <c r="C2" s="2">
-        <v>36.16</v>
+        <v>63.51</v>
       </c>
       <c r="D2" s="2">
-        <v>48.7</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="E2" s="2">
-        <v>18.17</v>
+        <v>21.92</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -743,7 +743,7 @@
         <v>100</v>
       </c>
       <c r="I2" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>60</v>
@@ -754,16 +754,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1804.6</v>
+        <v>1824.2</v>
       </c>
       <c r="C3" s="2">
-        <v>26.91</v>
+        <v>39.42</v>
       </c>
       <c r="D3" s="2">
-        <v>32.16</v>
+        <v>35.71</v>
       </c>
       <c r="E3" s="2">
-        <v>3.56</v>
+        <v>3.22</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
@@ -775,7 +775,7 @@
         <v>98</v>
       </c>
       <c r="I3" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>393.9</v>
+        <v>397.8</v>
       </c>
       <c r="C4" s="2">
-        <v>11.4</v>
+        <v>15.49</v>
       </c>
       <c r="D4" s="2">
-        <v>23.4</v>
+        <v>27.83</v>
       </c>
       <c r="E4" s="2">
-        <v>14.82</v>
+        <v>14.97</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
+        <v>96</v>
+      </c>
+      <c r="H4" s="2">
         <v>70</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>58</v>
-      </c>
-      <c r="I4" s="2">
-        <v>52</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,16 +818,16 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1126.7</v>
+        <v>1092.6</v>
       </c>
       <c r="C5" s="2">
-        <v>20.55</v>
+        <v>14.97</v>
       </c>
       <c r="D5" s="2">
-        <v>20.29</v>
+        <v>27.84</v>
       </c>
       <c r="E5" s="2">
-        <v>8.06</v>
+        <v>6.75</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
@@ -836,10 +836,10 @@
         <v>94</v>
       </c>
       <c r="H5" s="2">
+        <v>94</v>
+      </c>
+      <c r="I5" s="2">
         <v>90</v>
-      </c>
-      <c r="I5" s="2">
-        <v>92</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>3122.4</v>
+        <v>1401.3</v>
       </c>
       <c r="C6" s="2">
-        <v>11.13</v>
+        <v>7.56</v>
       </c>
       <c r="D6" s="2">
-        <v>16.36</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2">
-        <v>9.33</v>
+        <v>8.4</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="I6" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,16 +882,16 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>10460</v>
+        <v>3087.7</v>
       </c>
       <c r="C7" s="2">
-        <v>11.78</v>
+        <v>11.91</v>
       </c>
       <c r="D7" s="2">
-        <v>16.43</v>
+        <v>21.11</v>
       </c>
       <c r="E7" s="2">
-        <v>4.69</v>
+        <v>3.47</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
@@ -900,10 +900,10 @@
         <v>92</v>
       </c>
       <c r="H7" s="2">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I7" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>2671.6</v>
+        <v>8304.5</v>
       </c>
       <c r="C8" s="2">
-        <v>-3.09</v>
+        <v>22.23</v>
       </c>
       <c r="D8" s="2">
-        <v>19.36</v>
+        <v>12.03</v>
       </c>
       <c r="E8" s="2">
-        <v>9.130000000000001</v>
+        <v>2.75</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H8" s="2">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="I8" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>8176.5</v>
+        <v>2774.2</v>
       </c>
       <c r="C9" s="2">
-        <v>13.16</v>
+        <v>10.79</v>
       </c>
       <c r="D9" s="2">
-        <v>9.02</v>
+        <v>23.64</v>
       </c>
       <c r="E9" s="2">
-        <v>5.67</v>
+        <v>-0.47</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H9" s="2">
         <v>84</v>
       </c>
       <c r="I9" s="2">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>4224</v>
+        <v>2686.7</v>
       </c>
       <c r="C10" s="2">
-        <v>8.32</v>
+        <v>-0.63</v>
       </c>
       <c r="D10" s="2">
-        <v>16.22</v>
+        <v>21.17</v>
       </c>
       <c r="E10" s="2">
-        <v>1.58</v>
+        <v>4.7</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H10" s="2">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="I10" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>4076.5</v>
+        <v>10342</v>
       </c>
       <c r="C11" s="2">
-        <v>6.74</v>
+        <v>11.41</v>
       </c>
       <c r="D11" s="2">
-        <v>16.19</v>
+        <v>17.86</v>
       </c>
       <c r="E11" s="2">
-        <v>0.38</v>
+        <v>-1.02</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="H11" s="2">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="I11" s="2">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1421.5</v>
+        <v>1284</v>
       </c>
       <c r="C12" s="2">
-        <v>8.609999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="D12" s="2">
-        <v>17.78</v>
+        <v>13.26</v>
       </c>
       <c r="E12" s="2">
-        <v>-2.44</v>
+        <v>1.69</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H12" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="I12" s="2">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>1401</v>
+        <v>472.3</v>
       </c>
       <c r="C13" s="2">
-        <v>0.25</v>
+        <v>14.37</v>
       </c>
       <c r="D13" s="2">
-        <v>9.289999999999999</v>
+        <v>6.83</v>
       </c>
       <c r="E13" s="2">
-        <v>4.94</v>
+        <v>1.69</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="H13" s="2">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="I13" s="2">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>1278</v>
+        <v>3953.2</v>
       </c>
       <c r="C14" s="2">
-        <v>7.64</v>
+        <v>6.62</v>
       </c>
       <c r="D14" s="2">
-        <v>9.49</v>
+        <v>13.51</v>
       </c>
       <c r="E14" s="2">
-        <v>0.9</v>
+        <v>1.31</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H14" s="2">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="I14" s="2">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>1178.4</v>
+        <v>4260.2</v>
       </c>
       <c r="C15" s="2">
-        <v>-0.06</v>
+        <v>5.93</v>
       </c>
       <c r="D15" s="2">
-        <v>10.24</v>
+        <v>9.25</v>
       </c>
       <c r="E15" s="2">
-        <v>2.41</v>
+        <v>1.3</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="H15" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="I15" s="2">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>1303.5</v>
+        <v>256.5</v>
       </c>
       <c r="C16" s="2">
-        <v>10.89</v>
+        <v>-0.85</v>
       </c>
       <c r="D16" s="2">
-        <v>1.53</v>
+        <v>7.8</v>
       </c>
       <c r="E16" s="2">
-        <v>1.27</v>
+        <v>4.32</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="H16" s="2">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="I16" s="2">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>208.02</v>
+        <v>206.77</v>
       </c>
       <c r="C17" s="2">
-        <v>10.53</v>
+        <v>10.21</v>
       </c>
       <c r="D17" s="2">
-        <v>6.44</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="E17" s="2">
-        <v>-1.99</v>
+        <v>-2.5</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
+        <v>70</v>
+      </c>
+      <c r="H17" s="2">
         <v>78</v>
       </c>
-      <c r="H17" s="2">
+      <c r="I17" s="2">
         <v>76</v>
-      </c>
-      <c r="I17" s="2">
-        <v>86</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>386.9</v>
+        <v>1386.2</v>
       </c>
       <c r="C18" s="2">
-        <v>12.55</v>
+        <v>7.72</v>
       </c>
       <c r="D18" s="2">
-        <v>0.93</v>
+        <v>17.16</v>
       </c>
       <c r="E18" s="2">
-        <v>-3.29</v>
+        <v>-6.46</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="H18" s="2">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="I18" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1799.2</v>
+        <v>4481.3</v>
       </c>
       <c r="C19" s="2">
-        <v>8.51</v>
+        <v>-4.74</v>
       </c>
       <c r="D19" s="2">
-        <v>0.27</v>
+        <v>7.96</v>
       </c>
       <c r="E19" s="2">
-        <v>-1.33</v>
+        <v>4.23</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="H19" s="2">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="I19" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>1286.6</v>
+        <v>1272.3</v>
       </c>
       <c r="C20" s="2">
-        <v>-0.59</v>
+        <v>1.14</v>
       </c>
       <c r="D20" s="2">
-        <v>4.76</v>
+        <v>6.67</v>
       </c>
       <c r="E20" s="2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
+        <v>64</v>
+      </c>
+      <c r="H20" s="2">
         <v>52</v>
       </c>
-      <c r="H20" s="2">
+      <c r="I20" s="2">
         <v>34</v>
-      </c>
-      <c r="I20" s="2">
-        <v>32</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>4405</v>
+        <v>1278.2</v>
       </c>
       <c r="C21" s="2">
-        <v>-7.07</v>
+        <v>3.45</v>
       </c>
       <c r="D21" s="2">
-        <v>2.73</v>
+        <v>1.48</v>
       </c>
       <c r="E21" s="2">
-        <v>3.35</v>
+        <v>-0.13</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="H21" s="2">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="I21" s="2">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>384.2</v>
+        <v>1782.2</v>
       </c>
       <c r="C22" s="2">
-        <v>-8.130000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="D22" s="2">
-        <v>2.67</v>
+        <v>1.65</v>
       </c>
       <c r="E22" s="2">
-        <v>3.38</v>
+        <v>-4.83</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="H22" s="2">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="I22" s="2">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>1483.9</v>
+        <v>7070</v>
       </c>
       <c r="C23" s="2">
-        <v>-11.17</v>
+        <v>1.39</v>
       </c>
       <c r="D23" s="2">
-        <v>10.59</v>
+        <v>2.9</v>
       </c>
       <c r="E23" s="2">
-        <v>0.84</v>
+        <v>-1.84</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H23" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I23" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>7177</v>
+        <v>977.7</v>
       </c>
       <c r="C24" s="2">
-        <v>-1.89</v>
+        <v>-3.32</v>
       </c>
       <c r="D24" s="2">
-        <v>3.86</v>
+        <v>-3.44</v>
       </c>
       <c r="E24" s="2">
-        <v>-2.07</v>
+        <v>2.23</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H24" s="2">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="I24" s="2">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>457.9</v>
+        <v>264.75</v>
       </c>
       <c r="C25" s="2">
-        <v>7.65</v>
+        <v>10.39</v>
       </c>
       <c r="D25" s="2">
-        <v>-0.9399999999999999</v>
+        <v>-1.23</v>
       </c>
       <c r="E25" s="2">
-        <v>-4.59</v>
+        <v>-5.78</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="H25" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="I25" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>290.55</v>
+        <v>1798.2</v>
       </c>
       <c r="C26" s="2">
-        <v>14.19</v>
+        <v>-9.4</v>
       </c>
       <c r="D26" s="2">
-        <v>-2.66</v>
+        <v>-0.22</v>
       </c>
       <c r="E26" s="2">
-        <v>-8.93</v>
+        <v>2.18</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="H26" s="2">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I26" s="2">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>250.58</v>
+        <v>1483.5</v>
       </c>
       <c r="C27" s="2">
-        <v>-12.9</v>
+        <v>-12.79</v>
       </c>
       <c r="D27" s="2">
-        <v>6.8</v>
+        <v>3.55</v>
       </c>
       <c r="E27" s="2">
-        <v>-0.52</v>
+        <v>1.79</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="H27" s="2">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="I27" s="2">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>265.4</v>
+        <v>1262.1</v>
       </c>
       <c r="C28" s="2">
-        <v>9.9</v>
+        <v>-6.05</v>
       </c>
       <c r="D28" s="2">
-        <v>0.25</v>
+        <v>0.87</v>
       </c>
       <c r="E28" s="2">
-        <v>-9.390000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="H28" s="2">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="I28" s="2">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>11482</v>
+        <v>285.65</v>
       </c>
       <c r="C29" s="2">
-        <v>-7.24</v>
+        <v>13.66</v>
       </c>
       <c r="D29" s="2">
-        <v>3.29</v>
+        <v>-4.46</v>
       </c>
       <c r="E29" s="2">
-        <v>-2.35</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H29" s="2">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="I29" s="2">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>908.25</v>
+        <v>236.89</v>
       </c>
       <c r="C30" s="2">
-        <v>-4.42</v>
+        <v>-6.33</v>
       </c>
       <c r="D30" s="2">
-        <v>4.56</v>
+        <v>1.8</v>
       </c>
       <c r="E30" s="2">
-        <v>-4.41</v>
+        <v>-1.43</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="H30" s="2">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="I30" s="2">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>1783.6</v>
+        <v>198.37</v>
       </c>
       <c r="C31" s="2">
-        <v>-10.93</v>
+        <v>-14.64</v>
       </c>
       <c r="D31" s="2">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="E31" s="2">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H31" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I31" s="2">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>1829</v>
+        <v>889.4</v>
       </c>
       <c r="C32" s="2">
-        <v>-9.289999999999999</v>
+        <v>-4.14</v>
       </c>
       <c r="D32" s="2">
-        <v>0.11</v>
+        <v>4.76</v>
       </c>
       <c r="E32" s="2">
-        <v>0.1</v>
+        <v>-4.98</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="H32" s="2">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="I32" s="2">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>204.25</v>
+        <v>377.45</v>
       </c>
       <c r="C33" s="2">
-        <v>-21.66</v>
+        <v>-10.73</v>
       </c>
       <c r="D33" s="2">
-        <v>6.76</v>
+        <v>2.89</v>
       </c>
       <c r="E33" s="2">
-        <v>1.74</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="H33" s="2">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="I33" s="2">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>947.15</v>
+        <v>361.65</v>
       </c>
       <c r="C34" s="2">
-        <v>-4.85</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="D34" s="2">
-        <v>-5.72</v>
+        <v>-3.7</v>
       </c>
       <c r="E34" s="2">
-        <v>-1.38</v>
+        <v>-7.97</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="H34" s="2">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="I34" s="2">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>1256.4</v>
+        <v>977.25</v>
       </c>
       <c r="C35" s="2">
-        <v>-10.94</v>
+        <v>-1.43</v>
       </c>
       <c r="D35" s="2">
-        <v>-2.51</v>
+        <v>0.83</v>
       </c>
       <c r="E35" s="2">
-        <v>-1.13</v>
+        <v>-5.85</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H35" s="2">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="I35" s="2">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>1830.1</v>
+        <v>408.2</v>
       </c>
       <c r="C36" s="2">
-        <v>-11.93</v>
+        <v>-0.19</v>
       </c>
       <c r="D36" s="2">
-        <v>-5.28</v>
+        <v>-1.51</v>
       </c>
       <c r="E36" s="2">
-        <v>0.55</v>
+        <v>-5.5</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I36" s="2">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>410.75</v>
+        <v>1130.9</v>
       </c>
       <c r="C37" s="2">
-        <v>0.55</v>
+        <v>-1.13</v>
       </c>
       <c r="D37" s="2">
-        <v>-6.51</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E37" s="2">
-        <v>-5.26</v>
+        <v>-10.27</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="H37" s="2">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="I37" s="2">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>4074.9</v>
+        <v>923.3</v>
       </c>
       <c r="C38" s="2">
-        <v>-2.91</v>
+        <v>-8</v>
       </c>
       <c r="D38" s="2">
-        <v>-0.38</v>
+        <v>2.18</v>
       </c>
       <c r="E38" s="2">
-        <v>-6.6</v>
+        <v>-5.39</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H38" s="2">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I38" s="2">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>965.1</v>
+        <v>13050</v>
       </c>
       <c r="C39" s="2">
-        <v>-6.93</v>
+        <v>-15.64</v>
       </c>
       <c r="D39" s="2">
-        <v>-1.16</v>
+        <v>4.7</v>
       </c>
       <c r="E39" s="2">
-        <v>-4.59</v>
+        <v>-3.21</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="I39" s="2">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>286.9</v>
+        <v>280.7</v>
       </c>
       <c r="C40" s="2">
-        <v>-8.6</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="D40" s="2">
-        <v>-3.32</v>
+        <v>-1</v>
       </c>
       <c r="E40" s="2">
-        <v>-5.27</v>
+        <v>-5.72</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
+        <v>24</v>
+      </c>
+      <c r="H40" s="2">
         <v>40</v>
       </c>
-      <c r="H40" s="2">
+      <c r="I40" s="2">
         <v>54</v>
-      </c>
-      <c r="I40" s="2">
-        <v>16</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1970,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>2153.5</v>
+        <v>1703.2</v>
       </c>
       <c r="C41" s="2">
-        <v>-8.77</v>
+        <v>-12.61</v>
       </c>
       <c r="D41" s="2">
-        <v>-0.22</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E41" s="2">
-        <v>-6.75</v>
+        <v>-5.07</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H41" s="2">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="I41" s="2">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>13127</v>
+        <v>1782.8</v>
       </c>
       <c r="C42" s="2">
-        <v>-17.23</v>
+        <v>-10.85</v>
       </c>
       <c r="D42" s="2">
-        <v>1.19</v>
+        <v>-2.9</v>
       </c>
       <c r="E42" s="2">
-        <v>-3.34</v>
+        <v>-5.39</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="H42" s="2">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="I42" s="2">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>3045.6</v>
+        <v>747.05</v>
       </c>
       <c r="C43" s="2">
-        <v>-16.75</v>
+        <v>-18.45</v>
       </c>
       <c r="D43" s="2">
-        <v>-2.66</v>
+        <v>-2.33</v>
       </c>
       <c r="E43" s="2">
-        <v>-1.96</v>
+        <v>-2.17</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H43" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I43" s="2">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>594.8</v>
+        <v>2121.5</v>
       </c>
       <c r="C44" s="2">
-        <v>-18.8</v>
+        <v>-11.95</v>
       </c>
       <c r="D44" s="2">
-        <v>-7.4</v>
+        <v>1.75</v>
       </c>
       <c r="E44" s="2">
-        <v>1.1</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H44" s="2">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I44" s="2">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2098,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>238.95</v>
+        <v>10912</v>
       </c>
       <c r="C45" s="2">
-        <v>-14.29</v>
+        <v>-11.78</v>
       </c>
       <c r="D45" s="2">
-        <v>0.57</v>
+        <v>1.37</v>
       </c>
       <c r="E45" s="2">
-        <v>-5.46</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="H45" s="2">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="I45" s="2">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,28 +2130,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>964.4</v>
+        <v>3040.5</v>
       </c>
       <c r="C46" s="2">
-        <v>-5.81</v>
+        <v>-14.19</v>
       </c>
       <c r="D46" s="2">
-        <v>-7.79</v>
+        <v>0.3</v>
       </c>
       <c r="E46" s="2">
-        <v>-8.109999999999999</v>
+        <v>-6.33</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H46" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I46" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>1321.2</v>
+        <v>1291</v>
       </c>
       <c r="C47" s="2">
-        <v>-9.380000000000001</v>
+        <v>-6.43</v>
       </c>
       <c r="D47" s="2">
-        <v>-5.47</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="E47" s="2">
-        <v>-9.699999999999999</v>
+        <v>-6.57</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="H47" s="2">
         <v>38</v>
       </c>
       <c r="I47" s="2">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,16 +2194,16 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>1160.9</v>
+        <v>1197.5</v>
       </c>
       <c r="C48" s="2">
-        <v>-31.3</v>
+        <v>-28.33</v>
       </c>
       <c r="D48" s="2">
-        <v>-5.84</v>
+        <v>-6.32</v>
       </c>
       <c r="E48" s="2">
-        <v>-0.64</v>
+        <v>1.74</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
@@ -2212,7 +2212,7 @@
         <v>8</v>
       </c>
       <c r="H48" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I48" s="2">
         <v>4</v>
@@ -2226,28 +2226,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>1183.8</v>
+        <v>575.3</v>
       </c>
       <c r="C49" s="2">
-        <v>-28.95</v>
+        <v>-19.21</v>
       </c>
       <c r="D49" s="2">
-        <v>-8.68</v>
+        <v>-4.59</v>
       </c>
       <c r="E49" s="2">
-        <v>-1.39</v>
+        <v>-7.61</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H49" s="2">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="I49" s="2">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,28 +2258,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>744.55</v>
+        <v>2198.9</v>
       </c>
       <c r="C50" s="2">
-        <v>-20.04</v>
+        <v>-29.53</v>
       </c>
       <c r="D50" s="2">
-        <v>-11.92</v>
+        <v>-7.09</v>
       </c>
       <c r="E50" s="2">
-        <v>-4.47</v>
+        <v>-6.86</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H50" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I50" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2290,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>2258.9</v>
+        <v>1154.7</v>
       </c>
       <c r="C51" s="2">
-        <v>-28.6</v>
+        <v>-31.06</v>
       </c>
       <c r="D51" s="2">
-        <v>-4.27</v>
+        <v>-14.31</v>
       </c>
       <c r="E51" s="2">
-        <v>-5.83</v>
+        <v>-3.36</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H51" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I51" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2420,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>2937.4</v>
+        <v>3048.2</v>
       </c>
       <c r="C2" s="2">
-        <v>36.16</v>
+        <v>63.51</v>
       </c>
       <c r="D2" s="2">
-        <v>48.7</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="E2" s="2">
-        <v>18.17</v>
+        <v>21.92</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2483,7 +2483,7 @@
         <v>100</v>
       </c>
       <c r="I2" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2491,16 +2491,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1804.6</v>
+        <v>1824.2</v>
       </c>
       <c r="C3" s="2">
-        <v>26.91</v>
+        <v>39.42</v>
       </c>
       <c r="D3" s="2">
-        <v>32.16</v>
+        <v>35.71</v>
       </c>
       <c r="E3" s="2">
-        <v>3.56</v>
+        <v>3.22</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
@@ -2512,7 +2512,7 @@
         <v>98</v>
       </c>
       <c r="I3" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2520,16 +2520,16 @@
         <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>1126.7</v>
+        <v>1092.6</v>
       </c>
       <c r="C4" s="2">
-        <v>20.55</v>
+        <v>14.97</v>
       </c>
       <c r="D4" s="2">
-        <v>20.29</v>
+        <v>27.84</v>
       </c>
       <c r="E4" s="2">
-        <v>8.06</v>
+        <v>6.75</v>
       </c>
       <c r="F4" s="2">
         <v>94</v>
@@ -2538,101 +2538,72 @@
         <v>94</v>
       </c>
       <c r="H4" s="2">
+        <v>94</v>
+      </c>
+      <c r="I4" s="2">
         <v>90</v>
-      </c>
-      <c r="I4" s="2">
-        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1">
-        <v>10460</v>
+        <v>8304.5</v>
       </c>
       <c r="C5" s="2">
-        <v>11.78</v>
+        <v>22.23</v>
       </c>
       <c r="D5" s="2">
-        <v>16.43</v>
+        <v>12.03</v>
       </c>
       <c r="E5" s="2">
-        <v>4.69</v>
+        <v>2.75</v>
       </c>
       <c r="F5" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G5" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H5" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I5" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1">
-        <v>8176.5</v>
+        <v>10342</v>
       </c>
       <c r="C6" s="2">
-        <v>13.16</v>
+        <v>11.41</v>
       </c>
       <c r="D6" s="2">
-        <v>9.02</v>
+        <v>17.86</v>
       </c>
       <c r="E6" s="2">
-        <v>5.67</v>
+        <v>-1.02</v>
       </c>
       <c r="F6" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G6" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H6" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I6" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="1">
-        <v>1421.5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>8.609999999999999</v>
-      </c>
-      <c r="D7" s="2">
-        <v>17.78</v>
-      </c>
-      <c r="E7" s="2">
-        <v>-2.44</v>
-      </c>
-      <c r="F7" s="2">
         <v>80</v>
       </c>
-      <c r="G7" s="2">
-        <v>86</v>
-      </c>
-      <c r="H7" s="2">
-        <v>96</v>
-      </c>
-      <c r="I7" s="2">
-        <v>98</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2640,7 +2611,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2648,7 +2619,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E6">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2656,22 +2627,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I6">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2724,16 +2695,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>2937.4</v>
+        <v>3048.2</v>
       </c>
       <c r="C2" s="2">
-        <v>36.16</v>
+        <v>63.51</v>
       </c>
       <c r="D2" s="2">
-        <v>48.7</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="E2" s="2">
-        <v>18.17</v>
+        <v>21.92</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2745,7 +2716,7 @@
         <v>100</v>
       </c>
       <c r="I2" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2753,16 +2724,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1804.6</v>
+        <v>1824.2</v>
       </c>
       <c r="C3" s="2">
-        <v>26.91</v>
+        <v>39.42</v>
       </c>
       <c r="D3" s="2">
-        <v>32.16</v>
+        <v>35.71</v>
       </c>
       <c r="E3" s="2">
-        <v>3.56</v>
+        <v>3.22</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
@@ -2774,65 +2745,65 @@
         <v>98</v>
       </c>
       <c r="I3" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>1126.7</v>
+        <v>397.8</v>
       </c>
       <c r="C4" s="2">
-        <v>20.55</v>
+        <v>15.49</v>
       </c>
       <c r="D4" s="2">
-        <v>20.29</v>
+        <v>27.83</v>
       </c>
       <c r="E4" s="2">
-        <v>8.06</v>
+        <v>14.97</v>
       </c>
       <c r="F4" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H4" s="2">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="I4" s="2">
-        <v>92</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>3122.4</v>
+        <v>1092.6</v>
       </c>
       <c r="C5" s="2">
-        <v>11.13</v>
+        <v>14.97</v>
       </c>
       <c r="D5" s="2">
-        <v>16.36</v>
+        <v>27.84</v>
       </c>
       <c r="E5" s="2">
-        <v>9.33</v>
+        <v>6.75</v>
       </c>
       <c r="F5" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="I5" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2840,16 +2811,16 @@
         <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>10460</v>
+        <v>3087.7</v>
       </c>
       <c r="C6" s="2">
-        <v>11.78</v>
+        <v>11.91</v>
       </c>
       <c r="D6" s="2">
-        <v>16.43</v>
+        <v>21.11</v>
       </c>
       <c r="E6" s="2">
-        <v>4.69</v>
+        <v>3.47</v>
       </c>
       <c r="F6" s="2">
         <v>90</v>
@@ -2858,10 +2829,10 @@
         <v>92</v>
       </c>
       <c r="H6" s="2">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I6" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2869,28 +2840,28 @@
         <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>2671.6</v>
+        <v>8304.5</v>
       </c>
       <c r="C7" s="2">
-        <v>-3.09</v>
+        <v>22.23</v>
       </c>
       <c r="D7" s="2">
-        <v>19.36</v>
+        <v>12.03</v>
       </c>
       <c r="E7" s="2">
-        <v>9.130000000000001</v>
+        <v>2.75</v>
       </c>
       <c r="F7" s="2">
         <v>88</v>
       </c>
       <c r="G7" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H7" s="2">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="I7" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2898,28 +2869,28 @@
         <v>16</v>
       </c>
       <c r="B8" s="1">
-        <v>8176.5</v>
+        <v>2774.2</v>
       </c>
       <c r="C8" s="2">
-        <v>13.16</v>
+        <v>10.79</v>
       </c>
       <c r="D8" s="2">
-        <v>9.02</v>
+        <v>23.64</v>
       </c>
       <c r="E8" s="2">
-        <v>5.67</v>
+        <v>-0.47</v>
       </c>
       <c r="F8" s="2">
         <v>86</v>
       </c>
       <c r="G8" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H8" s="2">
         <v>84</v>
       </c>
       <c r="I8" s="2">
-        <v>84</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2927,57 +2898,57 @@
         <v>17</v>
       </c>
       <c r="B9" s="1">
-        <v>4224</v>
+        <v>2686.7</v>
       </c>
       <c r="C9" s="2">
-        <v>8.32</v>
+        <v>-0.63</v>
       </c>
       <c r="D9" s="2">
-        <v>16.22</v>
+        <v>21.17</v>
       </c>
       <c r="E9" s="2">
-        <v>1.58</v>
+        <v>4.7</v>
       </c>
       <c r="F9" s="2">
         <v>84</v>
       </c>
       <c r="G9" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H9" s="2">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="I9" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1">
-        <v>1421.5</v>
+        <v>10342</v>
       </c>
       <c r="C10" s="2">
-        <v>8.609999999999999</v>
+        <v>11.41</v>
       </c>
       <c r="D10" s="2">
-        <v>17.78</v>
+        <v>17.86</v>
       </c>
       <c r="E10" s="2">
-        <v>-2.44</v>
+        <v>-1.02</v>
       </c>
       <c r="F10" s="2">
+        <v>82</v>
+      </c>
+      <c r="G10" s="2">
+        <v>90</v>
+      </c>
+      <c r="H10" s="2">
+        <v>92</v>
+      </c>
+      <c r="I10" s="2">
         <v>80</v>
-      </c>
-      <c r="G10" s="2">
-        <v>86</v>
-      </c>
-      <c r="H10" s="2">
-        <v>96</v>
-      </c>
-      <c r="I10" s="2">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3056,10 +3027,10 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D2" s="2">
         <v>48</v>
@@ -3070,10 +3041,10 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
+        <v>36</v>
+      </c>
+      <c r="C3" s="2">
         <v>46</v>
-      </c>
-      <c r="C3" s="2">
-        <v>50</v>
       </c>
       <c r="D3" s="2">
         <v>48</v>
@@ -3084,13 +3055,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2">
         <v>50</v>
       </c>
       <c r="D4" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3098,13 +3069,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C5" s="2">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-06-05</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-06-05</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-06-05</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-06-05</t>
+    <t>Price_2026-06-12</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-06-12</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-06-12</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-06-12</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-06-12</t>
   </si>
   <si>
     <t>RS_Score_2026-06-05</t>
@@ -43,9 +46,6 @@
     <t>RS_Score_2026-05-22</t>
   </si>
   <si>
-    <t>RS_Score_2026-05-15</t>
-  </si>
-  <si>
     <t>ADANIENT</t>
   </si>
   <si>
@@ -55,141 +55,141 @@
     <t>TMPV</t>
   </si>
   <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
     <t>HINDALCO</t>
   </si>
   <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
   </si>
   <si>
     <t>COALINDIA</t>
   </si>
   <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>TITAN</t>
-  </si>
-  <si>
     <t>ETERNAL</t>
   </si>
   <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>SBIN</t>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
   </si>
   <si>
     <t>ONGC</t>
   </si>
   <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
     <t>TCS</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
     <t>2026-06-05</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-05-22</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3048.2</v>
+        <v>2921.6</v>
       </c>
       <c r="C2" s="2">
-        <v>63.51</v>
+        <v>46.48</v>
       </c>
       <c r="D2" s="2">
-        <v>67.68000000000001</v>
+        <v>59.36</v>
       </c>
       <c r="E2" s="2">
-        <v>21.92</v>
+        <v>8.67</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -754,16 +754,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1824.2</v>
+        <v>1812.9</v>
       </c>
       <c r="C3" s="2">
-        <v>39.42</v>
+        <v>29.75</v>
       </c>
       <c r="D3" s="2">
-        <v>35.71</v>
+        <v>32.15</v>
       </c>
       <c r="E3" s="2">
-        <v>3.22</v>
+        <v>1.84</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
@@ -786,16 +786,16 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>397.8</v>
+        <v>390</v>
       </c>
       <c r="C4" s="2">
-        <v>15.49</v>
+        <v>7.47</v>
       </c>
       <c r="D4" s="2">
-        <v>27.83</v>
+        <v>28.59</v>
       </c>
       <c r="E4" s="2">
-        <v>14.97</v>
+        <v>10.43</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
@@ -804,10 +804,10 @@
         <v>96</v>
       </c>
       <c r="H4" s="2">
+        <v>96</v>
+      </c>
+      <c r="I4" s="2">
         <v>70</v>
-      </c>
-      <c r="I4" s="2">
-        <v>58</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1092.6</v>
+        <v>2747.4</v>
       </c>
       <c r="C5" s="2">
-        <v>14.97</v>
+        <v>14.38</v>
       </c>
       <c r="D5" s="2">
-        <v>27.84</v>
+        <v>26.67</v>
       </c>
       <c r="E5" s="2">
-        <v>6.75</v>
+        <v>5.1</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H5" s="2">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="I5" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>1401.3</v>
+        <v>8498</v>
       </c>
       <c r="C6" s="2">
-        <v>7.56</v>
+        <v>22.73</v>
       </c>
       <c r="D6" s="2">
-        <v>16</v>
+        <v>16.13</v>
       </c>
       <c r="E6" s="2">
-        <v>8.4</v>
+        <v>5.95</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H6" s="2">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="I6" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>3087.7</v>
+        <v>3105.5</v>
       </c>
       <c r="C7" s="2">
-        <v>11.91</v>
+        <v>11.93</v>
       </c>
       <c r="D7" s="2">
         <v>21.11</v>
       </c>
       <c r="E7" s="2">
-        <v>3.47</v>
+        <v>5.49</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
+        <v>90</v>
+      </c>
+      <c r="H7" s="2">
         <v>92</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>96</v>
-      </c>
-      <c r="I7" s="2">
-        <v>74</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>8304.5</v>
+        <v>1356.3</v>
       </c>
       <c r="C8" s="2">
-        <v>22.23</v>
+        <v>3.42</v>
       </c>
       <c r="D8" s="2">
-        <v>12.03</v>
+        <v>13.22</v>
       </c>
       <c r="E8" s="2">
-        <v>2.75</v>
+        <v>9.56</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="H8" s="2">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="I8" s="2">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>2774.2</v>
+        <v>2755.3</v>
       </c>
       <c r="C9" s="2">
-        <v>10.79</v>
+        <v>11.24</v>
       </c>
       <c r="D9" s="2">
-        <v>23.64</v>
+        <v>16.57</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.47</v>
+        <v>2.65</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H9" s="2">
         <v>84</v>
       </c>
       <c r="I9" s="2">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>2686.7</v>
+        <v>4709.7</v>
       </c>
       <c r="C10" s="2">
-        <v>-0.63</v>
+        <v>0.48</v>
       </c>
       <c r="D10" s="2">
-        <v>21.17</v>
+        <v>12.31</v>
       </c>
       <c r="E10" s="2">
-        <v>4.7</v>
+        <v>10.15</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="H10" s="2">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="I10" s="2">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>10342</v>
+        <v>7312</v>
       </c>
       <c r="C11" s="2">
-        <v>11.41</v>
+        <v>4.67</v>
       </c>
       <c r="D11" s="2">
-        <v>17.86</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E11" s="2">
-        <v>-1.02</v>
+        <v>5.77</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="H11" s="2">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="I11" s="2">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,16 +1042,16 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1284</v>
+        <v>4049.3</v>
       </c>
       <c r="C12" s="2">
-        <v>9.74</v>
+        <v>4.27</v>
       </c>
       <c r="D12" s="2">
-        <v>13.26</v>
+        <v>13.17</v>
       </c>
       <c r="E12" s="2">
-        <v>1.69</v>
+        <v>4.37</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
@@ -1060,10 +1060,10 @@
         <v>76</v>
       </c>
       <c r="H12" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I12" s="2">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>472.3</v>
+        <v>10063</v>
       </c>
       <c r="C13" s="2">
-        <v>14.37</v>
+        <v>7.46</v>
       </c>
       <c r="D13" s="2">
-        <v>6.83</v>
+        <v>16.51</v>
       </c>
       <c r="E13" s="2">
-        <v>1.69</v>
+        <v>0.06</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H13" s="2">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="I13" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>3953.2</v>
+        <v>1340.8</v>
       </c>
       <c r="C14" s="2">
-        <v>6.62</v>
+        <v>-0.89</v>
       </c>
       <c r="D14" s="2">
-        <v>13.51</v>
+        <v>10.28</v>
       </c>
       <c r="E14" s="2">
-        <v>1.31</v>
+        <v>7.17</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="H14" s="2">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="I14" s="2">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>4260.2</v>
+        <v>1297.6</v>
       </c>
       <c r="C15" s="2">
-        <v>5.93</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="D15" s="2">
-        <v>9.25</v>
+        <v>13.69</v>
       </c>
       <c r="E15" s="2">
-        <v>1.3</v>
+        <v>0.37</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="H15" s="2">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="I15" s="2">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>256.5</v>
+        <v>1389.4</v>
       </c>
       <c r="C16" s="2">
-        <v>-0.85</v>
+        <v>6.93</v>
       </c>
       <c r="D16" s="2">
-        <v>7.8</v>
+        <v>17.61</v>
       </c>
       <c r="E16" s="2">
-        <v>4.32</v>
+        <v>-1.67</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="H16" s="2">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="I16" s="2">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>206.77</v>
+        <v>1017.15</v>
       </c>
       <c r="C17" s="2">
-        <v>10.21</v>
+        <v>0.66</v>
       </c>
       <c r="D17" s="2">
-        <v>8.380000000000001</v>
+        <v>1.68</v>
       </c>
       <c r="E17" s="2">
-        <v>-2.5</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="H17" s="2">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="I17" s="2">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>1386.2</v>
+        <v>403.3</v>
       </c>
       <c r="C18" s="2">
-        <v>7.72</v>
+        <v>-1.2</v>
       </c>
       <c r="D18" s="2">
-        <v>17.16</v>
+        <v>12.65</v>
       </c>
       <c r="E18" s="2">
-        <v>-6.46</v>
+        <v>2.94</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="H18" s="2">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="I18" s="2">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>4481.3</v>
+        <v>1021.6</v>
       </c>
       <c r="C19" s="2">
-        <v>-4.74</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="D19" s="2">
-        <v>7.96</v>
+        <v>11.5</v>
       </c>
       <c r="E19" s="2">
-        <v>4.23</v>
+        <v>-2.99</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="H19" s="2">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="I19" s="2">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>1272.3</v>
+        <v>1375.7</v>
       </c>
       <c r="C20" s="2">
-        <v>1.14</v>
+        <v>5.72</v>
       </c>
       <c r="D20" s="2">
-        <v>6.67</v>
+        <v>15.48</v>
       </c>
       <c r="E20" s="2">
-        <v>0</v>
+        <v>-3.91</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H20" s="2">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="I20" s="2">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>1278.2</v>
+        <v>918.3</v>
       </c>
       <c r="C21" s="2">
-        <v>3.45</v>
+        <v>1.62</v>
       </c>
       <c r="D21" s="2">
-        <v>1.48</v>
+        <v>11.06</v>
       </c>
       <c r="E21" s="2">
-        <v>-0.13</v>
+        <v>-0.3</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="H21" s="2">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="I21" s="2">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>1782.2</v>
+        <v>954.95</v>
       </c>
       <c r="C22" s="2">
-        <v>9.92</v>
+        <v>-0.74</v>
       </c>
       <c r="D22" s="2">
-        <v>1.65</v>
+        <v>7.11</v>
       </c>
       <c r="E22" s="2">
-        <v>-4.83</v>
+        <v>2.28</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="H22" s="2">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="I22" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>7070</v>
+        <v>4184</v>
       </c>
       <c r="C23" s="2">
-        <v>1.39</v>
+        <v>5.84</v>
       </c>
       <c r="D23" s="2">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="E23" s="2">
-        <v>-1.84</v>
+        <v>0.34</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="H23" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I23" s="2">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>977.7</v>
+        <v>1807.7</v>
       </c>
       <c r="C24" s="2">
-        <v>-3.32</v>
+        <v>11.77</v>
       </c>
       <c r="D24" s="2">
-        <v>-3.44</v>
+        <v>6.74</v>
       </c>
       <c r="E24" s="2">
-        <v>2.23</v>
+        <v>-5.15</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="H24" s="2">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="I24" s="2">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>264.75</v>
+        <v>1275.4</v>
       </c>
       <c r="C25" s="2">
-        <v>10.39</v>
+        <v>7.86</v>
       </c>
       <c r="D25" s="2">
-        <v>-1.23</v>
+        <v>4.77</v>
       </c>
       <c r="E25" s="2">
-        <v>-5.78</v>
+        <v>-4.19</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H25" s="2">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="I25" s="2">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,25 +1490,25 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>1798.2</v>
+        <v>1012.45</v>
       </c>
       <c r="C26" s="2">
-        <v>-9.4</v>
+        <v>5.67</v>
       </c>
       <c r="D26" s="2">
-        <v>-0.22</v>
+        <v>7.18</v>
       </c>
       <c r="E26" s="2">
-        <v>2.18</v>
+        <v>-4.36</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H26" s="2">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="I26" s="2">
         <v>62</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>1483.5</v>
+        <v>13366</v>
       </c>
       <c r="C27" s="2">
-        <v>-12.79</v>
+        <v>-7.08</v>
       </c>
       <c r="D27" s="2">
-        <v>3.55</v>
+        <v>5.82</v>
       </c>
       <c r="E27" s="2">
-        <v>1.79</v>
+        <v>2.69</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="H27" s="2">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I27" s="2">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>1262.1</v>
+        <v>197.86</v>
       </c>
       <c r="C28" s="2">
-        <v>-6.05</v>
+        <v>7.12</v>
       </c>
       <c r="D28" s="2">
-        <v>0.87</v>
+        <v>4.02</v>
       </c>
       <c r="E28" s="2">
-        <v>-0.34</v>
+        <v>-3.7</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="H28" s="2">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="I28" s="2">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>285.65</v>
+        <v>235.89</v>
       </c>
       <c r="C29" s="2">
-        <v>13.66</v>
+        <v>-3.36</v>
       </c>
       <c r="D29" s="2">
-        <v>-4.46</v>
+        <v>2.79</v>
       </c>
       <c r="E29" s="2">
-        <v>-8.119999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="H29" s="2">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="I29" s="2">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>236.89</v>
+        <v>284.8</v>
       </c>
       <c r="C30" s="2">
-        <v>-6.33</v>
+        <v>6.51</v>
       </c>
       <c r="D30" s="2">
-        <v>1.8</v>
+        <v>-1.78</v>
       </c>
       <c r="E30" s="2">
-        <v>-1.43</v>
+        <v>-3.96</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="I30" s="2">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>198.37</v>
+        <v>443.5</v>
       </c>
       <c r="C31" s="2">
-        <v>-14.64</v>
+        <v>6.11</v>
       </c>
       <c r="D31" s="2">
-        <v>5.1</v>
+        <v>-1.3</v>
       </c>
       <c r="E31" s="2">
-        <v>0.86</v>
+        <v>-4.03</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="H31" s="2">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I31" s="2">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>889.4</v>
+        <v>243.8</v>
       </c>
       <c r="C32" s="2">
-        <v>-4.14</v>
+        <v>-10.58</v>
       </c>
       <c r="D32" s="2">
-        <v>4.76</v>
+        <v>5.21</v>
       </c>
       <c r="E32" s="2">
-        <v>-4.98</v>
+        <v>0.99</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="H32" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I32" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>377.45</v>
+        <v>2168.8</v>
       </c>
       <c r="C33" s="2">
-        <v>-10.73</v>
+        <v>-8</v>
       </c>
       <c r="D33" s="2">
-        <v>2.89</v>
+        <v>5.01</v>
       </c>
       <c r="E33" s="2">
-        <v>-0.9399999999999999</v>
+        <v>-3.79</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="H33" s="2">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I33" s="2">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>361.65</v>
+        <v>772.45</v>
       </c>
       <c r="C34" s="2">
-        <v>8.220000000000001</v>
+        <v>-16.77</v>
       </c>
       <c r="D34" s="2">
-        <v>-3.7</v>
+        <v>2.87</v>
       </c>
       <c r="E34" s="2">
-        <v>-7.97</v>
+        <v>0.49</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="H34" s="2">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="I34" s="2">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>977.25</v>
+        <v>3042.9</v>
       </c>
       <c r="C35" s="2">
-        <v>-1.43</v>
+        <v>-12.14</v>
       </c>
       <c r="D35" s="2">
-        <v>0.83</v>
+        <v>1.04</v>
       </c>
       <c r="E35" s="2">
-        <v>-5.85</v>
+        <v>-1.32</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H35" s="2">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="I35" s="2">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>408.2</v>
+        <v>11117</v>
       </c>
       <c r="C36" s="2">
-        <v>-0.19</v>
+        <v>-11.31</v>
       </c>
       <c r="D36" s="2">
-        <v>-1.51</v>
+        <v>4.68</v>
       </c>
       <c r="E36" s="2">
-        <v>-5.5</v>
+        <v>-3.84</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H36" s="2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="I36" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>1130.9</v>
+        <v>1100.7</v>
       </c>
       <c r="C37" s="2">
-        <v>-1.13</v>
+        <v>-1.37</v>
       </c>
       <c r="D37" s="2">
-        <v>8.300000000000001</v>
+        <v>6.53</v>
       </c>
       <c r="E37" s="2">
-        <v>-10.27</v>
+        <v>-9.83</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
+        <v>30</v>
+      </c>
+      <c r="H37" s="2">
         <v>74</v>
       </c>
-      <c r="H37" s="2">
+      <c r="I37" s="2">
         <v>72</v>
-      </c>
-      <c r="I37" s="2">
-        <v>88</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>923.3</v>
+        <v>1293</v>
       </c>
       <c r="C38" s="2">
-        <v>-8</v>
+        <v>-6.58</v>
       </c>
       <c r="D38" s="2">
-        <v>2.18</v>
+        <v>-3.82</v>
       </c>
       <c r="E38" s="2">
-        <v>-5.39</v>
+        <v>-2.76</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="H38" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I38" s="2">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>13050</v>
+        <v>285.1</v>
       </c>
       <c r="C39" s="2">
-        <v>-15.64</v>
+        <v>-4.99</v>
       </c>
       <c r="D39" s="2">
-        <v>4.7</v>
+        <v>0.01</v>
       </c>
       <c r="E39" s="2">
-        <v>-3.21</v>
+        <v>-5.57</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H39" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I39" s="2">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>280.7</v>
+        <v>1689.1</v>
       </c>
       <c r="C40" s="2">
-        <v>-8.970000000000001</v>
+        <v>-12.49</v>
       </c>
       <c r="D40" s="2">
-        <v>-1</v>
+        <v>2.95</v>
       </c>
       <c r="E40" s="2">
-        <v>-5.72</v>
+        <v>-3.65</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H40" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I40" s="2">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1970,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>1703.2</v>
+        <v>1822.5</v>
       </c>
       <c r="C41" s="2">
-        <v>-12.61</v>
+        <v>-7.27</v>
       </c>
       <c r="D41" s="2">
-        <v>-0.07000000000000001</v>
+        <v>1.83</v>
       </c>
       <c r="E41" s="2">
-        <v>-5.07</v>
+        <v>-5.96</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H41" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I41" s="2">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>1782.8</v>
+        <v>353.9</v>
       </c>
       <c r="C42" s="2">
-        <v>-10.85</v>
+        <v>1.78</v>
       </c>
       <c r="D42" s="2">
-        <v>-2.9</v>
+        <v>-1.6</v>
       </c>
       <c r="E42" s="2">
-        <v>-5.39</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H42" s="2">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="I42" s="2">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>747.05</v>
+        <v>1429.2</v>
       </c>
       <c r="C43" s="2">
-        <v>-18.45</v>
+        <v>-17.1</v>
       </c>
       <c r="D43" s="2">
-        <v>-2.33</v>
+        <v>-0.85</v>
       </c>
       <c r="E43" s="2">
-        <v>-2.17</v>
+        <v>-0.06</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="H43" s="2">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="I43" s="2">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>2121.5</v>
+        <v>406.5</v>
       </c>
       <c r="C44" s="2">
-        <v>-11.95</v>
+        <v>-7.03</v>
       </c>
       <c r="D44" s="2">
-        <v>1.75</v>
+        <v>-3.58</v>
       </c>
       <c r="E44" s="2">
-        <v>-8.050000000000001</v>
+        <v>-4.71</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H44" s="2">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I44" s="2">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2098,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>10912</v>
+        <v>1706</v>
       </c>
       <c r="C45" s="2">
-        <v>-11.78</v>
+        <v>-14.62</v>
       </c>
       <c r="D45" s="2">
-        <v>1.37</v>
+        <v>-3.83</v>
       </c>
       <c r="E45" s="2">
-        <v>-8.039999999999999</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
+        <v>20</v>
+      </c>
+      <c r="H45" s="2">
+        <v>32</v>
+      </c>
+      <c r="I45" s="2">
         <v>46</v>
-      </c>
-      <c r="H45" s="2">
-        <v>44</v>
-      </c>
-      <c r="I45" s="2">
-        <v>42</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,28 +2130,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>3040.5</v>
+        <v>555.35</v>
       </c>
       <c r="C46" s="2">
-        <v>-14.19</v>
+        <v>-22.6</v>
       </c>
       <c r="D46" s="2">
-        <v>0.3</v>
+        <v>-1.9</v>
       </c>
       <c r="E46" s="2">
-        <v>-6.33</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H46" s="2">
         <v>16</v>
       </c>
       <c r="I46" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>1291</v>
+        <v>1116.4</v>
       </c>
       <c r="C47" s="2">
-        <v>-6.43</v>
+        <v>-30</v>
       </c>
       <c r="D47" s="2">
-        <v>-8.130000000000001</v>
+        <v>-12.32</v>
       </c>
       <c r="E47" s="2">
-        <v>-6.57</v>
+        <v>-0.17</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H47" s="2">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="I47" s="2">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,28 +2194,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>1197.5</v>
+        <v>180.14</v>
       </c>
       <c r="C48" s="2">
-        <v>-28.33</v>
+        <v>-25.65</v>
       </c>
       <c r="D48" s="2">
-        <v>-6.32</v>
+        <v>-7.58</v>
       </c>
       <c r="E48" s="2">
-        <v>1.74</v>
+        <v>-6.26</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="H48" s="2">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="I48" s="2">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,28 +2226,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>575.3</v>
+        <v>246.2</v>
       </c>
       <c r="C49" s="2">
-        <v>-19.21</v>
+        <v>-0.77</v>
       </c>
       <c r="D49" s="2">
-        <v>-4.59</v>
+        <v>-14.28</v>
       </c>
       <c r="E49" s="2">
-        <v>-7.61</v>
+        <v>-17.16</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="H49" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I49" s="2">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,28 +2258,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>2198.9</v>
+        <v>2161.4</v>
       </c>
       <c r="C50" s="2">
-        <v>-29.53</v>
+        <v>-30.88</v>
       </c>
       <c r="D50" s="2">
-        <v>-7.09</v>
+        <v>-10.61</v>
       </c>
       <c r="E50" s="2">
-        <v>-6.86</v>
+        <v>-4.05</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
+        <v>4</v>
+      </c>
+      <c r="H50" s="2">
         <v>2</v>
       </c>
-      <c r="H50" s="2">
+      <c r="I50" s="2">
         <v>4</v>
-      </c>
-      <c r="I50" s="2">
-        <v>6</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,25 +2290,25 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>1154.7</v>
+        <v>1109.6</v>
       </c>
       <c r="C51" s="2">
-        <v>-31.06</v>
+        <v>-32.56</v>
       </c>
       <c r="D51" s="2">
-        <v>-14.31</v>
+        <v>-19.35</v>
       </c>
       <c r="E51" s="2">
-        <v>-3.36</v>
+        <v>-3.23</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
+        <v>2</v>
+      </c>
+      <c r="H51" s="2">
         <v>6</v>
-      </c>
-      <c r="H51" s="2">
-        <v>2</v>
       </c>
       <c r="I51" s="2">
         <v>2</v>
@@ -2420,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3048.2</v>
+        <v>2921.6</v>
       </c>
       <c r="C2" s="2">
-        <v>63.51</v>
+        <v>46.48</v>
       </c>
       <c r="D2" s="2">
-        <v>67.68000000000001</v>
+        <v>59.36</v>
       </c>
       <c r="E2" s="2">
-        <v>21.92</v>
+        <v>8.67</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2491,16 +2491,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1824.2</v>
+        <v>1812.9</v>
       </c>
       <c r="C3" s="2">
-        <v>39.42</v>
+        <v>29.75</v>
       </c>
       <c r="D3" s="2">
-        <v>35.71</v>
+        <v>32.15</v>
       </c>
       <c r="E3" s="2">
-        <v>3.22</v>
+        <v>1.84</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
@@ -2520,77 +2520,77 @@
         <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>1092.6</v>
+        <v>2747.4</v>
       </c>
       <c r="C4" s="2">
-        <v>14.97</v>
+        <v>14.38</v>
       </c>
       <c r="D4" s="2">
-        <v>27.84</v>
+        <v>26.67</v>
       </c>
       <c r="E4" s="2">
-        <v>6.75</v>
+        <v>5.1</v>
       </c>
       <c r="F4" s="2">
         <v>94</v>
       </c>
       <c r="G4" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H4" s="2">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="I4" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>8304.5</v>
+        <v>8498</v>
       </c>
       <c r="C5" s="2">
-        <v>22.23</v>
+        <v>22.73</v>
       </c>
       <c r="D5" s="2">
-        <v>12.03</v>
+        <v>16.13</v>
       </c>
       <c r="E5" s="2">
-        <v>2.75</v>
+        <v>5.95</v>
       </c>
       <c r="F5" s="2">
+        <v>92</v>
+      </c>
+      <c r="G5" s="2">
         <v>88</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <v>86</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>88</v>
-      </c>
-      <c r="I5" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>10342</v>
+        <v>3105.5</v>
       </c>
       <c r="C6" s="2">
-        <v>11.41</v>
+        <v>11.93</v>
       </c>
       <c r="D6" s="2">
-        <v>17.86</v>
+        <v>21.11</v>
       </c>
       <c r="E6" s="2">
-        <v>-1.02</v>
+        <v>5.49</v>
       </c>
       <c r="F6" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G6" s="2">
         <v>90</v>
@@ -2599,11 +2599,40 @@
         <v>92</v>
       </c>
       <c r="I6" s="2">
-        <v>80</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2755.3</v>
+      </c>
+      <c r="C7" s="2">
+        <v>11.24</v>
+      </c>
+      <c r="D7" s="2">
+        <v>16.57</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2.65</v>
+      </c>
+      <c r="F7" s="2">
+        <v>86</v>
+      </c>
+      <c r="G7" s="2">
+        <v>86</v>
+      </c>
+      <c r="H7" s="2">
+        <v>84</v>
+      </c>
+      <c r="I7" s="2">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2611,7 +2640,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2619,7 +2648,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E6">
+  <conditionalFormatting sqref="E2:E7">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2627,22 +2656,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
+  <conditionalFormatting sqref="F2:F7">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G6">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H6">
+  <conditionalFormatting sqref="H2:H7">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
+  <conditionalFormatting sqref="I2:I7">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2653,7 +2682,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2695,16 +2724,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3048.2</v>
+        <v>2921.6</v>
       </c>
       <c r="C2" s="2">
-        <v>63.51</v>
+        <v>46.48</v>
       </c>
       <c r="D2" s="2">
-        <v>67.68000000000001</v>
+        <v>59.36</v>
       </c>
       <c r="E2" s="2">
-        <v>21.92</v>
+        <v>8.67</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2724,16 +2753,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1824.2</v>
+        <v>1812.9</v>
       </c>
       <c r="C3" s="2">
-        <v>39.42</v>
+        <v>29.75</v>
       </c>
       <c r="D3" s="2">
-        <v>35.71</v>
+        <v>32.15</v>
       </c>
       <c r="E3" s="2">
-        <v>3.22</v>
+        <v>1.84</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
@@ -2753,16 +2782,16 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>397.8</v>
+        <v>390</v>
       </c>
       <c r="C4" s="2">
-        <v>15.49</v>
+        <v>7.47</v>
       </c>
       <c r="D4" s="2">
-        <v>27.83</v>
+        <v>28.59</v>
       </c>
       <c r="E4" s="2">
-        <v>14.97</v>
+        <v>10.43</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
@@ -2771,10 +2800,10 @@
         <v>96</v>
       </c>
       <c r="H4" s="2">
+        <v>96</v>
+      </c>
+      <c r="I4" s="2">
         <v>70</v>
-      </c>
-      <c r="I4" s="2">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2782,86 +2811,86 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1092.6</v>
+        <v>2747.4</v>
       </c>
       <c r="C5" s="2">
-        <v>14.97</v>
+        <v>14.38</v>
       </c>
       <c r="D5" s="2">
-        <v>27.84</v>
+        <v>26.67</v>
       </c>
       <c r="E5" s="2">
-        <v>6.75</v>
+        <v>5.1</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H5" s="2">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="I5" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>3087.7</v>
+        <v>8498</v>
       </c>
       <c r="C6" s="2">
-        <v>11.91</v>
+        <v>22.73</v>
       </c>
       <c r="D6" s="2">
-        <v>21.11</v>
+        <v>16.13</v>
       </c>
       <c r="E6" s="2">
-        <v>3.47</v>
+        <v>5.95</v>
       </c>
       <c r="F6" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H6" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="I6" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>8304.5</v>
+        <v>3105.5</v>
       </c>
       <c r="C7" s="2">
-        <v>22.23</v>
+        <v>11.93</v>
       </c>
       <c r="D7" s="2">
-        <v>12.03</v>
+        <v>21.11</v>
       </c>
       <c r="E7" s="2">
-        <v>2.75</v>
+        <v>5.49</v>
       </c>
       <c r="F7" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H7" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I7" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2869,90 +2898,32 @@
         <v>16</v>
       </c>
       <c r="B8" s="1">
-        <v>2774.2</v>
+        <v>2755.3</v>
       </c>
       <c r="C8" s="2">
-        <v>10.79</v>
+        <v>11.24</v>
       </c>
       <c r="D8" s="2">
-        <v>23.64</v>
+        <v>16.57</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.47</v>
+        <v>2.65</v>
       </c>
       <c r="F8" s="2">
         <v>86</v>
       </c>
       <c r="G8" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H8" s="2">
         <v>84</v>
       </c>
       <c r="I8" s="2">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1">
-        <v>2686.7</v>
-      </c>
-      <c r="C9" s="2">
-        <v>-0.63</v>
-      </c>
-      <c r="D9" s="2">
-        <v>21.17</v>
-      </c>
-      <c r="E9" s="2">
-        <v>4.7</v>
-      </c>
-      <c r="F9" s="2">
         <v>84</v>
       </c>
-      <c r="G9" s="2">
-        <v>88</v>
-      </c>
-      <c r="H9" s="2">
-        <v>80</v>
-      </c>
-      <c r="I9" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1">
-        <v>10342</v>
-      </c>
-      <c r="C10" s="2">
-        <v>11.41</v>
-      </c>
-      <c r="D10" s="2">
-        <v>17.86</v>
-      </c>
-      <c r="E10" s="2">
-        <v>-1.02</v>
-      </c>
-      <c r="F10" s="2">
-        <v>82</v>
-      </c>
-      <c r="G10" s="2">
-        <v>90</v>
-      </c>
-      <c r="H10" s="2">
-        <v>92</v>
-      </c>
-      <c r="I10" s="2">
-        <v>80</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C10">
+  <conditionalFormatting sqref="C2:C8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2960,7 +2931,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D10">
+  <conditionalFormatting sqref="D2:D8">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2968,7 +2939,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E10">
+  <conditionalFormatting sqref="E2:E8">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2976,22 +2947,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F10">
+  <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G10">
+  <conditionalFormatting sqref="G2:G8">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H10">
+  <conditionalFormatting sqref="H2:H8">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I10">
+  <conditionalFormatting sqref="I2:I8">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -3027,13 +2998,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D2" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3041,10 +3012,10 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
+        <v>32</v>
+      </c>
+      <c r="C3" s="2">
         <v>36</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46</v>
       </c>
       <c r="D3" s="2">
         <v>48</v>
@@ -3055,10 +3026,10 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2">
         <v>46</v>
-      </c>
-      <c r="C4" s="2">
-        <v>50</v>
       </c>
       <c r="D4" s="2">
         <v>48</v>
@@ -3069,7 +3040,7 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2">
         <v>50</v>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-06-12</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-06-12</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-06-12</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-06-12</t>
+    <t>Price_2026-06-19</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-06-19</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-06-19</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-06-19</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-06-19</t>
   </si>
   <si>
     <t>RS_Score_2026-06-12</t>
@@ -43,159 +46,156 @@
     <t>RS_Score_2026-05-29</t>
   </si>
   <si>
-    <t>RS_Score_2026-05-22</t>
-  </si>
-  <si>
     <t>ADANIENT</t>
   </si>
   <si>
+    <t>TRENT</t>
+  </si>
+  <si>
     <t>ADANIPORTS</t>
   </si>
   <si>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>ETERNAL</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
     <t>TMPV</t>
   </si>
   <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
   </si>
   <si>
     <t>HINDALCO</t>
   </si>
   <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>TITAN</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>ETERNAL</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>NTPC</t>
   </si>
   <si>
     <t>HDFCBANK</t>
   </si>
   <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
     <t>M&amp;M</t>
   </si>
   <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>BEL</t>
+    <t>HDFCLIFE</t>
   </si>
   <si>
     <t>SBILIFE</t>
   </si>
   <si>
-    <t>HDFCLIFE</t>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>HCLTECH</t>
+  </si>
+  <si>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
   </si>
   <si>
     <t>INFY</t>
   </si>
   <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>HCLTECH</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
     <t>2026-06-12</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-05-29</t>
-  </si>
-  <si>
-    <t>2026-05-22</t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>2921.6</v>
+        <v>3038.4</v>
       </c>
       <c r="C2" s="2">
-        <v>46.48</v>
+        <v>35.09</v>
       </c>
       <c r="D2" s="2">
-        <v>59.36</v>
+        <v>45.67</v>
       </c>
       <c r="E2" s="2">
-        <v>8.67</v>
+        <v>6.67</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1812.9</v>
+        <v>3205.8</v>
       </c>
       <c r="C3" s="2">
-        <v>29.75</v>
+        <v>15.45</v>
       </c>
       <c r="D3" s="2">
-        <v>32.15</v>
+        <v>22.96</v>
       </c>
       <c r="E3" s="2">
-        <v>1.84</v>
+        <v>12</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="I3" s="2">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>390</v>
+        <v>1835.3</v>
       </c>
       <c r="C4" s="2">
-        <v>7.47</v>
+        <v>18.01</v>
       </c>
       <c r="D4" s="2">
-        <v>28.59</v>
+        <v>24.93</v>
       </c>
       <c r="E4" s="2">
-        <v>10.43</v>
+        <v>2.23</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>2747.4</v>
+        <v>1094.75</v>
       </c>
       <c r="C5" s="2">
-        <v>14.38</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="D5" s="2">
-        <v>26.67</v>
+        <v>14.83</v>
       </c>
       <c r="E5" s="2">
-        <v>5.1</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="H5" s="2">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="I5" s="2">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>8498</v>
+        <v>5021.5</v>
       </c>
       <c r="C6" s="2">
-        <v>22.73</v>
+        <v>1.16</v>
       </c>
       <c r="D6" s="2">
-        <v>16.13</v>
+        <v>10.26</v>
       </c>
       <c r="E6" s="2">
-        <v>5.95</v>
+        <v>11.54</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H6" s="2">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="I6" s="2">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>3105.5</v>
+        <v>2732.9</v>
       </c>
       <c r="C7" s="2">
-        <v>11.93</v>
+        <v>13.05</v>
       </c>
       <c r="D7" s="2">
-        <v>21.11</v>
+        <v>15.77</v>
       </c>
       <c r="E7" s="2">
-        <v>5.49</v>
+        <v>2.83</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="I7" s="2">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>1356.3</v>
+        <v>8489.5</v>
       </c>
       <c r="C8" s="2">
-        <v>3.42</v>
+        <v>17.89</v>
       </c>
       <c r="D8" s="2">
-        <v>13.22</v>
+        <v>13.02</v>
       </c>
       <c r="E8" s="2">
-        <v>9.56</v>
+        <v>1.02</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="H8" s="2">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="I8" s="2">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>2755.3</v>
+        <v>1414.8</v>
       </c>
       <c r="C9" s="2">
-        <v>11.24</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D9" s="2">
-        <v>16.57</v>
+        <v>13.25</v>
       </c>
       <c r="E9" s="2">
-        <v>2.65</v>
+        <v>0.08</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="H9" s="2">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="I9" s="2">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>4709.7</v>
+        <v>3149.5</v>
       </c>
       <c r="C10" s="2">
-        <v>0.48</v>
+        <v>7.63</v>
       </c>
       <c r="D10" s="2">
-        <v>12.31</v>
+        <v>14.84</v>
       </c>
       <c r="E10" s="2">
-        <v>10.15</v>
+        <v>-0.7</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H10" s="2">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="I10" s="2">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>7312</v>
+        <v>4209.4</v>
       </c>
       <c r="C11" s="2">
-        <v>4.67</v>
+        <v>3.33</v>
       </c>
       <c r="D11" s="2">
-        <v>9.960000000000001</v>
+        <v>7.34</v>
       </c>
       <c r="E11" s="2">
-        <v>5.77</v>
+        <v>4.36</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="H11" s="2">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="I11" s="2">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>4049.3</v>
+        <v>1838.3</v>
       </c>
       <c r="C12" s="2">
-        <v>4.27</v>
+        <v>7.84</v>
       </c>
       <c r="D12" s="2">
-        <v>13.17</v>
+        <v>11.08</v>
       </c>
       <c r="E12" s="2">
-        <v>4.37</v>
+        <v>-0.12</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="H12" s="2">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="I12" s="2">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>10063</v>
+        <v>264.3</v>
       </c>
       <c r="C13" s="2">
-        <v>7.46</v>
+        <v>-8.5</v>
       </c>
       <c r="D13" s="2">
-        <v>16.51</v>
+        <v>10.02</v>
       </c>
       <c r="E13" s="2">
-        <v>0.06</v>
+        <v>6.71</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="H13" s="2">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="I13" s="2">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>1340.8</v>
+        <v>4419.9</v>
       </c>
       <c r="C14" s="2">
-        <v>-0.89</v>
+        <v>3.81</v>
       </c>
       <c r="D14" s="2">
-        <v>10.28</v>
+        <v>-1.89</v>
       </c>
       <c r="E14" s="2">
-        <v>7.17</v>
+        <v>6.27</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H14" s="2">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="I14" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>1297.6</v>
+        <v>7611</v>
       </c>
       <c r="C15" s="2">
-        <v>8.210000000000001</v>
+        <v>5.77</v>
       </c>
       <c r="D15" s="2">
-        <v>13.69</v>
+        <v>2.52</v>
       </c>
       <c r="E15" s="2">
-        <v>0.37</v>
+        <v>2.66</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H15" s="2">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="I15" s="2">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>1389.4</v>
+        <v>1287.7</v>
       </c>
       <c r="C16" s="2">
-        <v>6.93</v>
+        <v>3.43</v>
       </c>
       <c r="D16" s="2">
-        <v>17.61</v>
+        <v>6</v>
       </c>
       <c r="E16" s="2">
-        <v>-1.67</v>
+        <v>-0.13</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="H16" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I16" s="2">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>1017.15</v>
+        <v>1357.9</v>
       </c>
       <c r="C17" s="2">
-        <v>0.66</v>
+        <v>1.23</v>
       </c>
       <c r="D17" s="2">
-        <v>1.68</v>
+        <v>0.53</v>
       </c>
       <c r="E17" s="2">
-        <v>8.279999999999999</v>
+        <v>3.56</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="H17" s="2">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="I17" s="2">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>403.3</v>
+        <v>451.3</v>
       </c>
       <c r="C18" s="2">
-        <v>-1.2</v>
+        <v>5.92</v>
       </c>
       <c r="D18" s="2">
-        <v>12.65</v>
+        <v>3.96</v>
       </c>
       <c r="E18" s="2">
-        <v>2.94</v>
+        <v>-1.46</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H18" s="2">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="I18" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1021.6</v>
+        <v>1346.5</v>
       </c>
       <c r="C19" s="2">
-        <v>9.789999999999999</v>
+        <v>-3.57</v>
       </c>
       <c r="D19" s="2">
-        <v>11.5</v>
+        <v>1.86</v>
       </c>
       <c r="E19" s="2">
-        <v>-2.99</v>
+        <v>4.23</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="I19" s="2">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>1375.7</v>
+        <v>961.8</v>
       </c>
       <c r="C20" s="2">
-        <v>5.72</v>
+        <v>-2.17</v>
       </c>
       <c r="D20" s="2">
-        <v>15.48</v>
+        <v>4.03</v>
       </c>
       <c r="E20" s="2">
-        <v>-3.91</v>
+        <v>2.11</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H20" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I20" s="2">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>918.3</v>
+        <v>1351.8</v>
       </c>
       <c r="C21" s="2">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="D21" s="2">
-        <v>11.06</v>
+        <v>10.98</v>
       </c>
       <c r="E21" s="2">
-        <v>-0.3</v>
+        <v>-3.5</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="H21" s="2">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="I21" s="2">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>954.95</v>
+        <v>10066</v>
       </c>
       <c r="C22" s="2">
-        <v>-0.74</v>
+        <v>6.44</v>
       </c>
       <c r="D22" s="2">
-        <v>7.11</v>
+        <v>4.02</v>
       </c>
       <c r="E22" s="2">
-        <v>2.28</v>
+        <v>-2.7</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="H22" s="2">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="I22" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>4184</v>
+        <v>1035.1</v>
       </c>
       <c r="C23" s="2">
-        <v>5.84</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="D23" s="2">
-        <v>2.12</v>
+        <v>-1.21</v>
       </c>
       <c r="E23" s="2">
-        <v>0.34</v>
+        <v>6.76</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H23" s="2">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="I23" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>1807.7</v>
+        <v>399.25</v>
       </c>
       <c r="C24" s="2">
-        <v>11.77</v>
+        <v>-6.89</v>
       </c>
       <c r="D24" s="2">
-        <v>6.74</v>
+        <v>6.59</v>
       </c>
       <c r="E24" s="2">
-        <v>-5.15</v>
+        <v>1.63</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H24" s="2">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="I24" s="2">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>1275.4</v>
+        <v>1001.9</v>
       </c>
       <c r="C25" s="2">
-        <v>7.86</v>
+        <v>-5.72</v>
       </c>
       <c r="D25" s="2">
-        <v>4.77</v>
+        <v>-2.5</v>
       </c>
       <c r="E25" s="2">
-        <v>-4.19</v>
+        <v>4.15</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H25" s="2">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I25" s="2">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>1012.45</v>
+        <v>1910.8</v>
       </c>
       <c r="C26" s="2">
-        <v>5.67</v>
+        <v>-6.25</v>
       </c>
       <c r="D26" s="2">
-        <v>7.18</v>
+        <v>2.18</v>
       </c>
       <c r="E26" s="2">
-        <v>-4.36</v>
+        <v>1.92</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H26" s="2">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="I26" s="2">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>13366</v>
+        <v>426.9</v>
       </c>
       <c r="C27" s="2">
-        <v>-7.08</v>
+        <v>-1.96</v>
       </c>
       <c r="D27" s="2">
-        <v>5.82</v>
+        <v>-3.51</v>
       </c>
       <c r="E27" s="2">
-        <v>2.69</v>
+        <v>1.2</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H27" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I27" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>197.86</v>
+        <v>359.5</v>
       </c>
       <c r="C28" s="2">
-        <v>7.12</v>
+        <v>-3.95</v>
       </c>
       <c r="D28" s="2">
-        <v>4.02</v>
+        <v>5.8</v>
       </c>
       <c r="E28" s="2">
-        <v>-3.7</v>
+        <v>-2.88</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="H28" s="2">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="I28" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,16 +1586,16 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>235.89</v>
+        <v>292.25</v>
       </c>
       <c r="C29" s="2">
-        <v>-3.36</v>
+        <v>0.86</v>
       </c>
       <c r="D29" s="2">
-        <v>2.79</v>
+        <v>-3.47</v>
       </c>
       <c r="E29" s="2">
-        <v>1.4</v>
+        <v>-1.05</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
@@ -1604,10 +1604,10 @@
         <v>44</v>
       </c>
       <c r="H29" s="2">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="I29" s="2">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>284.8</v>
+        <v>1272.1</v>
       </c>
       <c r="C30" s="2">
-        <v>6.51</v>
+        <v>-0.27</v>
       </c>
       <c r="D30" s="2">
-        <v>-1.78</v>
+        <v>3.24</v>
       </c>
       <c r="E30" s="2">
-        <v>-3.96</v>
+        <v>-4.45</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="H30" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="I30" s="2">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>443.5</v>
+        <v>244.45</v>
       </c>
       <c r="C31" s="2">
-        <v>6.11</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="D31" s="2">
-        <v>-1.3</v>
+        <v>0.51</v>
       </c>
       <c r="E31" s="2">
-        <v>-4.03</v>
+        <v>1.12</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H31" s="2">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="I31" s="2">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>243.8</v>
+        <v>198.96</v>
       </c>
       <c r="C32" s="2">
-        <v>-10.58</v>
+        <v>0.53</v>
       </c>
       <c r="D32" s="2">
-        <v>5.21</v>
+        <v>-1.72</v>
       </c>
       <c r="E32" s="2">
-        <v>0.99</v>
+        <v>-3.4</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="H32" s="2">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I32" s="2">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>2168.8</v>
+        <v>2194.6</v>
       </c>
       <c r="C33" s="2">
-        <v>-8</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="D33" s="2">
-        <v>5.01</v>
+        <v>1.82</v>
       </c>
       <c r="E33" s="2">
-        <v>-3.79</v>
+        <v>-0.09</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
+        <v>38</v>
+      </c>
+      <c r="H33" s="2">
         <v>16</v>
       </c>
-      <c r="H33" s="2">
+      <c r="I33" s="2">
         <v>22</v>
-      </c>
-      <c r="I33" s="2">
-        <v>36</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>772.45</v>
+        <v>13395</v>
       </c>
       <c r="C34" s="2">
-        <v>-16.77</v>
+        <v>-10.57</v>
       </c>
       <c r="D34" s="2">
-        <v>2.87</v>
+        <v>-2.29</v>
       </c>
       <c r="E34" s="2">
-        <v>0.49</v>
+        <v>1.71</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="H34" s="2">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="I34" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>3042.9</v>
+        <v>1010</v>
       </c>
       <c r="C35" s="2">
-        <v>-12.14</v>
+        <v>4.74</v>
       </c>
       <c r="D35" s="2">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="E35" s="2">
-        <v>-1.32</v>
+        <v>-8.15</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="H35" s="2">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="I35" s="2">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>11117</v>
+        <v>292.5</v>
       </c>
       <c r="C36" s="2">
-        <v>-11.31</v>
+        <v>-6.92</v>
       </c>
       <c r="D36" s="2">
-        <v>4.68</v>
+        <v>-1.24</v>
       </c>
       <c r="E36" s="2">
-        <v>-3.84</v>
+        <v>-1.15</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H36" s="2">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="I36" s="2">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,16 +1842,16 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>1100.7</v>
+        <v>1111.5</v>
       </c>
       <c r="C37" s="2">
-        <v>-1.37</v>
+        <v>-3.97</v>
       </c>
       <c r="D37" s="2">
-        <v>6.53</v>
+        <v>2.49</v>
       </c>
       <c r="E37" s="2">
-        <v>-9.83</v>
+        <v>-6.38</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
@@ -1860,10 +1860,10 @@
         <v>30</v>
       </c>
       <c r="H37" s="2">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2">
         <v>74</v>
-      </c>
-      <c r="I37" s="2">
-        <v>72</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>1293</v>
+        <v>365.8</v>
       </c>
       <c r="C38" s="2">
-        <v>-6.58</v>
+        <v>1.08</v>
       </c>
       <c r="D38" s="2">
-        <v>-3.82</v>
+        <v>-3.77</v>
       </c>
       <c r="E38" s="2">
-        <v>-2.76</v>
+        <v>-6.22</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H38" s="2">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="I38" s="2">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>285.1</v>
+        <v>779.8</v>
       </c>
       <c r="C39" s="2">
-        <v>-4.99</v>
+        <v>-15.42</v>
       </c>
       <c r="D39" s="2">
-        <v>0.01</v>
+        <v>-2.17</v>
       </c>
       <c r="E39" s="2">
-        <v>-5.57</v>
+        <v>0.74</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H39" s="2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I39" s="2">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>1689.1</v>
+        <v>1409.6</v>
       </c>
       <c r="C40" s="2">
-        <v>-12.49</v>
+        <v>-13.08</v>
       </c>
       <c r="D40" s="2">
-        <v>2.95</v>
+        <v>-2.12</v>
       </c>
       <c r="E40" s="2">
-        <v>-3.65</v>
+        <v>-1.8</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H40" s="2">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I40" s="2">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1970,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>1822.5</v>
+        <v>1769.4</v>
       </c>
       <c r="C41" s="2">
-        <v>-7.27</v>
+        <v>-12.6</v>
       </c>
       <c r="D41" s="2">
-        <v>1.83</v>
+        <v>-2.2</v>
       </c>
       <c r="E41" s="2">
-        <v>-5.96</v>
+        <v>-2.1</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="H41" s="2">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="I41" s="2">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>353.9</v>
+        <v>1309.5</v>
       </c>
       <c r="C42" s="2">
-        <v>1.78</v>
+        <v>-9.99</v>
       </c>
       <c r="D42" s="2">
-        <v>-1.6</v>
+        <v>-2.57</v>
       </c>
       <c r="E42" s="2">
-        <v>-8.859999999999999</v>
+        <v>-3.76</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H42" s="2">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="I42" s="2">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>1429.2</v>
+        <v>11367</v>
       </c>
       <c r="C43" s="2">
-        <v>-17.1</v>
+        <v>-12.88</v>
       </c>
       <c r="D43" s="2">
-        <v>-0.85</v>
+        <v>-1.92</v>
       </c>
       <c r="E43" s="2">
-        <v>-0.06</v>
+        <v>-3.06</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="H43" s="2">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="I43" s="2">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>406.5</v>
+        <v>3074.8</v>
       </c>
       <c r="C44" s="2">
-        <v>-7.03</v>
+        <v>-14.82</v>
       </c>
       <c r="D44" s="2">
-        <v>-3.58</v>
+        <v>-5.68</v>
       </c>
       <c r="E44" s="2">
-        <v>-4.71</v>
+        <v>-2.05</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H44" s="2">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I44" s="2">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2098,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>1706</v>
+        <v>591.85</v>
       </c>
       <c r="C45" s="2">
-        <v>-14.62</v>
+        <v>-16.1</v>
       </c>
       <c r="D45" s="2">
-        <v>-3.83</v>
+        <v>-1.69</v>
       </c>
       <c r="E45" s="2">
-        <v>-8.300000000000001</v>
+        <v>-4.2</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H45" s="2">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="I45" s="2">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,28 +2130,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>555.35</v>
+        <v>1800.2</v>
       </c>
       <c r="C46" s="2">
-        <v>-22.6</v>
+        <v>-10.93</v>
       </c>
       <c r="D46" s="2">
-        <v>-1.9</v>
+        <v>-6.4</v>
       </c>
       <c r="E46" s="2">
-        <v>-8.199999999999999</v>
+        <v>-5.35</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H46" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I46" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>1116.4</v>
+        <v>246.25</v>
       </c>
       <c r="C47" s="2">
-        <v>-30</v>
+        <v>-5.46</v>
       </c>
       <c r="D47" s="2">
-        <v>-12.32</v>
+        <v>-14.05</v>
       </c>
       <c r="E47" s="2">
-        <v>-0.17</v>
+        <v>-13.58</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H47" s="2">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="I47" s="2">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,28 +2194,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>180.14</v>
+        <v>1131.7</v>
       </c>
       <c r="C48" s="2">
-        <v>-25.65</v>
+        <v>-28</v>
       </c>
       <c r="D48" s="2">
-        <v>-7.58</v>
+        <v>-20.52</v>
       </c>
       <c r="E48" s="2">
-        <v>-6.26</v>
+        <v>-2.92</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H48" s="2">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="I48" s="2">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,28 +2226,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>246.2</v>
+        <v>2125</v>
       </c>
       <c r="C49" s="2">
-        <v>-0.77</v>
+        <v>-26.94</v>
       </c>
       <c r="D49" s="2">
-        <v>-14.28</v>
+        <v>-14.68</v>
       </c>
       <c r="E49" s="2">
-        <v>-17.16</v>
+        <v>-7.94</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="H49" s="2">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="I49" s="2">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,28 +2258,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>2161.4</v>
+        <v>180.8</v>
       </c>
       <c r="C50" s="2">
-        <v>-30.88</v>
+        <v>-21.42</v>
       </c>
       <c r="D50" s="2">
-        <v>-10.61</v>
+        <v>-11.75</v>
       </c>
       <c r="E50" s="2">
-        <v>-4.05</v>
+        <v>-12.59</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H50" s="2">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="I50" s="2">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2290,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>1109.6</v>
+        <v>1051.4</v>
       </c>
       <c r="C51" s="2">
-        <v>-32.56</v>
+        <v>-28.26</v>
       </c>
       <c r="D51" s="2">
-        <v>-19.35</v>
+        <v>-16.89</v>
       </c>
       <c r="E51" s="2">
-        <v>-3.23</v>
+        <v>-8.07</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H51" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I51" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>2921.6</v>
+        <v>3038.4</v>
       </c>
       <c r="C2" s="2">
-        <v>46.48</v>
+        <v>35.09</v>
       </c>
       <c r="D2" s="2">
-        <v>59.36</v>
+        <v>45.67</v>
       </c>
       <c r="E2" s="2">
-        <v>8.67</v>
+        <v>6.67</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2491,83 +2491,83 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1812.9</v>
+        <v>3205.8</v>
       </c>
       <c r="C3" s="2">
-        <v>29.75</v>
+        <v>15.45</v>
       </c>
       <c r="D3" s="2">
-        <v>32.15</v>
+        <v>22.96</v>
       </c>
       <c r="E3" s="2">
-        <v>1.84</v>
+        <v>12</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="I3" s="2">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>2747.4</v>
+        <v>1835.3</v>
       </c>
       <c r="C4" s="2">
-        <v>14.38</v>
+        <v>18.01</v>
       </c>
       <c r="D4" s="2">
-        <v>26.67</v>
+        <v>24.93</v>
       </c>
       <c r="E4" s="2">
-        <v>5.1</v>
+        <v>2.23</v>
       </c>
       <c r="F4" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>8498</v>
+        <v>2732.9</v>
       </c>
       <c r="C5" s="2">
-        <v>22.73</v>
+        <v>13.05</v>
       </c>
       <c r="D5" s="2">
-        <v>16.13</v>
+        <v>15.77</v>
       </c>
       <c r="E5" s="2">
-        <v>5.95</v>
+        <v>2.83</v>
       </c>
       <c r="F5" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I5" s="2">
         <v>88</v>
@@ -2575,60 +2575,60 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>3105.5</v>
+        <v>8489.5</v>
       </c>
       <c r="C6" s="2">
-        <v>11.93</v>
+        <v>17.89</v>
       </c>
       <c r="D6" s="2">
-        <v>21.11</v>
+        <v>13.02</v>
       </c>
       <c r="E6" s="2">
-        <v>5.49</v>
+        <v>1.02</v>
       </c>
       <c r="F6" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G6" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H6" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I6" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1">
-        <v>2755.3</v>
+        <v>3149.5</v>
       </c>
       <c r="C7" s="2">
-        <v>11.24</v>
+        <v>7.63</v>
       </c>
       <c r="D7" s="2">
-        <v>16.57</v>
+        <v>14.84</v>
       </c>
       <c r="E7" s="2">
-        <v>2.65</v>
+        <v>-0.7</v>
       </c>
       <c r="F7" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G7" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H7" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I7" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -2682,7 +2682,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2724,16 +2724,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>2921.6</v>
+        <v>3038.4</v>
       </c>
       <c r="C2" s="2">
-        <v>46.48</v>
+        <v>35.09</v>
       </c>
       <c r="D2" s="2">
-        <v>59.36</v>
+        <v>45.67</v>
       </c>
       <c r="E2" s="2">
-        <v>8.67</v>
+        <v>6.67</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2753,28 +2753,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1812.9</v>
+        <v>3205.8</v>
       </c>
       <c r="C3" s="2">
-        <v>29.75</v>
+        <v>15.45</v>
       </c>
       <c r="D3" s="2">
-        <v>32.15</v>
+        <v>22.96</v>
       </c>
       <c r="E3" s="2">
-        <v>1.84</v>
+        <v>12</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="I3" s="2">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2782,83 +2782,83 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>390</v>
+        <v>1835.3</v>
       </c>
       <c r="C4" s="2">
-        <v>7.47</v>
+        <v>18.01</v>
       </c>
       <c r="D4" s="2">
-        <v>28.59</v>
+        <v>24.93</v>
       </c>
       <c r="E4" s="2">
-        <v>10.43</v>
+        <v>2.23</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2">
-        <v>70</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>2747.4</v>
+        <v>5021.5</v>
       </c>
       <c r="C5" s="2">
-        <v>14.38</v>
+        <v>1.16</v>
       </c>
       <c r="D5" s="2">
-        <v>26.67</v>
+        <v>10.26</v>
       </c>
       <c r="E5" s="2">
-        <v>5.1</v>
+        <v>11.54</v>
       </c>
       <c r="F5" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G5" s="2">
         <v>84</v>
       </c>
       <c r="H5" s="2">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I5" s="2">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>8498</v>
+        <v>2732.9</v>
       </c>
       <c r="C6" s="2">
-        <v>22.73</v>
+        <v>13.05</v>
       </c>
       <c r="D6" s="2">
-        <v>16.13</v>
+        <v>15.77</v>
       </c>
       <c r="E6" s="2">
-        <v>5.95</v>
+        <v>2.83</v>
       </c>
       <c r="F6" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G6" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I6" s="2">
         <v>88</v>
@@ -2866,64 +2866,93 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>3105.5</v>
+        <v>8489.5</v>
       </c>
       <c r="C7" s="2">
-        <v>11.93</v>
+        <v>17.89</v>
       </c>
       <c r="D7" s="2">
-        <v>21.11</v>
+        <v>13.02</v>
       </c>
       <c r="E7" s="2">
-        <v>5.49</v>
+        <v>1.02</v>
       </c>
       <c r="F7" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G7" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H7" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I7" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1">
-        <v>2755.3</v>
+        <v>3149.5</v>
       </c>
       <c r="C8" s="2">
-        <v>11.24</v>
+        <v>7.63</v>
       </c>
       <c r="D8" s="2">
-        <v>16.57</v>
+        <v>14.84</v>
       </c>
       <c r="E8" s="2">
-        <v>2.65</v>
+        <v>-0.7</v>
       </c>
       <c r="F8" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G8" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H8" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I8" s="2">
-        <v>84</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1">
+        <v>4209.4</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3.33</v>
+      </c>
+      <c r="D9" s="2">
+        <v>7.34</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4.36</v>
+      </c>
+      <c r="F9" s="2">
+        <v>82</v>
+      </c>
+      <c r="G9" s="2">
+        <v>80</v>
+      </c>
+      <c r="H9" s="2">
+        <v>76</v>
+      </c>
+      <c r="I9" s="2">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C8">
+  <conditionalFormatting sqref="C2:C9">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2931,7 +2960,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2939,7 +2968,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E8">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2947,22 +2976,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F8">
+  <conditionalFormatting sqref="F2:F9">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H8">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I8">
+  <conditionalFormatting sqref="I2:I9">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2998,13 +3027,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D2" s="2">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3012,13 +3041,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C3" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D3" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3026,13 +3055,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
+        <v>32</v>
+      </c>
+      <c r="C4" s="2">
         <v>36</v>
       </c>
-      <c r="C4" s="2">
+      <c r="D4" s="2">
         <v>46</v>
-      </c>
-      <c r="D4" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3040,10 +3069,10 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
+        <v>36</v>
+      </c>
+      <c r="C5" s="2">
         <v>46</v>
-      </c>
-      <c r="C5" s="2">
-        <v>50</v>
       </c>
       <c r="D5" s="2">
         <v>48</v>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-06-19</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-06-19</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-06-19</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-06-19</t>
+    <t>Price_2026-06-26</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-06-26</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-06-26</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-06-26</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-06-26</t>
   </si>
   <si>
     <t>RS_Score_2026-06-19</t>
@@ -43,159 +46,156 @@
     <t>RS_Score_2026-06-05</t>
   </si>
   <si>
-    <t>RS_Score_2026-05-29</t>
-  </si>
-  <si>
     <t>ADANIENT</t>
   </si>
   <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
     <t>TRENT</t>
   </si>
   <si>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
     <t>ADANIPORTS</t>
   </si>
   <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
   </si>
   <si>
     <t>ASIANPAINT</t>
   </si>
   <si>
-    <t>APOLLOHOSP</t>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
   </si>
   <si>
     <t>NESTLEIND</t>
   </si>
   <si>
-    <t>GRASIM</t>
+    <t>SHRIRAMFIN</t>
   </si>
   <si>
     <t>LT</t>
   </si>
   <si>
-    <t>SUNPHARMA</t>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>ITC</t>
   </si>
   <si>
     <t>ETERNAL</t>
   </si>
   <si>
-    <t>TITAN</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
+    <t>BAJAJ-AUTO</t>
   </si>
   <si>
     <t>JSWSTEEL</t>
   </si>
   <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
   </si>
   <si>
     <t>BEL</t>
   </si>
   <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
     <t>TMPV</t>
   </si>
   <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
     <t>TATASTEEL</t>
   </si>
   <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
+    <t>NTPC</t>
   </si>
   <si>
     <t>HINDALCO</t>
   </si>
   <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
     <t>SBILIFE</t>
   </si>
   <si>
     <t>ONGC</t>
   </si>
   <si>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
     <t>HCLTECH</t>
   </si>
   <si>
-    <t>TCS</t>
-  </si>
-  <si>
     <t>WIPRO</t>
   </si>
   <si>
-    <t>INFY</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
     <t>2026-06-19</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>2026-05-29</t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3038.4</v>
+        <v>3038</v>
       </c>
       <c r="C2" s="2">
-        <v>35.09</v>
+        <v>42.25</v>
       </c>
       <c r="D2" s="2">
-        <v>45.67</v>
+        <v>37.01</v>
       </c>
       <c r="E2" s="2">
-        <v>6.67</v>
+        <v>3.47</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>3205.8</v>
+        <v>5450</v>
       </c>
       <c r="C3" s="2">
-        <v>15.45</v>
+        <v>10.57</v>
       </c>
       <c r="D3" s="2">
-        <v>22.96</v>
+        <v>17.5</v>
       </c>
       <c r="E3" s="2">
-        <v>12</v>
+        <v>23.72</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H3" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I3" s="2">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,16 +786,16 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>1835.3</v>
+        <v>3216.2</v>
       </c>
       <c r="C4" s="2">
-        <v>18.01</v>
+        <v>13.63</v>
       </c>
       <c r="D4" s="2">
-        <v>24.93</v>
+        <v>17.62</v>
       </c>
       <c r="E4" s="2">
-        <v>2.23</v>
+        <v>14.38</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
@@ -804,10 +804,10 @@
         <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="I4" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1094.75</v>
+        <v>1123.35</v>
       </c>
       <c r="C5" s="2">
-        <v>8.390000000000001</v>
+        <v>6.62</v>
       </c>
       <c r="D5" s="2">
-        <v>14.83</v>
+        <v>11.48</v>
       </c>
       <c r="E5" s="2">
-        <v>9.380000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
+        <v>94</v>
+      </c>
+      <c r="H5" s="2">
         <v>52</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>34</v>
-      </c>
-      <c r="I5" s="2">
-        <v>26</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>5021.5</v>
+        <v>8592</v>
       </c>
       <c r="C6" s="2">
-        <v>1.16</v>
+        <v>14.07</v>
       </c>
       <c r="D6" s="2">
-        <v>10.26</v>
+        <v>11.6</v>
       </c>
       <c r="E6" s="2">
-        <v>11.54</v>
+        <v>5.08</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H6" s="2">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="I6" s="2">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>2732.9</v>
+        <v>1440.1</v>
       </c>
       <c r="C7" s="2">
-        <v>13.05</v>
+        <v>9.17</v>
       </c>
       <c r="D7" s="2">
-        <v>15.77</v>
+        <v>17.15</v>
       </c>
       <c r="E7" s="2">
-        <v>2.83</v>
+        <v>3.76</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="H7" s="2">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="I7" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>8489.5</v>
+        <v>1796</v>
       </c>
       <c r="C8" s="2">
-        <v>17.89</v>
+        <v>18.73</v>
       </c>
       <c r="D8" s="2">
-        <v>13.02</v>
+        <v>14.63</v>
       </c>
       <c r="E8" s="2">
-        <v>1.02</v>
+        <v>-0.06</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H8" s="2">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="I8" s="2">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>1414.8</v>
+        <v>1862.8</v>
       </c>
       <c r="C9" s="2">
-        <v>9.199999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="D9" s="2">
-        <v>13.25</v>
+        <v>11.18</v>
       </c>
       <c r="E9" s="2">
-        <v>0.08</v>
+        <v>3.53</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="H9" s="2">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="I9" s="2">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>3149.5</v>
+        <v>3126.6</v>
       </c>
       <c r="C10" s="2">
-        <v>7.63</v>
+        <v>8.26</v>
       </c>
       <c r="D10" s="2">
-        <v>14.84</v>
+        <v>14.93</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.7</v>
+        <v>0.13</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H10" s="2">
         <v>90</v>
       </c>
       <c r="I10" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>4209.4</v>
+        <v>1350.5</v>
       </c>
       <c r="C11" s="2">
-        <v>3.33</v>
+        <v>6.5</v>
       </c>
       <c r="D11" s="2">
-        <v>7.34</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="E11" s="2">
-        <v>4.36</v>
+        <v>3.61</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="H11" s="2">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="I11" s="2">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1838.3</v>
+        <v>1387.5</v>
       </c>
       <c r="C12" s="2">
-        <v>7.84</v>
+        <v>-1.92</v>
       </c>
       <c r="D12" s="2">
-        <v>11.08</v>
+        <v>3.02</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.12</v>
+        <v>10.43</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H12" s="2">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="I12" s="2">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>264.3</v>
+        <v>2645.2</v>
       </c>
       <c r="C13" s="2">
-        <v>-8.5</v>
+        <v>12.75</v>
       </c>
       <c r="D13" s="2">
-        <v>10.02</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E13" s="2">
-        <v>6.71</v>
+        <v>-0.13</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="H13" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I13" s="2">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>4419.9</v>
+        <v>980.4</v>
       </c>
       <c r="C14" s="2">
-        <v>3.81</v>
+        <v>-4.33</v>
       </c>
       <c r="D14" s="2">
-        <v>-1.89</v>
+        <v>7.94</v>
       </c>
       <c r="E14" s="2">
-        <v>6.27</v>
+        <v>7.94</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H14" s="2">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="I14" s="2">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>7611</v>
+        <v>1377.2</v>
       </c>
       <c r="C15" s="2">
-        <v>5.77</v>
+        <v>3.37</v>
       </c>
       <c r="D15" s="2">
-        <v>2.52</v>
+        <v>1.33</v>
       </c>
       <c r="E15" s="2">
-        <v>2.66</v>
+        <v>7.04</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="H15" s="2">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="I15" s="2">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>1287.7</v>
+        <v>409</v>
       </c>
       <c r="C16" s="2">
-        <v>3.43</v>
+        <v>-2.77</v>
       </c>
       <c r="D16" s="2">
-        <v>6</v>
+        <v>6.62</v>
       </c>
       <c r="E16" s="2">
-        <v>-0.13</v>
+        <v>6.45</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H16" s="2">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="I16" s="2">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>1357.9</v>
+        <v>1402.6</v>
       </c>
       <c r="C17" s="2">
-        <v>1.23</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D17" s="2">
-        <v>0.53</v>
+        <v>9.1</v>
       </c>
       <c r="E17" s="2">
-        <v>3.56</v>
+        <v>-1.33</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H17" s="2">
         <v>64</v>
       </c>
       <c r="I17" s="2">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>451.3</v>
+        <v>1031.8</v>
       </c>
       <c r="C18" s="2">
-        <v>5.92</v>
+        <v>-3.19</v>
       </c>
       <c r="D18" s="2">
-        <v>3.96</v>
+        <v>-0.5</v>
       </c>
       <c r="E18" s="2">
-        <v>-1.46</v>
+        <v>8.94</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H18" s="2">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="I18" s="2">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1346.5</v>
+        <v>4216.4</v>
       </c>
       <c r="C19" s="2">
-        <v>-3.57</v>
+        <v>2</v>
       </c>
       <c r="D19" s="2">
-        <v>1.86</v>
+        <v>3.94</v>
       </c>
       <c r="E19" s="2">
-        <v>4.23</v>
+        <v>3.43</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
+        <v>82</v>
+      </c>
+      <c r="H19" s="2">
+        <v>80</v>
+      </c>
+      <c r="I19" s="2">
         <v>76</v>
-      </c>
-      <c r="H19" s="2">
-        <v>48</v>
-      </c>
-      <c r="I19" s="2">
-        <v>34</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>961.8</v>
+        <v>7598</v>
       </c>
       <c r="C20" s="2">
-        <v>-2.17</v>
+        <v>-5.79</v>
       </c>
       <c r="D20" s="2">
-        <v>4.03</v>
+        <v>5.68</v>
       </c>
       <c r="E20" s="2">
-        <v>2.11</v>
+        <v>5.87</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="H20" s="2">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="I20" s="2">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>1351.8</v>
+        <v>796.3</v>
       </c>
       <c r="C21" s="2">
-        <v>1.64</v>
+        <v>-10.45</v>
       </c>
       <c r="D21" s="2">
-        <v>10.98</v>
+        <v>1.2</v>
       </c>
       <c r="E21" s="2">
-        <v>-3.5</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="H21" s="2">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="I21" s="2">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>10066</v>
+        <v>4291.3</v>
       </c>
       <c r="C22" s="2">
-        <v>6.44</v>
+        <v>2.68</v>
       </c>
       <c r="D22" s="2">
-        <v>4.02</v>
+        <v>-5.18</v>
       </c>
       <c r="E22" s="2">
-        <v>-2.7</v>
+        <v>5.31</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H22" s="2">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="I22" s="2">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>1035.1</v>
+        <v>1045.4</v>
       </c>
       <c r="C23" s="2">
-        <v>-8.050000000000001</v>
+        <v>-11.21</v>
       </c>
       <c r="D23" s="2">
-        <v>-1.21</v>
+        <v>-1.48</v>
       </c>
       <c r="E23" s="2">
-        <v>6.76</v>
+        <v>8.4</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
+        <v>58</v>
+      </c>
+      <c r="H23" s="2">
         <v>70</v>
       </c>
-      <c r="H23" s="2">
+      <c r="I23" s="2">
         <v>56</v>
-      </c>
-      <c r="I23" s="2">
-        <v>12</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>399.25</v>
+        <v>13745</v>
       </c>
       <c r="C24" s="2">
-        <v>-6.89</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="D24" s="2">
-        <v>6.59</v>
+        <v>2.17</v>
       </c>
       <c r="E24" s="2">
-        <v>1.63</v>
+        <v>4.71</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="H24" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I24" s="2">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>1001.9</v>
+        <v>3182.2</v>
       </c>
       <c r="C25" s="2">
-        <v>-5.72</v>
+        <v>-9.94</v>
       </c>
       <c r="D25" s="2">
-        <v>-2.5</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E25" s="2">
-        <v>4.15</v>
+        <v>4.49</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="H25" s="2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I25" s="2">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>1910.8</v>
+        <v>435.4</v>
       </c>
       <c r="C26" s="2">
-        <v>-6.25</v>
+        <v>7.88</v>
       </c>
       <c r="D26" s="2">
-        <v>2.18</v>
+        <v>-0.76</v>
       </c>
       <c r="E26" s="2">
-        <v>1.92</v>
+        <v>-4.91</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="H26" s="2">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I26" s="2">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>426.9</v>
+        <v>2174.2</v>
       </c>
       <c r="C27" s="2">
-        <v>-1.96</v>
+        <v>-4.72</v>
       </c>
       <c r="D27" s="2">
-        <v>-3.51</v>
+        <v>-1.99</v>
       </c>
       <c r="E27" s="2">
-        <v>1.2</v>
+        <v>1.99</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
+        <v>38</v>
+      </c>
+      <c r="H27" s="2">
+        <v>38</v>
+      </c>
+      <c r="I27" s="2">
         <v>16</v>
-      </c>
-      <c r="H27" s="2">
-        <v>32</v>
-      </c>
-      <c r="I27" s="2">
-        <v>30</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>359.5</v>
+        <v>1131.3</v>
       </c>
       <c r="C28" s="2">
-        <v>-3.95</v>
+        <v>0.77</v>
       </c>
       <c r="D28" s="2">
-        <v>5.8</v>
+        <v>2.49</v>
       </c>
       <c r="E28" s="2">
-        <v>-2.88</v>
+        <v>-4</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="H28" s="2">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="I28" s="2">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,25 +1586,25 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>292.25</v>
+        <v>1850.7</v>
       </c>
       <c r="C29" s="2">
-        <v>0.86</v>
+        <v>-7.68</v>
       </c>
       <c r="D29" s="2">
-        <v>-3.47</v>
+        <v>0.21</v>
       </c>
       <c r="E29" s="2">
-        <v>-1.05</v>
+        <v>1.19</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H29" s="2">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="I29" s="2">
         <v>52</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>1272.1</v>
+        <v>290</v>
       </c>
       <c r="C30" s="2">
-        <v>-0.27</v>
+        <v>-5.05</v>
       </c>
       <c r="D30" s="2">
-        <v>3.24</v>
+        <v>-2.9</v>
       </c>
       <c r="E30" s="2">
-        <v>-4.45</v>
+        <v>1.08</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="H30" s="2">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="I30" s="2">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>244.45</v>
+        <v>255.15</v>
       </c>
       <c r="C31" s="2">
-        <v>-9.210000000000001</v>
+        <v>-10.54</v>
       </c>
       <c r="D31" s="2">
-        <v>0.51</v>
+        <v>1.01</v>
       </c>
       <c r="E31" s="2">
-        <v>1.12</v>
+        <v>1.82</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="H31" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I31" s="2">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>198.96</v>
+        <v>9843</v>
       </c>
       <c r="C32" s="2">
-        <v>0.53</v>
+        <v>2.27</v>
       </c>
       <c r="D32" s="2">
-        <v>-1.72</v>
+        <v>2.13</v>
       </c>
       <c r="E32" s="2">
-        <v>-3.4</v>
+        <v>-5.9</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H32" s="2">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="I32" s="2">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>2194.6</v>
+        <v>1231</v>
       </c>
       <c r="C33" s="2">
-        <v>-9.869999999999999</v>
+        <v>-0.08</v>
       </c>
       <c r="D33" s="2">
-        <v>1.82</v>
+        <v>-0.75</v>
       </c>
       <c r="E33" s="2">
-        <v>-0.09</v>
+        <v>-3.68</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="H33" s="2">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="I33" s="2">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>13395</v>
+        <v>1318.1</v>
       </c>
       <c r="C34" s="2">
-        <v>-10.57</v>
+        <v>-6.72</v>
       </c>
       <c r="D34" s="2">
-        <v>-2.29</v>
+        <v>-2.99</v>
       </c>
       <c r="E34" s="2">
-        <v>1.71</v>
+        <v>0.23</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I34" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>1010</v>
+        <v>239.43</v>
       </c>
       <c r="C35" s="2">
-        <v>4.74</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="D35" s="2">
-        <v>1.8</v>
+        <v>-1.82</v>
       </c>
       <c r="E35" s="2">
-        <v>-8.15</v>
+        <v>0.2</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="H35" s="2">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="I35" s="2">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>292.5</v>
+        <v>11489</v>
       </c>
       <c r="C36" s="2">
-        <v>-6.92</v>
+        <v>-11.37</v>
       </c>
       <c r="D36" s="2">
-        <v>-1.24</v>
+        <v>-3.34</v>
       </c>
       <c r="E36" s="2">
-        <v>-1.15</v>
+        <v>0.06</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H36" s="2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I36" s="2">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>1111.5</v>
+        <v>283.9</v>
       </c>
       <c r="C37" s="2">
-        <v>-3.97</v>
+        <v>-1.15</v>
       </c>
       <c r="D37" s="2">
-        <v>2.49</v>
+        <v>-10.75</v>
       </c>
       <c r="E37" s="2">
-        <v>-6.38</v>
+        <v>-2.29</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I37" s="2">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>365.8</v>
+        <v>1437.1</v>
       </c>
       <c r="C38" s="2">
-        <v>1.08</v>
+        <v>-6.34</v>
       </c>
       <c r="D38" s="2">
-        <v>-3.77</v>
+        <v>-4.92</v>
       </c>
       <c r="E38" s="2">
-        <v>-6.22</v>
+        <v>-3.15</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H38" s="2">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I38" s="2">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>779.8</v>
+        <v>1764.6</v>
       </c>
       <c r="C39" s="2">
-        <v>-15.42</v>
+        <v>-12.78</v>
       </c>
       <c r="D39" s="2">
-        <v>-2.17</v>
+        <v>-4.04</v>
       </c>
       <c r="E39" s="2">
-        <v>0.74</v>
+        <v>-1.07</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="H39" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I39" s="2">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>1409.6</v>
+        <v>407.2</v>
       </c>
       <c r="C40" s="2">
-        <v>-13.08</v>
+        <v>-6.11</v>
       </c>
       <c r="D40" s="2">
-        <v>-2.12</v>
+        <v>-12</v>
       </c>
       <c r="E40" s="2">
-        <v>-1.8</v>
+        <v>-0.86</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="H40" s="2">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="I40" s="2">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1970,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>1769.4</v>
+        <v>585.45</v>
       </c>
       <c r="C41" s="2">
-        <v>-12.6</v>
+        <v>-15.68</v>
       </c>
       <c r="D41" s="2">
-        <v>-2.2</v>
+        <v>-4.69</v>
       </c>
       <c r="E41" s="2">
-        <v>-2.1</v>
+        <v>-1.22</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H41" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I41" s="2">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>1309.5</v>
+        <v>353.2</v>
       </c>
       <c r="C42" s="2">
-        <v>-9.99</v>
+        <v>-6.34</v>
       </c>
       <c r="D42" s="2">
-        <v>-2.57</v>
+        <v>-1.1</v>
       </c>
       <c r="E42" s="2">
-        <v>-3.76</v>
+        <v>-9.59</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="H42" s="2">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="I42" s="2">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>11367</v>
+        <v>188.71</v>
       </c>
       <c r="C43" s="2">
-        <v>-12.88</v>
+        <v>-5.21</v>
       </c>
       <c r="D43" s="2">
-        <v>-1.92</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E43" s="2">
-        <v>-3.06</v>
+        <v>-7.41</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H43" s="2">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="I43" s="2">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>3074.8</v>
+        <v>352.05</v>
       </c>
       <c r="C44" s="2">
-        <v>-14.82</v>
+        <v>-3.02</v>
       </c>
       <c r="D44" s="2">
-        <v>-5.68</v>
+        <v>-10.56</v>
       </c>
       <c r="E44" s="2">
-        <v>-2.05</v>
+        <v>-9.01</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H44" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I44" s="2">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2098,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>591.85</v>
+        <v>953.2</v>
       </c>
       <c r="C45" s="2">
-        <v>-16.1</v>
+        <v>4.86</v>
       </c>
       <c r="D45" s="2">
-        <v>-1.69</v>
+        <v>-8.26</v>
       </c>
       <c r="E45" s="2">
-        <v>-4.2</v>
+        <v>-15.4</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="H45" s="2">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="I45" s="2">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,28 +2130,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>1800.2</v>
+        <v>1744.9</v>
       </c>
       <c r="C46" s="2">
-        <v>-10.93</v>
+        <v>-14.1</v>
       </c>
       <c r="D46" s="2">
-        <v>-6.4</v>
+        <v>-11.47</v>
       </c>
       <c r="E46" s="2">
-        <v>-5.35</v>
+        <v>-4.66</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
+        <v>12</v>
+      </c>
+      <c r="H46" s="2">
         <v>14</v>
       </c>
-      <c r="H46" s="2">
+      <c r="I46" s="2">
         <v>20</v>
-      </c>
-      <c r="I46" s="2">
-        <v>32</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>246.25</v>
+        <v>233.1</v>
       </c>
       <c r="C47" s="2">
-        <v>-5.46</v>
+        <v>-10.78</v>
       </c>
       <c r="D47" s="2">
-        <v>-14.05</v>
+        <v>-17.94</v>
       </c>
       <c r="E47" s="2">
-        <v>-13.58</v>
+        <v>-12.17</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
+        <v>10</v>
+      </c>
+      <c r="H47" s="2">
         <v>6</v>
       </c>
-      <c r="H47" s="2">
+      <c r="I47" s="2">
         <v>54</v>
-      </c>
-      <c r="I47" s="2">
-        <v>48</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,28 +2194,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>1131.7</v>
+        <v>2094.7</v>
       </c>
       <c r="C48" s="2">
-        <v>-28</v>
+        <v>-21.14</v>
       </c>
       <c r="D48" s="2">
-        <v>-20.52</v>
+        <v>-17.76</v>
       </c>
       <c r="E48" s="2">
-        <v>-2.92</v>
+        <v>-7.27</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H48" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I48" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,28 +2226,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>2125</v>
+        <v>1041.2</v>
       </c>
       <c r="C49" s="2">
-        <v>-26.94</v>
+        <v>-22.3</v>
       </c>
       <c r="D49" s="2">
-        <v>-14.68</v>
+        <v>-19.33</v>
       </c>
       <c r="E49" s="2">
-        <v>-7.94</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H49" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I49" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,16 +2258,16 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>180.8</v>
+        <v>1100.7</v>
       </c>
       <c r="C50" s="2">
-        <v>-21.42</v>
+        <v>-22.91</v>
       </c>
       <c r="D50" s="2">
-        <v>-11.75</v>
+        <v>-22.22</v>
       </c>
       <c r="E50" s="2">
-        <v>-12.59</v>
+        <v>-7.02</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
@@ -2276,10 +2276,10 @@
         <v>8</v>
       </c>
       <c r="H50" s="2">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="I50" s="2">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2290,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>1051.4</v>
+        <v>175</v>
       </c>
       <c r="C51" s="2">
-        <v>-28.26</v>
+        <v>-18.26</v>
       </c>
       <c r="D51" s="2">
-        <v>-16.89</v>
+        <v>-14.35</v>
       </c>
       <c r="E51" s="2">
-        <v>-8.07</v>
+        <v>-14.32</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H51" s="2">
         <v>8</v>
       </c>
       <c r="I51" s="2">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2420,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3038.4</v>
+        <v>3038</v>
       </c>
       <c r="C2" s="2">
-        <v>35.09</v>
+        <v>42.25</v>
       </c>
       <c r="D2" s="2">
-        <v>45.67</v>
+        <v>37.01</v>
       </c>
       <c r="E2" s="2">
-        <v>6.67</v>
+        <v>3.47</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2488,151 +2488,122 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1">
-        <v>3205.8</v>
+        <v>3216.2</v>
       </c>
       <c r="C3" s="2">
-        <v>15.45</v>
+        <v>13.63</v>
       </c>
       <c r="D3" s="2">
-        <v>22.96</v>
+        <v>17.62</v>
       </c>
       <c r="E3" s="2">
-        <v>12</v>
+        <v>14.38</v>
       </c>
       <c r="F3" s="2">
+        <v>96</v>
+      </c>
+      <c r="G3" s="2">
         <v>98</v>
-      </c>
-      <c r="G3" s="2">
-        <v>86</v>
       </c>
       <c r="H3" s="2">
         <v>86</v>
       </c>
       <c r="I3" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
-        <v>1835.3</v>
+        <v>8592</v>
       </c>
       <c r="C4" s="2">
-        <v>18.01</v>
+        <v>14.07</v>
       </c>
       <c r="D4" s="2">
-        <v>24.93</v>
+        <v>11.6</v>
       </c>
       <c r="E4" s="2">
-        <v>2.23</v>
+        <v>5.08</v>
       </c>
       <c r="F4" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G4" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H4" s="2">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="I4" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1">
-        <v>2732.9</v>
+        <v>1796</v>
       </c>
       <c r="C5" s="2">
-        <v>13.05</v>
+        <v>18.73</v>
       </c>
       <c r="D5" s="2">
-        <v>15.77</v>
+        <v>14.63</v>
       </c>
       <c r="E5" s="2">
-        <v>2.83</v>
+        <v>-0.06</v>
       </c>
       <c r="F5" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G5" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H5" s="2">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="I5" s="2">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1">
-        <v>8489.5</v>
+        <v>3126.6</v>
       </c>
       <c r="C6" s="2">
-        <v>17.89</v>
+        <v>8.26</v>
       </c>
       <c r="D6" s="2">
-        <v>13.02</v>
+        <v>14.93</v>
       </c>
       <c r="E6" s="2">
-        <v>1.02</v>
+        <v>0.13</v>
       </c>
       <c r="F6" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G6" s="2">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H6" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I6" s="2">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="1">
-        <v>3149.5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>7.63</v>
-      </c>
-      <c r="D7" s="2">
-        <v>14.84</v>
-      </c>
-      <c r="E7" s="2">
-        <v>-0.7</v>
-      </c>
-      <c r="F7" s="2">
-        <v>84</v>
-      </c>
-      <c r="G7" s="2">
         <v>90</v>
       </c>
-      <c r="H7" s="2">
-        <v>90</v>
-      </c>
-      <c r="I7" s="2">
-        <v>92</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2640,7 +2611,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2648,7 +2619,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E6">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2656,22 +2627,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I6">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2724,16 +2695,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3038.4</v>
+        <v>3038</v>
       </c>
       <c r="C2" s="2">
-        <v>35.09</v>
+        <v>42.25</v>
       </c>
       <c r="D2" s="2">
-        <v>45.67</v>
+        <v>37.01</v>
       </c>
       <c r="E2" s="2">
-        <v>6.67</v>
+        <v>3.47</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2753,28 +2724,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>3205.8</v>
+        <v>5450</v>
       </c>
       <c r="C3" s="2">
-        <v>15.45</v>
+        <v>10.57</v>
       </c>
       <c r="D3" s="2">
-        <v>22.96</v>
+        <v>17.5</v>
       </c>
       <c r="E3" s="2">
-        <v>12</v>
+        <v>23.72</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H3" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I3" s="2">
-        <v>84</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2782,16 +2753,16 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>1835.3</v>
+        <v>3216.2</v>
       </c>
       <c r="C4" s="2">
-        <v>18.01</v>
+        <v>13.63</v>
       </c>
       <c r="D4" s="2">
-        <v>24.93</v>
+        <v>17.62</v>
       </c>
       <c r="E4" s="2">
-        <v>2.23</v>
+        <v>14.38</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
@@ -2800,65 +2771,65 @@
         <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="I4" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>5021.5</v>
+        <v>1123.35</v>
       </c>
       <c r="C5" s="2">
-        <v>1.16</v>
+        <v>6.62</v>
       </c>
       <c r="D5" s="2">
-        <v>10.26</v>
+        <v>11.48</v>
       </c>
       <c r="E5" s="2">
-        <v>11.54</v>
+        <v>16.4</v>
       </c>
       <c r="F5" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="I5" s="2">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>2732.9</v>
+        <v>8592</v>
       </c>
       <c r="C6" s="2">
-        <v>13.05</v>
+        <v>14.07</v>
       </c>
       <c r="D6" s="2">
-        <v>15.77</v>
+        <v>11.6</v>
       </c>
       <c r="E6" s="2">
-        <v>2.83</v>
+        <v>5.08</v>
       </c>
       <c r="F6" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H6" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I6" s="2">
         <v>88</v>
@@ -2869,86 +2840,86 @@
         <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>8489.5</v>
+        <v>1796</v>
       </c>
       <c r="C7" s="2">
-        <v>17.89</v>
+        <v>18.73</v>
       </c>
       <c r="D7" s="2">
-        <v>13.02</v>
+        <v>14.63</v>
       </c>
       <c r="E7" s="2">
-        <v>1.02</v>
+        <v>-0.06</v>
       </c>
       <c r="F7" s="2">
         <v>88</v>
       </c>
       <c r="G7" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H7" s="2">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="I7" s="2">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1">
-        <v>3149.5</v>
+        <v>1862.8</v>
       </c>
       <c r="C8" s="2">
-        <v>7.63</v>
+        <v>9.74</v>
       </c>
       <c r="D8" s="2">
-        <v>14.84</v>
+        <v>11.18</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.7</v>
+        <v>3.53</v>
       </c>
       <c r="F8" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G8" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H8" s="2">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="I8" s="2">
-        <v>92</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1">
-        <v>4209.4</v>
+        <v>3126.6</v>
       </c>
       <c r="C9" s="2">
-        <v>3.33</v>
+        <v>8.26</v>
       </c>
       <c r="D9" s="2">
-        <v>7.34</v>
+        <v>14.93</v>
       </c>
       <c r="E9" s="2">
-        <v>4.36</v>
+        <v>0.13</v>
       </c>
       <c r="F9" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G9" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H9" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -3027,13 +2998,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D2" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3041,13 +3012,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C3" s="2">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D3" s="2">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3055,13 +3026,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D4" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3069,13 +3040,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
+        <v>32</v>
+      </c>
+      <c r="C5" s="2">
         <v>36</v>
       </c>
-      <c r="C5" s="2">
+      <c r="D5" s="2">
         <v>46</v>
-      </c>
-      <c r="D5" s="2">
-        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-06-26</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-06-26</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-06-26</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-06-26</t>
+    <t>Price_2026-07-03</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-07-03</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-07-03</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-07-03</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-07-03</t>
   </si>
   <si>
     <t>RS_Score_2026-06-26</t>
@@ -43,159 +46,156 @@
     <t>RS_Score_2026-06-12</t>
   </si>
   <si>
-    <t>RS_Score_2026-06-05</t>
-  </si>
-  <si>
     <t>ADANIENT</t>
   </si>
   <si>
+    <t>TRENT</t>
+  </si>
+  <si>
     <t>INDIGO</t>
   </si>
   <si>
-    <t>TRENT</t>
+    <t>BAJFINANCE</t>
   </si>
   <si>
     <t>MAXHEALTH</t>
   </si>
   <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>ETERNAL</t>
+  </si>
+  <si>
     <t>APOLLOHOSP</t>
   </si>
   <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
     <t>CIPLA</t>
   </si>
   <si>
-    <t>ADANIPORTS</t>
-  </si>
-  <si>
     <t>SUNPHARMA</t>
   </si>
   <si>
-    <t>GRASIM</t>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
   </si>
   <si>
     <t>DRREDDY</t>
   </si>
   <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
   </si>
   <si>
     <t>AXISBANK</t>
   </si>
   <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
     <t>KOTAKBANK</t>
   </si>
   <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>HINDUNILVR</t>
   </si>
   <si>
     <t>LT</t>
   </si>
   <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>TITAN</t>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>BEL</t>
   </si>
   <si>
     <t>SBIN</t>
   </si>
   <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
+    <t>JSWSTEEL</t>
   </si>
   <si>
     <t>COALINDIA</t>
   </si>
   <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>ETERNAL</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
+    <t>SBILIFE</t>
   </si>
   <si>
     <t>POWERGRID</t>
   </si>
   <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>BEL</t>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
   </si>
   <si>
     <t>HDFCLIFE</t>
   </si>
   <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>HCLTECH</t>
+  </si>
+  <si>
     <t>TMPV</t>
   </si>
   <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>HINDALCO</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>INFY</t>
   </si>
   <si>
     <t>ONGC</t>
   </si>
   <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>HCLTECH</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
     <t>2026-06-26</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3038</v>
+        <v>3212.1</v>
       </c>
       <c r="C2" s="2">
-        <v>42.25</v>
+        <v>46.67</v>
       </c>
       <c r="D2" s="2">
-        <v>37.01</v>
+        <v>38.41</v>
       </c>
       <c r="E2" s="2">
-        <v>3.47</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>5450</v>
+        <v>3340.6</v>
       </c>
       <c r="C3" s="2">
-        <v>10.57</v>
+        <v>23.76</v>
       </c>
       <c r="D3" s="2">
-        <v>17.5</v>
+        <v>17.78</v>
       </c>
       <c r="E3" s="2">
-        <v>23.72</v>
+        <v>22.81</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>92</v>
+        <v>95.92</v>
       </c>
       <c r="H3" s="2">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="I3" s="2">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>3216.2</v>
+        <v>5426.5</v>
       </c>
       <c r="C4" s="2">
-        <v>13.63</v>
+        <v>11.61</v>
       </c>
       <c r="D4" s="2">
-        <v>17.62</v>
+        <v>18.97</v>
       </c>
       <c r="E4" s="2">
-        <v>14.38</v>
+        <v>24.47</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>98</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="H4" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I4" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1123.35</v>
+        <v>1031.4</v>
       </c>
       <c r="C5" s="2">
-        <v>6.62</v>
+        <v>0.65</v>
       </c>
       <c r="D5" s="2">
-        <v>11.48</v>
+        <v>12.58</v>
       </c>
       <c r="E5" s="2">
-        <v>16.4</v>
+        <v>19.13</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>94</v>
+        <v>81.63</v>
       </c>
       <c r="H5" s="2">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="I5" s="2">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,25 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>8592</v>
+        <v>1153.4</v>
       </c>
       <c r="C6" s="2">
-        <v>14.07</v>
+        <v>6.63</v>
       </c>
       <c r="D6" s="2">
-        <v>11.6</v>
+        <v>14.42</v>
       </c>
       <c r="E6" s="2">
-        <v>5.08</v>
+        <v>14.69</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
-      <c r="G6" s="2">
-        <v>88</v>
-      </c>
       <c r="H6" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I6" s="2">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +879,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>1440.1</v>
+        <v>1063.6</v>
       </c>
       <c r="C7" s="2">
-        <v>9.17</v>
+        <v>0.46</v>
       </c>
       <c r="D7" s="2">
-        <v>17.15</v>
+        <v>9.74</v>
       </c>
       <c r="E7" s="2">
-        <v>3.76</v>
+        <v>19.29</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>62</v>
+        <v>69.39</v>
       </c>
       <c r="H7" s="2">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="I7" s="2">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,25 +911,25 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>1796</v>
+        <v>1874.2</v>
       </c>
       <c r="C8" s="2">
-        <v>18.73</v>
+        <v>20.97</v>
       </c>
       <c r="D8" s="2">
-        <v>14.63</v>
+        <v>15.57</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.06</v>
+        <v>4.27</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
+        <v>89.8</v>
+      </c>
+      <c r="H8" s="2">
         <v>96</v>
-      </c>
-      <c r="H8" s="2">
-        <v>98</v>
       </c>
       <c r="I8" s="2">
         <v>98</v>
@@ -946,28 +943,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>1862.8</v>
+        <v>281.65</v>
       </c>
       <c r="C9" s="2">
-        <v>9.74</v>
+        <v>5.09</v>
       </c>
       <c r="D9" s="2">
-        <v>11.18</v>
+        <v>10.24</v>
       </c>
       <c r="E9" s="2">
-        <v>3.53</v>
+        <v>13.43</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>80</v>
+        <v>42.86</v>
       </c>
       <c r="H9" s="2">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="I9" s="2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +975,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>3126.6</v>
+        <v>8893.5</v>
       </c>
       <c r="C10" s="2">
-        <v>8.26</v>
+        <v>15.61</v>
       </c>
       <c r="D10" s="2">
-        <v>14.93</v>
+        <v>13.65</v>
       </c>
       <c r="E10" s="2">
-        <v>0.13</v>
+        <v>6.4</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>84</v>
+        <v>93.88</v>
       </c>
       <c r="H10" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I10" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1007,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>1350.5</v>
+        <v>1411.4</v>
       </c>
       <c r="C11" s="2">
-        <v>6.5</v>
+        <v>0.86</v>
       </c>
       <c r="D11" s="2">
-        <v>9.289999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="E11" s="2">
-        <v>3.61</v>
+        <v>12.89</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>44</v>
+        <v>83.67</v>
       </c>
       <c r="H11" s="2">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="I11" s="2">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1039,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1387.5</v>
+        <v>3180.9</v>
       </c>
       <c r="C12" s="2">
-        <v>-1.92</v>
+        <v>10.7</v>
       </c>
       <c r="D12" s="2">
-        <v>3.02</v>
+        <v>14.49</v>
       </c>
       <c r="E12" s="2">
-        <v>10.43</v>
+        <v>4.29</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>66</v>
+        <v>79.59</v>
       </c>
       <c r="H12" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="I12" s="2">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1071,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>2645.2</v>
+        <v>1458.2</v>
       </c>
       <c r="C13" s="2">
-        <v>12.75</v>
+        <v>10.96</v>
       </c>
       <c r="D13" s="2">
-        <v>8.289999999999999</v>
+        <v>11.74</v>
       </c>
       <c r="E13" s="2">
-        <v>-0.13</v>
+        <v>5.07</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>90</v>
+        <v>91.84</v>
       </c>
       <c r="H13" s="2">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="I13" s="2">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1103,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>980.4</v>
+        <v>1904.8</v>
       </c>
       <c r="C14" s="2">
-        <v>-4.33</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="D14" s="2">
-        <v>7.94</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="E14" s="2">
-        <v>7.94</v>
+        <v>6.48</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>64</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="H14" s="2">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="I14" s="2">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1135,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>1377.2</v>
+        <v>2737.8</v>
       </c>
       <c r="C15" s="2">
-        <v>3.37</v>
+        <v>13.66</v>
       </c>
       <c r="D15" s="2">
-        <v>1.33</v>
+        <v>11.12</v>
       </c>
       <c r="E15" s="2">
-        <v>7.04</v>
+        <v>3.85</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>70</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="H15" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I15" s="2">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1167,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>409</v>
+        <v>14366</v>
       </c>
       <c r="C16" s="2">
-        <v>-2.77</v>
+        <v>-4.68</v>
       </c>
       <c r="D16" s="2">
-        <v>6.62</v>
+        <v>8.65</v>
       </c>
       <c r="E16" s="2">
-        <v>6.45</v>
+        <v>11.26</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>56</v>
+        <v>59.18</v>
       </c>
       <c r="H16" s="2">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="I16" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1199,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>1402.6</v>
+        <v>1895.6</v>
       </c>
       <c r="C17" s="2">
-        <v>9.359999999999999</v>
+        <v>-7.52</v>
       </c>
       <c r="D17" s="2">
-        <v>9.1</v>
+        <v>7.05</v>
       </c>
       <c r="E17" s="2">
-        <v>-1.33</v>
+        <v>13.29</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>86</v>
+        <v>30.61</v>
       </c>
       <c r="H17" s="2">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="I17" s="2">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1231,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>1031.8</v>
+        <v>1374.1</v>
       </c>
       <c r="C18" s="2">
-        <v>-3.19</v>
+        <v>5.1</v>
       </c>
       <c r="D18" s="2">
-        <v>-0.5</v>
+        <v>2.97</v>
       </c>
       <c r="E18" s="2">
-        <v>8.94</v>
+        <v>7.72</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H18" s="2">
+        <v>44</v>
+      </c>
+      <c r="I18" s="2">
         <v>54</v>
-      </c>
-      <c r="H18" s="2">
-        <v>60</v>
-      </c>
-      <c r="I18" s="2">
-        <v>28</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1263,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>4216.4</v>
+        <v>1459.8</v>
       </c>
       <c r="C19" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D19" s="2">
-        <v>3.94</v>
+        <v>3</v>
       </c>
       <c r="E19" s="2">
-        <v>3.43</v>
+        <v>4.35</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>82</v>
+        <v>73.47</v>
       </c>
       <c r="H19" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="I19" s="2">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,25 +1295,25 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>7598</v>
+        <v>4461.1</v>
       </c>
       <c r="C20" s="2">
-        <v>-5.79</v>
+        <v>4.41</v>
       </c>
       <c r="D20" s="2">
-        <v>5.68</v>
+        <v>0.43</v>
       </c>
       <c r="E20" s="2">
-        <v>5.87</v>
+        <v>6.41</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>74</v>
+        <v>63.27</v>
       </c>
       <c r="H20" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I20" s="2">
         <v>58</v>
@@ -1330,28 +1327,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>796.3</v>
+        <v>801.05</v>
       </c>
       <c r="C21" s="2">
-        <v>-10.45</v>
+        <v>-11.83</v>
       </c>
       <c r="D21" s="2">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="E21" s="2">
-        <v>8.720000000000001</v>
+        <v>10.24</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
+        <v>61.22</v>
+      </c>
+      <c r="H21" s="2">
         <v>26</v>
       </c>
-      <c r="H21" s="2">
+      <c r="I21" s="2">
         <v>36</v>
-      </c>
-      <c r="I21" s="2">
-        <v>18</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1359,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>4291.3</v>
+        <v>1910.4</v>
       </c>
       <c r="C22" s="2">
-        <v>2.68</v>
+        <v>-4.35</v>
       </c>
       <c r="D22" s="2">
-        <v>-5.18</v>
+        <v>4.96</v>
       </c>
       <c r="E22" s="2">
-        <v>5.31</v>
+        <v>5.35</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>76</v>
+        <v>44.9</v>
       </c>
       <c r="H22" s="2">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I22" s="2">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1391,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>1045.4</v>
+        <v>1342.1</v>
       </c>
       <c r="C23" s="2">
-        <v>-11.21</v>
+        <v>-3.22</v>
       </c>
       <c r="D23" s="2">
-        <v>-1.48</v>
+        <v>1.35</v>
       </c>
       <c r="E23" s="2">
-        <v>8.4</v>
+        <v>5.84</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>58</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H23" s="2">
         <v>70</v>
       </c>
       <c r="I23" s="2">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1423,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>13745</v>
+        <v>3136.9</v>
       </c>
       <c r="C24" s="2">
-        <v>-9.789999999999999</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="D24" s="2">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="E24" s="2">
-        <v>4.71</v>
+        <v>6.89</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>36</v>
+        <v>55.1</v>
       </c>
       <c r="H24" s="2">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="I24" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1455,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>3182.2</v>
+        <v>396.75</v>
       </c>
       <c r="C25" s="2">
-        <v>-9.94</v>
+        <v>-7.88</v>
       </c>
       <c r="D25" s="2">
-        <v>-0.5600000000000001</v>
+        <v>5.29</v>
       </c>
       <c r="E25" s="2">
-        <v>4.49</v>
+        <v>5.21</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
-        <v>16</v>
+        <v>77.55</v>
       </c>
       <c r="H25" s="2">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="I25" s="2">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1487,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>435.4</v>
+        <v>11723</v>
       </c>
       <c r="C26" s="2">
-        <v>7.88</v>
+        <v>-9.66</v>
       </c>
       <c r="D26" s="2">
-        <v>-0.76</v>
+        <v>-2.39</v>
       </c>
       <c r="E26" s="2">
-        <v>-4.91</v>
+        <v>8.6</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>68</v>
+        <v>36.73</v>
       </c>
       <c r="H26" s="2">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I26" s="2">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1519,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>2174.2</v>
+        <v>7339.5</v>
       </c>
       <c r="C27" s="2">
-        <v>-4.72</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="D27" s="2">
-        <v>-1.99</v>
+        <v>2.31</v>
       </c>
       <c r="E27" s="2">
-        <v>1.99</v>
+        <v>4.11</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>38</v>
+        <v>65.31</v>
       </c>
       <c r="H27" s="2">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="I27" s="2">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1551,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>1131.3</v>
+        <v>2201.2</v>
       </c>
       <c r="C28" s="2">
-        <v>0.77</v>
+        <v>-5.19</v>
       </c>
       <c r="D28" s="2">
-        <v>2.49</v>
+        <v>-4.5</v>
       </c>
       <c r="E28" s="2">
-        <v>-4</v>
+        <v>5.38</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>30</v>
+        <v>57.14</v>
       </c>
       <c r="H28" s="2">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I28" s="2">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1583,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>1850.7</v>
+        <v>4026.6</v>
       </c>
       <c r="C29" s="2">
-        <v>-7.68</v>
+        <v>-7.97</v>
       </c>
       <c r="D29" s="2">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="E29" s="2">
-        <v>1.19</v>
+        <v>3.9</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>52</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="H29" s="2">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="I29" s="2">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1615,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>290</v>
+        <v>289.95</v>
       </c>
       <c r="C30" s="2">
-        <v>-5.05</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="D30" s="2">
-        <v>-2.9</v>
+        <v>-1.97</v>
       </c>
       <c r="E30" s="2">
-        <v>1.08</v>
+        <v>3.76</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
+        <v>48.98</v>
+      </c>
+      <c r="H30" s="2">
         <v>32</v>
       </c>
-      <c r="H30" s="2">
+      <c r="I30" s="2">
         <v>26</v>
-      </c>
-      <c r="I30" s="2">
-        <v>24</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1647,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>255.15</v>
+        <v>1410.1</v>
       </c>
       <c r="C31" s="2">
-        <v>-10.54</v>
+        <v>0.52</v>
       </c>
       <c r="D31" s="2">
-        <v>1.01</v>
+        <v>3.74</v>
       </c>
       <c r="E31" s="2">
-        <v>1.82</v>
+        <v>-3.66</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>78</v>
+        <v>20.41</v>
       </c>
       <c r="H31" s="2">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I31" s="2">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1679,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>9843</v>
+        <v>239.35</v>
       </c>
       <c r="C32" s="2">
-        <v>2.27</v>
+        <v>-7.16</v>
       </c>
       <c r="D32" s="2">
-        <v>2.13</v>
+        <v>-5.63</v>
       </c>
       <c r="E32" s="2">
-        <v>-5.9</v>
+        <v>4.58</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>60</v>
+        <v>46.94</v>
       </c>
       <c r="H32" s="2">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="I32" s="2">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1711,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>1231</v>
+        <v>1116.7</v>
       </c>
       <c r="C33" s="2">
-        <v>-0.08</v>
+        <v>-3.9</v>
       </c>
       <c r="D33" s="2">
-        <v>-0.75</v>
+        <v>-2.96</v>
       </c>
       <c r="E33" s="2">
-        <v>-3.68</v>
+        <v>0.88</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>72</v>
+        <v>51.02</v>
       </c>
       <c r="H33" s="2">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="I33" s="2">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1743,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>1318.1</v>
+        <v>9785.5</v>
       </c>
       <c r="C34" s="2">
-        <v>-6.72</v>
+        <v>0.18</v>
       </c>
       <c r="D34" s="2">
-        <v>-2.99</v>
+        <v>2.7</v>
       </c>
       <c r="E34" s="2">
-        <v>0.23</v>
+        <v>-4.35</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>20</v>
+        <v>40.82</v>
       </c>
       <c r="H34" s="2">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="I34" s="2">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1775,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>239.43</v>
+        <v>1304</v>
       </c>
       <c r="C35" s="2">
-        <v>-9.289999999999999</v>
+        <v>-8.26</v>
       </c>
       <c r="D35" s="2">
-        <v>-1.82</v>
+        <v>-4.08</v>
       </c>
       <c r="E35" s="2">
-        <v>0.2</v>
+        <v>3.22</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>42</v>
+        <v>38.78</v>
       </c>
       <c r="H35" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="I35" s="2">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1807,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>11489</v>
+        <v>418.05</v>
       </c>
       <c r="C36" s="2">
-        <v>-11.37</v>
+        <v>-4.53</v>
       </c>
       <c r="D36" s="2">
-        <v>-3.34</v>
+        <v>-4.03</v>
       </c>
       <c r="E36" s="2">
-        <v>0.06</v>
+        <v>1.24</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>18</v>
+        <v>28.57</v>
       </c>
       <c r="H36" s="2">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="I36" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1839,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>283.9</v>
+        <v>1040</v>
       </c>
       <c r="C37" s="2">
-        <v>-1.15</v>
+        <v>-13.77</v>
       </c>
       <c r="D37" s="2">
-        <v>-10.75</v>
+        <v>-4.78</v>
       </c>
       <c r="E37" s="2">
-        <v>-2.29</v>
+        <v>5.91</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>46</v>
+        <v>53.06</v>
       </c>
       <c r="H37" s="2">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="I37" s="2">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1871,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>1437.1</v>
+        <v>1230.2</v>
       </c>
       <c r="C38" s="2">
-        <v>-6.34</v>
+        <v>-0.83</v>
       </c>
       <c r="D38" s="2">
-        <v>-4.92</v>
+        <v>-4.09</v>
       </c>
       <c r="E38" s="2">
-        <v>-3.15</v>
+        <v>-2.42</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>24</v>
+        <v>32.65</v>
       </c>
       <c r="H38" s="2">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="I38" s="2">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1903,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>1764.6</v>
+        <v>438.7</v>
       </c>
       <c r="C39" s="2">
-        <v>-12.78</v>
+        <v>2.98</v>
       </c>
       <c r="D39" s="2">
-        <v>-4.04</v>
+        <v>-3.05</v>
       </c>
       <c r="E39" s="2">
-        <v>-1.07</v>
+        <v>-5.64</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>22</v>
+        <v>34.69</v>
       </c>
       <c r="H39" s="2">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="I39" s="2">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1935,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>407.2</v>
+        <v>1788.7</v>
       </c>
       <c r="C40" s="2">
-        <v>-6.11</v>
+        <v>-15.09</v>
       </c>
       <c r="D40" s="2">
-        <v>-12</v>
+        <v>-1.47</v>
       </c>
       <c r="E40" s="2">
-        <v>-0.86</v>
+        <v>1.38</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>50</v>
+        <v>14.29</v>
       </c>
       <c r="H40" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I40" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1967,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>585.45</v>
+        <v>287.85</v>
       </c>
       <c r="C41" s="2">
-        <v>-15.68</v>
+        <v>-5.11</v>
       </c>
       <c r="D41" s="2">
-        <v>-4.69</v>
+        <v>-10.3</v>
       </c>
       <c r="E41" s="2">
-        <v>-1.22</v>
+        <v>-0.84</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>14</v>
+        <v>26.53</v>
       </c>
       <c r="H41" s="2">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="I41" s="2">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +1999,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>353.2</v>
+        <v>356.45</v>
       </c>
       <c r="C42" s="2">
-        <v>-6.34</v>
+        <v>-5.06</v>
       </c>
       <c r="D42" s="2">
-        <v>-1.1</v>
+        <v>-13.1</v>
       </c>
       <c r="E42" s="2">
-        <v>-9.59</v>
+        <v>-1.64</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>48</v>
+        <v>18.37</v>
       </c>
       <c r="H42" s="2">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I42" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2031,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>188.71</v>
+        <v>189.8</v>
       </c>
       <c r="C43" s="2">
-        <v>-5.21</v>
+        <v>-6.93</v>
       </c>
       <c r="D43" s="2">
-        <v>-9.199999999999999</v>
+        <v>-9.17</v>
       </c>
       <c r="E43" s="2">
-        <v>-7.41</v>
+        <v>-4.44</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
+        <v>16.33</v>
+      </c>
+      <c r="H43" s="2">
         <v>40</v>
       </c>
-      <c r="H43" s="2">
+      <c r="I43" s="2">
         <v>48</v>
-      </c>
-      <c r="I43" s="2">
-        <v>70</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2063,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>352.05</v>
+        <v>567.7</v>
       </c>
       <c r="C44" s="2">
-        <v>-3.02</v>
+        <v>-23.26</v>
       </c>
       <c r="D44" s="2">
-        <v>-10.56</v>
+        <v>-4.62</v>
       </c>
       <c r="E44" s="2">
-        <v>-9.01</v>
+        <v>0.92</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>28</v>
+        <v>24.49</v>
       </c>
       <c r="H44" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I44" s="2">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2101,25 +2098,25 @@
         <v>953.2</v>
       </c>
       <c r="C45" s="2">
-        <v>4.86</v>
+        <v>4.04</v>
       </c>
       <c r="D45" s="2">
-        <v>-8.26</v>
+        <v>-10.23</v>
       </c>
       <c r="E45" s="2">
-        <v>-15.4</v>
+        <v>-10.28</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
+        <v>12.24</v>
+      </c>
+      <c r="H45" s="2">
         <v>34</v>
       </c>
-      <c r="H45" s="2">
+      <c r="I45" s="2">
         <v>66</v>
-      </c>
-      <c r="I45" s="2">
-        <v>94</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,28 +2127,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>1744.9</v>
+        <v>1139</v>
       </c>
       <c r="C46" s="2">
-        <v>-14.1</v>
+        <v>-18.61</v>
       </c>
       <c r="D46" s="2">
-        <v>-11.47</v>
+        <v>-7.26</v>
       </c>
       <c r="E46" s="2">
-        <v>-4.66</v>
+        <v>-1.07</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>12</v>
+        <v>6.12</v>
       </c>
       <c r="H46" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I46" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2159,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>233.1</v>
+        <v>344.1</v>
       </c>
       <c r="C47" s="2">
-        <v>-10.78</v>
+        <v>-8.68</v>
       </c>
       <c r="D47" s="2">
-        <v>-17.94</v>
+        <v>-2.09</v>
       </c>
       <c r="E47" s="2">
-        <v>-12.17</v>
+        <v>-10.81</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>10</v>
+        <v>22.45</v>
       </c>
       <c r="H47" s="2">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="I47" s="2">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,28 +2191,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>2094.7</v>
+        <v>176.08</v>
       </c>
       <c r="C48" s="2">
-        <v>-21.14</v>
+        <v>-14.48</v>
       </c>
       <c r="D48" s="2">
-        <v>-17.76</v>
+        <v>-14.13</v>
       </c>
       <c r="E48" s="2">
-        <v>-7.27</v>
+        <v>-3.12</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>6</v>
+        <v>4.08</v>
       </c>
       <c r="H48" s="2">
         <v>4</v>
       </c>
       <c r="I48" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,28 +2223,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>1041.2</v>
+        <v>2093.5</v>
       </c>
       <c r="C49" s="2">
-        <v>-22.3</v>
+        <v>-20.72</v>
       </c>
       <c r="D49" s="2">
-        <v>-19.33</v>
+        <v>-13.31</v>
       </c>
       <c r="E49" s="2">
-        <v>-8.369999999999999</v>
+        <v>-2.69</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>2</v>
+        <v>8.16</v>
       </c>
       <c r="H49" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I49" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,28 +2255,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>1100.7</v>
+        <v>1047.2</v>
       </c>
       <c r="C50" s="2">
-        <v>-22.91</v>
+        <v>-19.41</v>
       </c>
       <c r="D50" s="2">
-        <v>-22.22</v>
+        <v>-8.58</v>
       </c>
       <c r="E50" s="2">
-        <v>-7.02</v>
+        <v>-9.91</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
-        <v>8</v>
+        <v>2.04</v>
       </c>
       <c r="H50" s="2">
         <v>2</v>
       </c>
       <c r="I50" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2287,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>175</v>
+        <v>237.84</v>
       </c>
       <c r="C51" s="2">
-        <v>-18.26</v>
+        <v>-13.72</v>
       </c>
       <c r="D51" s="2">
-        <v>-14.35</v>
+        <v>-16.81</v>
       </c>
       <c r="E51" s="2">
-        <v>-14.32</v>
+        <v>-10.13</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
-        <v>4</v>
+        <v>10.2</v>
       </c>
       <c r="H51" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I51" s="2">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2462,16 +2459,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3038</v>
+        <v>3212.1</v>
       </c>
       <c r="C2" s="2">
-        <v>42.25</v>
+        <v>46.67</v>
       </c>
       <c r="D2" s="2">
-        <v>37.01</v>
+        <v>38.41</v>
       </c>
       <c r="E2" s="2">
-        <v>3.47</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2488,28 +2485,28 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>3216.2</v>
+        <v>3340.6</v>
       </c>
       <c r="C3" s="2">
-        <v>13.63</v>
+        <v>23.76</v>
       </c>
       <c r="D3" s="2">
-        <v>17.62</v>
+        <v>17.78</v>
       </c>
       <c r="E3" s="2">
-        <v>14.38</v>
+        <v>22.81</v>
       </c>
       <c r="F3" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G3" s="2">
+        <v>95.92</v>
+      </c>
+      <c r="H3" s="2">
         <v>98</v>
-      </c>
-      <c r="H3" s="2">
-        <v>86</v>
       </c>
       <c r="I3" s="2">
         <v>86</v>
@@ -2517,31 +2514,31 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>8592</v>
+        <v>5426.5</v>
       </c>
       <c r="C4" s="2">
-        <v>14.07</v>
+        <v>11.61</v>
       </c>
       <c r="D4" s="2">
-        <v>11.6</v>
+        <v>18.97</v>
       </c>
       <c r="E4" s="2">
-        <v>5.08</v>
+        <v>24.47</v>
       </c>
       <c r="F4" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>88</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="H4" s="2">
         <v>92</v>
       </c>
       <c r="I4" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2549,25 +2546,25 @@
         <v>15</v>
       </c>
       <c r="B5" s="1">
-        <v>1796</v>
+        <v>1874.2</v>
       </c>
       <c r="C5" s="2">
-        <v>18.73</v>
+        <v>20.97</v>
       </c>
       <c r="D5" s="2">
-        <v>14.63</v>
+        <v>15.57</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.06</v>
+        <v>4.27</v>
       </c>
       <c r="F5" s="2">
         <v>88</v>
       </c>
       <c r="G5" s="2">
+        <v>89.8</v>
+      </c>
+      <c r="H5" s="2">
         <v>96</v>
-      </c>
-      <c r="H5" s="2">
-        <v>98</v>
       </c>
       <c r="I5" s="2">
         <v>98</v>
@@ -2578,28 +2575,28 @@
         <v>17</v>
       </c>
       <c r="B6" s="1">
-        <v>3126.6</v>
+        <v>8893.5</v>
       </c>
       <c r="C6" s="2">
-        <v>8.26</v>
+        <v>15.61</v>
       </c>
       <c r="D6" s="2">
-        <v>14.93</v>
+        <v>13.65</v>
       </c>
       <c r="E6" s="2">
-        <v>0.13</v>
+        <v>6.4</v>
       </c>
       <c r="F6" s="2">
         <v>84</v>
       </c>
       <c r="G6" s="2">
-        <v>84</v>
+        <v>93.88</v>
       </c>
       <c r="H6" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I6" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -2653,7 +2650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2695,16 +2692,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3038</v>
+        <v>3212.1</v>
       </c>
       <c r="C2" s="2">
-        <v>42.25</v>
+        <v>46.67</v>
       </c>
       <c r="D2" s="2">
-        <v>37.01</v>
+        <v>38.41</v>
       </c>
       <c r="E2" s="2">
-        <v>3.47</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2724,28 +2721,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>5450</v>
+        <v>3340.6</v>
       </c>
       <c r="C3" s="2">
-        <v>10.57</v>
+        <v>23.76</v>
       </c>
       <c r="D3" s="2">
-        <v>17.5</v>
+        <v>17.78</v>
       </c>
       <c r="E3" s="2">
-        <v>23.72</v>
+        <v>22.81</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>92</v>
+        <v>95.92</v>
       </c>
       <c r="H3" s="2">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="I3" s="2">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2753,28 +2750,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>3216.2</v>
+        <v>5426.5</v>
       </c>
       <c r="C4" s="2">
-        <v>13.63</v>
+        <v>11.61</v>
       </c>
       <c r="D4" s="2">
-        <v>17.62</v>
+        <v>18.97</v>
       </c>
       <c r="E4" s="2">
-        <v>14.38</v>
+        <v>24.47</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>98</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="H4" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I4" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2782,148 +2779,119 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1123.35</v>
+        <v>1031.4</v>
       </c>
       <c r="C5" s="2">
-        <v>6.62</v>
+        <v>0.65</v>
       </c>
       <c r="D5" s="2">
-        <v>11.48</v>
+        <v>12.58</v>
       </c>
       <c r="E5" s="2">
-        <v>16.4</v>
+        <v>19.13</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>94</v>
+        <v>81.63</v>
       </c>
       <c r="H5" s="2">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="I5" s="2">
-        <v>34</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>8592</v>
+        <v>1874.2</v>
       </c>
       <c r="C6" s="2">
-        <v>14.07</v>
+        <v>20.97</v>
       </c>
       <c r="D6" s="2">
-        <v>11.6</v>
+        <v>15.57</v>
       </c>
       <c r="E6" s="2">
-        <v>5.08</v>
+        <v>4.27</v>
       </c>
       <c r="F6" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G6" s="2">
-        <v>88</v>
+        <v>89.8</v>
       </c>
       <c r="H6" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I6" s="2">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1">
-        <v>1796</v>
+        <v>8893.5</v>
       </c>
       <c r="C7" s="2">
-        <v>18.73</v>
+        <v>15.61</v>
       </c>
       <c r="D7" s="2">
-        <v>14.63</v>
+        <v>13.65</v>
       </c>
       <c r="E7" s="2">
-        <v>-0.06</v>
+        <v>6.4</v>
       </c>
       <c r="F7" s="2">
+        <v>84</v>
+      </c>
+      <c r="G7" s="2">
+        <v>93.88</v>
+      </c>
+      <c r="H7" s="2">
         <v>88</v>
       </c>
-      <c r="G7" s="2">
-        <v>96</v>
-      </c>
-      <c r="H7" s="2">
-        <v>98</v>
-      </c>
       <c r="I7" s="2">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1">
-        <v>1862.8</v>
+        <v>1411.4</v>
       </c>
       <c r="C8" s="2">
-        <v>9.74</v>
+        <v>0.86</v>
       </c>
       <c r="D8" s="2">
-        <v>11.18</v>
+        <v>7.4</v>
       </c>
       <c r="E8" s="2">
-        <v>3.53</v>
+        <v>12.89</v>
       </c>
       <c r="F8" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G8" s="2">
-        <v>80</v>
+        <v>83.67</v>
       </c>
       <c r="H8" s="2">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I8" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1">
-        <v>3126.6</v>
-      </c>
-      <c r="C9" s="2">
-        <v>8.26</v>
-      </c>
-      <c r="D9" s="2">
-        <v>14.93</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="F9" s="2">
-        <v>84</v>
-      </c>
-      <c r="G9" s="2">
-        <v>84</v>
-      </c>
-      <c r="H9" s="2">
-        <v>90</v>
-      </c>
-      <c r="I9" s="2">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C2:C8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2931,7 +2899,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D8">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2939,7 +2907,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E8">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2947,22 +2915,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G8">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H8">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
+  <conditionalFormatting sqref="I2:I8">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -3001,10 +2969,10 @@
         <v>62</v>
       </c>
       <c r="C2" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D2" s="2">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3012,13 +2980,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C3" s="2">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D3" s="2">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3026,13 +2994,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C4" s="2">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3040,13 +3008,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-07-03</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-07-03</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-07-03</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-07-03</t>
+    <t>Price_2026-07-10</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-07-10</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-07-10</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-07-10</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-07-10</t>
   </si>
   <si>
     <t>RS_Score_2026-07-03</t>
@@ -43,159 +46,156 @@
     <t>RS_Score_2026-06-19</t>
   </si>
   <si>
-    <t>RS_Score_2026-06-12</t>
-  </si>
-  <si>
     <t>ADANIENT</t>
   </si>
   <si>
+    <t>ETERNAL</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
     <t>TRENT</t>
   </si>
   <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>TMPV</t>
+  </si>
+  <si>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>LT</t>
   </si>
   <si>
     <t>MAXHEALTH</t>
   </si>
   <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>ADANIPORTS</t>
-  </si>
-  <si>
-    <t>ETERNAL</t>
-  </si>
-  <si>
     <t>APOLLOHOSP</t>
   </si>
   <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
+    <t>HCLTECH</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
   </si>
   <si>
     <t>CIPLA</t>
   </si>
   <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>TITAN</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
     <t>TATACONSUM</t>
   </si>
   <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
-    <t>HINDALCO</t>
-  </si>
-  <si>
-    <t>HCLTECH</t>
-  </si>
-  <si>
-    <t>TMPV</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>ONGC</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
     <t>2026-07-03</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3212.1</v>
+        <v>3157.3</v>
       </c>
       <c r="C2" s="2">
-        <v>46.67</v>
+        <v>48.67</v>
       </c>
       <c r="D2" s="2">
-        <v>38.41</v>
+        <v>27.08</v>
       </c>
       <c r="E2" s="2">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>3340.6</v>
+        <v>289.65</v>
       </c>
       <c r="C3" s="2">
-        <v>23.76</v>
+        <v>19.26</v>
       </c>
       <c r="D3" s="2">
-        <v>17.78</v>
+        <v>14.99</v>
       </c>
       <c r="E3" s="2">
-        <v>22.81</v>
+        <v>14.94</v>
       </c>
       <c r="F3" s="2">
-        <v>98</v>
+        <v>97.22</v>
       </c>
       <c r="G3" s="2">
-        <v>95.92</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="I3" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>5426.5</v>
+        <v>5312</v>
       </c>
       <c r="C4" s="2">
-        <v>11.61</v>
+        <v>17.51</v>
       </c>
       <c r="D4" s="2">
-        <v>18.97</v>
+        <v>24.62</v>
       </c>
       <c r="E4" s="2">
-        <v>24.47</v>
+        <v>8.84</v>
       </c>
       <c r="F4" s="2">
+        <v>94.44</v>
+      </c>
+      <c r="G4" s="2">
         <v>96</v>
       </c>
-      <c r="G4" s="2">
-        <v>97.95999999999999</v>
-      </c>
       <c r="H4" s="2">
+        <v>98</v>
+      </c>
+      <c r="I4" s="2">
         <v>92</v>
-      </c>
-      <c r="I4" s="2">
-        <v>84</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1031.4</v>
+        <v>1828.1</v>
       </c>
       <c r="C5" s="2">
-        <v>0.65</v>
+        <v>24.86</v>
       </c>
       <c r="D5" s="2">
-        <v>12.58</v>
+        <v>5.35</v>
       </c>
       <c r="E5" s="2">
-        <v>19.13</v>
+        <v>1.29</v>
       </c>
       <c r="F5" s="2">
-        <v>94</v>
+        <v>91.67</v>
       </c>
       <c r="G5" s="2">
-        <v>81.63</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="I5" s="2">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,25 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>1153.4</v>
+        <v>1935.5</v>
       </c>
       <c r="C6" s="2">
-        <v>6.63</v>
+        <v>10.73</v>
       </c>
       <c r="D6" s="2">
-        <v>14.42</v>
+        <v>6.42</v>
       </c>
       <c r="E6" s="2">
-        <v>14.69</v>
+        <v>7.45</v>
       </c>
       <c r="F6" s="2">
-        <v>92</v>
+        <v>88.89</v>
+      </c>
+      <c r="G6" s="2">
+        <v>76</v>
       </c>
       <c r="H6" s="2">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I6" s="2">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -879,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>1063.6</v>
+        <v>3213.6</v>
       </c>
       <c r="C7" s="2">
-        <v>0.46</v>
+        <v>15.71</v>
       </c>
       <c r="D7" s="2">
-        <v>9.74</v>
+        <v>12.52</v>
       </c>
       <c r="E7" s="2">
-        <v>19.29</v>
+        <v>1.55</v>
       </c>
       <c r="F7" s="2">
-        <v>90</v>
+        <v>86.11</v>
       </c>
       <c r="G7" s="2">
-        <v>69.39</v>
+        <v>80</v>
       </c>
       <c r="H7" s="2">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="I7" s="2">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -911,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>1874.2</v>
+        <v>1020.5</v>
       </c>
       <c r="C8" s="2">
-        <v>20.97</v>
+        <v>4.96</v>
       </c>
       <c r="D8" s="2">
-        <v>15.57</v>
+        <v>8.06</v>
       </c>
       <c r="E8" s="2">
-        <v>4.27</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F8" s="2">
-        <v>88</v>
+        <v>83.33</v>
       </c>
       <c r="G8" s="2">
-        <v>89.8</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="I8" s="2">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -943,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>281.65</v>
+        <v>4584.4</v>
       </c>
       <c r="C9" s="2">
-        <v>5.09</v>
+        <v>7.71</v>
       </c>
       <c r="D9" s="2">
-        <v>10.24</v>
+        <v>5.42</v>
       </c>
       <c r="E9" s="2">
-        <v>13.43</v>
+        <v>7.38</v>
       </c>
       <c r="F9" s="2">
-        <v>86</v>
+        <v>80.56</v>
       </c>
       <c r="G9" s="2">
-        <v>42.86</v>
+        <v>64</v>
       </c>
       <c r="H9" s="2">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="I9" s="2">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -975,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>8893.5</v>
+        <v>2677.8</v>
       </c>
       <c r="C10" s="2">
-        <v>15.61</v>
+        <v>17.07</v>
       </c>
       <c r="D10" s="2">
-        <v>13.65</v>
+        <v>10.33</v>
       </c>
       <c r="E10" s="2">
-        <v>6.4</v>
+        <v>-1.4</v>
       </c>
       <c r="F10" s="2">
-        <v>84</v>
+        <v>77.78</v>
       </c>
       <c r="G10" s="2">
-        <v>93.88</v>
+        <v>74</v>
       </c>
       <c r="H10" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="I10" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1007,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>1411.4</v>
+        <v>1454.8</v>
       </c>
       <c r="C11" s="2">
-        <v>0.86</v>
+        <v>10.94</v>
       </c>
       <c r="D11" s="2">
-        <v>7.4</v>
+        <v>1.43</v>
       </c>
       <c r="E11" s="2">
-        <v>12.89</v>
+        <v>4.7</v>
       </c>
       <c r="F11" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G11" s="2">
-        <v>83.67</v>
+        <v>42</v>
       </c>
       <c r="H11" s="2">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="I11" s="2">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1039,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>3180.9</v>
+        <v>1044.1</v>
       </c>
       <c r="C12" s="2">
-        <v>10.7</v>
+        <v>-0.24</v>
       </c>
       <c r="D12" s="2">
-        <v>14.49</v>
+        <v>9.32</v>
       </c>
       <c r="E12" s="2">
-        <v>4.29</v>
+        <v>4.93</v>
       </c>
       <c r="F12" s="2">
-        <v>80</v>
+        <v>72.22</v>
       </c>
       <c r="G12" s="2">
-        <v>79.59</v>
+        <v>90</v>
       </c>
       <c r="H12" s="2">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="I12" s="2">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1071,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>1458.2</v>
+        <v>824.95</v>
       </c>
       <c r="C13" s="2">
-        <v>10.96</v>
+        <v>-4.64</v>
       </c>
       <c r="D13" s="2">
-        <v>11.74</v>
+        <v>7.59</v>
       </c>
       <c r="E13" s="2">
-        <v>5.07</v>
+        <v>7.88</v>
       </c>
       <c r="F13" s="2">
-        <v>78</v>
+        <v>69.44</v>
       </c>
       <c r="G13" s="2">
-        <v>91.84</v>
+        <v>62</v>
       </c>
       <c r="H13" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I13" s="2">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1103,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>1904.8</v>
+        <v>2902.8</v>
       </c>
       <c r="C14" s="2">
-        <v>9.960000000000001</v>
+        <v>13.31</v>
       </c>
       <c r="D14" s="2">
-        <v>9.880000000000001</v>
+        <v>4.86</v>
       </c>
       <c r="E14" s="2">
-        <v>6.48</v>
+        <v>0.06</v>
       </c>
       <c r="F14" s="2">
-        <v>76</v>
+        <v>66.67</v>
       </c>
       <c r="G14" s="2">
-        <v>87.76000000000001</v>
+        <v>98</v>
       </c>
       <c r="H14" s="2">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I14" s="2">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1135,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>2737.8</v>
+        <v>1862.9</v>
       </c>
       <c r="C15" s="2">
-        <v>13.66</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="D15" s="2">
-        <v>11.12</v>
+        <v>2.35</v>
       </c>
       <c r="E15" s="2">
-        <v>3.85</v>
+        <v>5.88</v>
       </c>
       <c r="F15" s="2">
-        <v>74</v>
+        <v>63.89</v>
       </c>
       <c r="G15" s="2">
-        <v>75.51000000000001</v>
+        <v>24</v>
       </c>
       <c r="H15" s="2">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="I15" s="2">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1167,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>14366</v>
+        <v>13854</v>
       </c>
       <c r="C16" s="2">
-        <v>-4.68</v>
+        <v>-3.71</v>
       </c>
       <c r="D16" s="2">
-        <v>8.65</v>
+        <v>2.02</v>
       </c>
       <c r="E16" s="2">
-        <v>11.26</v>
+        <v>0.35</v>
       </c>
       <c r="F16" s="2">
+        <v>61.11</v>
+      </c>
+      <c r="G16" s="2">
         <v>72</v>
       </c>
-      <c r="G16" s="2">
-        <v>59.18</v>
-      </c>
       <c r="H16" s="2">
+        <v>58</v>
+      </c>
+      <c r="I16" s="2">
         <v>36</v>
-      </c>
-      <c r="I16" s="2">
-        <v>50</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1199,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>1895.6</v>
+        <v>11711</v>
       </c>
       <c r="C17" s="2">
-        <v>-7.52</v>
+        <v>-6.47</v>
       </c>
       <c r="D17" s="2">
-        <v>7.05</v>
+        <v>-0.4</v>
       </c>
       <c r="E17" s="2">
-        <v>13.29</v>
+        <v>2.14</v>
       </c>
       <c r="F17" s="2">
-        <v>70</v>
+        <v>58.33</v>
       </c>
       <c r="G17" s="2">
-        <v>30.61</v>
+        <v>52</v>
       </c>
       <c r="H17" s="2">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I17" s="2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1231,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>1374.1</v>
+        <v>241.96</v>
       </c>
       <c r="C18" s="2">
-        <v>5.1</v>
+        <v>-2.83</v>
       </c>
       <c r="D18" s="2">
-        <v>2.97</v>
+        <v>-4.27</v>
       </c>
       <c r="E18" s="2">
-        <v>7.72</v>
+        <v>1.02</v>
       </c>
       <c r="F18" s="2">
-        <v>68</v>
+        <v>55.56</v>
       </c>
       <c r="G18" s="2">
-        <v>85.70999999999999</v>
+        <v>40</v>
       </c>
       <c r="H18" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I18" s="2">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1263,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1459.8</v>
+        <v>1323.7</v>
       </c>
       <c r="C19" s="2">
-        <v>11</v>
+        <v>-3.47</v>
       </c>
       <c r="D19" s="2">
-        <v>3</v>
+        <v>3.89</v>
       </c>
       <c r="E19" s="2">
-        <v>4.35</v>
+        <v>-3.18</v>
       </c>
       <c r="F19" s="2">
-        <v>66</v>
+        <v>52.78</v>
       </c>
       <c r="G19" s="2">
-        <v>73.47</v>
+        <v>58</v>
       </c>
       <c r="H19" s="2">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="I19" s="2">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1295,25 +1298,25 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>4461.1</v>
+        <v>1036</v>
       </c>
       <c r="C20" s="2">
-        <v>4.41</v>
+        <v>-11.36</v>
       </c>
       <c r="D20" s="2">
-        <v>0.43</v>
+        <v>-1.28</v>
       </c>
       <c r="E20" s="2">
-        <v>6.41</v>
+        <v>1.48</v>
       </c>
       <c r="F20" s="2">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G20" s="2">
-        <v>63.27</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="I20" s="2">
         <v>58</v>
@@ -1327,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>801.05</v>
+        <v>414.85</v>
       </c>
       <c r="C21" s="2">
-        <v>-11.83</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="D21" s="2">
-        <v>3.1</v>
+        <v>-4.31</v>
       </c>
       <c r="E21" s="2">
-        <v>10.24</v>
+        <v>1.29</v>
       </c>
       <c r="F21" s="2">
-        <v>62</v>
+        <v>47.22</v>
       </c>
       <c r="G21" s="2">
-        <v>61.22</v>
+        <v>32</v>
       </c>
       <c r="H21" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I21" s="2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1359,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>1910.4</v>
+        <v>2150.6</v>
       </c>
       <c r="C22" s="2">
-        <v>-4.35</v>
+        <v>-6.38</v>
       </c>
       <c r="D22" s="2">
-        <v>4.96</v>
+        <v>-5.92</v>
       </c>
       <c r="E22" s="2">
-        <v>5.35</v>
+        <v>0.76</v>
       </c>
       <c r="F22" s="2">
-        <v>60</v>
+        <v>44.44</v>
       </c>
       <c r="G22" s="2">
-        <v>44.9</v>
+        <v>48</v>
       </c>
       <c r="H22" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I22" s="2">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1391,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>1342.1</v>
+        <v>967.45</v>
       </c>
       <c r="C23" s="2">
-        <v>-3.22</v>
+        <v>3.46</v>
       </c>
       <c r="D23" s="2">
-        <v>1.35</v>
+        <v>-6.73</v>
       </c>
       <c r="E23" s="2">
-        <v>5.84</v>
+        <v>-4.08</v>
       </c>
       <c r="F23" s="2">
-        <v>58</v>
+        <v>41.67</v>
       </c>
       <c r="G23" s="2">
-        <v>71.43000000000001</v>
+        <v>14</v>
       </c>
       <c r="H23" s="2">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="I23" s="2">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1423,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>3136.9</v>
+        <v>7365.5</v>
       </c>
       <c r="C24" s="2">
-        <v>-8.029999999999999</v>
+        <v>-5.88</v>
       </c>
       <c r="D24" s="2">
-        <v>2.19</v>
+        <v>0.5</v>
       </c>
       <c r="E24" s="2">
-        <v>6.89</v>
+        <v>-3.4</v>
       </c>
       <c r="F24" s="2">
-        <v>56</v>
+        <v>38.89</v>
       </c>
       <c r="G24" s="2">
-        <v>55.1</v>
+        <v>50</v>
       </c>
       <c r="H24" s="2">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="I24" s="2">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1455,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>396.75</v>
+        <v>1307.8</v>
       </c>
       <c r="C25" s="2">
-        <v>-7.88</v>
+        <v>-3.25</v>
       </c>
       <c r="D25" s="2">
-        <v>5.29</v>
+        <v>-10.2</v>
       </c>
       <c r="E25" s="2">
-        <v>5.21</v>
+        <v>0.06</v>
       </c>
       <c r="F25" s="2">
-        <v>54</v>
+        <v>36.11</v>
       </c>
       <c r="G25" s="2">
-        <v>77.55</v>
+        <v>34</v>
       </c>
       <c r="H25" s="2">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I25" s="2">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1487,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>11723</v>
+        <v>429.3</v>
       </c>
       <c r="C26" s="2">
-        <v>-9.66</v>
+        <v>0.72</v>
       </c>
       <c r="D26" s="2">
-        <v>-2.39</v>
+        <v>-10.55</v>
       </c>
       <c r="E26" s="2">
-        <v>8.6</v>
+        <v>-3.32</v>
       </c>
       <c r="F26" s="2">
-        <v>52</v>
+        <v>33.33</v>
       </c>
       <c r="G26" s="2">
-        <v>36.73</v>
+        <v>26</v>
       </c>
       <c r="H26" s="2">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I26" s="2">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1519,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>7339.5</v>
+        <v>283.1</v>
       </c>
       <c r="C27" s="2">
-        <v>-8.699999999999999</v>
+        <v>-4.62</v>
       </c>
       <c r="D27" s="2">
-        <v>2.31</v>
+        <v>-11.27</v>
       </c>
       <c r="E27" s="2">
-        <v>4.11</v>
+        <v>-0.91</v>
       </c>
       <c r="F27" s="2">
-        <v>50</v>
+        <v>30.56</v>
       </c>
       <c r="G27" s="2">
-        <v>65.31</v>
+        <v>22</v>
       </c>
       <c r="H27" s="2">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="I27" s="2">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1551,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>2201.2</v>
+        <v>281.75</v>
       </c>
       <c r="C28" s="2">
-        <v>-5.19</v>
+        <v>-8.09</v>
       </c>
       <c r="D28" s="2">
-        <v>-4.5</v>
+        <v>-6.97</v>
       </c>
       <c r="E28" s="2">
-        <v>5.38</v>
+        <v>-2.14</v>
       </c>
       <c r="F28" s="2">
+        <v>27.78</v>
+      </c>
+      <c r="G28" s="2">
+        <v>44</v>
+      </c>
+      <c r="H28" s="2">
         <v>48</v>
       </c>
-      <c r="G28" s="2">
-        <v>57.14</v>
-      </c>
-      <c r="H28" s="2">
-        <v>38</v>
-      </c>
       <c r="I28" s="2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1583,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>4026.6</v>
+        <v>377.6</v>
       </c>
       <c r="C29" s="2">
-        <v>-7.97</v>
+        <v>-8.59</v>
       </c>
       <c r="D29" s="2">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="E29" s="2">
-        <v>3.9</v>
+        <v>-6.94</v>
       </c>
       <c r="F29" s="2">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="G29" s="2">
-        <v>67.34999999999999</v>
+        <v>54</v>
       </c>
       <c r="H29" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I29" s="2">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1615,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>289.95</v>
+        <v>191.19</v>
       </c>
       <c r="C30" s="2">
-        <v>-8.470000000000001</v>
+        <v>-7.52</v>
       </c>
       <c r="D30" s="2">
-        <v>-1.97</v>
+        <v>-8.06</v>
       </c>
       <c r="E30" s="2">
-        <v>3.76</v>
+        <v>-3.09</v>
       </c>
       <c r="F30" s="2">
-        <v>44</v>
+        <v>22.22</v>
       </c>
       <c r="G30" s="2">
-        <v>48.98</v>
+        <v>18</v>
       </c>
       <c r="H30" s="2">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I30" s="2">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1647,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>1410.1</v>
+        <v>344.55</v>
       </c>
       <c r="C31" s="2">
-        <v>0.52</v>
+        <v>-8.74</v>
       </c>
       <c r="D31" s="2">
-        <v>3.74</v>
+        <v>-13.87</v>
       </c>
       <c r="E31" s="2">
-        <v>-3.66</v>
+        <v>-1.02</v>
       </c>
       <c r="F31" s="2">
-        <v>42</v>
+        <v>19.44</v>
       </c>
       <c r="G31" s="2">
-        <v>20.41</v>
+        <v>20</v>
       </c>
       <c r="H31" s="2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I31" s="2">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1679,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>239.35</v>
+        <v>567.7</v>
       </c>
       <c r="C32" s="2">
-        <v>-7.16</v>
+        <v>-19.45</v>
       </c>
       <c r="D32" s="2">
-        <v>-5.63</v>
+        <v>-3.17</v>
       </c>
       <c r="E32" s="2">
-        <v>4.58</v>
+        <v>-1.97</v>
       </c>
       <c r="F32" s="2">
-        <v>40</v>
+        <v>16.67</v>
       </c>
       <c r="G32" s="2">
-        <v>46.94</v>
+        <v>16</v>
       </c>
       <c r="H32" s="2">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="I32" s="2">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1711,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>1116.7</v>
+        <v>244.96</v>
       </c>
       <c r="C33" s="2">
-        <v>-3.9</v>
+        <v>-13.2</v>
       </c>
       <c r="D33" s="2">
-        <v>-2.96</v>
+        <v>-16.37</v>
       </c>
       <c r="E33" s="2">
-        <v>0.88</v>
+        <v>0.54</v>
       </c>
       <c r="F33" s="2">
-        <v>38</v>
+        <v>13.89</v>
       </c>
       <c r="G33" s="2">
-        <v>51.02</v>
+        <v>2</v>
       </c>
       <c r="H33" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I33" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1743,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>9785.5</v>
+        <v>175.46</v>
       </c>
       <c r="C34" s="2">
-        <v>0.18</v>
+        <v>-11.64</v>
       </c>
       <c r="D34" s="2">
-        <v>2.7</v>
+        <v>-12.6</v>
       </c>
       <c r="E34" s="2">
-        <v>-4.35</v>
+        <v>-3.26</v>
       </c>
       <c r="F34" s="2">
-        <v>36</v>
+        <v>11.11</v>
       </c>
       <c r="G34" s="2">
-        <v>40.82</v>
+        <v>8</v>
       </c>
       <c r="H34" s="2">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="I34" s="2">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1775,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>1304</v>
+        <v>1068</v>
       </c>
       <c r="C35" s="2">
-        <v>-8.26</v>
+        <v>-15.35</v>
       </c>
       <c r="D35" s="2">
-        <v>-4.08</v>
+        <v>-6.61</v>
       </c>
       <c r="E35" s="2">
-        <v>3.22</v>
+        <v>-5.89</v>
       </c>
       <c r="F35" s="2">
-        <v>34</v>
+        <v>8.33</v>
       </c>
       <c r="G35" s="2">
-        <v>38.78</v>
+        <v>4</v>
       </c>
       <c r="H35" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I35" s="2">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1807,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>418.05</v>
+        <v>337.95</v>
       </c>
       <c r="C36" s="2">
-        <v>-4.53</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="D36" s="2">
-        <v>-4.03</v>
+        <v>-0.67</v>
       </c>
       <c r="E36" s="2">
-        <v>1.24</v>
+        <v>-14.04</v>
       </c>
       <c r="F36" s="2">
-        <v>32</v>
+        <v>5.56</v>
       </c>
       <c r="G36" s="2">
-        <v>28.57</v>
+        <v>10</v>
       </c>
       <c r="H36" s="2">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I36" s="2">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1839,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>1040</v>
+        <v>2069</v>
       </c>
       <c r="C37" s="2">
-        <v>-13.77</v>
+        <v>-19.76</v>
       </c>
       <c r="D37" s="2">
-        <v>-4.78</v>
+        <v>-13.75</v>
       </c>
       <c r="E37" s="2">
-        <v>5.91</v>
+        <v>-4.3</v>
       </c>
       <c r="F37" s="2">
-        <v>30</v>
+        <v>2.78</v>
       </c>
       <c r="G37" s="2">
-        <v>53.06</v>
+        <v>6</v>
       </c>
       <c r="H37" s="2">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="I37" s="2">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1870,29 +1873,14 @@
       <c r="A38" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="1">
-        <v>1230.2</v>
-      </c>
-      <c r="C38" s="2">
-        <v>-0.83</v>
-      </c>
-      <c r="D38" s="2">
-        <v>-4.09</v>
-      </c>
-      <c r="E38" s="2">
-        <v>-2.42</v>
-      </c>
-      <c r="F38" s="2">
-        <v>28</v>
-      </c>
       <c r="G38" s="2">
-        <v>32.65</v>
+        <v>82</v>
       </c>
       <c r="H38" s="2">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="I38" s="2">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1902,29 +1890,14 @@
       <c r="A39" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B39" s="1">
-        <v>438.7</v>
-      </c>
-      <c r="C39" s="2">
-        <v>2.98</v>
-      </c>
-      <c r="D39" s="2">
-        <v>-3.05</v>
-      </c>
-      <c r="E39" s="2">
-        <v>-5.64</v>
-      </c>
-      <c r="F39" s="2">
-        <v>26</v>
-      </c>
       <c r="G39" s="2">
-        <v>34.69</v>
+        <v>60</v>
       </c>
       <c r="H39" s="2">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="I39" s="2">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1934,29 +1907,14 @@
       <c r="A40" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="1">
-        <v>1788.7</v>
-      </c>
-      <c r="C40" s="2">
-        <v>-15.09</v>
-      </c>
-      <c r="D40" s="2">
-        <v>-1.47</v>
-      </c>
-      <c r="E40" s="2">
-        <v>1.38</v>
-      </c>
-      <c r="F40" s="2">
-        <v>24</v>
-      </c>
       <c r="G40" s="2">
-        <v>14.29</v>
+        <v>56</v>
       </c>
       <c r="H40" s="2">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="I40" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1966,29 +1924,14 @@
       <c r="A41" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B41" s="1">
-        <v>287.85</v>
-      </c>
-      <c r="C41" s="2">
-        <v>-5.11</v>
-      </c>
-      <c r="D41" s="2">
-        <v>-10.3</v>
-      </c>
-      <c r="E41" s="2">
-        <v>-0.84</v>
-      </c>
-      <c r="F41" s="2">
-        <v>22</v>
-      </c>
       <c r="G41" s="2">
-        <v>26.53</v>
+        <v>46</v>
       </c>
       <c r="H41" s="2">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="I41" s="2">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -1998,29 +1941,14 @@
       <c r="A42" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="1">
-        <v>356.45</v>
-      </c>
-      <c r="C42" s="2">
-        <v>-5.06</v>
-      </c>
-      <c r="D42" s="2">
-        <v>-13.1</v>
-      </c>
-      <c r="E42" s="2">
-        <v>-1.64</v>
-      </c>
-      <c r="F42" s="2">
-        <v>20</v>
-      </c>
       <c r="G42" s="2">
-        <v>18.37</v>
+        <v>92</v>
       </c>
       <c r="H42" s="2">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="I42" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2030,29 +1958,14 @@
       <c r="A43" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B43" s="1">
-        <v>189.8</v>
-      </c>
-      <c r="C43" s="2">
-        <v>-6.93</v>
-      </c>
-      <c r="D43" s="2">
-        <v>-9.17</v>
-      </c>
-      <c r="E43" s="2">
-        <v>-4.44</v>
-      </c>
-      <c r="F43" s="2">
-        <v>18</v>
-      </c>
       <c r="G43" s="2">
-        <v>16.33</v>
+        <v>84</v>
       </c>
       <c r="H43" s="2">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="I43" s="2">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2062,29 +1975,14 @@
       <c r="A44" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B44" s="1">
-        <v>567.7</v>
-      </c>
-      <c r="C44" s="2">
-        <v>-23.26</v>
-      </c>
-      <c r="D44" s="2">
-        <v>-4.62</v>
-      </c>
-      <c r="E44" s="2">
-        <v>0.92</v>
-      </c>
-      <c r="F44" s="2">
-        <v>16</v>
-      </c>
       <c r="G44" s="2">
-        <v>24.49</v>
+        <v>12</v>
       </c>
       <c r="H44" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I44" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2094,29 +1992,14 @@
       <c r="A45" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B45" s="1">
-        <v>953.2</v>
-      </c>
-      <c r="C45" s="2">
-        <v>4.04</v>
-      </c>
-      <c r="D45" s="2">
-        <v>-10.23</v>
-      </c>
-      <c r="E45" s="2">
-        <v>-10.28</v>
-      </c>
-      <c r="F45" s="2">
-        <v>14</v>
-      </c>
       <c r="G45" s="2">
-        <v>12.24</v>
+        <v>66</v>
       </c>
       <c r="H45" s="2">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="I45" s="2">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2126,29 +2009,14 @@
       <c r="A46" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="1">
-        <v>1139</v>
-      </c>
-      <c r="C46" s="2">
-        <v>-18.61</v>
-      </c>
-      <c r="D46" s="2">
-        <v>-7.26</v>
-      </c>
-      <c r="E46" s="2">
-        <v>-1.07</v>
-      </c>
-      <c r="F46" s="2">
-        <v>12</v>
-      </c>
       <c r="G46" s="2">
-        <v>6.12</v>
+        <v>28</v>
       </c>
       <c r="H46" s="2">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I46" s="2">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2158,29 +2026,14 @@
       <c r="A47" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B47" s="1">
-        <v>344.1</v>
-      </c>
-      <c r="C47" s="2">
-        <v>-8.68</v>
-      </c>
-      <c r="D47" s="2">
-        <v>-2.09</v>
-      </c>
-      <c r="E47" s="2">
-        <v>-10.81</v>
-      </c>
-      <c r="F47" s="2">
-        <v>10</v>
-      </c>
       <c r="G47" s="2">
-        <v>22.45</v>
+        <v>36</v>
       </c>
       <c r="H47" s="2">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I47" s="2">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2190,29 +2043,14 @@
       <c r="A48" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B48" s="1">
-        <v>176.08</v>
-      </c>
-      <c r="C48" s="2">
-        <v>-14.48</v>
-      </c>
-      <c r="D48" s="2">
-        <v>-14.13</v>
-      </c>
-      <c r="E48" s="2">
-        <v>-3.12</v>
-      </c>
-      <c r="F48" s="2">
-        <v>8</v>
-      </c>
       <c r="G48" s="2">
-        <v>4.08</v>
+        <v>70</v>
       </c>
       <c r="H48" s="2">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="I48" s="2">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2222,29 +2060,14 @@
       <c r="A49" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B49" s="1">
-        <v>2093.5</v>
-      </c>
-      <c r="C49" s="2">
-        <v>-20.72</v>
-      </c>
-      <c r="D49" s="2">
-        <v>-13.31</v>
-      </c>
-      <c r="E49" s="2">
-        <v>-2.69</v>
-      </c>
-      <c r="F49" s="2">
-        <v>6</v>
-      </c>
       <c r="G49" s="2">
-        <v>8.16</v>
+        <v>68</v>
       </c>
       <c r="H49" s="2">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="I49" s="2">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2254,29 +2077,14 @@
       <c r="A50" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B50" s="1">
-        <v>1047.2</v>
-      </c>
-      <c r="C50" s="2">
-        <v>-19.41</v>
-      </c>
-      <c r="D50" s="2">
-        <v>-8.58</v>
-      </c>
-      <c r="E50" s="2">
-        <v>-9.91</v>
-      </c>
-      <c r="F50" s="2">
-        <v>4</v>
-      </c>
       <c r="G50" s="2">
-        <v>2.04</v>
+        <v>78</v>
       </c>
       <c r="H50" s="2">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="I50" s="2">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2286,29 +2094,14 @@
       <c r="A51" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="1">
-        <v>237.84</v>
-      </c>
-      <c r="C51" s="2">
-        <v>-13.72</v>
-      </c>
-      <c r="D51" s="2">
-        <v>-16.81</v>
-      </c>
-      <c r="E51" s="2">
-        <v>-10.13</v>
-      </c>
-      <c r="F51" s="2">
-        <v>2</v>
-      </c>
       <c r="G51" s="2">
-        <v>10.2</v>
+        <v>38</v>
       </c>
       <c r="H51" s="2">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I51" s="2">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2417,7 +2210,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2459,16 +2252,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3212.1</v>
+        <v>3157.3</v>
       </c>
       <c r="C2" s="2">
-        <v>46.67</v>
+        <v>48.67</v>
       </c>
       <c r="D2" s="2">
-        <v>38.41</v>
+        <v>27.08</v>
       </c>
       <c r="E2" s="2">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2485,122 +2278,64 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1">
-        <v>3340.6</v>
+        <v>5312</v>
       </c>
       <c r="C3" s="2">
-        <v>23.76</v>
+        <v>17.51</v>
       </c>
       <c r="D3" s="2">
-        <v>17.78</v>
+        <v>24.62</v>
       </c>
       <c r="E3" s="2">
-        <v>22.81</v>
+        <v>8.84</v>
       </c>
       <c r="F3" s="2">
-        <v>98</v>
+        <v>94.44</v>
       </c>
       <c r="G3" s="2">
-        <v>95.92</v>
+        <v>96</v>
       </c>
       <c r="H3" s="2">
         <v>98</v>
       </c>
       <c r="I3" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>5426.5</v>
+        <v>1828.1</v>
       </c>
       <c r="C4" s="2">
-        <v>11.61</v>
+        <v>24.86</v>
       </c>
       <c r="D4" s="2">
-        <v>18.97</v>
+        <v>5.35</v>
       </c>
       <c r="E4" s="2">
-        <v>24.47</v>
+        <v>1.29</v>
       </c>
       <c r="F4" s="2">
+        <v>91.67</v>
+      </c>
+      <c r="G4" s="2">
+        <v>88</v>
+      </c>
+      <c r="H4" s="2">
+        <v>88</v>
+      </c>
+      <c r="I4" s="2">
         <v>96</v>
       </c>
-      <c r="G4" s="2">
-        <v>97.95999999999999</v>
-      </c>
-      <c r="H4" s="2">
-        <v>92</v>
-      </c>
-      <c r="I4" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1874.2</v>
-      </c>
-      <c r="C5" s="2">
-        <v>20.97</v>
-      </c>
-      <c r="D5" s="2">
-        <v>15.57</v>
-      </c>
-      <c r="E5" s="2">
-        <v>4.27</v>
-      </c>
-      <c r="F5" s="2">
-        <v>88</v>
-      </c>
-      <c r="G5" s="2">
-        <v>89.8</v>
-      </c>
-      <c r="H5" s="2">
-        <v>96</v>
-      </c>
-      <c r="I5" s="2">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1">
-        <v>8893.5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>15.61</v>
-      </c>
-      <c r="D6" s="2">
-        <v>13.65</v>
-      </c>
-      <c r="E6" s="2">
-        <v>6.4</v>
-      </c>
-      <c r="F6" s="2">
-        <v>84</v>
-      </c>
-      <c r="G6" s="2">
-        <v>93.88</v>
-      </c>
-      <c r="H6" s="2">
-        <v>88</v>
-      </c>
-      <c r="I6" s="2">
-        <v>92</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C4">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2608,7 +2343,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="D2:D4">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2616,7 +2351,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E6">
+  <conditionalFormatting sqref="E2:E4">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2624,22 +2359,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
+  <conditionalFormatting sqref="F2:F4">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G6">
+  <conditionalFormatting sqref="G2:G4">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H6">
+  <conditionalFormatting sqref="H2:H4">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
+  <conditionalFormatting sqref="I2:I4">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2650,7 +2385,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2692,16 +2427,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3212.1</v>
+        <v>3157.3</v>
       </c>
       <c r="C2" s="2">
-        <v>46.67</v>
+        <v>48.67</v>
       </c>
       <c r="D2" s="2">
-        <v>38.41</v>
+        <v>27.08</v>
       </c>
       <c r="E2" s="2">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2721,28 +2456,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>3340.6</v>
+        <v>289.65</v>
       </c>
       <c r="C3" s="2">
-        <v>23.76</v>
+        <v>19.26</v>
       </c>
       <c r="D3" s="2">
-        <v>17.78</v>
+        <v>14.99</v>
       </c>
       <c r="E3" s="2">
-        <v>22.81</v>
+        <v>14.94</v>
       </c>
       <c r="F3" s="2">
-        <v>98</v>
+        <v>97.22</v>
       </c>
       <c r="G3" s="2">
-        <v>95.92</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="I3" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2750,28 +2485,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>5426.5</v>
+        <v>5312</v>
       </c>
       <c r="C4" s="2">
-        <v>11.61</v>
+        <v>17.51</v>
       </c>
       <c r="D4" s="2">
-        <v>18.97</v>
+        <v>24.62</v>
       </c>
       <c r="E4" s="2">
-        <v>24.47</v>
+        <v>8.84</v>
       </c>
       <c r="F4" s="2">
+        <v>94.44</v>
+      </c>
+      <c r="G4" s="2">
         <v>96</v>
       </c>
-      <c r="G4" s="2">
-        <v>97.95999999999999</v>
-      </c>
       <c r="H4" s="2">
+        <v>98</v>
+      </c>
+      <c r="I4" s="2">
         <v>92</v>
-      </c>
-      <c r="I4" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2779,119 +2514,90 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1031.4</v>
+        <v>1828.1</v>
       </c>
       <c r="C5" s="2">
-        <v>0.65</v>
+        <v>24.86</v>
       </c>
       <c r="D5" s="2">
-        <v>12.58</v>
+        <v>5.35</v>
       </c>
       <c r="E5" s="2">
-        <v>19.13</v>
+        <v>1.29</v>
       </c>
       <c r="F5" s="2">
-        <v>94</v>
+        <v>91.67</v>
       </c>
       <c r="G5" s="2">
-        <v>81.63</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="I5" s="2">
-        <v>62</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>1874.2</v>
+        <v>3213.6</v>
       </c>
       <c r="C6" s="2">
-        <v>20.97</v>
+        <v>15.71</v>
       </c>
       <c r="D6" s="2">
-        <v>15.57</v>
+        <v>12.52</v>
       </c>
       <c r="E6" s="2">
-        <v>4.27</v>
+        <v>1.55</v>
       </c>
       <c r="F6" s="2">
-        <v>88</v>
+        <v>86.11</v>
       </c>
       <c r="G6" s="2">
-        <v>89.8</v>
+        <v>80</v>
       </c>
       <c r="H6" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="I6" s="2">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>8893.5</v>
+        <v>1020.5</v>
       </c>
       <c r="C7" s="2">
-        <v>15.61</v>
+        <v>4.96</v>
       </c>
       <c r="D7" s="2">
-        <v>13.65</v>
+        <v>8.06</v>
       </c>
       <c r="E7" s="2">
-        <v>6.4</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F7" s="2">
-        <v>84</v>
+        <v>83.33</v>
       </c>
       <c r="G7" s="2">
-        <v>93.88</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I7" s="2">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1">
-        <v>1411.4</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0.86</v>
-      </c>
-      <c r="D8" s="2">
-        <v>7.4</v>
-      </c>
-      <c r="E8" s="2">
-        <v>12.89</v>
-      </c>
-      <c r="F8" s="2">
-        <v>82</v>
-      </c>
-      <c r="G8" s="2">
-        <v>83.67</v>
-      </c>
-      <c r="H8" s="2">
-        <v>66</v>
-      </c>
-      <c r="I8" s="2">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C8">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2899,7 +2605,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2907,7 +2613,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E8">
+  <conditionalFormatting sqref="E2:E7">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2915,22 +2621,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F8">
+  <conditionalFormatting sqref="F2:F7">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H8">
+  <conditionalFormatting sqref="H2:H7">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I8">
+  <conditionalFormatting sqref="I2:I7">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2966,13 +2672,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C2" s="2">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D2" s="2">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2980,13 +2686,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D3" s="2">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2994,13 +2700,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D4" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3008,13 +2714,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C5" s="2">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-07-10</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-07-10</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-07-10</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-07-10</t>
+    <t>Price_2026-07-17</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-07-17</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-07-17</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-07-17</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-07-17</t>
   </si>
   <si>
     <t>RS_Score_2026-07-10</t>
@@ -43,159 +46,156 @@
     <t>RS_Score_2026-06-26</t>
   </si>
   <si>
-    <t>RS_Score_2026-06-19</t>
-  </si>
-  <si>
     <t>ADANIENT</t>
   </si>
   <si>
     <t>ETERNAL</t>
   </si>
   <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>HCLTECH</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>TMPV</t>
+  </si>
+  <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
     <t>INDIGO</t>
   </si>
   <si>
-    <t>ADANIPORTS</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>TITAN</t>
-  </si>
-  <si>
     <t>ASIANPAINT</t>
   </si>
   <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>TRENT</t>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
   </si>
   <si>
     <t>SBILIFE</t>
   </si>
   <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>HINDALCO</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>TMPV</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>HCLTECH</t>
-  </si>
-  <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
     <t>2026-07-10</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3157.3</v>
+        <v>3160.7</v>
       </c>
       <c r="C2" s="2">
-        <v>48.67</v>
+        <v>58.38</v>
       </c>
       <c r="D2" s="2">
-        <v>27.08</v>
+        <v>26.47</v>
       </c>
       <c r="E2" s="2">
-        <v>7.3</v>
+        <v>3.3</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>289.65</v>
+        <v>286.6</v>
       </c>
       <c r="C3" s="2">
-        <v>19.26</v>
+        <v>26.47</v>
       </c>
       <c r="D3" s="2">
-        <v>14.99</v>
+        <v>16.57</v>
       </c>
       <c r="E3" s="2">
-        <v>14.94</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F3" s="2">
         <v>97.22</v>
       </c>
       <c r="G3" s="2">
+        <v>98</v>
+      </c>
+      <c r="H3" s="2">
         <v>86</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>42</v>
-      </c>
-      <c r="I3" s="2">
-        <v>78</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>5312</v>
+        <v>1572.9</v>
       </c>
       <c r="C4" s="2">
-        <v>17.51</v>
+        <v>20.74</v>
       </c>
       <c r="D4" s="2">
-        <v>24.62</v>
+        <v>10.73</v>
       </c>
       <c r="E4" s="2">
-        <v>8.84</v>
+        <v>12.44</v>
       </c>
       <c r="F4" s="2">
         <v>94.44</v>
       </c>
       <c r="G4" s="2">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="H4" s="2">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="I4" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1828.1</v>
+        <v>1444.3</v>
       </c>
       <c r="C5" s="2">
-        <v>24.86</v>
+        <v>10.09</v>
       </c>
       <c r="D5" s="2">
-        <v>5.35</v>
+        <v>14.05</v>
       </c>
       <c r="E5" s="2">
-        <v>1.29</v>
+        <v>6.8</v>
       </c>
       <c r="F5" s="2">
         <v>91.67</v>
       </c>
       <c r="G5" s="2">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="H5" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I5" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>1935.5</v>
+        <v>1837.4</v>
       </c>
       <c r="C6" s="2">
-        <v>10.73</v>
+        <v>29.57</v>
       </c>
       <c r="D6" s="2">
-        <v>6.42</v>
+        <v>4.4</v>
       </c>
       <c r="E6" s="2">
-        <v>7.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F6" s="2">
         <v>88.89</v>
       </c>
       <c r="G6" s="2">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="H6" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I6" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>3213.6</v>
+        <v>4638.1</v>
       </c>
       <c r="C7" s="2">
-        <v>15.71</v>
+        <v>10.27</v>
       </c>
       <c r="D7" s="2">
-        <v>12.52</v>
+        <v>10.65</v>
       </c>
       <c r="E7" s="2">
-        <v>1.55</v>
+        <v>6.42</v>
       </c>
       <c r="F7" s="2">
         <v>86.11</v>
       </c>
       <c r="G7" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H7" s="2">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="I7" s="2">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>1020.5</v>
+        <v>1418.7</v>
       </c>
       <c r="C8" s="2">
-        <v>4.96</v>
+        <v>7.39</v>
       </c>
       <c r="D8" s="2">
-        <v>8.06</v>
+        <v>9.74</v>
       </c>
       <c r="E8" s="2">
-        <v>8.960000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="F8" s="2">
         <v>83.33</v>
       </c>
       <c r="G8" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="H8" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I8" s="2">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>4584.4</v>
+        <v>1427.2</v>
       </c>
       <c r="C9" s="2">
-        <v>7.71</v>
+        <v>15.54</v>
       </c>
       <c r="D9" s="2">
-        <v>5.42</v>
+        <v>-3.23</v>
       </c>
       <c r="E9" s="2">
-        <v>7.38</v>
+        <v>2.29</v>
       </c>
       <c r="F9" s="2">
         <v>80.56</v>
       </c>
       <c r="G9" s="2">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="H9" s="2">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I9" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>2677.8</v>
+        <v>819.6</v>
       </c>
       <c r="C10" s="2">
-        <v>17.07</v>
+        <v>-1.92</v>
       </c>
       <c r="D10" s="2">
-        <v>10.33</v>
+        <v>9.1</v>
       </c>
       <c r="E10" s="2">
-        <v>-1.4</v>
+        <v>4.22</v>
       </c>
       <c r="F10" s="2">
         <v>77.78</v>
       </c>
       <c r="G10" s="2">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H10" s="2">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="I10" s="2">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>1454.8</v>
+        <v>10443</v>
       </c>
       <c r="C11" s="2">
-        <v>10.94</v>
+        <v>10.2</v>
       </c>
       <c r="D11" s="2">
-        <v>1.43</v>
+        <v>-0.05</v>
       </c>
       <c r="E11" s="2">
-        <v>4.7</v>
+        <v>2.47</v>
       </c>
       <c r="F11" s="2">
         <v>75</v>
       </c>
       <c r="G11" s="2">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H11" s="2">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I11" s="2">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1044.1</v>
+        <v>3109.7</v>
       </c>
       <c r="C12" s="2">
-        <v>-0.24</v>
+        <v>13.33</v>
       </c>
       <c r="D12" s="2">
-        <v>9.32</v>
+        <v>4.21</v>
       </c>
       <c r="E12" s="2">
-        <v>4.93</v>
+        <v>-2.06</v>
       </c>
       <c r="F12" s="2">
         <v>72.22</v>
       </c>
       <c r="G12" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="I12" s="2">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>824.95</v>
+        <v>1854</v>
       </c>
       <c r="C13" s="2">
-        <v>-4.64</v>
+        <v>-0.65</v>
       </c>
       <c r="D13" s="2">
-        <v>7.59</v>
+        <v>3.42</v>
       </c>
       <c r="E13" s="2">
-        <v>7.88</v>
+        <v>4.12</v>
       </c>
       <c r="F13" s="2">
         <v>69.44</v>
       </c>
       <c r="G13" s="2">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H13" s="2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I13" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>2902.8</v>
+        <v>1908.8</v>
       </c>
       <c r="C14" s="2">
-        <v>13.31</v>
+        <v>3.16</v>
       </c>
       <c r="D14" s="2">
-        <v>4.86</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E14" s="2">
-        <v>0.06</v>
+        <v>-0.41</v>
       </c>
       <c r="F14" s="2">
         <v>66.67</v>
       </c>
       <c r="G14" s="2">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="H14" s="2">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="I14" s="2">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>1862.9</v>
+        <v>1203.9</v>
       </c>
       <c r="C15" s="2">
-        <v>-8.199999999999999</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="D15" s="2">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="E15" s="2">
-        <v>5.88</v>
+        <v>7.58</v>
       </c>
       <c r="F15" s="2">
         <v>63.89</v>
       </c>
       <c r="G15" s="2">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="H15" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I15" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>13854</v>
+        <v>3179.2</v>
       </c>
       <c r="C16" s="2">
-        <v>-3.71</v>
+        <v>-2.46</v>
       </c>
       <c r="D16" s="2">
-        <v>2.02</v>
+        <v>-1.03</v>
       </c>
       <c r="E16" s="2">
-        <v>0.35</v>
+        <v>4.87</v>
       </c>
       <c r="F16" s="2">
         <v>61.11</v>
       </c>
       <c r="G16" s="2">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="H16" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I16" s="2">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>11711</v>
+        <v>1044.3</v>
       </c>
       <c r="C17" s="2">
-        <v>-6.47</v>
+        <v>-4.41</v>
       </c>
       <c r="D17" s="2">
-        <v>-0.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E17" s="2">
-        <v>2.14</v>
+        <v>0.34</v>
       </c>
       <c r="F17" s="2">
         <v>58.33</v>
       </c>
       <c r="G17" s="2">
+        <v>40</v>
+      </c>
+      <c r="H17" s="2">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2">
         <v>52</v>
-      </c>
-      <c r="H17" s="2">
-        <v>36</v>
-      </c>
-      <c r="I17" s="2">
-        <v>18</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>241.96</v>
+        <v>242.98</v>
       </c>
       <c r="C18" s="2">
-        <v>-2.83</v>
+        <v>2.96</v>
       </c>
       <c r="D18" s="2">
-        <v>-4.27</v>
+        <v>1.1</v>
       </c>
       <c r="E18" s="2">
-        <v>1.02</v>
+        <v>-0.16</v>
       </c>
       <c r="F18" s="2">
         <v>55.56</v>
       </c>
       <c r="G18" s="2">
+        <v>48</v>
+      </c>
+      <c r="H18" s="2">
         <v>40</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <v>46</v>
-      </c>
-      <c r="I18" s="2">
-        <v>42</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1323.7</v>
+        <v>7563.5</v>
       </c>
       <c r="C19" s="2">
-        <v>-3.47</v>
+        <v>0.36</v>
       </c>
       <c r="D19" s="2">
-        <v>3.89</v>
+        <v>5.01</v>
       </c>
       <c r="E19" s="2">
-        <v>-3.18</v>
+        <v>-0.99</v>
       </c>
       <c r="F19" s="2">
         <v>52.78</v>
       </c>
       <c r="G19" s="2">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="I19" s="2">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>1036</v>
+        <v>2269</v>
       </c>
       <c r="C20" s="2">
-        <v>-11.36</v>
+        <v>-7.99</v>
       </c>
       <c r="D20" s="2">
-        <v>-1.28</v>
+        <v>-3.37</v>
       </c>
       <c r="E20" s="2">
-        <v>1.48</v>
+        <v>7.22</v>
       </c>
       <c r="F20" s="2">
         <v>50</v>
       </c>
       <c r="G20" s="2">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H20" s="2">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="I20" s="2">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>414.85</v>
+        <v>1328.5</v>
       </c>
       <c r="C21" s="2">
-        <v>-8.220000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="D21" s="2">
-        <v>-4.31</v>
+        <v>4.5</v>
       </c>
       <c r="E21" s="2">
-        <v>1.29</v>
+        <v>-2.14</v>
       </c>
       <c r="F21" s="2">
         <v>47.22</v>
       </c>
       <c r="G21" s="2">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="I21" s="2">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>2150.6</v>
+        <v>389.95</v>
       </c>
       <c r="C22" s="2">
-        <v>-6.38</v>
+        <v>-0.31</v>
       </c>
       <c r="D22" s="2">
-        <v>-5.92</v>
+        <v>2.51</v>
       </c>
       <c r="E22" s="2">
-        <v>0.76</v>
+        <v>-2.87</v>
       </c>
       <c r="F22" s="2">
         <v>44.44</v>
       </c>
       <c r="G22" s="2">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="H22" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I22" s="2">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>967.45</v>
+        <v>2842.4</v>
       </c>
       <c r="C23" s="2">
-        <v>3.46</v>
+        <v>14.93</v>
       </c>
       <c r="D23" s="2">
-        <v>-6.73</v>
+        <v>2.12</v>
       </c>
       <c r="E23" s="2">
-        <v>-4.08</v>
+        <v>-10.63</v>
       </c>
       <c r="F23" s="2">
         <v>41.67</v>
       </c>
       <c r="G23" s="2">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="H23" s="2">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="I23" s="2">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>7365.5</v>
+        <v>1237.3</v>
       </c>
       <c r="C24" s="2">
-        <v>-5.88</v>
+        <v>2.48</v>
       </c>
       <c r="D24" s="2">
-        <v>0.5</v>
+        <v>-1.44</v>
       </c>
       <c r="E24" s="2">
-        <v>-3.4</v>
+        <v>-2.96</v>
       </c>
       <c r="F24" s="2">
         <v>38.89</v>
       </c>
       <c r="G24" s="2">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H24" s="2">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="I24" s="2">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,16 +1458,16 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>1307.8</v>
+        <v>2143.8</v>
       </c>
       <c r="C25" s="2">
-        <v>-3.25</v>
+        <v>-1.12</v>
       </c>
       <c r="D25" s="2">
-        <v>-10.2</v>
+        <v>-6.14</v>
       </c>
       <c r="E25" s="2">
-        <v>0.06</v>
+        <v>-0.88</v>
       </c>
       <c r="F25" s="2">
         <v>36.11</v>
@@ -1476,10 +1476,10 @@
         <v>34</v>
       </c>
       <c r="H25" s="2">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I25" s="2">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>429.3</v>
+        <v>1327.2</v>
       </c>
       <c r="C26" s="2">
-        <v>0.72</v>
+        <v>-5.36</v>
       </c>
       <c r="D26" s="2">
-        <v>-10.55</v>
+        <v>-3.95</v>
       </c>
       <c r="E26" s="2">
-        <v>-3.32</v>
+        <v>0.05</v>
       </c>
       <c r="F26" s="2">
         <v>33.33</v>
       </c>
       <c r="G26" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H26" s="2">
         <v>34</v>
       </c>
       <c r="I26" s="2">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>283.1</v>
+        <v>1096.5</v>
       </c>
       <c r="C27" s="2">
-        <v>-4.62</v>
+        <v>-13.54</v>
       </c>
       <c r="D27" s="2">
-        <v>-11.27</v>
+        <v>-4.82</v>
       </c>
       <c r="E27" s="2">
-        <v>-0.91</v>
+        <v>2.92</v>
       </c>
       <c r="F27" s="2">
         <v>30.56</v>
       </c>
       <c r="G27" s="2">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H27" s="2">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="I27" s="2">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>281.75</v>
+        <v>1088.6</v>
       </c>
       <c r="C28" s="2">
-        <v>-8.09</v>
+        <v>-0.15</v>
       </c>
       <c r="D28" s="2">
-        <v>-6.97</v>
+        <v>-13.63</v>
       </c>
       <c r="E28" s="2">
-        <v>-2.14</v>
+        <v>-2.18</v>
       </c>
       <c r="F28" s="2">
         <v>27.78</v>
       </c>
       <c r="G28" s="2">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H28" s="2">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="I28" s="2">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>377.6</v>
+        <v>335.6</v>
       </c>
       <c r="C29" s="2">
-        <v>-8.59</v>
+        <v>-1.97</v>
       </c>
       <c r="D29" s="2">
-        <v>1.6</v>
+        <v>-2.2</v>
       </c>
       <c r="E29" s="2">
-        <v>-6.94</v>
+        <v>-7.16</v>
       </c>
       <c r="F29" s="2">
         <v>25</v>
       </c>
       <c r="G29" s="2">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="H29" s="2">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="I29" s="2">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>191.19</v>
+        <v>247.29</v>
       </c>
       <c r="C30" s="2">
-        <v>-7.52</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="D30" s="2">
-        <v>-8.06</v>
+        <v>-12</v>
       </c>
       <c r="E30" s="2">
-        <v>-3.09</v>
+        <v>0.75</v>
       </c>
       <c r="F30" s="2">
         <v>22.22</v>
       </c>
       <c r="G30" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H30" s="2">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I30" s="2">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,16 +1650,16 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>344.55</v>
+        <v>280.7</v>
       </c>
       <c r="C31" s="2">
-        <v>-8.74</v>
+        <v>-6.7</v>
       </c>
       <c r="D31" s="2">
-        <v>-13.87</v>
+        <v>-5.72</v>
       </c>
       <c r="E31" s="2">
-        <v>-1.02</v>
+        <v>-3.62</v>
       </c>
       <c r="F31" s="2">
         <v>19.44</v>
@@ -1668,10 +1668,10 @@
         <v>20</v>
       </c>
       <c r="H31" s="2">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="I31" s="2">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>567.7</v>
+        <v>427.65</v>
       </c>
       <c r="C32" s="2">
-        <v>-19.45</v>
+        <v>-3.58</v>
       </c>
       <c r="D32" s="2">
-        <v>-3.17</v>
+        <v>-7.92</v>
       </c>
       <c r="E32" s="2">
-        <v>-1.97</v>
+        <v>-4.76</v>
       </c>
       <c r="F32" s="2">
         <v>16.67</v>
       </c>
       <c r="G32" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H32" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I32" s="2">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>244.96</v>
+        <v>1211.2</v>
       </c>
       <c r="C33" s="2">
-        <v>-13.2</v>
+        <v>-7.28</v>
       </c>
       <c r="D33" s="2">
-        <v>-16.37</v>
+        <v>-4.77</v>
       </c>
       <c r="E33" s="2">
-        <v>0.54</v>
+        <v>-5.56</v>
       </c>
       <c r="F33" s="2">
         <v>13.89</v>
       </c>
       <c r="G33" s="2">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="H33" s="2">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="I33" s="2">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>175.46</v>
+        <v>185.89</v>
       </c>
       <c r="C34" s="2">
-        <v>-11.64</v>
+        <v>-2.71</v>
       </c>
       <c r="D34" s="2">
-        <v>-12.6</v>
+        <v>-10.54</v>
       </c>
       <c r="E34" s="2">
-        <v>-3.26</v>
+        <v>-6.57</v>
       </c>
       <c r="F34" s="2">
         <v>11.11</v>
       </c>
       <c r="G34" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H34" s="2">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="I34" s="2">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>1068</v>
+        <v>409.45</v>
       </c>
       <c r="C35" s="2">
-        <v>-15.35</v>
+        <v>-11.63</v>
       </c>
       <c r="D35" s="2">
-        <v>-6.61</v>
+        <v>-5.21</v>
       </c>
       <c r="E35" s="2">
-        <v>-5.89</v>
+        <v>-5.11</v>
       </c>
       <c r="F35" s="2">
         <v>8.33</v>
       </c>
       <c r="G35" s="2">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="H35" s="2">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="I35" s="2">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>337.95</v>
+        <v>176</v>
       </c>
       <c r="C36" s="2">
-        <v>-8.050000000000001</v>
+        <v>-12.41</v>
       </c>
       <c r="D36" s="2">
-        <v>-0.67</v>
+        <v>-10.51</v>
       </c>
       <c r="E36" s="2">
-        <v>-14.04</v>
+        <v>-2.32</v>
       </c>
       <c r="F36" s="2">
         <v>5.56</v>
       </c>
       <c r="G36" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H36" s="2">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I36" s="2">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>2069</v>
+        <v>341.85</v>
       </c>
       <c r="C37" s="2">
-        <v>-19.76</v>
+        <v>-9.4</v>
       </c>
       <c r="D37" s="2">
-        <v>-13.75</v>
+        <v>-13</v>
       </c>
       <c r="E37" s="2">
-        <v>-4.3</v>
+        <v>-6.87</v>
       </c>
       <c r="F37" s="2">
         <v>2.78</v>
       </c>
       <c r="G37" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H37" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I37" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,10 +1874,10 @@
         <v>45</v>
       </c>
       <c r="G38" s="2">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="H38" s="2">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="I38" s="2">
         <v>66</v>
@@ -1891,13 +1891,13 @@
         <v>46</v>
       </c>
       <c r="G39" s="2">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H39" s="2">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="I39" s="2">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1908,13 +1908,13 @@
         <v>47</v>
       </c>
       <c r="G40" s="2">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="H40" s="2">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="I40" s="2">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1925,13 +1925,13 @@
         <v>48</v>
       </c>
       <c r="G41" s="2">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="H41" s="2">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="I41" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -1942,13 +1942,13 @@
         <v>49</v>
       </c>
       <c r="G42" s="2">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="H42" s="2">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="I42" s="2">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -1959,13 +1959,13 @@
         <v>50</v>
       </c>
       <c r="G43" s="2">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="H43" s="2">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="I43" s="2">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -1976,13 +1976,13 @@
         <v>51</v>
       </c>
       <c r="G44" s="2">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="H44" s="2">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="I44" s="2">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -1993,13 +1993,13 @@
         <v>52</v>
       </c>
       <c r="G45" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H45" s="2">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="I45" s="2">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2010,13 +2010,13 @@
         <v>53</v>
       </c>
       <c r="G46" s="2">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="H46" s="2">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="I46" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2027,13 +2027,13 @@
         <v>54</v>
       </c>
       <c r="G47" s="2">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="H47" s="2">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="I47" s="2">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2044,13 +2044,13 @@
         <v>55</v>
       </c>
       <c r="G48" s="2">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H48" s="2">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="I48" s="2">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2061,13 +2061,13 @@
         <v>56</v>
       </c>
       <c r="G49" s="2">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="H49" s="2">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="I49" s="2">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2078,13 +2078,13 @@
         <v>57</v>
       </c>
       <c r="G50" s="2">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="H50" s="2">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="I50" s="2">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2095,13 +2095,13 @@
         <v>58</v>
       </c>
       <c r="G51" s="2">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="H51" s="2">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="I51" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2210,7 +2210,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2252,16 +2252,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3157.3</v>
+        <v>3160.7</v>
       </c>
       <c r="C2" s="2">
-        <v>48.67</v>
+        <v>58.38</v>
       </c>
       <c r="D2" s="2">
-        <v>27.08</v>
+        <v>26.47</v>
       </c>
       <c r="E2" s="2">
-        <v>7.3</v>
+        <v>3.3</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2278,64 +2278,35 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1">
-        <v>5312</v>
+        <v>1837.4</v>
       </c>
       <c r="C3" s="2">
-        <v>17.51</v>
+        <v>29.57</v>
       </c>
       <c r="D3" s="2">
-        <v>24.62</v>
+        <v>4.4</v>
       </c>
       <c r="E3" s="2">
-        <v>8.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F3" s="2">
-        <v>94.44</v>
+        <v>88.89</v>
       </c>
       <c r="G3" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H3" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="I3" s="2">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1828.1</v>
-      </c>
-      <c r="C4" s="2">
-        <v>24.86</v>
-      </c>
-      <c r="D4" s="2">
-        <v>5.35</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1.29</v>
-      </c>
-      <c r="F4" s="2">
-        <v>91.67</v>
-      </c>
-      <c r="G4" s="2">
         <v>88</v>
       </c>
-      <c r="H4" s="2">
-        <v>88</v>
-      </c>
-      <c r="I4" s="2">
-        <v>96</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C4">
+  <conditionalFormatting sqref="C2:C3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2343,7 +2314,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
+  <conditionalFormatting sqref="D2:D3">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2351,7 +2322,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4">
+  <conditionalFormatting sqref="E2:E3">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2359,22 +2330,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4">
+  <conditionalFormatting sqref="F2:F3">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G4">
+  <conditionalFormatting sqref="G2:G3">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H4">
+  <conditionalFormatting sqref="H2:H3">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4">
+  <conditionalFormatting sqref="I2:I3">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2385,7 +2356,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2427,16 +2398,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3157.3</v>
+        <v>3160.7</v>
       </c>
       <c r="C2" s="2">
-        <v>48.67</v>
+        <v>58.38</v>
       </c>
       <c r="D2" s="2">
-        <v>27.08</v>
+        <v>26.47</v>
       </c>
       <c r="E2" s="2">
-        <v>7.3</v>
+        <v>3.3</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2456,148 +2427,119 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>289.65</v>
+        <v>286.6</v>
       </c>
       <c r="C3" s="2">
-        <v>19.26</v>
+        <v>26.47</v>
       </c>
       <c r="D3" s="2">
-        <v>14.99</v>
+        <v>16.57</v>
       </c>
       <c r="E3" s="2">
-        <v>14.94</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F3" s="2">
         <v>97.22</v>
       </c>
       <c r="G3" s="2">
+        <v>98</v>
+      </c>
+      <c r="H3" s="2">
         <v>86</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>42</v>
-      </c>
-      <c r="I3" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
-        <v>5312</v>
+        <v>1837.4</v>
       </c>
       <c r="C4" s="2">
-        <v>17.51</v>
+        <v>29.57</v>
       </c>
       <c r="D4" s="2">
-        <v>24.62</v>
+        <v>4.4</v>
       </c>
       <c r="E4" s="2">
-        <v>8.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F4" s="2">
-        <v>94.44</v>
+        <v>88.89</v>
       </c>
       <c r="G4" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H4" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="I4" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>1828.1</v>
+        <v>4638.1</v>
       </c>
       <c r="C5" s="2">
-        <v>24.86</v>
+        <v>10.27</v>
       </c>
       <c r="D5" s="2">
-        <v>5.35</v>
+        <v>10.65</v>
       </c>
       <c r="E5" s="2">
-        <v>1.29</v>
+        <v>6.42</v>
       </c>
       <c r="F5" s="2">
-        <v>91.67</v>
+        <v>86.11</v>
       </c>
       <c r="G5" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H5" s="2">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="I5" s="2">
-        <v>96</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1">
-        <v>3213.6</v>
+        <v>1427.2</v>
       </c>
       <c r="C6" s="2">
-        <v>15.71</v>
+        <v>15.54</v>
       </c>
       <c r="D6" s="2">
-        <v>12.52</v>
+        <v>-3.23</v>
       </c>
       <c r="E6" s="2">
-        <v>1.55</v>
+        <v>2.29</v>
       </c>
       <c r="F6" s="2">
-        <v>86.11</v>
+        <v>80.56</v>
       </c>
       <c r="G6" s="2">
         <v>80</v>
       </c>
       <c r="H6" s="2">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="I6" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1">
-        <v>1020.5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>4.96</v>
-      </c>
-      <c r="D7" s="2">
-        <v>8.06</v>
-      </c>
-      <c r="E7" s="2">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="F7" s="2">
-        <v>83.33</v>
-      </c>
-      <c r="G7" s="2">
-        <v>94</v>
-      </c>
-      <c r="H7" s="2">
-        <v>80</v>
-      </c>
-      <c r="I7" s="2">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2605,7 +2547,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2613,7 +2555,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E6">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2621,22 +2563,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I6">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2672,13 +2614,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D2" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2686,13 +2628,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C3" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D3" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2703,10 +2645,10 @@
         <v>62</v>
       </c>
       <c r="C4" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2714,13 +2656,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D5" s="2">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-07-17</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-07-17</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-07-17</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-07-17</t>
+    <t>Price_2026-07-24</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-07-24</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-07-24</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-07-24</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-07-24</t>
   </si>
   <si>
     <t>RS_Score_2026-07-17</t>
@@ -43,156 +46,153 @@
     <t>RS_Score_2026-07-03</t>
   </si>
   <si>
-    <t>RS_Score_2026-06-26</t>
-  </si>
-  <si>
     <t>ADANIENT</t>
   </si>
   <si>
     <t>ETERNAL</t>
   </si>
   <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>TMPV</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
     <t>TECHM</t>
   </si>
   <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>ADANIPORTS</t>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
   </si>
   <si>
     <t>TITAN</t>
   </si>
   <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>HCLTECH</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
     <t>CIPLA</t>
   </si>
   <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>HCLTECH</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>TMPV</t>
-  </si>
-  <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>HINDALCO</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
     <t>SBILIFE</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
     <t>2026-07-17</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3160.7</v>
+        <v>3026.4</v>
       </c>
       <c r="C2" s="2">
-        <v>58.38</v>
+        <v>53.27</v>
       </c>
       <c r="D2" s="2">
-        <v>26.47</v>
+        <v>12.56</v>
       </c>
       <c r="E2" s="2">
-        <v>3.3</v>
+        <v>2.16</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>286.6</v>
+        <v>280</v>
       </c>
       <c r="C3" s="2">
-        <v>26.47</v>
+        <v>19.34</v>
       </c>
       <c r="D3" s="2">
-        <v>16.57</v>
+        <v>15.99</v>
       </c>
       <c r="E3" s="2">
-        <v>8.699999999999999</v>
+        <v>7.94</v>
       </c>
       <c r="F3" s="2">
-        <v>97.22</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="G3" s="2">
         <v>98</v>
       </c>
       <c r="H3" s="2">
+        <v>98</v>
+      </c>
+      <c r="I3" s="2">
         <v>86</v>
-      </c>
-      <c r="I3" s="2">
-        <v>42</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>1572.9</v>
+        <v>1443.5</v>
       </c>
       <c r="C4" s="2">
-        <v>20.74</v>
+        <v>20.18</v>
       </c>
       <c r="D4" s="2">
-        <v>10.73</v>
+        <v>1.31</v>
       </c>
       <c r="E4" s="2">
-        <v>12.44</v>
+        <v>4.55</v>
       </c>
       <c r="F4" s="2">
-        <v>94.44</v>
+        <v>92.86</v>
       </c>
       <c r="G4" s="2">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H4" s="2">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="I4" s="2">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1444.3</v>
+        <v>3089.4</v>
       </c>
       <c r="C5" s="2">
-        <v>10.09</v>
+        <v>15.13</v>
       </c>
       <c r="D5" s="2">
-        <v>14.05</v>
+        <v>4.95</v>
       </c>
       <c r="E5" s="2">
-        <v>6.8</v>
+        <v>0.3</v>
       </c>
       <c r="F5" s="2">
-        <v>91.67</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H5" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I5" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>1837.4</v>
+        <v>4985</v>
       </c>
       <c r="C6" s="2">
-        <v>29.57</v>
+        <v>16.26</v>
       </c>
       <c r="D6" s="2">
-        <v>4.4</v>
+        <v>16.59</v>
       </c>
       <c r="E6" s="2">
-        <v>0.5600000000000001</v>
+        <v>-6.21</v>
       </c>
       <c r="F6" s="2">
-        <v>88.89</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="I6" s="2">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>4638.1</v>
+        <v>2254.3</v>
       </c>
       <c r="C7" s="2">
-        <v>10.27</v>
+        <v>-3.94</v>
       </c>
       <c r="D7" s="2">
-        <v>10.65</v>
+        <v>0.62</v>
       </c>
       <c r="E7" s="2">
-        <v>6.42</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="F7" s="2">
-        <v>86.11</v>
+        <v>82.14</v>
       </c>
       <c r="G7" s="2">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="I7" s="2">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>1418.7</v>
+        <v>13442</v>
       </c>
       <c r="C8" s="2">
-        <v>7.39</v>
+        <v>3.62</v>
       </c>
       <c r="D8" s="2">
-        <v>9.74</v>
+        <v>3.27</v>
       </c>
       <c r="E8" s="2">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="F8" s="2">
-        <v>83.33</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="H8" s="2">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="I8" s="2">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>1427.2</v>
+        <v>1005.1</v>
       </c>
       <c r="C9" s="2">
-        <v>15.54</v>
+        <v>0.62</v>
       </c>
       <c r="D9" s="2">
-        <v>-3.23</v>
+        <v>8.26</v>
       </c>
       <c r="E9" s="2">
-        <v>2.29</v>
+        <v>-2.12</v>
       </c>
       <c r="F9" s="2">
-        <v>80.56</v>
+        <v>75</v>
       </c>
       <c r="G9" s="2">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H9" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I9" s="2">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>819.6</v>
+        <v>1015</v>
       </c>
       <c r="C10" s="2">
-        <v>-1.92</v>
+        <v>-2.95</v>
       </c>
       <c r="D10" s="2">
-        <v>9.1</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="E10" s="2">
-        <v>4.22</v>
+        <v>-2.04</v>
       </c>
       <c r="F10" s="2">
-        <v>77.78</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="G10" s="2">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="H10" s="2">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="I10" s="2">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,25 +1010,25 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>10443</v>
+        <v>234.71</v>
       </c>
       <c r="C11" s="2">
-        <v>10.2</v>
+        <v>-1.22</v>
       </c>
       <c r="D11" s="2">
-        <v>-0.05</v>
+        <v>0.89</v>
       </c>
       <c r="E11" s="2">
-        <v>2.47</v>
+        <v>-0.84</v>
       </c>
       <c r="F11" s="2">
-        <v>75</v>
+        <v>67.86</v>
       </c>
       <c r="G11" s="2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H11" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I11" s="2">
         <v>40</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>3109.7</v>
+        <v>384.75</v>
       </c>
       <c r="C12" s="2">
-        <v>13.33</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2">
-        <v>4.21</v>
+        <v>-1.63</v>
       </c>
       <c r="E12" s="2">
-        <v>-2.06</v>
+        <v>-2.55</v>
       </c>
       <c r="F12" s="2">
-        <v>72.22</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G12" s="2">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="H12" s="2">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I12" s="2">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>1854</v>
+        <v>288.2</v>
       </c>
       <c r="C13" s="2">
-        <v>-0.65</v>
+        <v>-3.45</v>
       </c>
       <c r="D13" s="2">
-        <v>3.42</v>
+        <v>-2.82</v>
       </c>
       <c r="E13" s="2">
-        <v>4.12</v>
+        <v>0.68</v>
       </c>
       <c r="F13" s="2">
-        <v>69.44</v>
+        <v>60.71</v>
       </c>
       <c r="G13" s="2">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="H13" s="2">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="I13" s="2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>1908.8</v>
+        <v>248.76</v>
       </c>
       <c r="C14" s="2">
-        <v>3.16</v>
+        <v>-6.04</v>
       </c>
       <c r="D14" s="2">
-        <v>8.470000000000001</v>
+        <v>-16.3</v>
       </c>
       <c r="E14" s="2">
-        <v>-0.41</v>
+        <v>6.28</v>
       </c>
       <c r="F14" s="2">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="G14" s="2">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="H14" s="2">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I14" s="2">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>1203.9</v>
+        <v>942.8</v>
       </c>
       <c r="C15" s="2">
-        <v>-8.960000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="D15" s="2">
-        <v>1.78</v>
+        <v>-10.01</v>
       </c>
       <c r="E15" s="2">
-        <v>7.58</v>
+        <v>-1.67</v>
       </c>
       <c r="F15" s="2">
-        <v>63.89</v>
+        <v>53.57</v>
       </c>
       <c r="G15" s="2">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="H15" s="2">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="I15" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>3179.2</v>
+        <v>3785.6</v>
       </c>
       <c r="C16" s="2">
-        <v>-2.46</v>
+        <v>7.9</v>
       </c>
       <c r="D16" s="2">
-        <v>-1.03</v>
+        <v>-2.43</v>
       </c>
       <c r="E16" s="2">
-        <v>4.87</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="F16" s="2">
-        <v>61.11</v>
+        <v>50</v>
       </c>
       <c r="G16" s="2">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="H16" s="2">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="I16" s="2">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>1044.3</v>
+        <v>177.12</v>
       </c>
       <c r="C17" s="2">
-        <v>-4.41</v>
+        <v>-7.42</v>
       </c>
       <c r="D17" s="2">
-        <v>9.199999999999999</v>
+        <v>-7.83</v>
       </c>
       <c r="E17" s="2">
-        <v>0.34</v>
+        <v>0.93</v>
       </c>
       <c r="F17" s="2">
-        <v>58.33</v>
+        <v>46.43</v>
       </c>
       <c r="G17" s="2">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="H17" s="2">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="I17" s="2">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>242.98</v>
+        <v>1088</v>
       </c>
       <c r="C18" s="2">
-        <v>2.96</v>
+        <v>1.78</v>
       </c>
       <c r="D18" s="2">
-        <v>1.1</v>
+        <v>-10.87</v>
       </c>
       <c r="E18" s="2">
-        <v>-0.16</v>
+        <v>-2.23</v>
       </c>
       <c r="F18" s="2">
-        <v>55.56</v>
+        <v>42.86</v>
       </c>
       <c r="G18" s="2">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="H18" s="2">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="I18" s="2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>7563.5</v>
+        <v>1278</v>
       </c>
       <c r="C19" s="2">
-        <v>0.36</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="D19" s="2">
-        <v>5.01</v>
+        <v>-3.89</v>
       </c>
       <c r="E19" s="2">
-        <v>-0.99</v>
+        <v>-1.77</v>
       </c>
       <c r="F19" s="2">
-        <v>52.78</v>
+        <v>39.29</v>
       </c>
       <c r="G19" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H19" s="2">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="I19" s="2">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>2269</v>
+        <v>283.45</v>
       </c>
       <c r="C20" s="2">
-        <v>-7.99</v>
+        <v>-4.49</v>
       </c>
       <c r="D20" s="2">
-        <v>-3.37</v>
+        <v>-6.12</v>
       </c>
       <c r="E20" s="2">
-        <v>7.22</v>
+        <v>-2.49</v>
       </c>
       <c r="F20" s="2">
-        <v>50</v>
+        <v>35.71</v>
       </c>
       <c r="G20" s="2">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H20" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I20" s="2">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>1328.5</v>
+        <v>405</v>
       </c>
       <c r="C21" s="2">
-        <v>1.13</v>
+        <v>-7.82</v>
       </c>
       <c r="D21" s="2">
-        <v>4.5</v>
+        <v>-5.06</v>
       </c>
       <c r="E21" s="2">
-        <v>-2.14</v>
+        <v>-1.6</v>
       </c>
       <c r="F21" s="2">
-        <v>47.22</v>
+        <v>32.14</v>
       </c>
       <c r="G21" s="2">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="H21" s="2">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="I21" s="2">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>389.95</v>
+        <v>323.8</v>
       </c>
       <c r="C22" s="2">
-        <v>-0.31</v>
+        <v>2.28</v>
       </c>
       <c r="D22" s="2">
-        <v>2.51</v>
+        <v>-7.55</v>
       </c>
       <c r="E22" s="2">
-        <v>-2.87</v>
+        <v>-6.16</v>
       </c>
       <c r="F22" s="2">
-        <v>44.44</v>
+        <v>28.57</v>
       </c>
       <c r="G22" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H22" s="2">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="I22" s="2">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>2842.4</v>
+        <v>1040.9</v>
       </c>
       <c r="C23" s="2">
-        <v>14.93</v>
+        <v>-13.75</v>
       </c>
       <c r="D23" s="2">
-        <v>2.12</v>
+        <v>-6.92</v>
       </c>
       <c r="E23" s="2">
-        <v>-10.63</v>
+        <v>0.41</v>
       </c>
       <c r="F23" s="2">
-        <v>41.67</v>
+        <v>25</v>
       </c>
       <c r="G23" s="2">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="H23" s="2">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="I23" s="2">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>1237.3</v>
+        <v>427.4</v>
       </c>
       <c r="C24" s="2">
-        <v>2.48</v>
+        <v>-7.54</v>
       </c>
       <c r="D24" s="2">
-        <v>-1.44</v>
+        <v>-7.51</v>
       </c>
       <c r="E24" s="2">
-        <v>-2.96</v>
+        <v>-3.92</v>
       </c>
       <c r="F24" s="2">
-        <v>38.89</v>
+        <v>21.43</v>
       </c>
       <c r="G24" s="2">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="H24" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I24" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>2143.8</v>
+        <v>182.67</v>
       </c>
       <c r="C25" s="2">
-        <v>-1.12</v>
+        <v>-4.6</v>
       </c>
       <c r="D25" s="2">
-        <v>-6.14</v>
+        <v>-11.1</v>
       </c>
       <c r="E25" s="2">
-        <v>-0.88</v>
+        <v>-3.64</v>
       </c>
       <c r="F25" s="2">
-        <v>36.11</v>
+        <v>17.86</v>
       </c>
       <c r="G25" s="2">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H25" s="2">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I25" s="2">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>1327.2</v>
+        <v>347.2</v>
       </c>
       <c r="C26" s="2">
-        <v>-5.36</v>
+        <v>-9.43</v>
       </c>
       <c r="D26" s="2">
-        <v>-3.95</v>
+        <v>-10.58</v>
       </c>
       <c r="E26" s="2">
-        <v>0.05</v>
+        <v>-2.5</v>
       </c>
       <c r="F26" s="2">
-        <v>33.33</v>
+        <v>14.29</v>
       </c>
       <c r="G26" s="2">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="H26" s="2">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="I26" s="2">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>1096.5</v>
+        <v>742.8</v>
       </c>
       <c r="C27" s="2">
-        <v>-13.54</v>
+        <v>-10.68</v>
       </c>
       <c r="D27" s="2">
-        <v>-4.82</v>
+        <v>-1.76</v>
       </c>
       <c r="E27" s="2">
-        <v>2.92</v>
+        <v>-7.02</v>
       </c>
       <c r="F27" s="2">
-        <v>30.56</v>
+        <v>10.71</v>
       </c>
       <c r="G27" s="2">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="H27" s="2">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="I27" s="2">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>1088.6</v>
+        <v>555.05</v>
       </c>
       <c r="C28" s="2">
-        <v>-0.15</v>
+        <v>-13.28</v>
       </c>
       <c r="D28" s="2">
-        <v>-13.63</v>
+        <v>-7.92</v>
       </c>
       <c r="E28" s="2">
-        <v>-2.18</v>
+        <v>-4.83</v>
       </c>
       <c r="F28" s="2">
-        <v>27.78</v>
+        <v>7.14</v>
       </c>
       <c r="G28" s="2">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="H28" s="2">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I28" s="2">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>335.6</v>
+        <v>1151.7</v>
       </c>
       <c r="C29" s="2">
-        <v>-1.97</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="D29" s="2">
-        <v>-2.2</v>
+        <v>-12.94</v>
       </c>
       <c r="E29" s="2">
-        <v>-7.16</v>
+        <v>-15.75</v>
       </c>
       <c r="F29" s="2">
-        <v>25</v>
+        <v>3.57</v>
       </c>
       <c r="G29" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H29" s="2">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="I29" s="2">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1617,29 +1617,14 @@
       <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="1">
-        <v>247.29</v>
-      </c>
-      <c r="C30" s="2">
-        <v>-8.140000000000001</v>
-      </c>
-      <c r="D30" s="2">
-        <v>-12</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="F30" s="2">
-        <v>22.22</v>
-      </c>
       <c r="G30" s="2">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="H30" s="2">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="I30" s="2">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1649,29 +1634,14 @@
       <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="1">
-        <v>280.7</v>
-      </c>
-      <c r="C31" s="2">
-        <v>-6.7</v>
-      </c>
-      <c r="D31" s="2">
-        <v>-5.72</v>
-      </c>
-      <c r="E31" s="2">
-        <v>-3.62</v>
-      </c>
-      <c r="F31" s="2">
-        <v>19.44</v>
-      </c>
       <c r="G31" s="2">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H31" s="2">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I31" s="2">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1681,29 +1651,14 @@
       <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="1">
-        <v>427.65</v>
-      </c>
-      <c r="C32" s="2">
-        <v>-3.58</v>
-      </c>
-      <c r="D32" s="2">
-        <v>-7.92</v>
-      </c>
-      <c r="E32" s="2">
-        <v>-4.76</v>
-      </c>
-      <c r="F32" s="2">
-        <v>16.67</v>
-      </c>
       <c r="G32" s="2">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="H32" s="2">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="I32" s="2">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1713,29 +1668,14 @@
       <c r="A33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="1">
-        <v>1211.2</v>
-      </c>
-      <c r="C33" s="2">
-        <v>-7.28</v>
-      </c>
-      <c r="D33" s="2">
-        <v>-4.77</v>
-      </c>
-      <c r="E33" s="2">
-        <v>-5.56</v>
-      </c>
-      <c r="F33" s="2">
-        <v>13.89</v>
-      </c>
       <c r="G33" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H33" s="2">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="I33" s="2">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1745,29 +1685,14 @@
       <c r="A34" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="1">
-        <v>185.89</v>
-      </c>
-      <c r="C34" s="2">
-        <v>-2.71</v>
-      </c>
-      <c r="D34" s="2">
-        <v>-10.54</v>
-      </c>
-      <c r="E34" s="2">
-        <v>-6.57</v>
-      </c>
-      <c r="F34" s="2">
-        <v>11.11</v>
-      </c>
       <c r="G34" s="2">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="H34" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I34" s="2">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1777,29 +1702,14 @@
       <c r="A35" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="1">
-        <v>409.45</v>
-      </c>
-      <c r="C35" s="2">
-        <v>-11.63</v>
-      </c>
-      <c r="D35" s="2">
-        <v>-5.21</v>
-      </c>
-      <c r="E35" s="2">
-        <v>-5.11</v>
-      </c>
-      <c r="F35" s="2">
-        <v>8.33</v>
-      </c>
       <c r="G35" s="2">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="H35" s="2">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="I35" s="2">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1809,29 +1719,14 @@
       <c r="A36" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="1">
-        <v>176</v>
-      </c>
-      <c r="C36" s="2">
-        <v>-12.41</v>
-      </c>
-      <c r="D36" s="2">
-        <v>-10.51</v>
-      </c>
-      <c r="E36" s="2">
-        <v>-2.32</v>
-      </c>
-      <c r="F36" s="2">
-        <v>5.56</v>
-      </c>
       <c r="G36" s="2">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="H36" s="2">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="I36" s="2">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1841,29 +1736,14 @@
       <c r="A37" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="1">
-        <v>341.85</v>
-      </c>
-      <c r="C37" s="2">
-        <v>-9.4</v>
-      </c>
-      <c r="D37" s="2">
-        <v>-13</v>
-      </c>
-      <c r="E37" s="2">
-        <v>-6.87</v>
-      </c>
-      <c r="F37" s="2">
-        <v>2.78</v>
-      </c>
       <c r="G37" s="2">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="H37" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="I37" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,13 +1754,13 @@
         <v>45</v>
       </c>
       <c r="G38" s="2">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="H38" s="2">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="I38" s="2">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1891,13 +1771,13 @@
         <v>46</v>
       </c>
       <c r="G39" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H39" s="2">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I39" s="2">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1908,13 +1788,13 @@
         <v>47</v>
       </c>
       <c r="G40" s="2">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="H40" s="2">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="I40" s="2">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1925,13 +1805,13 @@
         <v>48</v>
       </c>
       <c r="G41" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H41" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="I41" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -1942,13 +1822,13 @@
         <v>49</v>
       </c>
       <c r="G42" s="2">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H42" s="2">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="I42" s="2">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -1959,13 +1839,13 @@
         <v>50</v>
       </c>
       <c r="G43" s="2">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="H43" s="2">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="I43" s="2">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -1976,13 +1856,13 @@
         <v>51</v>
       </c>
       <c r="G44" s="2">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H44" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I44" s="2">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -1993,13 +1873,13 @@
         <v>52</v>
       </c>
       <c r="G45" s="2">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="H45" s="2">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="I45" s="2">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2010,13 +1890,13 @@
         <v>53</v>
       </c>
       <c r="G46" s="2">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="H46" s="2">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="I46" s="2">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2027,13 +1907,13 @@
         <v>54</v>
       </c>
       <c r="G47" s="2">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="H47" s="2">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="I47" s="2">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2044,10 +1924,10 @@
         <v>55</v>
       </c>
       <c r="G48" s="2">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="H48" s="2">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="I48" s="2">
         <v>36</v>
@@ -2061,13 +1941,13 @@
         <v>56</v>
       </c>
       <c r="G49" s="2">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="H49" s="2">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="I49" s="2">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2078,13 +1958,13 @@
         <v>57</v>
       </c>
       <c r="G50" s="2">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="H50" s="2">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="I50" s="2">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2095,13 +1975,13 @@
         <v>58</v>
       </c>
       <c r="G51" s="2">
+        <v>36</v>
+      </c>
+      <c r="H51" s="2">
         <v>58</v>
       </c>
-      <c r="H51" s="2">
+      <c r="I51" s="2">
         <v>24</v>
-      </c>
-      <c r="I51" s="2">
-        <v>14</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2210,7 +2090,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2252,16 +2132,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3160.7</v>
+        <v>3026.4</v>
       </c>
       <c r="C2" s="2">
-        <v>58.38</v>
+        <v>53.27</v>
       </c>
       <c r="D2" s="2">
-        <v>26.47</v>
+        <v>12.56</v>
       </c>
       <c r="E2" s="2">
-        <v>3.3</v>
+        <v>2.16</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2278,35 +2158,64 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1">
+        <v>280</v>
+      </c>
+      <c r="C3" s="2">
+        <v>19.34</v>
+      </c>
+      <c r="D3" s="2">
+        <v>15.99</v>
+      </c>
+      <c r="E3" s="2">
+        <v>7.94</v>
+      </c>
+      <c r="F3" s="2">
+        <v>96.43000000000001</v>
+      </c>
+      <c r="G3" s="2">
+        <v>98</v>
+      </c>
+      <c r="H3" s="2">
+        <v>98</v>
+      </c>
+      <c r="I3" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1">
-        <v>1837.4</v>
-      </c>
-      <c r="C3" s="2">
-        <v>29.57</v>
-      </c>
-      <c r="D3" s="2">
-        <v>4.4</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F3" s="2">
-        <v>88.89</v>
-      </c>
-      <c r="G3" s="2">
-        <v>92</v>
-      </c>
-      <c r="H3" s="2">
-        <v>88</v>
-      </c>
-      <c r="I3" s="2">
-        <v>88</v>
+      <c r="B4" s="1">
+        <v>4985</v>
+      </c>
+      <c r="C4" s="2">
+        <v>16.26</v>
+      </c>
+      <c r="D4" s="2">
+        <v>16.59</v>
+      </c>
+      <c r="E4" s="2">
+        <v>-6.21</v>
+      </c>
+      <c r="F4" s="2">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="G4" s="2">
+        <v>94</v>
+      </c>
+      <c r="H4" s="2">
+        <v>96</v>
+      </c>
+      <c r="I4" s="2">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C3">
+  <conditionalFormatting sqref="C2:C4">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2314,7 +2223,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D3">
+  <conditionalFormatting sqref="D2:D4">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2322,7 +2231,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
+  <conditionalFormatting sqref="E2:E4">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2330,22 +2239,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
+  <conditionalFormatting sqref="F2:F4">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G3">
+  <conditionalFormatting sqref="G2:G4">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
+  <conditionalFormatting sqref="H2:H4">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I3">
+  <conditionalFormatting sqref="I2:I4">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2356,7 +2265,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2398,16 +2307,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3160.7</v>
+        <v>3026.4</v>
       </c>
       <c r="C2" s="2">
-        <v>58.38</v>
+        <v>53.27</v>
       </c>
       <c r="D2" s="2">
-        <v>26.47</v>
+        <v>12.56</v>
       </c>
       <c r="E2" s="2">
-        <v>3.3</v>
+        <v>2.16</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2427,28 +2336,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>286.6</v>
+        <v>280</v>
       </c>
       <c r="C3" s="2">
-        <v>26.47</v>
+        <v>19.34</v>
       </c>
       <c r="D3" s="2">
-        <v>16.57</v>
+        <v>15.99</v>
       </c>
       <c r="E3" s="2">
-        <v>8.699999999999999</v>
+        <v>7.94</v>
       </c>
       <c r="F3" s="2">
-        <v>97.22</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="G3" s="2">
         <v>98</v>
       </c>
       <c r="H3" s="2">
+        <v>98</v>
+      </c>
+      <c r="I3" s="2">
         <v>86</v>
-      </c>
-      <c r="I3" s="2">
-        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2456,90 +2365,32 @@
         <v>13</v>
       </c>
       <c r="B4" s="1">
-        <v>1837.4</v>
+        <v>4985</v>
       </c>
       <c r="C4" s="2">
-        <v>29.57</v>
+        <v>16.26</v>
       </c>
       <c r="D4" s="2">
-        <v>4.4</v>
+        <v>16.59</v>
       </c>
       <c r="E4" s="2">
-        <v>0.5600000000000001</v>
+        <v>-6.21</v>
       </c>
       <c r="F4" s="2">
-        <v>88.89</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H4" s="2">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="I4" s="2">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1">
-        <v>4638.1</v>
-      </c>
-      <c r="C5" s="2">
-        <v>10.27</v>
-      </c>
-      <c r="D5" s="2">
-        <v>10.65</v>
-      </c>
-      <c r="E5" s="2">
-        <v>6.42</v>
-      </c>
-      <c r="F5" s="2">
-        <v>86.11</v>
-      </c>
-      <c r="G5" s="2">
-        <v>82</v>
-      </c>
-      <c r="H5" s="2">
-        <v>64</v>
-      </c>
-      <c r="I5" s="2">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1427.2</v>
-      </c>
-      <c r="C6" s="2">
-        <v>15.54</v>
-      </c>
-      <c r="D6" s="2">
-        <v>-3.23</v>
-      </c>
-      <c r="E6" s="2">
-        <v>2.29</v>
-      </c>
-      <c r="F6" s="2">
-        <v>80.56</v>
-      </c>
-      <c r="G6" s="2">
-        <v>80</v>
-      </c>
-      <c r="H6" s="2">
-        <v>66</v>
-      </c>
-      <c r="I6" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C4">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2547,7 +2398,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="D2:D4">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2555,7 +2406,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E6">
+  <conditionalFormatting sqref="E2:E4">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2563,22 +2414,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
+  <conditionalFormatting sqref="F2:F4">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G6">
+  <conditionalFormatting sqref="G2:G4">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H6">
+  <conditionalFormatting sqref="H2:H4">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
+  <conditionalFormatting sqref="I2:I4">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2614,13 +2465,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2628,13 +2479,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D3" s="2">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2642,13 +2493,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2659,10 +2510,10 @@
         <v>62</v>
       </c>
       <c r="C5" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-07-24</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-07-24</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-07-24</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-07-24</t>
+    <t>Price_2026-07-31</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-07-31</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-07-31</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-07-31</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-07-31</t>
   </si>
   <si>
     <t>RS_Score_2026-07-24</t>
@@ -43,156 +46,153 @@
     <t>RS_Score_2026-07-10</t>
   </si>
   <si>
-    <t>RS_Score_2026-07-03</t>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>ETERNAL</t>
+  </si>
+  <si>
+    <t>TITAN</t>
   </si>
   <si>
     <t>ADANIENT</t>
   </si>
   <si>
-    <t>ETERNAL</t>
+    <t>HCLTECH</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
   </si>
   <si>
     <t>NESTLEIND</t>
   </si>
   <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>TMPV</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
     <t>GRASIM</t>
   </si>
   <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>HINDALCO</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>TMPV</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>ADANIPORTS</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>TITAN</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>HCLTECH</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
     <t>BAJAJ-AUTO</t>
   </si>
   <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
     <t>SBILIFE</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
     <t>2026-07-24</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
   </si>
 </sst>
 </file>
@@ -722,28 +722,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3026.4</v>
+        <v>1141.2</v>
       </c>
       <c r="C2" s="2">
-        <v>53.27</v>
+        <v>35.24</v>
       </c>
       <c r="D2" s="2">
-        <v>12.56</v>
+        <v>21.9</v>
       </c>
       <c r="E2" s="2">
-        <v>2.16</v>
+        <v>10.89</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H2" s="2">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="I2" s="2">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>60</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>280</v>
+        <v>1651.3</v>
       </c>
       <c r="C3" s="2">
-        <v>19.34</v>
+        <v>18.25</v>
       </c>
       <c r="D3" s="2">
-        <v>15.99</v>
+        <v>18.02</v>
       </c>
       <c r="E3" s="2">
-        <v>7.94</v>
+        <v>17.4</v>
       </c>
       <c r="F3" s="2">
-        <v>96.43000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="G3" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H3" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I3" s="2">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>1443.5</v>
+        <v>302.45</v>
       </c>
       <c r="C4" s="2">
-        <v>20.18</v>
+        <v>27.11</v>
       </c>
       <c r="D4" s="2">
-        <v>1.31</v>
+        <v>22.12</v>
       </c>
       <c r="E4" s="2">
-        <v>4.55</v>
+        <v>6.72</v>
       </c>
       <c r="F4" s="2">
-        <v>92.86</v>
+        <v>95</v>
       </c>
       <c r="G4" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="H4" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>3089.4</v>
+        <v>4875.2</v>
       </c>
       <c r="C5" s="2">
-        <v>15.13</v>
+        <v>25.43</v>
       </c>
       <c r="D5" s="2">
-        <v>4.95</v>
+        <v>17.6</v>
       </c>
       <c r="E5" s="2">
-        <v>0.3</v>
+        <v>9.07</v>
       </c>
       <c r="F5" s="2">
-        <v>89.29000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="G5" s="2">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="H5" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I5" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>4985</v>
+        <v>3009.5</v>
       </c>
       <c r="C6" s="2">
-        <v>16.26</v>
+        <v>65.62</v>
       </c>
       <c r="D6" s="2">
-        <v>16.59</v>
+        <v>5.65</v>
       </c>
       <c r="E6" s="2">
-        <v>-6.21</v>
+        <v>-6.15</v>
       </c>
       <c r="F6" s="2">
-        <v>85.70999999999999</v>
+        <v>90</v>
       </c>
       <c r="G6" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H6" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I6" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>2254.3</v>
+        <v>1346.9</v>
       </c>
       <c r="C7" s="2">
-        <v>-3.94</v>
+        <v>0.98</v>
       </c>
       <c r="D7" s="2">
-        <v>0.62</v>
+        <v>16.72</v>
       </c>
       <c r="E7" s="2">
-        <v>8.039999999999999</v>
+        <v>19.97</v>
       </c>
       <c r="F7" s="2">
-        <v>82.14</v>
+        <v>87.5</v>
       </c>
       <c r="G7" s="2">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="H7" s="2">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="I7" s="2">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>13442</v>
+        <v>2029.1</v>
       </c>
       <c r="C8" s="2">
-        <v>3.62</v>
+        <v>19.15</v>
       </c>
       <c r="D8" s="2">
-        <v>3.27</v>
+        <v>12.36</v>
       </c>
       <c r="E8" s="2">
-        <v>0.22</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="F8" s="2">
-        <v>78.56999999999999</v>
+        <v>85</v>
       </c>
       <c r="G8" s="2">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="H8" s="2">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I8" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>1005.1</v>
+        <v>1509.6</v>
       </c>
       <c r="C9" s="2">
-        <v>0.62</v>
+        <v>28.2</v>
       </c>
       <c r="D9" s="2">
-        <v>8.26</v>
+        <v>7.3</v>
       </c>
       <c r="E9" s="2">
-        <v>-2.12</v>
+        <v>2.93</v>
       </c>
       <c r="F9" s="2">
-        <v>75</v>
+        <v>82.5</v>
       </c>
       <c r="G9" s="2">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="H9" s="2">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="I9" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>1015</v>
+        <v>3398.5</v>
       </c>
       <c r="C10" s="2">
-        <v>-2.95</v>
+        <v>13.29</v>
       </c>
       <c r="D10" s="2">
-        <v>8.050000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="E10" s="2">
-        <v>-2.04</v>
+        <v>6.16</v>
       </c>
       <c r="F10" s="2">
-        <v>71.43000000000001</v>
+        <v>80</v>
       </c>
       <c r="G10" s="2">
+        <v>60</v>
+      </c>
+      <c r="H10" s="2">
+        <v>56</v>
+      </c>
+      <c r="I10" s="2">
         <v>54</v>
-      </c>
-      <c r="H10" s="2">
-        <v>40</v>
-      </c>
-      <c r="I10" s="2">
-        <v>30</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>234.71</v>
+        <v>2365.6</v>
       </c>
       <c r="C11" s="2">
-        <v>-1.22</v>
+        <v>0.5</v>
       </c>
       <c r="D11" s="2">
-        <v>0.89</v>
+        <v>3.05</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.84</v>
+        <v>15.6</v>
       </c>
       <c r="F11" s="2">
-        <v>67.86</v>
+        <v>77.5</v>
       </c>
       <c r="G11" s="2">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H11" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I11" s="2">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>384.75</v>
+        <v>7833.5</v>
       </c>
       <c r="C12" s="2">
-        <v>3</v>
+        <v>15.2</v>
       </c>
       <c r="D12" s="2">
-        <v>-1.63</v>
+        <v>6.76</v>
       </c>
       <c r="E12" s="2">
-        <v>-2.55</v>
+        <v>5.94</v>
       </c>
       <c r="F12" s="2">
-        <v>64.29000000000001</v>
+        <v>75</v>
       </c>
       <c r="G12" s="2">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="H12" s="2">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I12" s="2">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>288.2</v>
+        <v>1990.5</v>
       </c>
       <c r="C13" s="2">
-        <v>-3.45</v>
+        <v>13.83</v>
       </c>
       <c r="D13" s="2">
-        <v>-2.82</v>
+        <v>8.43</v>
       </c>
       <c r="E13" s="2">
-        <v>0.68</v>
+        <v>4.33</v>
       </c>
       <c r="F13" s="2">
-        <v>60.71</v>
+        <v>72.5</v>
       </c>
       <c r="G13" s="2">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="H13" s="2">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="I13" s="2">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>248.76</v>
+        <v>5171</v>
       </c>
       <c r="C14" s="2">
-        <v>-6.04</v>
+        <v>24.58</v>
       </c>
       <c r="D14" s="2">
-        <v>-16.3</v>
+        <v>14.86</v>
       </c>
       <c r="E14" s="2">
-        <v>6.28</v>
+        <v>-4.39</v>
       </c>
       <c r="F14" s="2">
-        <v>57.14</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="H14" s="2">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="I14" s="2">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>942.8</v>
+        <v>256.46</v>
       </c>
       <c r="C15" s="2">
-        <v>1.18</v>
+        <v>10.21</v>
       </c>
       <c r="D15" s="2">
-        <v>-10.01</v>
+        <v>6.09</v>
       </c>
       <c r="E15" s="2">
-        <v>-1.67</v>
+        <v>6.86</v>
       </c>
       <c r="F15" s="2">
-        <v>53.57</v>
+        <v>67.5</v>
       </c>
       <c r="G15" s="2">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="H15" s="2">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="I15" s="2">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>3785.6</v>
+        <v>1473.2</v>
       </c>
       <c r="C16" s="2">
-        <v>7.9</v>
+        <v>21.95</v>
       </c>
       <c r="D16" s="2">
-        <v>-2.43</v>
+        <v>5.17</v>
       </c>
       <c r="E16" s="2">
-        <v>-9.109999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="F16" s="2">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G16" s="2">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="H16" s="2">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="I16" s="2">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>177.12</v>
+        <v>1435.4</v>
       </c>
       <c r="C17" s="2">
-        <v>-7.42</v>
+        <v>14.72</v>
       </c>
       <c r="D17" s="2">
-        <v>-7.83</v>
+        <v>11.12</v>
       </c>
       <c r="E17" s="2">
-        <v>0.93</v>
+        <v>0.6</v>
       </c>
       <c r="F17" s="2">
-        <v>46.43</v>
+        <v>62.5</v>
       </c>
       <c r="G17" s="2">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="H17" s="2">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="I17" s="2">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>1088</v>
+        <v>1972</v>
       </c>
       <c r="C18" s="2">
-        <v>1.78</v>
+        <v>10.81</v>
       </c>
       <c r="D18" s="2">
-        <v>-10.87</v>
+        <v>6.51</v>
       </c>
       <c r="E18" s="2">
-        <v>-2.23</v>
+        <v>3.69</v>
       </c>
       <c r="F18" s="2">
-        <v>42.86</v>
+        <v>60</v>
       </c>
       <c r="G18" s="2">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="H18" s="2">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="I18" s="2">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1278</v>
+        <v>1046.7</v>
       </c>
       <c r="C19" s="2">
-        <v>-8.130000000000001</v>
+        <v>16.49</v>
       </c>
       <c r="D19" s="2">
-        <v>-3.89</v>
+        <v>9.43</v>
       </c>
       <c r="E19" s="2">
-        <v>-1.77</v>
+        <v>-1.47</v>
       </c>
       <c r="F19" s="2">
-        <v>39.29</v>
+        <v>57.5</v>
       </c>
       <c r="G19" s="2">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H19" s="2">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="I19" s="2">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>283.45</v>
+        <v>1098.5</v>
       </c>
       <c r="C20" s="2">
-        <v>-4.49</v>
+        <v>13.54</v>
       </c>
       <c r="D20" s="2">
-        <v>-6.12</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E20" s="2">
-        <v>-2.49</v>
+        <v>-3</v>
       </c>
       <c r="F20" s="2">
-        <v>35.71</v>
+        <v>55</v>
       </c>
       <c r="G20" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="I20" s="2">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>405</v>
+        <v>1270</v>
       </c>
       <c r="C21" s="2">
-        <v>-7.82</v>
+        <v>12.67</v>
       </c>
       <c r="D21" s="2">
-        <v>-5.06</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E21" s="2">
-        <v>-1.6</v>
+        <v>2.74</v>
       </c>
       <c r="F21" s="2">
-        <v>32.14</v>
+        <v>52.5</v>
       </c>
       <c r="G21" s="2">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="H21" s="2">
         <v>38</v>
       </c>
       <c r="I21" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>323.8</v>
+        <v>1130.1</v>
       </c>
       <c r="C22" s="2">
-        <v>2.28</v>
+        <v>-9.68</v>
       </c>
       <c r="D22" s="2">
-        <v>-7.55</v>
+        <v>-1.19</v>
       </c>
       <c r="E22" s="2">
-        <v>-6.16</v>
+        <v>8.43</v>
       </c>
       <c r="F22" s="2">
-        <v>28.57</v>
+        <v>50</v>
       </c>
       <c r="G22" s="2">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H22" s="2">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="I22" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>1040.9</v>
+        <v>3938.9</v>
       </c>
       <c r="C23" s="2">
-        <v>-13.75</v>
+        <v>13.1</v>
       </c>
       <c r="D23" s="2">
-        <v>-6.92</v>
+        <v>-2.34</v>
       </c>
       <c r="E23" s="2">
-        <v>0.41</v>
+        <v>-2.53</v>
       </c>
       <c r="F23" s="2">
-        <v>25</v>
+        <v>47.5</v>
       </c>
       <c r="G23" s="2">
         <v>30</v>
       </c>
       <c r="H23" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I23" s="2">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>427.4</v>
+        <v>1027.4</v>
       </c>
       <c r="C24" s="2">
-        <v>-7.54</v>
+        <v>1.47</v>
       </c>
       <c r="D24" s="2">
-        <v>-7.51</v>
+        <v>5.96</v>
       </c>
       <c r="E24" s="2">
-        <v>-3.92</v>
+        <v>-0.99</v>
       </c>
       <c r="F24" s="2">
-        <v>21.43</v>
+        <v>45</v>
       </c>
       <c r="G24" s="2">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="H24" s="2">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="I24" s="2">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>182.67</v>
+        <v>1696.5</v>
       </c>
       <c r="C25" s="2">
-        <v>-4.6</v>
+        <v>26.74</v>
       </c>
       <c r="D25" s="2">
-        <v>-11.1</v>
+        <v>-5.51</v>
       </c>
       <c r="E25" s="2">
-        <v>-3.64</v>
+        <v>-9.01</v>
       </c>
       <c r="F25" s="2">
-        <v>17.86</v>
+        <v>42.5</v>
       </c>
       <c r="G25" s="2">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="H25" s="2">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="I25" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>347.2</v>
+        <v>183.65</v>
       </c>
       <c r="C26" s="2">
-        <v>-9.43</v>
+        <v>-1.59</v>
       </c>
       <c r="D26" s="2">
-        <v>-10.58</v>
+        <v>-10.2</v>
       </c>
       <c r="E26" s="2">
-        <v>-2.5</v>
+        <v>6.56</v>
       </c>
       <c r="F26" s="2">
-        <v>14.29</v>
+        <v>40</v>
       </c>
       <c r="G26" s="2">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="H26" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I26" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>742.8</v>
+        <v>339.75</v>
       </c>
       <c r="C27" s="2">
-        <v>-10.68</v>
+        <v>10.08</v>
       </c>
       <c r="D27" s="2">
-        <v>-1.76</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="E27" s="2">
-        <v>-7.02</v>
+        <v>-2.1</v>
       </c>
       <c r="F27" s="2">
-        <v>10.71</v>
+        <v>37.5</v>
       </c>
       <c r="G27" s="2">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="H27" s="2">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="I27" s="2">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,25 +1554,25 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>555.05</v>
+        <v>189.69</v>
       </c>
       <c r="C28" s="2">
-        <v>-13.28</v>
+        <v>1.47</v>
       </c>
       <c r="D28" s="2">
-        <v>-7.92</v>
+        <v>-7.91</v>
       </c>
       <c r="E28" s="2">
-        <v>-4.83</v>
+        <v>-0.62</v>
       </c>
       <c r="F28" s="2">
-        <v>7.14</v>
+        <v>35</v>
       </c>
       <c r="G28" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H28" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I28" s="2">
         <v>16</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>1151.7</v>
+        <v>284.25</v>
       </c>
       <c r="C29" s="2">
-        <v>-9.720000000000001</v>
+        <v>-4.93</v>
       </c>
       <c r="D29" s="2">
-        <v>-12.94</v>
+        <v>-3.76</v>
       </c>
       <c r="E29" s="2">
-        <v>-15.75</v>
+        <v>-0.4</v>
       </c>
       <c r="F29" s="2">
-        <v>3.57</v>
+        <v>32.5</v>
       </c>
       <c r="G29" s="2">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H29" s="2">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I29" s="2">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1617,14 +1617,29 @@
       <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="B30" s="1">
+        <v>2101.3</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1.81</v>
+      </c>
+      <c r="D30" s="2">
+        <v>-3.36</v>
+      </c>
+      <c r="E30" s="2">
+        <v>-4.57</v>
+      </c>
+      <c r="F30" s="2">
+        <v>30</v>
+      </c>
       <c r="G30" s="2">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="H30" s="2">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="I30" s="2">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1634,14 +1649,29 @@
       <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="B31" s="1">
+        <v>281</v>
+      </c>
+      <c r="C31" s="2">
+        <v>-0.89</v>
+      </c>
+      <c r="D31" s="2">
+        <v>-5.03</v>
+      </c>
+      <c r="E31" s="2">
+        <v>-2.52</v>
+      </c>
+      <c r="F31" s="2">
+        <v>27.5</v>
+      </c>
       <c r="G31" s="2">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="H31" s="2">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="I31" s="2">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1651,14 +1681,29 @@
       <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="B32" s="1">
+        <v>1083.1</v>
+      </c>
+      <c r="C32" s="2">
+        <v>3.72</v>
+      </c>
+      <c r="D32" s="2">
+        <v>-8.77</v>
+      </c>
+      <c r="E32" s="2">
+        <v>-3.11</v>
+      </c>
+      <c r="F32" s="2">
+        <v>25</v>
+      </c>
       <c r="G32" s="2">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="H32" s="2">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="I32" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1668,14 +1713,29 @@
       <c r="A33" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="B33" s="1">
+        <v>1307.8</v>
+      </c>
+      <c r="C33" s="2">
+        <v>-6.94</v>
+      </c>
+      <c r="D33" s="2">
+        <v>-3.89</v>
+      </c>
+      <c r="E33" s="2">
+        <v>-1.02</v>
+      </c>
+      <c r="F33" s="2">
+        <v>22.5</v>
+      </c>
       <c r="G33" s="2">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="H33" s="2">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="I33" s="2">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1685,14 +1745,29 @@
       <c r="A34" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="B34" s="1">
+        <v>1229.5</v>
+      </c>
+      <c r="C34" s="2">
+        <v>3.16</v>
+      </c>
+      <c r="D34" s="2">
+        <v>-6.16</v>
+      </c>
+      <c r="E34" s="2">
+        <v>-8.15</v>
+      </c>
+      <c r="F34" s="2">
+        <v>20</v>
+      </c>
       <c r="G34" s="2">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="H34" s="2">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="I34" s="2">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1702,14 +1777,29 @@
       <c r="A35" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="B35" s="1">
+        <v>414.15</v>
+      </c>
+      <c r="C35" s="2">
+        <v>-5.07</v>
+      </c>
+      <c r="D35" s="2">
+        <v>-8.369999999999999</v>
+      </c>
+      <c r="E35" s="2">
+        <v>-2.93</v>
+      </c>
+      <c r="F35" s="2">
+        <v>17.5</v>
+      </c>
       <c r="G35" s="2">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="H35" s="2">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I35" s="2">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1719,14 +1809,29 @@
       <c r="A36" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="B36" s="1">
+        <v>347.25</v>
+      </c>
+      <c r="C36" s="2">
+        <v>-7.54</v>
+      </c>
+      <c r="D36" s="2">
+        <v>-10.97</v>
+      </c>
+      <c r="E36" s="2">
+        <v>-2.53</v>
+      </c>
+      <c r="F36" s="2">
+        <v>15</v>
+      </c>
       <c r="G36" s="2">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="H36" s="2">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="I36" s="2">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1736,14 +1841,29 @@
       <c r="A37" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="B37" s="1">
+        <v>748.15</v>
+      </c>
+      <c r="C37" s="2">
+        <v>-0.57</v>
+      </c>
+      <c r="D37" s="2">
+        <v>-3.35</v>
+      </c>
+      <c r="E37" s="2">
+        <v>-9.85</v>
+      </c>
+      <c r="F37" s="2">
+        <v>12.5</v>
+      </c>
       <c r="G37" s="2">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="H37" s="2">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I37" s="2">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1753,14 +1873,29 @@
       <c r="A38" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="B38" s="1">
+        <v>548.5</v>
+      </c>
+      <c r="C38" s="2">
+        <v>-8.710000000000001</v>
+      </c>
+      <c r="D38" s="2">
+        <v>-11.22</v>
+      </c>
+      <c r="E38" s="2">
+        <v>-2.78</v>
+      </c>
+      <c r="F38" s="2">
+        <v>10</v>
+      </c>
       <c r="G38" s="2">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="H38" s="2">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="I38" s="2">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1770,14 +1905,29 @@
       <c r="A39" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="B39" s="1">
+        <v>242.53</v>
+      </c>
+      <c r="C39" s="2">
+        <v>-9.52</v>
+      </c>
+      <c r="D39" s="2">
+        <v>-14.89</v>
+      </c>
+      <c r="E39" s="2">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F39" s="2">
+        <v>7.5</v>
+      </c>
       <c r="G39" s="2">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="H39" s="2">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="I39" s="2">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1787,14 +1937,29 @@
       <c r="A40" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="B40" s="1">
+        <v>387.85</v>
+      </c>
+      <c r="C40" s="2">
+        <v>-6.42</v>
+      </c>
+      <c r="D40" s="2">
+        <v>-8.06</v>
+      </c>
+      <c r="E40" s="2">
+        <v>-8.859999999999999</v>
+      </c>
+      <c r="F40" s="2">
+        <v>5</v>
+      </c>
       <c r="G40" s="2">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H40" s="2">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="I40" s="2">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1804,14 +1969,29 @@
       <c r="A41" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="B41" s="1">
+        <v>1148.1</v>
+      </c>
+      <c r="C41" s="2">
+        <v>-8.27</v>
+      </c>
+      <c r="D41" s="2">
+        <v>-13.22</v>
+      </c>
+      <c r="E41" s="2">
+        <v>-15.54</v>
+      </c>
+      <c r="F41" s="2">
+        <v>2.5</v>
+      </c>
       <c r="G41" s="2">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="H41" s="2">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="I41" s="2">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -1822,13 +2002,13 @@
         <v>49</v>
       </c>
       <c r="G42" s="2">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="H42" s="2">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I42" s="2">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -1839,13 +2019,13 @@
         <v>50</v>
       </c>
       <c r="G43" s="2">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="H43" s="2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I43" s="2">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -1856,13 +2036,13 @@
         <v>51</v>
       </c>
       <c r="G44" s="2">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="H44" s="2">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="I44" s="2">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -1873,13 +2053,13 @@
         <v>52</v>
       </c>
       <c r="G45" s="2">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="H45" s="2">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="I45" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -1890,13 +2070,13 @@
         <v>53</v>
       </c>
       <c r="G46" s="2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H46" s="2">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="I46" s="2">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -1907,13 +2087,13 @@
         <v>54</v>
       </c>
       <c r="G47" s="2">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="H47" s="2">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="I47" s="2">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -1924,13 +2104,13 @@
         <v>55</v>
       </c>
       <c r="G48" s="2">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="H48" s="2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I48" s="2">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -1941,13 +2121,13 @@
         <v>56</v>
       </c>
       <c r="G49" s="2">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H49" s="2">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I49" s="2">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -1958,13 +2138,13 @@
         <v>57</v>
       </c>
       <c r="G50" s="2">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="H50" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I50" s="2">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -1975,13 +2155,13 @@
         <v>58</v>
       </c>
       <c r="G51" s="2">
+        <v>58</v>
+      </c>
+      <c r="H51" s="2">
         <v>36</v>
       </c>
-      <c r="H51" s="2">
+      <c r="I51" s="2">
         <v>58</v>
-      </c>
-      <c r="I51" s="2">
-        <v>24</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2090,7 +2270,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2132,90 +2312,119 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3026.4</v>
+        <v>1141.2</v>
       </c>
       <c r="C2" s="2">
-        <v>53.27</v>
+        <v>35.24</v>
       </c>
       <c r="D2" s="2">
-        <v>12.56</v>
+        <v>21.9</v>
       </c>
       <c r="E2" s="2">
-        <v>2.16</v>
+        <v>10.89</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H2" s="2">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="I2" s="2">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1">
-        <v>280</v>
+        <v>302.45</v>
       </c>
       <c r="C3" s="2">
-        <v>19.34</v>
+        <v>27.11</v>
       </c>
       <c r="D3" s="2">
-        <v>15.99</v>
+        <v>22.12</v>
       </c>
       <c r="E3" s="2">
-        <v>7.94</v>
+        <v>6.72</v>
       </c>
       <c r="F3" s="2">
-        <v>96.43000000000001</v>
+        <v>95</v>
       </c>
       <c r="G3" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H3" s="2">
         <v>98</v>
       </c>
       <c r="I3" s="2">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1">
+        <v>4875.2</v>
+      </c>
+      <c r="C4" s="2">
+        <v>25.43</v>
+      </c>
+      <c r="D4" s="2">
+        <v>17.6</v>
+      </c>
+      <c r="E4" s="2">
+        <v>9.07</v>
+      </c>
+      <c r="F4" s="2">
+        <v>92.5</v>
+      </c>
+      <c r="G4" s="2">
+        <v>92</v>
+      </c>
+      <c r="H4" s="2">
+        <v>86</v>
+      </c>
+      <c r="I4" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="1">
-        <v>4985</v>
-      </c>
-      <c r="C4" s="2">
-        <v>16.26</v>
-      </c>
-      <c r="D4" s="2">
-        <v>16.59</v>
-      </c>
-      <c r="E4" s="2">
-        <v>-6.21</v>
-      </c>
-      <c r="F4" s="2">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="G4" s="2">
-        <v>94</v>
-      </c>
-      <c r="H4" s="2">
-        <v>96</v>
-      </c>
-      <c r="I4" s="2">
-        <v>96</v>
+      <c r="B5" s="1">
+        <v>3009.5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>65.62</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5.65</v>
+      </c>
+      <c r="E5" s="2">
+        <v>-6.15</v>
+      </c>
+      <c r="F5" s="2">
+        <v>90</v>
+      </c>
+      <c r="G5" s="2">
+        <v>100</v>
+      </c>
+      <c r="H5" s="2">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C4">
+  <conditionalFormatting sqref="C2:C5">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2223,7 +2432,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
+  <conditionalFormatting sqref="D2:D5">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2231,7 +2440,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4">
+  <conditionalFormatting sqref="E2:E5">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2239,22 +2448,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4">
+  <conditionalFormatting sqref="F2:F5">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G4">
+  <conditionalFormatting sqref="G2:G5">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H4">
+  <conditionalFormatting sqref="H2:H5">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4">
+  <conditionalFormatting sqref="I2:I5">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2265,7 +2474,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2307,28 +2516,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>3026.4</v>
+        <v>1141.2</v>
       </c>
       <c r="C2" s="2">
-        <v>53.27</v>
+        <v>35.24</v>
       </c>
       <c r="D2" s="2">
-        <v>12.56</v>
+        <v>21.9</v>
       </c>
       <c r="E2" s="2">
-        <v>2.16</v>
+        <v>10.89</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H2" s="2">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="I2" s="2">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2336,61 +2545,177 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>280</v>
+        <v>1651.3</v>
       </c>
       <c r="C3" s="2">
-        <v>19.34</v>
+        <v>18.25</v>
       </c>
       <c r="D3" s="2">
-        <v>15.99</v>
+        <v>18.02</v>
       </c>
       <c r="E3" s="2">
-        <v>7.94</v>
+        <v>17.4</v>
       </c>
       <c r="F3" s="2">
-        <v>96.43000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="G3" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H3" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I3" s="2">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>4985</v>
+        <v>302.45</v>
       </c>
       <c r="C4" s="2">
-        <v>16.26</v>
+        <v>27.11</v>
       </c>
       <c r="D4" s="2">
-        <v>16.59</v>
+        <v>22.12</v>
       </c>
       <c r="E4" s="2">
-        <v>-6.21</v>
+        <v>6.72</v>
       </c>
       <c r="F4" s="2">
-        <v>85.70999999999999</v>
+        <v>95</v>
       </c>
       <c r="G4" s="2">
         <v>94</v>
       </c>
       <c r="H4" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2">
-        <v>96</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4875.2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>25.43</v>
+      </c>
+      <c r="D5" s="2">
+        <v>17.6</v>
+      </c>
+      <c r="E5" s="2">
+        <v>9.07</v>
+      </c>
+      <c r="F5" s="2">
+        <v>92.5</v>
+      </c>
+      <c r="G5" s="2">
+        <v>92</v>
+      </c>
+      <c r="H5" s="2">
+        <v>86</v>
+      </c>
+      <c r="I5" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3009.5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>65.62</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5.65</v>
+      </c>
+      <c r="E6" s="2">
+        <v>-6.15</v>
+      </c>
+      <c r="F6" s="2">
+        <v>90</v>
+      </c>
+      <c r="G6" s="2">
+        <v>100</v>
+      </c>
+      <c r="H6" s="2">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1346.9</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="D7" s="2">
+        <v>16.72</v>
+      </c>
+      <c r="E7" s="2">
+        <v>19.97</v>
+      </c>
+      <c r="F7" s="2">
+        <v>87.5</v>
+      </c>
+      <c r="G7" s="2">
+        <v>90</v>
+      </c>
+      <c r="H7" s="2">
+        <v>60</v>
+      </c>
+      <c r="I7" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1509.6</v>
+      </c>
+      <c r="C8" s="2">
+        <v>28.2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="F8" s="2">
+        <v>82.5</v>
+      </c>
+      <c r="G8" s="2">
+        <v>82</v>
+      </c>
+      <c r="H8" s="2">
+        <v>76</v>
+      </c>
+      <c r="I8" s="2">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C4">
+  <conditionalFormatting sqref="C2:C8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2398,7 +2723,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
+  <conditionalFormatting sqref="D2:D8">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2406,7 +2731,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4">
+  <conditionalFormatting sqref="E2:E8">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2414,22 +2739,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4">
+  <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G4">
+  <conditionalFormatting sqref="G2:G8">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H4">
+  <conditionalFormatting sqref="H2:H8">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4">
+  <conditionalFormatting sqref="I2:I8">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2465,13 +2790,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D2" s="2">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2479,10 +2804,10 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C3" s="2">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2">
         <v>50</v>
@@ -2493,13 +2818,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D4" s="2">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2507,13 +2832,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C5" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D5" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-07-31</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-07-31</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-07-31</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-07-31</t>
+    <t>Price_2026-08-07</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-08-07</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-08-07</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-08-07</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-08-07</t>
   </si>
   <si>
     <t>RS_Score_2026-07-31</t>
@@ -43,156 +46,153 @@
     <t>RS_Score_2026-07-17</t>
   </si>
   <si>
-    <t>RS_Score_2026-07-10</t>
+    <t>ETERNAL</t>
   </si>
   <si>
     <t>BAJFINANCE</t>
   </si>
   <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
     <t>TECHM</t>
   </si>
   <si>
-    <t>ETERNAL</t>
-  </si>
-  <si>
-    <t>TITAN</t>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>HCLTECH</t>
+  </si>
+  <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>TMPV</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>MAXHEALTH</t>
   </si>
   <si>
     <t>ADANIENT</t>
   </si>
   <si>
-    <t>HCLTECH</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO</t>
   </si>
   <si>
     <t>CIPLA</t>
   </si>
   <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>ADANIPORTS</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>TMPV</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
-    <t>HINDALCO</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
     <t>SBILIFE</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
     <t>2026-07-31</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-07-17</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
   </si>
 </sst>
 </file>
@@ -722,28 +722,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>1141.2</v>
+        <v>315</v>
       </c>
       <c r="C2" s="2">
-        <v>35.24</v>
+        <v>35.94</v>
       </c>
       <c r="D2" s="2">
-        <v>21.9</v>
+        <v>26.96</v>
       </c>
       <c r="E2" s="2">
-        <v>10.89</v>
+        <v>10.45</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H2" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I2" s="2">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>60</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1651.3</v>
+        <v>1078</v>
       </c>
       <c r="C3" s="2">
-        <v>18.25</v>
+        <v>31.18</v>
       </c>
       <c r="D3" s="2">
-        <v>18.02</v>
+        <v>22</v>
       </c>
       <c r="E3" s="2">
-        <v>17.4</v>
+        <v>5.42</v>
       </c>
       <c r="F3" s="2">
-        <v>97.5</v>
+        <v>97.62</v>
       </c>
       <c r="G3" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H3" s="2">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I3" s="2">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>302.45</v>
+        <v>1115</v>
       </c>
       <c r="C4" s="2">
-        <v>27.11</v>
+        <v>25.76</v>
       </c>
       <c r="D4" s="2">
-        <v>22.12</v>
+        <v>22.01</v>
       </c>
       <c r="E4" s="2">
-        <v>6.72</v>
+        <v>6.38</v>
       </c>
       <c r="F4" s="2">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>94</v>
+        <v>57.5</v>
       </c>
       <c r="H4" s="2">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="I4" s="2">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>4875.2</v>
+        <v>4941</v>
       </c>
       <c r="C5" s="2">
-        <v>25.43</v>
+        <v>20.99</v>
       </c>
       <c r="D5" s="2">
-        <v>17.6</v>
+        <v>23.17</v>
       </c>
       <c r="E5" s="2">
-        <v>9.07</v>
+        <v>7.38</v>
       </c>
       <c r="F5" s="2">
+        <v>92.86</v>
+      </c>
+      <c r="G5" s="2">
         <v>92.5</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <v>92</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>86</v>
-      </c>
-      <c r="I5" s="2">
-        <v>82</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>3009.5</v>
+        <v>3502</v>
       </c>
       <c r="C6" s="2">
-        <v>65.62</v>
+        <v>17.5</v>
       </c>
       <c r="D6" s="2">
-        <v>5.65</v>
+        <v>19.14</v>
       </c>
       <c r="E6" s="2">
-        <v>-6.15</v>
+        <v>10.81</v>
       </c>
       <c r="F6" s="2">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="G6" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H6" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I6" s="2">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>1346.9</v>
+        <v>8020</v>
       </c>
       <c r="C7" s="2">
-        <v>0.98</v>
+        <v>21.87</v>
       </c>
       <c r="D7" s="2">
-        <v>16.72</v>
+        <v>14.13</v>
       </c>
       <c r="E7" s="2">
-        <v>19.97</v>
+        <v>11.07</v>
       </c>
       <c r="F7" s="2">
-        <v>87.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="H7" s="2">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="I7" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>2029.1</v>
+        <v>1540</v>
       </c>
       <c r="C8" s="2">
-        <v>19.15</v>
+        <v>29.89</v>
       </c>
       <c r="D8" s="2">
-        <v>12.36</v>
+        <v>11.18</v>
       </c>
       <c r="E8" s="2">
-        <v>8.470000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="F8" s="2">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>78</v>
+        <v>82.5</v>
       </c>
       <c r="H8" s="2">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="I8" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>1509.6</v>
+        <v>5333</v>
       </c>
       <c r="C9" s="2">
-        <v>28.2</v>
+        <v>27.17</v>
       </c>
       <c r="D9" s="2">
-        <v>7.3</v>
+        <v>19.75</v>
       </c>
       <c r="E9" s="2">
-        <v>2.93</v>
+        <v>1.98</v>
       </c>
       <c r="F9" s="2">
-        <v>82.5</v>
+        <v>83.33</v>
       </c>
       <c r="G9" s="2">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="H9" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I9" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,25 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>3398.5</v>
+        <v>3323</v>
       </c>
       <c r="C10" s="2">
-        <v>13.29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="2">
-        <v>9.4</v>
+        <v>7.44</v>
       </c>
       <c r="E10" s="2">
-        <v>6.16</v>
+        <v>6.01</v>
       </c>
       <c r="F10" s="2">
-        <v>80</v>
-      </c>
-      <c r="G10" s="2">
-        <v>60</v>
+        <v>80.95</v>
       </c>
       <c r="H10" s="2">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="I10" s="2">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1007,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>2365.6</v>
+        <v>2008.9</v>
       </c>
       <c r="C11" s="2">
-        <v>0.5</v>
+        <v>22.55</v>
       </c>
       <c r="D11" s="2">
-        <v>3.05</v>
+        <v>14.31</v>
       </c>
       <c r="E11" s="2">
-        <v>15.6</v>
+        <v>5.28</v>
       </c>
       <c r="F11" s="2">
-        <v>77.5</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="G11" s="2">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="H11" s="2">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="I11" s="2">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1039,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>7833.5</v>
+        <v>1635</v>
       </c>
       <c r="C12" s="2">
-        <v>15.2</v>
+        <v>16.37</v>
       </c>
       <c r="D12" s="2">
-        <v>6.76</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E12" s="2">
-        <v>5.94</v>
+        <v>8.67</v>
       </c>
       <c r="F12" s="2">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="G12" s="2">
-        <v>76</v>
+        <v>97.5</v>
       </c>
       <c r="H12" s="2">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="I12" s="2">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1071,25 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>1990.5</v>
+        <v>2997</v>
       </c>
       <c r="C13" s="2">
-        <v>13.83</v>
+        <v>26.8</v>
       </c>
       <c r="D13" s="2">
-        <v>8.43</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E13" s="2">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="F13" s="2">
-        <v>72.5</v>
-      </c>
-      <c r="G13" s="2">
-        <v>68</v>
+        <v>73.81</v>
       </c>
       <c r="H13" s="2">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="I13" s="2">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1100,25 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>5171</v>
+        <v>12105</v>
       </c>
       <c r="C14" s="2">
-        <v>24.58</v>
+        <v>16.31</v>
       </c>
       <c r="D14" s="2">
-        <v>14.86</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E14" s="2">
-        <v>-4.39</v>
+        <v>6.75</v>
       </c>
       <c r="F14" s="2">
-        <v>70</v>
-      </c>
-      <c r="G14" s="2">
-        <v>72</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H14" s="2">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="I14" s="2">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1129,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>256.46</v>
+        <v>1356.6</v>
       </c>
       <c r="C15" s="2">
-        <v>10.21</v>
+        <v>-0.39</v>
       </c>
       <c r="D15" s="2">
-        <v>6.09</v>
+        <v>14.67</v>
       </c>
       <c r="E15" s="2">
-        <v>6.86</v>
+        <v>12.22</v>
       </c>
       <c r="F15" s="2">
-        <v>67.5</v>
+        <v>69.05</v>
       </c>
       <c r="G15" s="2">
-        <v>42</v>
+        <v>87.5</v>
       </c>
       <c r="H15" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="I15" s="2">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1161,25 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>1473.2</v>
+        <v>2735</v>
       </c>
       <c r="C16" s="2">
-        <v>21.95</v>
+        <v>27.19</v>
       </c>
       <c r="D16" s="2">
-        <v>5.17</v>
+        <v>4.8</v>
       </c>
       <c r="E16" s="2">
-        <v>0.06</v>
+        <v>3.13</v>
       </c>
       <c r="F16" s="2">
-        <v>65</v>
-      </c>
-      <c r="G16" s="2">
-        <v>52</v>
+        <v>66.67</v>
       </c>
       <c r="H16" s="2">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="I16" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1190,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>1435.4</v>
+        <v>1421</v>
       </c>
       <c r="C17" s="2">
-        <v>14.72</v>
+        <v>17.86</v>
       </c>
       <c r="D17" s="2">
-        <v>11.12</v>
+        <v>15.59</v>
       </c>
       <c r="E17" s="2">
-        <v>0.6</v>
+        <v>1.67</v>
       </c>
       <c r="F17" s="2">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="G17" s="2">
         <v>62.5</v>
       </c>
-      <c r="G17" s="2">
+      <c r="H17" s="2">
         <v>86</v>
       </c>
-      <c r="H17" s="2">
+      <c r="I17" s="2">
         <v>90</v>
-      </c>
-      <c r="I17" s="2">
-        <v>72</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1222,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>1972</v>
+        <v>1097.2</v>
       </c>
       <c r="C18" s="2">
-        <v>10.81</v>
+        <v>9.68</v>
       </c>
       <c r="D18" s="2">
-        <v>6.51</v>
+        <v>15</v>
       </c>
       <c r="E18" s="2">
-        <v>3.69</v>
+        <v>5.81</v>
       </c>
       <c r="F18" s="2">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="G18" s="2">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="H18" s="2">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="I18" s="2">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1254,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1046.7</v>
+        <v>2452.7</v>
       </c>
       <c r="C19" s="2">
-        <v>16.49</v>
+        <v>1.99</v>
       </c>
       <c r="D19" s="2">
-        <v>9.43</v>
+        <v>7.35</v>
       </c>
       <c r="E19" s="2">
-        <v>-1.47</v>
+        <v>13.05</v>
       </c>
       <c r="F19" s="2">
-        <v>57.5</v>
+        <v>59.52</v>
       </c>
       <c r="G19" s="2">
-        <v>50</v>
+        <v>77.5</v>
       </c>
       <c r="H19" s="2">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I19" s="2">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1286,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>1098.5</v>
+        <v>256.8</v>
       </c>
       <c r="C20" s="2">
-        <v>13.54</v>
+        <v>11.91</v>
       </c>
       <c r="D20" s="2">
-        <v>9.949999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E20" s="2">
-        <v>-3</v>
+        <v>6.38</v>
       </c>
       <c r="F20" s="2">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="G20" s="2">
-        <v>46</v>
+        <v>67.5</v>
       </c>
       <c r="H20" s="2">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I20" s="2">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1318,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>1270</v>
+        <v>1959.9</v>
       </c>
       <c r="C21" s="2">
-        <v>12.67</v>
+        <v>10.89</v>
       </c>
       <c r="D21" s="2">
-        <v>-0.9399999999999999</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E21" s="2">
-        <v>2.74</v>
+        <v>4.35</v>
       </c>
       <c r="F21" s="2">
-        <v>52.5</v>
+        <v>54.76</v>
       </c>
       <c r="G21" s="2">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H21" s="2">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="I21" s="2">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1350,25 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>1130.1</v>
+        <v>1059.6</v>
       </c>
       <c r="C22" s="2">
-        <v>-9.68</v>
+        <v>16.25</v>
       </c>
       <c r="D22" s="2">
-        <v>-1.19</v>
+        <v>-6.67</v>
       </c>
       <c r="E22" s="2">
-        <v>8.43</v>
+        <v>9.59</v>
       </c>
       <c r="F22" s="2">
-        <v>50</v>
-      </c>
-      <c r="G22" s="2">
-        <v>14</v>
+        <v>52.38</v>
       </c>
       <c r="H22" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I22" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1379,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>3938.9</v>
+        <v>1945</v>
       </c>
       <c r="C23" s="2">
-        <v>13.1</v>
+        <v>15.15</v>
       </c>
       <c r="D23" s="2">
-        <v>-2.34</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E23" s="2">
-        <v>-2.53</v>
+        <v>1.23</v>
       </c>
       <c r="F23" s="2">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="G23" s="2">
-        <v>30</v>
+        <v>72.5</v>
       </c>
       <c r="H23" s="2">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="I23" s="2">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1411,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>1027.4</v>
+        <v>4056</v>
       </c>
       <c r="C24" s="2">
-        <v>1.47</v>
+        <v>13.35</v>
       </c>
       <c r="D24" s="2">
-        <v>5.96</v>
+        <v>1.13</v>
       </c>
       <c r="E24" s="2">
-        <v>-0.99</v>
+        <v>3.25</v>
       </c>
       <c r="F24" s="2">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="G24" s="2">
-        <v>44</v>
+        <v>47.5</v>
       </c>
       <c r="H24" s="2">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="I24" s="2">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1443,25 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>1696.5</v>
+        <v>390.75</v>
       </c>
       <c r="C25" s="2">
-        <v>26.74</v>
+        <v>9.34</v>
       </c>
       <c r="D25" s="2">
-        <v>-5.51</v>
+        <v>3.72</v>
       </c>
       <c r="E25" s="2">
-        <v>-9.01</v>
+        <v>1.76</v>
       </c>
       <c r="F25" s="2">
-        <v>42.5</v>
-      </c>
-      <c r="G25" s="2">
-        <v>80</v>
+        <v>45.24</v>
       </c>
       <c r="H25" s="2">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="I25" s="2">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1472,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>183.65</v>
+        <v>347</v>
       </c>
       <c r="C26" s="2">
-        <v>-1.59</v>
+        <v>15.36</v>
       </c>
       <c r="D26" s="2">
-        <v>-10.2</v>
+        <v>-9.1</v>
       </c>
       <c r="E26" s="2">
-        <v>6.56</v>
+        <v>1.39</v>
       </c>
       <c r="F26" s="2">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="G26" s="2">
-        <v>28</v>
+        <v>37.5</v>
       </c>
       <c r="H26" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I26" s="2">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1504,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>339.75</v>
+        <v>286.1</v>
       </c>
       <c r="C27" s="2">
-        <v>10.08</v>
+        <v>0.36</v>
       </c>
       <c r="D27" s="2">
-        <v>-8.220000000000001</v>
+        <v>2.31</v>
       </c>
       <c r="E27" s="2">
-        <v>-2.1</v>
+        <v>2.31</v>
       </c>
       <c r="F27" s="2">
-        <v>37.5</v>
+        <v>40.48</v>
       </c>
       <c r="G27" s="2">
-        <v>18</v>
+        <v>27.5</v>
       </c>
       <c r="H27" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I27" s="2">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1536,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>189.69</v>
+        <v>1334.8</v>
       </c>
       <c r="C28" s="2">
-        <v>1.47</v>
+        <v>-0.71</v>
       </c>
       <c r="D28" s="2">
-        <v>-7.91</v>
+        <v>1.59</v>
       </c>
       <c r="E28" s="2">
-        <v>-0.62</v>
+        <v>2.92</v>
       </c>
       <c r="F28" s="2">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="G28" s="2">
-        <v>10</v>
+        <v>22.5</v>
       </c>
       <c r="H28" s="2">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="I28" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1568,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>284.25</v>
+        <v>1693.5</v>
       </c>
       <c r="C29" s="2">
-        <v>-4.93</v>
+        <v>23.45</v>
       </c>
       <c r="D29" s="2">
-        <v>-3.76</v>
+        <v>-4.65</v>
       </c>
       <c r="E29" s="2">
-        <v>-0.4</v>
+        <v>-6.45</v>
       </c>
       <c r="F29" s="2">
-        <v>32.5</v>
+        <v>35.71</v>
       </c>
       <c r="G29" s="2">
-        <v>36</v>
+        <v>42.5</v>
       </c>
       <c r="H29" s="2">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="I29" s="2">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1600,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>2101.3</v>
+        <v>1175.1</v>
       </c>
       <c r="C30" s="2">
-        <v>1.81</v>
+        <v>-7.71</v>
       </c>
       <c r="D30" s="2">
-        <v>-3.36</v>
+        <v>-0.16</v>
       </c>
       <c r="E30" s="2">
-        <v>-4.57</v>
+        <v>6.58</v>
       </c>
       <c r="F30" s="2">
+        <v>33.33</v>
+      </c>
+      <c r="G30" s="2">
+        <v>50</v>
+      </c>
+      <c r="H30" s="2">
+        <v>14</v>
+      </c>
+      <c r="I30" s="2">
         <v>30</v>
-      </c>
-      <c r="G30" s="2">
-        <v>38</v>
-      </c>
-      <c r="H30" s="2">
-        <v>34</v>
-      </c>
-      <c r="I30" s="2">
-        <v>34</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1632,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>281</v>
+        <v>187.53</v>
       </c>
       <c r="C31" s="2">
-        <v>-0.89</v>
+        <v>-2.69</v>
       </c>
       <c r="D31" s="2">
-        <v>-5.03</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="E31" s="2">
-        <v>-2.52</v>
+        <v>6.3</v>
       </c>
       <c r="F31" s="2">
-        <v>27.5</v>
+        <v>30.95</v>
       </c>
       <c r="G31" s="2">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H31" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I31" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1664,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>1083.1</v>
+        <v>2096</v>
       </c>
       <c r="C32" s="2">
-        <v>3.72</v>
+        <v>2.52</v>
       </c>
       <c r="D32" s="2">
-        <v>-8.77</v>
+        <v>1.58</v>
       </c>
       <c r="E32" s="2">
-        <v>-3.11</v>
+        <v>-1.62</v>
       </c>
       <c r="F32" s="2">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="G32" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="I32" s="2">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1696,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>1307.8</v>
+        <v>1082.3</v>
       </c>
       <c r="C33" s="2">
-        <v>-6.94</v>
+        <v>4.75</v>
       </c>
       <c r="D33" s="2">
-        <v>-3.89</v>
+        <v>-5.34</v>
       </c>
       <c r="E33" s="2">
-        <v>-1.02</v>
+        <v>-1.48</v>
       </c>
       <c r="F33" s="2">
-        <v>22.5</v>
+        <v>26.19</v>
       </c>
       <c r="G33" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H33" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I33" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1728,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>1229.5</v>
+        <v>187.55</v>
       </c>
       <c r="C34" s="2">
-        <v>3.16</v>
+        <v>-1.4</v>
       </c>
       <c r="D34" s="2">
-        <v>-6.16</v>
+        <v>-9.1</v>
       </c>
       <c r="E34" s="2">
-        <v>-8.15</v>
+        <v>0.24</v>
       </c>
       <c r="F34" s="2">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="G34" s="2">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H34" s="2">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="I34" s="2">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1760,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>414.15</v>
+        <v>401</v>
       </c>
       <c r="C35" s="2">
-        <v>-5.07</v>
+        <v>-4.89</v>
       </c>
       <c r="D35" s="2">
-        <v>-8.369999999999999</v>
+        <v>-1.52</v>
       </c>
       <c r="E35" s="2">
-        <v>-2.93</v>
+        <v>-2.39</v>
       </c>
       <c r="F35" s="2">
-        <v>17.5</v>
+        <v>21.43</v>
       </c>
       <c r="G35" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H35" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I35" s="2">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1792,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>347.25</v>
+        <v>1238</v>
       </c>
       <c r="C36" s="2">
-        <v>-7.54</v>
+        <v>3.43</v>
       </c>
       <c r="D36" s="2">
-        <v>-10.97</v>
+        <v>-2.9</v>
       </c>
       <c r="E36" s="2">
-        <v>-2.53</v>
+        <v>-6.17</v>
       </c>
       <c r="F36" s="2">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="G36" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H36" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I36" s="2">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1824,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>748.15</v>
+        <v>342.5</v>
       </c>
       <c r="C37" s="2">
-        <v>-0.57</v>
+        <v>-4.77</v>
       </c>
       <c r="D37" s="2">
-        <v>-3.35</v>
+        <v>-9.56</v>
       </c>
       <c r="E37" s="2">
-        <v>-9.85</v>
+        <v>-2.63</v>
       </c>
       <c r="F37" s="2">
-        <v>12.5</v>
+        <v>16.67</v>
       </c>
       <c r="G37" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H37" s="2">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="I37" s="2">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1856,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>548.5</v>
+        <v>271.6</v>
       </c>
       <c r="C38" s="2">
-        <v>-8.710000000000001</v>
+        <v>-6.33</v>
       </c>
       <c r="D38" s="2">
-        <v>-11.22</v>
+        <v>-5.08</v>
       </c>
       <c r="E38" s="2">
-        <v>-2.78</v>
+        <v>-5.03</v>
       </c>
       <c r="F38" s="2">
-        <v>10</v>
+        <v>14.29</v>
       </c>
       <c r="G38" s="2">
-        <v>4</v>
+        <v>32.5</v>
       </c>
       <c r="H38" s="2">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="I38" s="2">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1888,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>242.53</v>
+        <v>415.25</v>
       </c>
       <c r="C39" s="2">
-        <v>-9.52</v>
+        <v>-6.35</v>
       </c>
       <c r="D39" s="2">
-        <v>-14.89</v>
+        <v>-10.96</v>
       </c>
       <c r="E39" s="2">
-        <v>-0.5600000000000001</v>
+        <v>-2.19</v>
       </c>
       <c r="F39" s="2">
-        <v>7.5</v>
+        <v>11.9</v>
       </c>
       <c r="G39" s="2">
-        <v>34</v>
+        <v>17.5</v>
       </c>
       <c r="H39" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I39" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1920,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>387.85</v>
+        <v>1172</v>
       </c>
       <c r="C40" s="2">
-        <v>-6.42</v>
+        <v>-3.11</v>
       </c>
       <c r="D40" s="2">
-        <v>-8.06</v>
+        <v>-8.6</v>
       </c>
       <c r="E40" s="2">
-        <v>-8.859999999999999</v>
+        <v>-5.06</v>
       </c>
       <c r="F40" s="2">
-        <v>5</v>
+        <v>9.52</v>
       </c>
       <c r="G40" s="2">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="H40" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I40" s="2">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1952,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>1148.1</v>
+        <v>731</v>
       </c>
       <c r="C41" s="2">
-        <v>-8.27</v>
+        <v>-1.04</v>
       </c>
       <c r="D41" s="2">
-        <v>-13.22</v>
+        <v>0.05</v>
       </c>
       <c r="E41" s="2">
-        <v>-15.54</v>
+        <v>-10.63</v>
       </c>
       <c r="F41" s="2">
-        <v>2.5</v>
+        <v>7.14</v>
       </c>
       <c r="G41" s="2">
-        <v>2</v>
+        <v>12.5</v>
       </c>
       <c r="H41" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I41" s="2">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2001,14 +1983,29 @@
       <c r="A42" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="B42" s="1">
+        <v>540</v>
+      </c>
+      <c r="C42" s="2">
+        <v>-4.27</v>
+      </c>
+      <c r="D42" s="2">
+        <v>-7.61</v>
+      </c>
+      <c r="E42" s="2">
+        <v>-5.82</v>
+      </c>
+      <c r="F42" s="2">
+        <v>4.76</v>
+      </c>
       <c r="G42" s="2">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H42" s="2">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="I42" s="2">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2018,14 +2015,29 @@
       <c r="A43" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="B43" s="1">
+        <v>238.85</v>
+      </c>
+      <c r="C43" s="2">
+        <v>-16.83</v>
+      </c>
+      <c r="D43" s="2">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="E43" s="2">
+        <v>-3.86</v>
+      </c>
+      <c r="F43" s="2">
+        <v>2.38</v>
+      </c>
       <c r="G43" s="2">
-        <v>32</v>
+        <v>7.5</v>
       </c>
       <c r="H43" s="2">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I43" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2036,13 +2048,13 @@
         <v>51</v>
       </c>
       <c r="G44" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H44" s="2">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="I44" s="2">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2053,13 +2065,13 @@
         <v>52</v>
       </c>
       <c r="G45" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H45" s="2">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="I45" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2069,14 +2081,11 @@
       <c r="A46" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G46" s="2">
-        <v>70</v>
-      </c>
       <c r="H46" s="2">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="I46" s="2">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2086,14 +2095,11 @@
       <c r="A47" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G47" s="2">
-        <v>66</v>
-      </c>
       <c r="H47" s="2">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="I47" s="2">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2104,13 +2110,13 @@
         <v>55</v>
       </c>
       <c r="G48" s="2">
-        <v>48</v>
+        <v>52.5</v>
       </c>
       <c r="H48" s="2">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="I48" s="2">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2120,14 +2126,11 @@
       <c r="A49" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G49" s="2">
-        <v>74</v>
-      </c>
       <c r="H49" s="2">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="I49" s="2">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2138,13 +2141,13 @@
         <v>57</v>
       </c>
       <c r="G50" s="2">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="H50" s="2">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="I50" s="2">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2154,14 +2157,11 @@
       <c r="A51" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G51" s="2">
+      <c r="H51" s="2">
         <v>58</v>
       </c>
-      <c r="H51" s="2">
+      <c r="I51" s="2">
         <v>36</v>
-      </c>
-      <c r="I51" s="2">
-        <v>58</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2270,7 +2270,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2312,57 +2312,57 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>1141.2</v>
+        <v>315</v>
       </c>
       <c r="C2" s="2">
-        <v>35.24</v>
+        <v>35.94</v>
       </c>
       <c r="D2" s="2">
-        <v>21.9</v>
+        <v>26.96</v>
       </c>
       <c r="E2" s="2">
-        <v>10.89</v>
+        <v>10.45</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H2" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I2" s="2">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>302.45</v>
+        <v>1078</v>
       </c>
       <c r="C3" s="2">
-        <v>27.11</v>
+        <v>31.18</v>
       </c>
       <c r="D3" s="2">
-        <v>22.12</v>
+        <v>22</v>
       </c>
       <c r="E3" s="2">
-        <v>6.72</v>
+        <v>5.42</v>
       </c>
       <c r="F3" s="2">
-        <v>95</v>
+        <v>97.62</v>
       </c>
       <c r="G3" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H3" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="I3" s="2">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2370,61 +2370,32 @@
         <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>4875.2</v>
+        <v>4941</v>
       </c>
       <c r="C4" s="2">
-        <v>25.43</v>
+        <v>20.99</v>
       </c>
       <c r="D4" s="2">
-        <v>17.6</v>
+        <v>23.17</v>
       </c>
       <c r="E4" s="2">
-        <v>9.07</v>
+        <v>7.38</v>
       </c>
       <c r="F4" s="2">
+        <v>92.86</v>
+      </c>
+      <c r="G4" s="2">
         <v>92.5</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>92</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>86</v>
       </c>
-      <c r="I4" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3009.5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>65.62</v>
-      </c>
-      <c r="D5" s="2">
-        <v>5.65</v>
-      </c>
-      <c r="E5" s="2">
-        <v>-6.15</v>
-      </c>
-      <c r="F5" s="2">
-        <v>90</v>
-      </c>
-      <c r="G5" s="2">
-        <v>100</v>
-      </c>
-      <c r="H5" s="2">
-        <v>100</v>
-      </c>
-      <c r="I5" s="2">
-        <v>100</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C5">
+  <conditionalFormatting sqref="C2:C4">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2432,7 +2403,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D5">
+  <conditionalFormatting sqref="D2:D4">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2440,7 +2411,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E5">
+  <conditionalFormatting sqref="E2:E4">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2448,22 +2419,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F5">
+  <conditionalFormatting sqref="F2:F4">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G5">
+  <conditionalFormatting sqref="G2:G4">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H5">
+  <conditionalFormatting sqref="H2:H4">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5">
+  <conditionalFormatting sqref="I2:I4">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2474,7 +2445,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2516,28 +2487,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>1141.2</v>
+        <v>315</v>
       </c>
       <c r="C2" s="2">
-        <v>35.24</v>
+        <v>35.94</v>
       </c>
       <c r="D2" s="2">
-        <v>21.9</v>
+        <v>26.96</v>
       </c>
       <c r="E2" s="2">
-        <v>10.89</v>
+        <v>10.45</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H2" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I2" s="2">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2545,177 +2516,119 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1651.3</v>
+        <v>1078</v>
       </c>
       <c r="C3" s="2">
-        <v>18.25</v>
+        <v>31.18</v>
       </c>
       <c r="D3" s="2">
-        <v>18.02</v>
+        <v>22</v>
       </c>
       <c r="E3" s="2">
-        <v>17.4</v>
+        <v>5.42</v>
       </c>
       <c r="F3" s="2">
-        <v>97.5</v>
+        <v>97.62</v>
       </c>
       <c r="G3" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H3" s="2">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I3" s="2">
-        <v>70</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>302.45</v>
+        <v>4941</v>
       </c>
       <c r="C4" s="2">
-        <v>27.11</v>
+        <v>20.99</v>
       </c>
       <c r="D4" s="2">
-        <v>22.12</v>
+        <v>23.17</v>
       </c>
       <c r="E4" s="2">
-        <v>6.72</v>
+        <v>7.38</v>
       </c>
       <c r="F4" s="2">
-        <v>95</v>
+        <v>92.86</v>
       </c>
       <c r="G4" s="2">
-        <v>94</v>
+        <v>92.5</v>
       </c>
       <c r="H4" s="2">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="I4" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>4875.2</v>
+        <v>3502</v>
       </c>
       <c r="C5" s="2">
-        <v>25.43</v>
+        <v>17.5</v>
       </c>
       <c r="D5" s="2">
-        <v>17.6</v>
+        <v>19.14</v>
       </c>
       <c r="E5" s="2">
-        <v>9.07</v>
+        <v>10.81</v>
       </c>
       <c r="F5" s="2">
-        <v>92.5</v>
+        <v>90.48</v>
       </c>
       <c r="G5" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H5" s="2">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="I5" s="2">
-        <v>82</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>3009.5</v>
+        <v>1540</v>
       </c>
       <c r="C6" s="2">
-        <v>65.62</v>
+        <v>29.89</v>
       </c>
       <c r="D6" s="2">
-        <v>5.65</v>
+        <v>11.18</v>
       </c>
       <c r="E6" s="2">
-        <v>-6.15</v>
+        <v>7.92</v>
       </c>
       <c r="F6" s="2">
-        <v>90</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>100</v>
+        <v>82.5</v>
       </c>
       <c r="H6" s="2">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="I6" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1">
-        <v>1346.9</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0.98</v>
-      </c>
-      <c r="D7" s="2">
-        <v>16.72</v>
-      </c>
-      <c r="E7" s="2">
-        <v>19.97</v>
-      </c>
-      <c r="F7" s="2">
-        <v>87.5</v>
-      </c>
-      <c r="G7" s="2">
-        <v>90</v>
-      </c>
-      <c r="H7" s="2">
-        <v>60</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="1">
-        <v>1509.6</v>
-      </c>
-      <c r="C8" s="2">
-        <v>28.2</v>
-      </c>
-      <c r="D8" s="2">
-        <v>7.3</v>
-      </c>
-      <c r="E8" s="2">
-        <v>2.93</v>
-      </c>
-      <c r="F8" s="2">
-        <v>82.5</v>
-      </c>
-      <c r="G8" s="2">
-        <v>82</v>
-      </c>
-      <c r="H8" s="2">
         <v>76</v>
       </c>
-      <c r="I8" s="2">
-        <v>80</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C8">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2723,7 +2636,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2731,7 +2644,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E8">
+  <conditionalFormatting sqref="E2:E6">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2739,22 +2652,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F8">
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H8">
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I8">
+  <conditionalFormatting sqref="I2:I6">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2790,13 +2703,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C2" s="2">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D2" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2804,13 +2717,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C3" s="2">
         <v>46</v>
       </c>
       <c r="D3" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2818,13 +2731,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2832,13 +2745,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D5" s="2">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-08-07</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-08-07</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-08-07</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-08-07</t>
+    <t>Price_2026-08-14</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-08-14</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-08-14</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-08-14</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-08-14</t>
   </si>
   <si>
     <t>RS_Score_2026-08-07</t>
@@ -43,156 +46,153 @@
     <t>RS_Score_2026-07-24</t>
   </si>
   <si>
-    <t>RS_Score_2026-07-17</t>
-  </si>
-  <si>
     <t>ETERNAL</t>
   </si>
   <si>
     <t>BAJAJ-AUTO</t>
   </si>
   <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
     <t>BAJFINANCE</t>
   </si>
   <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>TITAN</t>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>HCLTECH</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
   </si>
   <si>
     <t>ADANIENT</t>
   </si>
   <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
     <t>NESTLEIND</t>
   </si>
   <si>
-    <t>INDIGO</t>
+    <t>TECHM</t>
   </si>
   <si>
     <t>GRASIM</t>
   </si>
   <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>TECHM</t>
-  </si>
-  <si>
     <t>TRENT</t>
   </si>
   <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
     <t>ULTRACEMCO</t>
   </si>
   <si>
-    <t>HCLTECH</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
+    <t>KOTAKBANK</t>
   </si>
   <si>
     <t>SBIN</t>
   </si>
   <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>HINDALCO</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
     <t>JSWSTEEL</t>
   </si>
   <si>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
     <t>MAXHEALTH</t>
   </si>
   <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
     <t>TMPV</t>
   </si>
   <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>ADANIPORTS</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
+    <t>AXISBANK</t>
   </si>
   <si>
     <t>TATASTEEL</t>
   </si>
   <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
     <t>NTPC</t>
   </si>
   <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
     <t>POWERGRID</t>
   </si>
   <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
     <t>ONGC</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
     <t>2026-08-07</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-17</t>
   </si>
 </sst>
 </file>
@@ -722,28 +722,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>315</v>
+        <v>318.5</v>
       </c>
       <c r="C2" s="2">
-        <v>35.94</v>
+        <v>32.58</v>
       </c>
       <c r="D2" s="2">
-        <v>26.96</v>
+        <v>28.27</v>
       </c>
       <c r="E2" s="2">
-        <v>10.45</v>
+        <v>10.99</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H2" s="2">
         <v>94</v>
       </c>
       <c r="I2" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>60</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>11662</v>
+        <v>11700</v>
       </c>
       <c r="C3" s="2">
-        <v>35.02</v>
+        <v>20.9</v>
       </c>
       <c r="D3" s="2">
-        <v>12.39</v>
+        <v>14.36</v>
       </c>
       <c r="E3" s="2">
-        <v>12.34</v>
+        <v>11.19</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
+        <v>98</v>
+      </c>
+      <c r="H3" s="2">
         <v>96</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>98</v>
-      </c>
-      <c r="I3" s="2">
-        <v>72</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>1078</v>
+        <v>1122</v>
       </c>
       <c r="C4" s="2">
-        <v>31.18</v>
+        <v>9.81</v>
       </c>
       <c r="D4" s="2">
-        <v>22</v>
+        <v>25.84</v>
       </c>
       <c r="E4" s="2">
-        <v>5.42</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H4" s="2">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="I4" s="2">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1115</v>
+        <v>5056.2</v>
       </c>
       <c r="C5" s="2">
-        <v>25.76</v>
+        <v>12.6</v>
       </c>
       <c r="D5" s="2">
-        <v>22.01</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2">
-        <v>6.38</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="H5" s="2">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="I5" s="2">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>4941</v>
+        <v>2025</v>
       </c>
       <c r="C6" s="2">
-        <v>20.99</v>
+        <v>12.02</v>
       </c>
       <c r="D6" s="2">
-        <v>23.17</v>
+        <v>21.03</v>
       </c>
       <c r="E6" s="2">
-        <v>7.38</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="I6" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>3020</v>
+        <v>1087</v>
       </c>
       <c r="C7" s="2">
-        <v>64.72</v>
+        <v>18.29</v>
       </c>
       <c r="D7" s="2">
-        <v>3.85</v>
+        <v>25.55</v>
       </c>
       <c r="E7" s="2">
-        <v>-4.96</v>
+        <v>2.16</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H7" s="2">
         <v>100</v>
       </c>
       <c r="I7" s="2">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>3502</v>
+        <v>8100</v>
       </c>
       <c r="C8" s="2">
-        <v>17.5</v>
+        <v>10.25</v>
       </c>
       <c r="D8" s="2">
-        <v>19.14</v>
+        <v>16.1</v>
       </c>
       <c r="E8" s="2">
-        <v>10.81</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H8" s="2">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="I8" s="2">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>8020</v>
+        <v>1370</v>
       </c>
       <c r="C9" s="2">
-        <v>21.87</v>
+        <v>-2.81</v>
       </c>
       <c r="D9" s="2">
-        <v>14.13</v>
+        <v>20.21</v>
       </c>
       <c r="E9" s="2">
-        <v>11.07</v>
+        <v>12.18</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H9" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I9" s="2">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>1540</v>
+        <v>5310</v>
       </c>
       <c r="C10" s="2">
-        <v>29.89</v>
+        <v>16.6</v>
       </c>
       <c r="D10" s="2">
-        <v>11.18</v>
+        <v>21.8</v>
       </c>
       <c r="E10" s="2">
-        <v>7.92</v>
+        <v>1.55</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H10" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I10" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>5333</v>
+        <v>3428.2</v>
       </c>
       <c r="C11" s="2">
-        <v>27.17</v>
+        <v>6.27</v>
       </c>
       <c r="D11" s="2">
-        <v>19.75</v>
+        <v>16.8</v>
       </c>
       <c r="E11" s="2">
-        <v>1.98</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H11" s="2">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="I11" s="2">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>3323</v>
+        <v>3035.1</v>
       </c>
       <c r="C12" s="2">
-        <v>30</v>
+        <v>45.51</v>
       </c>
       <c r="D12" s="2">
-        <v>7.44</v>
+        <v>2.24</v>
       </c>
       <c r="E12" s="2">
-        <v>6.01</v>
+        <v>-4.66</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="H12" s="2">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="I12" s="2">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>2008.9</v>
+        <v>1506.9</v>
       </c>
       <c r="C13" s="2">
-        <v>22.55</v>
+        <v>21.2</v>
       </c>
       <c r="D13" s="2">
-        <v>14.31</v>
+        <v>8.24</v>
       </c>
       <c r="E13" s="2">
-        <v>5.28</v>
+        <v>4.19</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H13" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I13" s="2">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,25 +1106,25 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>1635</v>
+        <v>1632.8</v>
       </c>
       <c r="C14" s="2">
-        <v>16.37</v>
+        <v>16.32</v>
       </c>
       <c r="D14" s="2">
-        <v>8.699999999999999</v>
+        <v>11.43</v>
       </c>
       <c r="E14" s="2">
-        <v>8.67</v>
+        <v>3.58</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
+        <v>76</v>
+      </c>
+      <c r="H14" s="2">
         <v>98</v>
-      </c>
-      <c r="H14" s="2">
-        <v>96</v>
       </c>
       <c r="I14" s="2">
         <v>96</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>2997</v>
+        <v>3248.7</v>
       </c>
       <c r="C15" s="2">
-        <v>26.8</v>
+        <v>18.82</v>
       </c>
       <c r="D15" s="2">
-        <v>8.289999999999999</v>
+        <v>6.84</v>
       </c>
       <c r="E15" s="2">
-        <v>3.34</v>
+        <v>3.66</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="H15" s="2">
         <v>48</v>
       </c>
       <c r="I15" s="2">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>12105</v>
+        <v>2978</v>
       </c>
       <c r="C16" s="2">
-        <v>16.31</v>
+        <v>14.22</v>
       </c>
       <c r="D16" s="2">
-        <v>9.970000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="E16" s="2">
-        <v>6.75</v>
+        <v>1.78</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="H16" s="2">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I16" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>1356.6</v>
+        <v>1992.1</v>
       </c>
       <c r="C17" s="2">
-        <v>-0.39</v>
+        <v>7.87</v>
       </c>
       <c r="D17" s="2">
-        <v>14.67</v>
+        <v>11.24</v>
       </c>
       <c r="E17" s="2">
-        <v>12.22</v>
+        <v>3.97</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="H17" s="2">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="I17" s="2">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>2735</v>
+        <v>8920.5</v>
       </c>
       <c r="C18" s="2">
-        <v>27.19</v>
+        <v>18.9</v>
       </c>
       <c r="D18" s="2">
-        <v>4.8</v>
+        <v>6.85</v>
       </c>
       <c r="E18" s="2">
-        <v>3.13</v>
+        <v>0.29</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H18" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I18" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1421</v>
+        <v>1450</v>
       </c>
       <c r="C19" s="2">
-        <v>17.86</v>
+        <v>19.04</v>
       </c>
       <c r="D19" s="2">
-        <v>15.59</v>
+        <v>4.47</v>
       </c>
       <c r="E19" s="2">
-        <v>1.67</v>
+        <v>0.58</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H19" s="2">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="I19" s="2">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>1097.2</v>
+        <v>1930</v>
       </c>
       <c r="C20" s="2">
-        <v>9.68</v>
+        <v>16.93</v>
       </c>
       <c r="D20" s="2">
-        <v>15</v>
+        <v>8.18</v>
       </c>
       <c r="E20" s="2">
-        <v>5.81</v>
+        <v>-1.35</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H20" s="2">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="I20" s="2">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>8945</v>
+        <v>249.05</v>
       </c>
       <c r="C21" s="2">
-        <v>22.24</v>
+        <v>2.65</v>
       </c>
       <c r="D21" s="2">
-        <v>10.32</v>
+        <v>9.08</v>
       </c>
       <c r="E21" s="2">
-        <v>1.85</v>
+        <v>4.48</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="H21" s="2">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="I21" s="2">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>2452.7</v>
+        <v>4057</v>
       </c>
       <c r="C22" s="2">
-        <v>1.99</v>
+        <v>3.45</v>
       </c>
       <c r="D22" s="2">
-        <v>7.35</v>
+        <v>4.68</v>
       </c>
       <c r="E22" s="2">
-        <v>13.05</v>
+        <v>5.68</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="H22" s="2">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="I22" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>1463.8</v>
+        <v>1029.5</v>
       </c>
       <c r="C23" s="2">
-        <v>23.91</v>
+        <v>4.31</v>
       </c>
       <c r="D23" s="2">
-        <v>6.27</v>
+        <v>-2.59</v>
       </c>
       <c r="E23" s="2">
-        <v>2.6</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H23" s="2">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="I23" s="2">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>256.8</v>
+        <v>2696.3</v>
       </c>
       <c r="C24" s="2">
-        <v>11.91</v>
+        <v>15.21</v>
       </c>
       <c r="D24" s="2">
-        <v>9.300000000000001</v>
+        <v>2.27</v>
       </c>
       <c r="E24" s="2">
-        <v>6.38</v>
+        <v>0.18</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
+        <v>68</v>
+      </c>
+      <c r="H24" s="2">
+        <v>68</v>
+      </c>
+      <c r="I24" s="2">
         <v>70</v>
-      </c>
-      <c r="H24" s="2">
-        <v>42</v>
-      </c>
-      <c r="I24" s="2">
-        <v>50</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>1959.9</v>
+        <v>13834</v>
       </c>
       <c r="C25" s="2">
-        <v>10.89</v>
+        <v>1.93</v>
       </c>
       <c r="D25" s="2">
-        <v>9.609999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E25" s="2">
-        <v>4.35</v>
+        <v>3.4</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="H25" s="2">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I25" s="2">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>14037</v>
+        <v>2361</v>
       </c>
       <c r="C26" s="2">
-        <v>12.25</v>
+        <v>-4.68</v>
       </c>
       <c r="D26" s="2">
-        <v>9.52</v>
+        <v>10.34</v>
       </c>
       <c r="E26" s="2">
-        <v>3.53</v>
+        <v>4.88</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H26" s="2">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="I26" s="2">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>1059.6</v>
+        <v>1406.8</v>
       </c>
       <c r="C27" s="2">
-        <v>16.25</v>
+        <v>7.32</v>
       </c>
       <c r="D27" s="2">
-        <v>-6.67</v>
+        <v>13.47</v>
       </c>
       <c r="E27" s="2">
-        <v>9.59</v>
+        <v>-2.84</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="H27" s="2">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="I27" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>1945</v>
+        <v>11706</v>
       </c>
       <c r="C28" s="2">
-        <v>15.15</v>
+        <v>3.07</v>
       </c>
       <c r="D28" s="2">
-        <v>8.550000000000001</v>
+        <v>10.65</v>
       </c>
       <c r="E28" s="2">
-        <v>1.23</v>
+        <v>0.35</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H28" s="2">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="I28" s="2">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>1299.5</v>
+        <v>391.15</v>
       </c>
       <c r="C29" s="2">
-        <v>14.52</v>
+        <v>4.61</v>
       </c>
       <c r="D29" s="2">
-        <v>0.58</v>
+        <v>3.9</v>
       </c>
       <c r="E29" s="2">
-        <v>5.02</v>
+        <v>2.38</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H29" s="2">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="I29" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>1070</v>
+        <v>1067.7</v>
       </c>
       <c r="C30" s="2">
-        <v>13.48</v>
+        <v>1.9</v>
       </c>
       <c r="D30" s="2">
-        <v>14.22</v>
+        <v>8.73</v>
       </c>
       <c r="E30" s="2">
-        <v>-3.27</v>
+        <v>0.73</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="H30" s="2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="I30" s="2">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>4056</v>
+        <v>1270</v>
       </c>
       <c r="C31" s="2">
-        <v>13.35</v>
+        <v>5.14</v>
       </c>
       <c r="D31" s="2">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="E31" s="2">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H31" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I31" s="2">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>390.75</v>
+        <v>1169.2</v>
       </c>
       <c r="C32" s="2">
-        <v>9.34</v>
+        <v>-7.58</v>
       </c>
       <c r="D32" s="2">
-        <v>3.72</v>
+        <v>0.58</v>
       </c>
       <c r="E32" s="2">
-        <v>1.76</v>
+        <v>7.55</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H32" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I32" s="2">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>347</v>
+        <v>184</v>
       </c>
       <c r="C33" s="2">
-        <v>15.36</v>
+        <v>-9.17</v>
       </c>
       <c r="D33" s="2">
-        <v>-9.1</v>
+        <v>2.39</v>
       </c>
       <c r="E33" s="2">
-        <v>1.39</v>
+        <v>5.51</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H33" s="2">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I33" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>286.1</v>
+        <v>1310</v>
       </c>
       <c r="C34" s="2">
-        <v>0.36</v>
+        <v>-2.53</v>
       </c>
       <c r="D34" s="2">
-        <v>2.31</v>
+        <v>3.7</v>
       </c>
       <c r="E34" s="2">
-        <v>2.31</v>
+        <v>-0.99</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H34" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I34" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>1855.5</v>
+        <v>1079.5</v>
       </c>
       <c r="C35" s="2">
-        <v>4.59</v>
+        <v>-0.46</v>
       </c>
       <c r="D35" s="2">
-        <v>2.37</v>
+        <v>-2.48</v>
       </c>
       <c r="E35" s="2">
-        <v>-0.02</v>
+        <v>-1.14</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="H35" s="2">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="I35" s="2">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>1334.8</v>
+        <v>1700</v>
       </c>
       <c r="C36" s="2">
-        <v>-0.71</v>
+        <v>15.72</v>
       </c>
       <c r="D36" s="2">
-        <v>1.59</v>
+        <v>-5.42</v>
       </c>
       <c r="E36" s="2">
-        <v>2.92</v>
+        <v>-7.81</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I36" s="2">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>1693.5</v>
+        <v>410.8</v>
       </c>
       <c r="C37" s="2">
-        <v>23.45</v>
+        <v>-7.03</v>
       </c>
       <c r="D37" s="2">
-        <v>-4.65</v>
+        <v>-0.39</v>
       </c>
       <c r="E37" s="2">
-        <v>-6.45</v>
+        <v>0.79</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H37" s="2">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="I37" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>1175.1</v>
+        <v>1795</v>
       </c>
       <c r="C38" s="2">
-        <v>-7.71</v>
+        <v>-6.67</v>
       </c>
       <c r="D38" s="2">
-        <v>-0.16</v>
+        <v>1.73</v>
       </c>
       <c r="E38" s="2">
-        <v>6.58</v>
+        <v>-1.62</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H38" s="2">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="I38" s="2">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>187.53</v>
+        <v>2077</v>
       </c>
       <c r="C39" s="2">
-        <v>-2.69</v>
+        <v>-2.65</v>
       </c>
       <c r="D39" s="2">
-        <v>-8.109999999999999</v>
+        <v>-0.57</v>
       </c>
       <c r="E39" s="2">
-        <v>6.3</v>
+        <v>-2.93</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H39" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I39" s="2">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>2096</v>
+        <v>1206</v>
       </c>
       <c r="C40" s="2">
-        <v>2.52</v>
+        <v>-1.51</v>
       </c>
       <c r="D40" s="2">
-        <v>1.58</v>
+        <v>-4.86</v>
       </c>
       <c r="E40" s="2">
-        <v>-1.62</v>
+        <v>-1.4</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="H40" s="2">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="I40" s="2">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1970,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>1082.3</v>
+        <v>278.2</v>
       </c>
       <c r="C41" s="2">
-        <v>4.75</v>
+        <v>-6.07</v>
       </c>
       <c r="D41" s="2">
-        <v>-5.34</v>
+        <v>-0.45</v>
       </c>
       <c r="E41" s="2">
-        <v>-1.48</v>
+        <v>-1.59</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H41" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I41" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>187.55</v>
+        <v>1008.6</v>
       </c>
       <c r="C42" s="2">
-        <v>-1.4</v>
+        <v>5.98</v>
       </c>
       <c r="D42" s="2">
-        <v>-9.1</v>
+        <v>0.29</v>
       </c>
       <c r="E42" s="2">
-        <v>0.24</v>
+        <v>-8.51</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H42" s="2">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="I42" s="2">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>401</v>
+        <v>334.5</v>
       </c>
       <c r="C43" s="2">
-        <v>-4.89</v>
+        <v>-1.55</v>
       </c>
       <c r="D43" s="2">
-        <v>-1.52</v>
+        <v>-13.3</v>
       </c>
       <c r="E43" s="2">
-        <v>-2.39</v>
+        <v>-0.58</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="H43" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I43" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,16 +2066,16 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>1238</v>
+        <v>1217.4</v>
       </c>
       <c r="C44" s="2">
-        <v>3.43</v>
+        <v>-9.81</v>
       </c>
       <c r="D44" s="2">
-        <v>-2.9</v>
+        <v>-3.92</v>
       </c>
       <c r="E44" s="2">
-        <v>-6.17</v>
+        <v>-3.07</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
@@ -2087,7 +2087,7 @@
         <v>16</v>
       </c>
       <c r="I44" s="2">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2098,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>342.5</v>
+        <v>183.5</v>
       </c>
       <c r="C45" s="2">
-        <v>-4.77</v>
+        <v>-9.35</v>
       </c>
       <c r="D45" s="2">
-        <v>-9.56</v>
+        <v>-7.61</v>
       </c>
       <c r="E45" s="2">
-        <v>-2.63</v>
+        <v>-1.56</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="I45" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,28 +2130,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>271.6</v>
+        <v>340</v>
       </c>
       <c r="C46" s="2">
-        <v>-6.33</v>
+        <v>-10.56</v>
       </c>
       <c r="D46" s="2">
-        <v>-5.08</v>
+        <v>-6.18</v>
       </c>
       <c r="E46" s="2">
-        <v>-5.03</v>
+        <v>-2.09</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H46" s="2">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I46" s="2">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>415.25</v>
+        <v>727</v>
       </c>
       <c r="C47" s="2">
-        <v>-6.35</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="D47" s="2">
-        <v>-10.96</v>
+        <v>0.05</v>
       </c>
       <c r="E47" s="2">
-        <v>-2.19</v>
+        <v>-6.51</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H47" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I47" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,25 +2194,25 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>1172</v>
+        <v>407.1</v>
       </c>
       <c r="C48" s="2">
-        <v>-3.11</v>
+        <v>-4.97</v>
       </c>
       <c r="D48" s="2">
-        <v>-8.6</v>
+        <v>-11.26</v>
       </c>
       <c r="E48" s="2">
-        <v>-5.06</v>
+        <v>-3.93</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H48" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I48" s="2">
         <v>12</v>
@@ -2226,28 +2226,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>731</v>
+        <v>535.85</v>
       </c>
       <c r="C49" s="2">
-        <v>-1.04</v>
+        <v>-10.99</v>
       </c>
       <c r="D49" s="2">
-        <v>0.05</v>
+        <v>-4.75</v>
       </c>
       <c r="E49" s="2">
-        <v>-10.63</v>
+        <v>-5.1</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H49" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I49" s="2">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,28 +2258,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>540</v>
+        <v>266.6</v>
       </c>
       <c r="C50" s="2">
-        <v>-4.27</v>
+        <v>-11.94</v>
       </c>
       <c r="D50" s="2">
-        <v>-7.61</v>
+        <v>-8.16</v>
       </c>
       <c r="E50" s="2">
-        <v>-5.82</v>
+        <v>-7.66</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H50" s="2">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="I50" s="2">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2290,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>238.85</v>
+        <v>236.4</v>
       </c>
       <c r="C51" s="2">
-        <v>-16.83</v>
+        <v>-17.49</v>
       </c>
       <c r="D51" s="2">
-        <v>-9.630000000000001</v>
+        <v>-10.67</v>
       </c>
       <c r="E51" s="2">
-        <v>-3.86</v>
+        <v>-5.28</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
+        <v>2</v>
+      </c>
+      <c r="H51" s="2">
         <v>6</v>
       </c>
-      <c r="H51" s="2">
+      <c r="I51" s="2">
         <v>34</v>
-      </c>
-      <c r="I51" s="2">
-        <v>22</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2420,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2462,77 +2462,77 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>315</v>
+        <v>318.5</v>
       </c>
       <c r="C2" s="2">
-        <v>35.94</v>
+        <v>32.58</v>
       </c>
       <c r="D2" s="2">
-        <v>26.96</v>
+        <v>28.27</v>
       </c>
       <c r="E2" s="2">
-        <v>10.45</v>
+        <v>10.99</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H2" s="2">
         <v>94</v>
       </c>
       <c r="I2" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>1078</v>
+        <v>11700</v>
       </c>
       <c r="C3" s="2">
-        <v>31.18</v>
+        <v>20.9</v>
       </c>
       <c r="D3" s="2">
-        <v>22</v>
+        <v>14.36</v>
       </c>
       <c r="E3" s="2">
-        <v>5.42</v>
+        <v>11.19</v>
       </c>
       <c r="F3" s="2">
+        <v>98</v>
+      </c>
+      <c r="G3" s="2">
+        <v>98</v>
+      </c>
+      <c r="H3" s="2">
         <v>96</v>
       </c>
-      <c r="G3" s="2">
-        <v>100</v>
-      </c>
-      <c r="H3" s="2">
-        <v>88</v>
-      </c>
       <c r="I3" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>4941</v>
+        <v>5056.2</v>
       </c>
       <c r="C4" s="2">
-        <v>20.99</v>
+        <v>12.6</v>
       </c>
       <c r="D4" s="2">
-        <v>23.17</v>
+        <v>21</v>
       </c>
       <c r="E4" s="2">
-        <v>7.38</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F4" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G4" s="2">
         <v>92</v>
@@ -2541,7 +2541,7 @@
         <v>92</v>
       </c>
       <c r="I4" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2549,32 +2549,61 @@
         <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>3020</v>
+        <v>1087</v>
       </c>
       <c r="C5" s="2">
-        <v>64.72</v>
+        <v>18.29</v>
       </c>
       <c r="D5" s="2">
-        <v>3.85</v>
+        <v>25.55</v>
       </c>
       <c r="E5" s="2">
-        <v>-4.96</v>
+        <v>2.16</v>
       </c>
       <c r="F5" s="2">
         <v>90</v>
       </c>
       <c r="G5" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H5" s="2">
         <v>100</v>
       </c>
       <c r="I5" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3035.1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>45.51</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2.24</v>
+      </c>
+      <c r="E6" s="2">
+        <v>-4.66</v>
+      </c>
+      <c r="F6" s="2">
+        <v>80</v>
+      </c>
+      <c r="G6" s="2">
+        <v>90</v>
+      </c>
+      <c r="H6" s="2">
+        <v>90</v>
+      </c>
+      <c r="I6" s="2">
         <v>100</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C5">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2582,7 +2611,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D5">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2590,7 +2619,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E5">
+  <conditionalFormatting sqref="E2:E6">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2598,22 +2627,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F5">
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G5">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H5">
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5">
+  <conditionalFormatting sqref="I2:I6">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2624,7 +2653,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2666,28 +2695,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>315</v>
+        <v>318.5</v>
       </c>
       <c r="C2" s="2">
-        <v>35.94</v>
+        <v>32.58</v>
       </c>
       <c r="D2" s="2">
-        <v>26.96</v>
+        <v>28.27</v>
       </c>
       <c r="E2" s="2">
-        <v>10.45</v>
+        <v>10.99</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H2" s="2">
         <v>94</v>
       </c>
       <c r="I2" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2695,28 +2724,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>11662</v>
+        <v>11700</v>
       </c>
       <c r="C3" s="2">
-        <v>35.02</v>
+        <v>20.9</v>
       </c>
       <c r="D3" s="2">
-        <v>12.39</v>
+        <v>14.36</v>
       </c>
       <c r="E3" s="2">
-        <v>12.34</v>
+        <v>11.19</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
+        <v>98</v>
+      </c>
+      <c r="H3" s="2">
         <v>96</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>98</v>
-      </c>
-      <c r="I3" s="2">
-        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2724,48 +2753,48 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>1078</v>
+        <v>1122</v>
       </c>
       <c r="C4" s="2">
-        <v>31.18</v>
+        <v>9.81</v>
       </c>
       <c r="D4" s="2">
-        <v>22</v>
+        <v>25.84</v>
       </c>
       <c r="E4" s="2">
-        <v>5.42</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H4" s="2">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="I4" s="2">
-        <v>92</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>4941</v>
+        <v>5056.2</v>
       </c>
       <c r="C5" s="2">
-        <v>20.99</v>
+        <v>12.6</v>
       </c>
       <c r="D5" s="2">
-        <v>23.17</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2">
-        <v>7.38</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F5" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G5" s="2">
         <v>92</v>
@@ -2774,7 +2803,7 @@
         <v>92</v>
       </c>
       <c r="I5" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2782,28 +2811,28 @@
         <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>3020</v>
+        <v>1087</v>
       </c>
       <c r="C6" s="2">
-        <v>64.72</v>
+        <v>18.29</v>
       </c>
       <c r="D6" s="2">
-        <v>3.85</v>
+        <v>25.55</v>
       </c>
       <c r="E6" s="2">
-        <v>-4.96</v>
+        <v>2.16</v>
       </c>
       <c r="F6" s="2">
         <v>90</v>
       </c>
       <c r="G6" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H6" s="2">
         <v>100</v>
       </c>
       <c r="I6" s="2">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2811,28 +2840,28 @@
         <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>3502</v>
+        <v>8100</v>
       </c>
       <c r="C7" s="2">
-        <v>17.5</v>
+        <v>10.25</v>
       </c>
       <c r="D7" s="2">
-        <v>19.14</v>
+        <v>16.1</v>
       </c>
       <c r="E7" s="2">
-        <v>10.81</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F7" s="2">
         <v>88</v>
       </c>
       <c r="G7" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H7" s="2">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="I7" s="2">
-        <v>56</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2840,32 +2869,90 @@
         <v>17</v>
       </c>
       <c r="B8" s="1">
-        <v>1540</v>
+        <v>5310</v>
       </c>
       <c r="C8" s="2">
-        <v>29.89</v>
+        <v>16.6</v>
       </c>
       <c r="D8" s="2">
-        <v>11.18</v>
+        <v>21.8</v>
       </c>
       <c r="E8" s="2">
-        <v>7.92</v>
+        <v>1.55</v>
       </c>
       <c r="F8" s="2">
         <v>84</v>
       </c>
       <c r="G8" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H8" s="2">
+        <v>74</v>
+      </c>
+      <c r="I8" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1">
+        <v>3428.2</v>
+      </c>
+      <c r="C9" s="2">
+        <v>6.27</v>
+      </c>
+      <c r="D9" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="E9" s="2">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F9" s="2">
         <v>82</v>
       </c>
-      <c r="I8" s="2">
-        <v>76</v>
+      <c r="G9" s="2">
+        <v>88</v>
+      </c>
+      <c r="H9" s="2">
+        <v>82</v>
+      </c>
+      <c r="I9" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1">
+        <v>3035.1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>45.51</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2.24</v>
+      </c>
+      <c r="E10" s="2">
+        <v>-4.66</v>
+      </c>
+      <c r="F10" s="2">
+        <v>80</v>
+      </c>
+      <c r="G10" s="2">
+        <v>90</v>
+      </c>
+      <c r="H10" s="2">
+        <v>90</v>
+      </c>
+      <c r="I10" s="2">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C8">
+  <conditionalFormatting sqref="C2:C10">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2873,7 +2960,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8">
+  <conditionalFormatting sqref="D2:D10">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2881,7 +2968,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E8">
+  <conditionalFormatting sqref="E2:E10">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2889,22 +2976,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F8">
+  <conditionalFormatting sqref="F2:F10">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="G2:G10">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H8">
+  <conditionalFormatting sqref="H2:H10">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I8">
+  <conditionalFormatting sqref="I2:I10">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2940,13 +3027,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C2" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D2" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2954,13 +3041,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" s="2">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D3" s="2">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2968,13 +3055,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="C4" s="2">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D4" s="2">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2982,10 +3069,10 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C5" s="2">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D5" s="2">
         <v>48</v>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-08-14</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-08-14</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-08-14</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-08-14</t>
+    <t>Price_2026-08-21</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-08-21</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-08-21</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-08-21</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-08-21</t>
   </si>
   <si>
     <t>RS_Score_2026-08-14</t>
@@ -43,97 +46,103 @@
     <t>RS_Score_2026-07-31</t>
   </si>
   <si>
-    <t>RS_Score_2026-07-24</t>
-  </si>
-  <si>
     <t>ETERNAL</t>
   </si>
   <si>
     <t>BAJAJ-AUTO</t>
   </si>
   <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
     <t>SHRIRAMFIN</t>
   </si>
   <si>
-    <t>TITAN</t>
-  </si>
-  <si>
     <t>BAJAJFINSV</t>
   </si>
   <si>
-    <t>BAJFINANCE</t>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>ADANIENT</t>
   </si>
   <si>
     <t>EICHERMOT</t>
   </si>
   <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
     <t>HCLTECH</t>
   </si>
   <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
-    <t>ADANIENT</t>
-  </si>
-  <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>SBIN</t>
   </si>
   <si>
     <t>TRENT</t>
   </si>
   <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>HINDALCO</t>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>TCS</t>
   </si>
   <si>
     <t>ASIANPAINT</t>
   </si>
   <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>ADANIPORTS</t>
   </si>
   <si>
     <t>INFY</t>
@@ -142,60 +151,51 @@
     <t>WIPRO</t>
   </si>
   <si>
-    <t>RELIANCE</t>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
   </si>
   <si>
     <t>TATACONSUM</t>
   </si>
   <si>
-    <t>ADANIPORTS</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>MAXHEALTH</t>
   </si>
   <si>
     <t>HINDUNILVR</t>
   </si>
   <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
     <t>ITC</t>
   </si>
   <si>
-    <t>MAXHEALTH</t>
+    <t>POWERGRID</t>
   </si>
   <si>
     <t>TMPV</t>
   </si>
   <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>ONGC</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
     <t>2026-08-14</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>318.5</v>
+        <v>328</v>
       </c>
       <c r="C2" s="2">
-        <v>32.58</v>
+        <v>28.69</v>
       </c>
       <c r="D2" s="2">
-        <v>28.27</v>
+        <v>30.16</v>
       </c>
       <c r="E2" s="2">
-        <v>10.99</v>
+        <v>10.87</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -740,7 +740,7 @@
         <v>100</v>
       </c>
       <c r="H2" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2">
         <v>94</v>
@@ -757,13 +757,13 @@
         <v>11700</v>
       </c>
       <c r="C3" s="2">
-        <v>20.9</v>
+        <v>21.03</v>
       </c>
       <c r="D3" s="2">
-        <v>14.36</v>
+        <v>17.67</v>
       </c>
       <c r="E3" s="2">
-        <v>11.19</v>
+        <v>4.62</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
@@ -772,7 +772,7 @@
         <v>98</v>
       </c>
       <c r="H3" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I3" s="2">
         <v>98</v>
@@ -786,16 +786,16 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>1122</v>
+        <v>5086.1</v>
       </c>
       <c r="C4" s="2">
-        <v>9.81</v>
+        <v>13.07</v>
       </c>
       <c r="D4" s="2">
-        <v>25.84</v>
+        <v>19.13</v>
       </c>
       <c r="E4" s="2">
-        <v>8.359999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
@@ -804,10 +804,10 @@
         <v>94</v>
       </c>
       <c r="H4" s="2">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="I4" s="2">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,16 +818,16 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>5056.2</v>
+        <v>1095</v>
       </c>
       <c r="C5" s="2">
-        <v>12.6</v>
+        <v>20.05</v>
       </c>
       <c r="D5" s="2">
-        <v>21</v>
+        <v>16.92</v>
       </c>
       <c r="E5" s="2">
-        <v>8.890000000000001</v>
+        <v>4.45</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
@@ -836,10 +836,10 @@
         <v>92</v>
       </c>
       <c r="H5" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I5" s="2">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>2025</v>
+        <v>1130</v>
       </c>
       <c r="C6" s="2">
-        <v>12.02</v>
+        <v>8.73</v>
       </c>
       <c r="D6" s="2">
-        <v>21.03</v>
+        <v>13.57</v>
       </c>
       <c r="E6" s="2">
-        <v>8.779999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="H6" s="2">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="I6" s="2">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>1087</v>
+        <v>2032.5</v>
       </c>
       <c r="C7" s="2">
-        <v>18.29</v>
+        <v>11.12</v>
       </c>
       <c r="D7" s="2">
-        <v>25.55</v>
+        <v>16.23</v>
       </c>
       <c r="E7" s="2">
-        <v>2.16</v>
+        <v>6.25</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H7" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="I7" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>8100</v>
+        <v>3308</v>
       </c>
       <c r="C8" s="2">
-        <v>10.25</v>
+        <v>20.22</v>
       </c>
       <c r="D8" s="2">
-        <v>16.1</v>
+        <v>4.86</v>
       </c>
       <c r="E8" s="2">
-        <v>8.210000000000001</v>
+        <v>6.62</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="H8" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I8" s="2">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,25 +946,25 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>1370</v>
+        <v>2994.9</v>
       </c>
       <c r="C9" s="2">
-        <v>-2.81</v>
+        <v>34.38</v>
       </c>
       <c r="D9" s="2">
-        <v>20.21</v>
+        <v>1.78</v>
       </c>
       <c r="E9" s="2">
-        <v>12.18</v>
+        <v>-1.37</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H9" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2">
         <v>90</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>5310</v>
+        <v>8042</v>
       </c>
       <c r="C10" s="2">
-        <v>16.6</v>
+        <v>12.19</v>
       </c>
       <c r="D10" s="2">
-        <v>21.8</v>
+        <v>6.58</v>
       </c>
       <c r="E10" s="2">
-        <v>1.55</v>
+        <v>4.59</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H10" s="2">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="I10" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>3428.2</v>
+        <v>3412.2</v>
       </c>
       <c r="C11" s="2">
-        <v>6.27</v>
+        <v>7.03</v>
       </c>
       <c r="D11" s="2">
-        <v>16.8</v>
+        <v>10.01</v>
       </c>
       <c r="E11" s="2">
-        <v>8.300000000000001</v>
+        <v>5.36</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
+        <v>84</v>
+      </c>
+      <c r="H11" s="2">
         <v>88</v>
       </c>
-      <c r="H11" s="2">
+      <c r="I11" s="2">
         <v>82</v>
-      </c>
-      <c r="I11" s="2">
-        <v>60</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>3035.1</v>
+        <v>1477.1</v>
       </c>
       <c r="C12" s="2">
-        <v>45.51</v>
+        <v>15.38</v>
       </c>
       <c r="D12" s="2">
-        <v>2.24</v>
+        <v>7.97</v>
       </c>
       <c r="E12" s="2">
-        <v>-4.66</v>
+        <v>2.14</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H12" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I12" s="2">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>1506.9</v>
+        <v>1432.2</v>
       </c>
       <c r="C13" s="2">
-        <v>21.2</v>
+        <v>17.58</v>
       </c>
       <c r="D13" s="2">
-        <v>8.24</v>
+        <v>3.68</v>
       </c>
       <c r="E13" s="2">
-        <v>4.19</v>
+        <v>1.62</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="H13" s="2">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="I13" s="2">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,16 +1106,16 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>1632.8</v>
+        <v>1584</v>
       </c>
       <c r="C14" s="2">
-        <v>16.32</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="D14" s="2">
-        <v>11.43</v>
+        <v>14</v>
       </c>
       <c r="E14" s="2">
-        <v>3.58</v>
+        <v>0.57</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
@@ -1124,7 +1124,7 @@
         <v>76</v>
       </c>
       <c r="H14" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="I14" s="2">
         <v>96</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>3248.7</v>
+        <v>1029.85</v>
       </c>
       <c r="C15" s="2">
-        <v>18.82</v>
+        <v>1.97</v>
       </c>
       <c r="D15" s="2">
-        <v>6.84</v>
+        <v>2.1</v>
       </c>
       <c r="E15" s="2">
-        <v>3.66</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="H15" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I15" s="2">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>2978</v>
+        <v>1946</v>
       </c>
       <c r="C16" s="2">
-        <v>14.22</v>
+        <v>6.74</v>
       </c>
       <c r="D16" s="2">
-        <v>9.48</v>
+        <v>7.02</v>
       </c>
       <c r="E16" s="2">
-        <v>1.78</v>
+        <v>2.14</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H16" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I16" s="2">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>1992.1</v>
+        <v>402.8</v>
       </c>
       <c r="C17" s="2">
-        <v>7.87</v>
+        <v>6.41</v>
       </c>
       <c r="D17" s="2">
-        <v>11.24</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E17" s="2">
-        <v>3.97</v>
+        <v>4.72</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H17" s="2">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="I17" s="2">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>8920.5</v>
+        <v>4093</v>
       </c>
       <c r="C18" s="2">
-        <v>18.9</v>
+        <v>2.02</v>
       </c>
       <c r="D18" s="2">
-        <v>6.85</v>
+        <v>-1.84</v>
       </c>
       <c r="E18" s="2">
-        <v>0.29</v>
+        <v>7.54</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H18" s="2">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="I18" s="2">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1450</v>
+        <v>5165</v>
       </c>
       <c r="C19" s="2">
-        <v>19.04</v>
+        <v>10.41</v>
       </c>
       <c r="D19" s="2">
-        <v>4.47</v>
+        <v>5.83</v>
       </c>
       <c r="E19" s="2">
-        <v>0.58</v>
+        <v>-1.24</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="H19" s="2">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="I19" s="2">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>1930</v>
+        <v>8693</v>
       </c>
       <c r="C20" s="2">
-        <v>16.93</v>
+        <v>13.66</v>
       </c>
       <c r="D20" s="2">
-        <v>8.18</v>
+        <v>2.77</v>
       </c>
       <c r="E20" s="2">
-        <v>-1.35</v>
+        <v>-1.59</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="H20" s="2">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="I20" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>249.05</v>
+        <v>1904</v>
       </c>
       <c r="C21" s="2">
-        <v>2.65</v>
+        <v>14.41</v>
       </c>
       <c r="D21" s="2">
-        <v>9.08</v>
+        <v>5.7</v>
       </c>
       <c r="E21" s="2">
-        <v>4.48</v>
+        <v>-3.53</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="H21" s="2">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="I21" s="2">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>4057</v>
+        <v>1302.5</v>
       </c>
       <c r="C22" s="2">
-        <v>3.45</v>
+        <v>-6.11</v>
       </c>
       <c r="D22" s="2">
-        <v>4.68</v>
+        <v>17.56</v>
       </c>
       <c r="E22" s="2">
-        <v>5.68</v>
+        <v>0.51</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="H22" s="2">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="I22" s="2">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>1029.5</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2">
-        <v>4.31</v>
+        <v>3.13</v>
       </c>
       <c r="D23" s="2">
-        <v>-2.59</v>
+        <v>2.11</v>
       </c>
       <c r="E23" s="2">
-        <v>8.619999999999999</v>
+        <v>3.56</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H23" s="2">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="I23" s="2">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>2696.3</v>
+        <v>1420</v>
       </c>
       <c r="C24" s="2">
-        <v>15.21</v>
+        <v>5.59</v>
       </c>
       <c r="D24" s="2">
-        <v>2.27</v>
+        <v>7.86</v>
       </c>
       <c r="E24" s="2">
-        <v>0.18</v>
+        <v>-0.95</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="H24" s="2">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I24" s="2">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>13834</v>
+        <v>1293.7</v>
       </c>
       <c r="C25" s="2">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="D25" s="2">
-        <v>8.220000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="E25" s="2">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="H25" s="2">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I25" s="2">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>2361</v>
+        <v>1048.7</v>
       </c>
       <c r="C26" s="2">
-        <v>-4.68</v>
+        <v>-3.63</v>
       </c>
       <c r="D26" s="2">
-        <v>10.34</v>
+        <v>2.73</v>
       </c>
       <c r="E26" s="2">
-        <v>4.88</v>
+        <v>2.75</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="I26" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>1406.8</v>
+        <v>2924</v>
       </c>
       <c r="C27" s="2">
-        <v>7.32</v>
+        <v>3.53</v>
       </c>
       <c r="D27" s="2">
-        <v>13.47</v>
+        <v>0.79</v>
       </c>
       <c r="E27" s="2">
-        <v>-2.84</v>
+        <v>-0.49</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H27" s="2">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="I27" s="2">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>11706</v>
+        <v>1316</v>
       </c>
       <c r="C28" s="2">
-        <v>3.07</v>
+        <v>-3.02</v>
       </c>
       <c r="D28" s="2">
-        <v>10.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E28" s="2">
-        <v>0.35</v>
+        <v>2.81</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="H28" s="2">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="I28" s="2">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>391.15</v>
+        <v>11570</v>
       </c>
       <c r="C29" s="2">
-        <v>4.61</v>
+        <v>-0.93</v>
       </c>
       <c r="D29" s="2">
-        <v>3.9</v>
+        <v>2.97</v>
       </c>
       <c r="E29" s="2">
-        <v>2.38</v>
+        <v>-0.63</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H29" s="2">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="I29" s="2">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>1067.7</v>
+        <v>13565</v>
       </c>
       <c r="C30" s="2">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="D30" s="2">
-        <v>8.73</v>
+        <v>-0.75</v>
       </c>
       <c r="E30" s="2">
-        <v>0.73</v>
+        <v>-0.21</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H30" s="2">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I30" s="2">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>1270</v>
+        <v>2302</v>
       </c>
       <c r="C31" s="2">
-        <v>5.14</v>
+        <v>-9.06</v>
       </c>
       <c r="D31" s="2">
-        <v>1.32</v>
+        <v>7.06</v>
       </c>
       <c r="E31" s="2">
-        <v>1.03</v>
+        <v>0.28</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H31" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I31" s="2">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>1169.2</v>
+        <v>2640</v>
       </c>
       <c r="C32" s="2">
-        <v>-7.58</v>
+        <v>5.81</v>
       </c>
       <c r="D32" s="2">
-        <v>0.58</v>
+        <v>-2.79</v>
       </c>
       <c r="E32" s="2">
-        <v>7.55</v>
+        <v>-2.59</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="H32" s="2">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="I32" s="2">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>184</v>
+        <v>414</v>
       </c>
       <c r="C33" s="2">
-        <v>-9.17</v>
+        <v>-9.4</v>
       </c>
       <c r="D33" s="2">
-        <v>2.39</v>
+        <v>1.22</v>
       </c>
       <c r="E33" s="2">
-        <v>5.51</v>
+        <v>1.82</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H33" s="2">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I33" s="2">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,16 +1746,16 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>1310</v>
+        <v>1700</v>
       </c>
       <c r="C34" s="2">
-        <v>-2.53</v>
+        <v>8.16</v>
       </c>
       <c r="D34" s="2">
-        <v>3.7</v>
+        <v>-5.81</v>
       </c>
       <c r="E34" s="2">
-        <v>-0.99</v>
+        <v>-3.98</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
@@ -1764,10 +1764,10 @@
         <v>32</v>
       </c>
       <c r="H34" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="I34" s="2">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>1079.5</v>
+        <v>1121</v>
       </c>
       <c r="C35" s="2">
-        <v>-0.46</v>
+        <v>-12.75</v>
       </c>
       <c r="D35" s="2">
-        <v>-2.48</v>
+        <v>-1.22</v>
       </c>
       <c r="E35" s="2">
-        <v>-1.14</v>
+        <v>3.87</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H35" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I35" s="2">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>1700</v>
+        <v>180.79</v>
       </c>
       <c r="C36" s="2">
-        <v>15.72</v>
+        <v>-9.69</v>
       </c>
       <c r="D36" s="2">
-        <v>-5.42</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E36" s="2">
-        <v>-7.81</v>
+        <v>1.27</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H36" s="2">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I36" s="2">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>410.8</v>
+        <v>1174.7</v>
       </c>
       <c r="C37" s="2">
-        <v>-7.03</v>
+        <v>-4.09</v>
       </c>
       <c r="D37" s="2">
-        <v>-0.39</v>
+        <v>-7.61</v>
       </c>
       <c r="E37" s="2">
-        <v>0.79</v>
+        <v>2.08</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H37" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I37" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>1795</v>
+        <v>554.8</v>
       </c>
       <c r="C38" s="2">
-        <v>-6.67</v>
+        <v>-8.69</v>
       </c>
       <c r="D38" s="2">
-        <v>1.73</v>
+        <v>-4.2</v>
       </c>
       <c r="E38" s="2">
-        <v>-1.62</v>
+        <v>0.35</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H38" s="2">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="I38" s="2">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>2077</v>
+        <v>1245.8</v>
       </c>
       <c r="C39" s="2">
-        <v>-2.65</v>
+        <v>-7.97</v>
       </c>
       <c r="D39" s="2">
-        <v>-0.57</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="E39" s="2">
-        <v>-2.93</v>
+        <v>1.49</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H39" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I39" s="2">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>1206</v>
+        <v>726.95</v>
       </c>
       <c r="C40" s="2">
-        <v>-1.51</v>
+        <v>-7.1</v>
       </c>
       <c r="D40" s="2">
-        <v>-4.86</v>
+        <v>-4.94</v>
       </c>
       <c r="E40" s="2">
-        <v>-1.4</v>
+        <v>-1.7</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H40" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I40" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1970,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>278.2</v>
+        <v>1792.9</v>
       </c>
       <c r="C41" s="2">
-        <v>-6.07</v>
+        <v>-9.56</v>
       </c>
       <c r="D41" s="2">
-        <v>-0.45</v>
+        <v>1.9</v>
       </c>
       <c r="E41" s="2">
-        <v>-1.59</v>
+        <v>-3.96</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H41" s="2">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I41" s="2">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>1008.6</v>
+        <v>183</v>
       </c>
       <c r="C42" s="2">
-        <v>5.98</v>
+        <v>-11.78</v>
       </c>
       <c r="D42" s="2">
-        <v>0.29</v>
+        <v>-7.24</v>
       </c>
       <c r="E42" s="2">
-        <v>-8.51</v>
+        <v>-0.68</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="H42" s="2">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="I42" s="2">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>334.5</v>
+        <v>1049</v>
       </c>
       <c r="C43" s="2">
-        <v>-1.55</v>
+        <v>-5.58</v>
       </c>
       <c r="D43" s="2">
-        <v>-13.3</v>
+        <v>-4.67</v>
       </c>
       <c r="E43" s="2">
-        <v>-0.58</v>
+        <v>-5.27</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H43" s="2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I43" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>1217.4</v>
+        <v>236.4</v>
       </c>
       <c r="C44" s="2">
-        <v>-9.81</v>
+        <v>-16.57</v>
       </c>
       <c r="D44" s="2">
-        <v>-3.92</v>
+        <v>-2.98</v>
       </c>
       <c r="E44" s="2">
-        <v>-3.07</v>
+        <v>-0.91</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H44" s="2">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I44" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2098,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>183.5</v>
+        <v>405.2</v>
       </c>
       <c r="C45" s="2">
-        <v>-9.35</v>
+        <v>-7.05</v>
       </c>
       <c r="D45" s="2">
-        <v>-7.61</v>
+        <v>-7.53</v>
       </c>
       <c r="E45" s="2">
-        <v>-1.56</v>
+        <v>-3.95</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H45" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="I45" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2133,25 +2133,25 @@
         <v>340</v>
       </c>
       <c r="C46" s="2">
-        <v>-10.56</v>
+        <v>-14.57</v>
       </c>
       <c r="D46" s="2">
-        <v>-6.18</v>
+        <v>-2.33</v>
       </c>
       <c r="E46" s="2">
-        <v>-2.09</v>
+        <v>-3.08</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
+        <v>12</v>
+      </c>
+      <c r="H46" s="2">
         <v>14</v>
       </c>
-      <c r="H46" s="2">
+      <c r="I46" s="2">
         <v>12</v>
-      </c>
-      <c r="I46" s="2">
-        <v>8</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>727</v>
+        <v>1000</v>
       </c>
       <c r="C47" s="2">
-        <v>-8.800000000000001</v>
+        <v>-0.95</v>
       </c>
       <c r="D47" s="2">
-        <v>0.05</v>
+        <v>-2.64</v>
       </c>
       <c r="E47" s="2">
-        <v>-6.51</v>
+        <v>-10.28</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H47" s="2">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="I47" s="2">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,28 +2194,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>407.1</v>
+        <v>2028</v>
       </c>
       <c r="C48" s="2">
-        <v>-4.97</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="D48" s="2">
-        <v>-11.26</v>
+        <v>-4.98</v>
       </c>
       <c r="E48" s="2">
-        <v>-3.93</v>
+        <v>-6.74</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H48" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I48" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,28 +2226,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>535.85</v>
+        <v>269.4</v>
       </c>
       <c r="C49" s="2">
-        <v>-10.99</v>
+        <v>-9.27</v>
       </c>
       <c r="D49" s="2">
-        <v>-4.75</v>
+        <v>-6.43</v>
       </c>
       <c r="E49" s="2">
-        <v>-5.1</v>
+        <v>-5.75</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H49" s="2">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="I49" s="2">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,28 +2258,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>266.6</v>
+        <v>272.4</v>
       </c>
       <c r="C50" s="2">
-        <v>-11.94</v>
+        <v>-14.8</v>
       </c>
       <c r="D50" s="2">
-        <v>-8.16</v>
+        <v>-4.66</v>
       </c>
       <c r="E50" s="2">
-        <v>-7.66</v>
+        <v>-5.7</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
+        <v>4</v>
+      </c>
+      <c r="H50" s="2">
         <v>12</v>
       </c>
-      <c r="H50" s="2">
+      <c r="I50" s="2">
         <v>26</v>
-      </c>
-      <c r="I50" s="2">
-        <v>36</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2290,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>236.4</v>
+        <v>317.9</v>
       </c>
       <c r="C51" s="2">
-        <v>-17.49</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="D51" s="2">
-        <v>-10.67</v>
+        <v>-19.14</v>
       </c>
       <c r="E51" s="2">
-        <v>-5.28</v>
+        <v>-2.98</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H51" s="2">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="I51" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2420,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>318.5</v>
+        <v>328</v>
       </c>
       <c r="C2" s="2">
-        <v>32.58</v>
+        <v>28.69</v>
       </c>
       <c r="D2" s="2">
-        <v>28.27</v>
+        <v>30.16</v>
       </c>
       <c r="E2" s="2">
-        <v>10.99</v>
+        <v>10.87</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2480,7 +2480,7 @@
         <v>100</v>
       </c>
       <c r="H2" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2">
         <v>94</v>
@@ -2494,13 +2494,13 @@
         <v>11700</v>
       </c>
       <c r="C3" s="2">
-        <v>20.9</v>
+        <v>21.03</v>
       </c>
       <c r="D3" s="2">
-        <v>14.36</v>
+        <v>17.67</v>
       </c>
       <c r="E3" s="2">
-        <v>11.19</v>
+        <v>4.62</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
@@ -2509,7 +2509,7 @@
         <v>98</v>
       </c>
       <c r="H3" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I3" s="2">
         <v>98</v>
@@ -2517,25 +2517,25 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>5056.2</v>
+        <v>5086.1</v>
       </c>
       <c r="C4" s="2">
-        <v>12.6</v>
+        <v>13.07</v>
       </c>
       <c r="D4" s="2">
-        <v>21</v>
+        <v>19.13</v>
       </c>
       <c r="E4" s="2">
-        <v>8.890000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="F4" s="2">
+        <v>96</v>
+      </c>
+      <c r="G4" s="2">
         <v>94</v>
-      </c>
-      <c r="G4" s="2">
-        <v>92</v>
       </c>
       <c r="H4" s="2">
         <v>92</v>
@@ -2546,64 +2546,93 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="C5" s="2">
-        <v>18.29</v>
+        <v>20.05</v>
       </c>
       <c r="D5" s="2">
-        <v>25.55</v>
+        <v>16.92</v>
       </c>
       <c r="E5" s="2">
-        <v>2.16</v>
+        <v>4.45</v>
       </c>
       <c r="F5" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G5" s="2">
+        <v>92</v>
+      </c>
+      <c r="H5" s="2">
         <v>96</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>100</v>
-      </c>
-      <c r="I5" s="2">
-        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1">
-        <v>3035.1</v>
+        <v>2994.9</v>
       </c>
       <c r="C6" s="2">
-        <v>45.51</v>
+        <v>34.38</v>
       </c>
       <c r="D6" s="2">
-        <v>2.24</v>
+        <v>1.78</v>
       </c>
       <c r="E6" s="2">
-        <v>-4.66</v>
+        <v>-1.37</v>
       </c>
       <c r="F6" s="2">
+        <v>86</v>
+      </c>
+      <c r="G6" s="2">
         <v>80</v>
-      </c>
-      <c r="G6" s="2">
-        <v>90</v>
       </c>
       <c r="H6" s="2">
         <v>90</v>
       </c>
       <c r="I6" s="2">
-        <v>100</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3412.2</v>
+      </c>
+      <c r="C7" s="2">
+        <v>7.03</v>
+      </c>
+      <c r="D7" s="2">
+        <v>10.01</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5.36</v>
+      </c>
+      <c r="F7" s="2">
+        <v>82</v>
+      </c>
+      <c r="G7" s="2">
+        <v>84</v>
+      </c>
+      <c r="H7" s="2">
+        <v>88</v>
+      </c>
+      <c r="I7" s="2">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2611,7 +2640,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2619,7 +2648,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E6">
+  <conditionalFormatting sqref="E2:E7">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2627,22 +2656,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
+  <conditionalFormatting sqref="F2:F7">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G6">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H6">
+  <conditionalFormatting sqref="H2:H7">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
+  <conditionalFormatting sqref="I2:I7">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2695,16 +2724,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>318.5</v>
+        <v>328</v>
       </c>
       <c r="C2" s="2">
-        <v>32.58</v>
+        <v>28.69</v>
       </c>
       <c r="D2" s="2">
-        <v>28.27</v>
+        <v>30.16</v>
       </c>
       <c r="E2" s="2">
-        <v>10.99</v>
+        <v>10.87</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2713,7 +2742,7 @@
         <v>100</v>
       </c>
       <c r="H2" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2">
         <v>94</v>
@@ -2727,13 +2756,13 @@
         <v>11700</v>
       </c>
       <c r="C3" s="2">
-        <v>20.9</v>
+        <v>21.03</v>
       </c>
       <c r="D3" s="2">
-        <v>14.36</v>
+        <v>17.67</v>
       </c>
       <c r="E3" s="2">
-        <v>11.19</v>
+        <v>4.62</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
@@ -2742,7 +2771,7 @@
         <v>98</v>
       </c>
       <c r="H3" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I3" s="2">
         <v>98</v>
@@ -2753,16 +2782,16 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>1122</v>
+        <v>5086.1</v>
       </c>
       <c r="C4" s="2">
-        <v>9.81</v>
+        <v>13.07</v>
       </c>
       <c r="D4" s="2">
-        <v>25.84</v>
+        <v>19.13</v>
       </c>
       <c r="E4" s="2">
-        <v>8.359999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
@@ -2771,10 +2800,10 @@
         <v>94</v>
       </c>
       <c r="H4" s="2">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="I4" s="2">
-        <v>50</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2782,16 +2811,16 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>5056.2</v>
+        <v>1095</v>
       </c>
       <c r="C5" s="2">
-        <v>12.6</v>
+        <v>20.05</v>
       </c>
       <c r="D5" s="2">
-        <v>21</v>
+        <v>16.92</v>
       </c>
       <c r="E5" s="2">
-        <v>8.890000000000001</v>
+        <v>4.45</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
@@ -2800,155 +2829,155 @@
         <v>92</v>
       </c>
       <c r="H5" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I5" s="2">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>1087</v>
+        <v>1130</v>
       </c>
       <c r="C6" s="2">
-        <v>18.29</v>
+        <v>8.73</v>
       </c>
       <c r="D6" s="2">
-        <v>25.55</v>
+        <v>13.57</v>
       </c>
       <c r="E6" s="2">
-        <v>2.16</v>
+        <v>8.84</v>
       </c>
       <c r="F6" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G6" s="2">
         <v>96</v>
       </c>
       <c r="H6" s="2">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I6" s="2">
-        <v>88</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>8100</v>
+        <v>2032.5</v>
       </c>
       <c r="C7" s="2">
-        <v>10.25</v>
+        <v>11.12</v>
       </c>
       <c r="D7" s="2">
-        <v>16.1</v>
+        <v>16.23</v>
       </c>
       <c r="E7" s="2">
-        <v>8.210000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="F7" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H7" s="2">
         <v>78</v>
       </c>
       <c r="I7" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1">
-        <v>5310</v>
+        <v>2994.9</v>
       </c>
       <c r="C8" s="2">
-        <v>16.6</v>
+        <v>34.38</v>
       </c>
       <c r="D8" s="2">
-        <v>21.8</v>
+        <v>1.78</v>
       </c>
       <c r="E8" s="2">
-        <v>1.55</v>
+        <v>-1.37</v>
       </c>
       <c r="F8" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G8" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H8" s="2">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="I8" s="2">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1">
-        <v>3428.2</v>
+        <v>8042</v>
       </c>
       <c r="C9" s="2">
-        <v>6.27</v>
+        <v>12.19</v>
       </c>
       <c r="D9" s="2">
-        <v>16.8</v>
+        <v>6.58</v>
       </c>
       <c r="E9" s="2">
-        <v>8.300000000000001</v>
+        <v>4.59</v>
       </c>
       <c r="F9" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G9" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H9" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I9" s="2">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1">
-        <v>3035.1</v>
+        <v>3412.2</v>
       </c>
       <c r="C10" s="2">
-        <v>45.51</v>
+        <v>7.03</v>
       </c>
       <c r="D10" s="2">
-        <v>2.24</v>
+        <v>10.01</v>
       </c>
       <c r="E10" s="2">
-        <v>-4.66</v>
+        <v>5.36</v>
       </c>
       <c r="F10" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G10" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H10" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I10" s="2">
-        <v>100</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -3027,10 +3056,10 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
+        <v>36</v>
+      </c>
+      <c r="C2" s="2">
         <v>52</v>
-      </c>
-      <c r="C2" s="2">
-        <v>66</v>
       </c>
       <c r="D2" s="2">
         <v>54</v>
@@ -3041,10 +3070,10 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C3" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D3" s="2">
         <v>54</v>
@@ -3055,13 +3084,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C4" s="2">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D4" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3069,13 +3098,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="C5" s="2">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D5" s="2">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -22,16 +22,19 @@
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-08-21</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-08-21</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-08-21</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-08-21</t>
+    <t>Price_2026-08-28</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-08-28</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-08-28</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-08-28</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-08-28</t>
   </si>
   <si>
     <t>RS_Score_2026-08-21</t>
@@ -43,159 +46,156 @@
     <t>RS_Score_2026-08-07</t>
   </si>
   <si>
-    <t>RS_Score_2026-07-31</t>
-  </si>
-  <si>
     <t>ETERNAL</t>
   </si>
   <si>
+    <t>ADANIENT</t>
+  </si>
+  <si>
     <t>BAJAJ-AUTO</t>
   </si>
   <si>
     <t>TITAN</t>
   </si>
   <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
     <t>BAJFINANCE</t>
   </si>
   <si>
-    <t>SHRIRAMFIN</t>
+    <t>HCLTECH</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
   </si>
   <si>
     <t>BAJAJFINSV</t>
   </si>
   <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
-    <t>ADANIENT</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
+    <t>APOLLOHOSP</t>
   </si>
   <si>
     <t>M&amp;M</t>
   </si>
   <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>TCS</t>
+  </si>
+  <si>
     <t>NESTLEIND</t>
   </si>
   <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>HINDALCO</t>
+    <t>SBIN</t>
   </si>
   <si>
     <t>BHARTIARTL</t>
   </si>
   <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>HCLTECH</t>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
   </si>
   <si>
     <t>JIOFIN</t>
   </si>
   <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>ADANIPORTS</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
+    <t>COALINDIA</t>
   </si>
   <si>
     <t>TATACONSUM</t>
   </si>
   <si>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
     <t>ONGC</t>
   </si>
   <si>
-    <t>COALINDIA</t>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>TMPV</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
   </si>
   <si>
     <t>NTPC</t>
   </si>
   <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>TMPV</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
     <t>2026-08-21</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-08-07</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
   </si>
 </sst>
 </file>
@@ -725,13 +725,13 @@
         <v>328</v>
       </c>
       <c r="C2" s="2">
-        <v>28.69</v>
+        <v>28.38</v>
       </c>
       <c r="D2" s="2">
-        <v>30.16</v>
+        <v>24.41</v>
       </c>
       <c r="E2" s="2">
-        <v>10.87</v>
+        <v>5.64</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -743,7 +743,7 @@
         <v>100</v>
       </c>
       <c r="I2" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>60</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>11700</v>
+        <v>3168.5</v>
       </c>
       <c r="C3" s="2">
-        <v>21.03</v>
+        <v>36.53</v>
       </c>
       <c r="D3" s="2">
-        <v>17.67</v>
+        <v>3.56</v>
       </c>
       <c r="E3" s="2">
-        <v>4.62</v>
+        <v>3.28</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="I3" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>5086.1</v>
+        <v>11910</v>
       </c>
       <c r="C4" s="2">
-        <v>13.07</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2">
-        <v>19.13</v>
+        <v>16.87</v>
       </c>
       <c r="E4" s="2">
-        <v>7.3</v>
+        <v>0.46</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1095</v>
+        <v>5169.2</v>
       </c>
       <c r="C5" s="2">
-        <v>20.05</v>
+        <v>16.76</v>
       </c>
       <c r="D5" s="2">
-        <v>16.92</v>
+        <v>18.61</v>
       </c>
       <c r="E5" s="2">
-        <v>4.45</v>
+        <v>3.38</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
+        <v>96</v>
+      </c>
+      <c r="H5" s="2">
+        <v>94</v>
+      </c>
+      <c r="I5" s="2">
         <v>92</v>
-      </c>
-      <c r="H5" s="2">
-        <v>96</v>
-      </c>
-      <c r="I5" s="2">
-        <v>100</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>1130</v>
+        <v>1640.9</v>
       </c>
       <c r="C6" s="2">
-        <v>8.73</v>
+        <v>20.59</v>
       </c>
       <c r="D6" s="2">
-        <v>13.57</v>
+        <v>17.3</v>
       </c>
       <c r="E6" s="2">
-        <v>8.84</v>
+        <v>-0.49</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="H6" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="I6" s="2">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>2032.5</v>
+        <v>423.7</v>
       </c>
       <c r="C7" s="2">
-        <v>11.12</v>
+        <v>12.64</v>
       </c>
       <c r="D7" s="2">
-        <v>16.23</v>
+        <v>5.54</v>
       </c>
       <c r="E7" s="2">
-        <v>6.25</v>
+        <v>6.59</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H7" s="2">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="I7" s="2">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>3308</v>
+        <v>1086.9</v>
       </c>
       <c r="C8" s="2">
-        <v>20.22</v>
+        <v>12.15</v>
       </c>
       <c r="D8" s="2">
-        <v>4.86</v>
+        <v>10.09</v>
       </c>
       <c r="E8" s="2">
-        <v>6.62</v>
+        <v>-0.3</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="H8" s="2">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I8" s="2">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>2994.9</v>
+        <v>3258</v>
       </c>
       <c r="C9" s="2">
-        <v>34.38</v>
+        <v>17.64</v>
       </c>
       <c r="D9" s="2">
-        <v>1.78</v>
+        <v>2.93</v>
       </c>
       <c r="E9" s="2">
-        <v>-1.37</v>
+        <v>0.25</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
+        <v>88</v>
+      </c>
+      <c r="H9" s="2">
+        <v>74</v>
+      </c>
+      <c r="I9" s="2">
         <v>80</v>
-      </c>
-      <c r="H9" s="2">
-        <v>90</v>
-      </c>
-      <c r="I9" s="2">
-        <v>90</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>8042</v>
+        <v>8059</v>
       </c>
       <c r="C10" s="2">
-        <v>12.19</v>
+        <v>13.51</v>
       </c>
       <c r="D10" s="2">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
       <c r="E10" s="2">
-        <v>4.59</v>
+        <v>0.11</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H10" s="2">
         <v>86</v>
       </c>
       <c r="I10" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>3412.2</v>
+        <v>1079.9</v>
       </c>
       <c r="C11" s="2">
-        <v>7.03</v>
+        <v>17.87</v>
       </c>
       <c r="D11" s="2">
-        <v>10.01</v>
+        <v>12.21</v>
       </c>
       <c r="E11" s="2">
-        <v>5.36</v>
+        <v>-6.34</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H11" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I11" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1477.1</v>
+        <v>1316.1</v>
       </c>
       <c r="C12" s="2">
-        <v>15.38</v>
+        <v>8.25</v>
       </c>
       <c r="D12" s="2">
-        <v>7.97</v>
+        <v>17.61</v>
       </c>
       <c r="E12" s="2">
-        <v>2.14</v>
+        <v>-4.42</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="H12" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I12" s="2">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>1432.2</v>
+        <v>1337.5</v>
       </c>
       <c r="C13" s="2">
-        <v>17.58</v>
+        <v>4.87</v>
       </c>
       <c r="D13" s="2">
-        <v>3.68</v>
+        <v>4.9</v>
       </c>
       <c r="E13" s="2">
-        <v>1.62</v>
+        <v>3.5</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="H13" s="2">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="I13" s="2">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>1584</v>
+        <v>2002</v>
       </c>
       <c r="C14" s="2">
-        <v>8.029999999999999</v>
+        <v>13.06</v>
       </c>
       <c r="D14" s="2">
-        <v>14</v>
+        <v>12.43</v>
       </c>
       <c r="E14" s="2">
-        <v>0.57</v>
+        <v>-4.48</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="H14" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="I14" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>1029.85</v>
+        <v>8800</v>
       </c>
       <c r="C15" s="2">
-        <v>1.97</v>
+        <v>12.59</v>
       </c>
       <c r="D15" s="2">
-        <v>2.1</v>
+        <v>4.03</v>
       </c>
       <c r="E15" s="2">
-        <v>8.949999999999999</v>
+        <v>-0.11</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H15" s="2">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="I15" s="2">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>1946</v>
+        <v>3334</v>
       </c>
       <c r="C16" s="2">
-        <v>6.74</v>
+        <v>8.59</v>
       </c>
       <c r="D16" s="2">
-        <v>7.02</v>
+        <v>9.98</v>
       </c>
       <c r="E16" s="2">
-        <v>2.14</v>
+        <v>-2.76</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H16" s="2">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="I16" s="2">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>402.8</v>
+        <v>1422.8</v>
       </c>
       <c r="C17" s="2">
-        <v>6.41</v>
+        <v>9.18</v>
       </c>
       <c r="D17" s="2">
-        <v>-0.5600000000000001</v>
+        <v>6.09</v>
       </c>
       <c r="E17" s="2">
-        <v>4.72</v>
+        <v>-2.55</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H17" s="2">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I17" s="2">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>4093</v>
+        <v>1037.4</v>
       </c>
       <c r="C18" s="2">
-        <v>2.02</v>
+        <v>-1.79</v>
       </c>
       <c r="D18" s="2">
-        <v>-1.84</v>
+        <v>2.82</v>
       </c>
       <c r="E18" s="2">
-        <v>7.54</v>
+        <v>4.27</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="H18" s="2">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="I18" s="2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>5165</v>
+        <v>1913.3</v>
       </c>
       <c r="C19" s="2">
-        <v>10.41</v>
+        <v>10.66</v>
       </c>
       <c r="D19" s="2">
-        <v>5.83</v>
+        <v>2.97</v>
       </c>
       <c r="E19" s="2">
-        <v>-1.24</v>
+        <v>-2.56</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="H19" s="2">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="I19" s="2">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>8693</v>
+        <v>5166</v>
       </c>
       <c r="C20" s="2">
-        <v>13.66</v>
+        <v>13.26</v>
       </c>
       <c r="D20" s="2">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="E20" s="2">
-        <v>-1.59</v>
+        <v>-4.33</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="H20" s="2">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="I20" s="2">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>1904</v>
+        <v>1423.5</v>
       </c>
       <c r="C21" s="2">
-        <v>14.41</v>
+        <v>9.08</v>
       </c>
       <c r="D21" s="2">
-        <v>5.7</v>
+        <v>0.55</v>
       </c>
       <c r="E21" s="2">
-        <v>-3.53</v>
+        <v>-3.45</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="I21" s="2">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>1302.5</v>
+        <v>1144</v>
       </c>
       <c r="C22" s="2">
-        <v>-6.11</v>
+        <v>-0.13</v>
       </c>
       <c r="D22" s="2">
-        <v>17.56</v>
+        <v>7.38</v>
       </c>
       <c r="E22" s="2">
-        <v>0.51</v>
+        <v>-3.05</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="H22" s="2">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="I22" s="2">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>244</v>
+        <v>411.9</v>
       </c>
       <c r="C23" s="2">
-        <v>3.13</v>
+        <v>-5.31</v>
       </c>
       <c r="D23" s="2">
-        <v>2.11</v>
+        <v>-4.41</v>
       </c>
       <c r="E23" s="2">
-        <v>3.56</v>
+        <v>5.18</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="H23" s="2">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="I23" s="2">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>1420</v>
+        <v>1707.5</v>
       </c>
       <c r="C24" s="2">
-        <v>5.59</v>
+        <v>5.29</v>
       </c>
       <c r="D24" s="2">
-        <v>7.86</v>
+        <v>-6.55</v>
       </c>
       <c r="E24" s="2">
-        <v>-0.95</v>
+        <v>0.38</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="H24" s="2">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="I24" s="2">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>1293.7</v>
+        <v>4045.8</v>
       </c>
       <c r="C25" s="2">
-        <v>2.09</v>
+        <v>0.78</v>
       </c>
       <c r="D25" s="2">
-        <v>0.36</v>
+        <v>-3.7</v>
       </c>
       <c r="E25" s="2">
-        <v>3.95</v>
+        <v>0.52</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
+        <v>68</v>
+      </c>
+      <c r="H25" s="2">
+        <v>60</v>
+      </c>
+      <c r="I25" s="2">
         <v>42</v>
-      </c>
-      <c r="H25" s="2">
-        <v>46</v>
-      </c>
-      <c r="I25" s="2">
-        <v>50</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>1048.7</v>
+        <v>2342</v>
       </c>
       <c r="C26" s="2">
-        <v>-3.63</v>
+        <v>-2.49</v>
       </c>
       <c r="D26" s="2">
-        <v>2.73</v>
+        <v>10.67</v>
       </c>
       <c r="E26" s="2">
-        <v>2.75</v>
+        <v>-5.32</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H26" s="2">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="I26" s="2">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>2924</v>
+        <v>1454.6</v>
       </c>
       <c r="C27" s="2">
-        <v>3.53</v>
+        <v>3.13</v>
       </c>
       <c r="D27" s="2">
-        <v>0.79</v>
+        <v>4.26</v>
       </c>
       <c r="E27" s="2">
-        <v>-0.49</v>
+        <v>-4.93</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H27" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I27" s="2">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>1316</v>
+        <v>1047.5</v>
       </c>
       <c r="C28" s="2">
-        <v>-3.02</v>
+        <v>-4.09</v>
       </c>
       <c r="D28" s="2">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="E28" s="2">
-        <v>2.81</v>
+        <v>0.24</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="H28" s="2">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I28" s="2">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>11570</v>
+        <v>1882.4</v>
       </c>
       <c r="C29" s="2">
-        <v>-0.93</v>
+        <v>4.72</v>
       </c>
       <c r="D29" s="2">
-        <v>2.97</v>
+        <v>-0.55</v>
       </c>
       <c r="E29" s="2">
-        <v>-0.63</v>
+        <v>-4.47</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="H29" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I29" s="2">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>13565</v>
+        <v>11589</v>
       </c>
       <c r="C30" s="2">
-        <v>1.87</v>
+        <v>-1.54</v>
       </c>
       <c r="D30" s="2">
-        <v>-0.75</v>
+        <v>3.71</v>
       </c>
       <c r="E30" s="2">
-        <v>-0.21</v>
+        <v>-3.86</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I30" s="2">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>2302</v>
+        <v>13376</v>
       </c>
       <c r="C31" s="2">
-        <v>-9.06</v>
+        <v>2.18</v>
       </c>
       <c r="D31" s="2">
-        <v>7.06</v>
+        <v>0.67</v>
       </c>
       <c r="E31" s="2">
-        <v>0.28</v>
+        <v>-4.52</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H31" s="2">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I31" s="2">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,25 +1682,25 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>2640</v>
+        <v>2608.7</v>
       </c>
       <c r="C32" s="2">
-        <v>5.81</v>
+        <v>5.88</v>
       </c>
       <c r="D32" s="2">
-        <v>-2.79</v>
+        <v>-1.6</v>
       </c>
       <c r="E32" s="2">
-        <v>-2.59</v>
+        <v>-7.16</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
+        <v>40</v>
+      </c>
+      <c r="H32" s="2">
         <v>54</v>
-      </c>
-      <c r="H32" s="2">
-        <v>68</v>
       </c>
       <c r="I32" s="2">
         <v>68</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>414</v>
+        <v>1265</v>
       </c>
       <c r="C33" s="2">
-        <v>-9.4</v>
+        <v>-4.4</v>
       </c>
       <c r="D33" s="2">
-        <v>1.22</v>
+        <v>-6.82</v>
       </c>
       <c r="E33" s="2">
-        <v>1.82</v>
+        <v>-0.55</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H33" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I33" s="2">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>1700</v>
+        <v>1287</v>
       </c>
       <c r="C34" s="2">
-        <v>8.16</v>
+        <v>-5.33</v>
       </c>
       <c r="D34" s="2">
-        <v>-5.81</v>
+        <v>-2.98</v>
       </c>
       <c r="E34" s="2">
-        <v>-3.98</v>
+        <v>-2.43</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
+        <v>48</v>
+      </c>
+      <c r="H34" s="2">
+        <v>36</v>
+      </c>
+      <c r="I34" s="2">
         <v>32</v>
-      </c>
-      <c r="H34" s="2">
-        <v>30</v>
-      </c>
-      <c r="I34" s="2">
-        <v>34</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>1121</v>
+        <v>2898</v>
       </c>
       <c r="C35" s="2">
-        <v>-12.75</v>
+        <v>2.17</v>
       </c>
       <c r="D35" s="2">
-        <v>-1.22</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="E35" s="2">
-        <v>3.87</v>
+        <v>-4.98</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H35" s="2">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="I35" s="2">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>180.79</v>
+        <v>180.95</v>
       </c>
       <c r="C36" s="2">
-        <v>-9.69</v>
+        <v>-10.75</v>
       </c>
       <c r="D36" s="2">
-        <v>0.8100000000000001</v>
+        <v>1.57</v>
       </c>
       <c r="E36" s="2">
-        <v>1.27</v>
+        <v>-4.09</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
+        <v>32</v>
+      </c>
+      <c r="H36" s="2">
         <v>38</v>
       </c>
-      <c r="H36" s="2">
+      <c r="I36" s="2">
         <v>26</v>
-      </c>
-      <c r="I36" s="2">
-        <v>32</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>1174.7</v>
+        <v>548</v>
       </c>
       <c r="C37" s="2">
-        <v>-4.09</v>
+        <v>-7.93</v>
       </c>
       <c r="D37" s="2">
-        <v>-7.61</v>
+        <v>-8.23</v>
       </c>
       <c r="E37" s="2">
-        <v>2.08</v>
+        <v>-0.92</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H37" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I37" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>554.8</v>
+        <v>1773.2</v>
       </c>
       <c r="C38" s="2">
-        <v>-8.69</v>
+        <v>-2.32</v>
       </c>
       <c r="D38" s="2">
-        <v>-4.2</v>
+        <v>-1.79</v>
       </c>
       <c r="E38" s="2">
-        <v>0.35</v>
+        <v>-7.4</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H38" s="2">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="I38" s="2">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>1245.8</v>
+        <v>1178</v>
       </c>
       <c r="C39" s="2">
-        <v>-7.97</v>
+        <v>-11.17</v>
       </c>
       <c r="D39" s="2">
-        <v>-8.880000000000001</v>
+        <v>-8.15</v>
       </c>
       <c r="E39" s="2">
-        <v>1.49</v>
+        <v>-0.17</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H39" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I39" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>726.95</v>
+        <v>186.5</v>
       </c>
       <c r="C40" s="2">
-        <v>-7.1</v>
+        <v>-10.75</v>
       </c>
       <c r="D40" s="2">
-        <v>-4.94</v>
+        <v>-6.27</v>
       </c>
       <c r="E40" s="2">
-        <v>-1.7</v>
+        <v>-2.36</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H40" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I40" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1970,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>1792.9</v>
+        <v>1014.1</v>
       </c>
       <c r="C41" s="2">
-        <v>-9.56</v>
+        <v>0.6</v>
       </c>
       <c r="D41" s="2">
-        <v>1.9</v>
+        <v>-7.23</v>
       </c>
       <c r="E41" s="2">
-        <v>-3.96</v>
+        <v>-7.84</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H41" s="2">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I41" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>183</v>
+        <v>720.3</v>
       </c>
       <c r="C42" s="2">
-        <v>-11.78</v>
+        <v>-7.29</v>
       </c>
       <c r="D42" s="2">
-        <v>-7.24</v>
+        <v>-8.41</v>
       </c>
       <c r="E42" s="2">
-        <v>-0.68</v>
+        <v>-4.34</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H42" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I42" s="2">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>1049</v>
+        <v>238.4</v>
       </c>
       <c r="C43" s="2">
-        <v>-5.58</v>
+        <v>-5.79</v>
       </c>
       <c r="D43" s="2">
-        <v>-4.67</v>
+        <v>-1.82</v>
       </c>
       <c r="E43" s="2">
-        <v>-5.27</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="H43" s="2">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="I43" s="2">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>236.4</v>
+        <v>401</v>
       </c>
       <c r="C44" s="2">
-        <v>-16.57</v>
+        <v>-10.2</v>
       </c>
       <c r="D44" s="2">
-        <v>-2.98</v>
+        <v>-9.5</v>
       </c>
       <c r="E44" s="2">
-        <v>-0.91</v>
+        <v>-3.61</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H44" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I44" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2098,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>405.2</v>
+        <v>1040.7</v>
       </c>
       <c r="C45" s="2">
-        <v>-7.05</v>
+        <v>-9.56</v>
       </c>
       <c r="D45" s="2">
-        <v>-7.53</v>
+        <v>-6.49</v>
       </c>
       <c r="E45" s="2">
-        <v>-3.95</v>
+        <v>-6.24</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H45" s="2">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="I45" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,28 +2130,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>340</v>
+        <v>2010.4</v>
       </c>
       <c r="C46" s="2">
-        <v>-14.57</v>
+        <v>-12.78</v>
       </c>
       <c r="D46" s="2">
-        <v>-2.33</v>
+        <v>-7.05</v>
       </c>
       <c r="E46" s="2">
-        <v>-3.08</v>
+        <v>-5.97</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H46" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I46" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>1000</v>
+        <v>232.25</v>
       </c>
       <c r="C47" s="2">
-        <v>-0.95</v>
+        <v>-18.77</v>
       </c>
       <c r="D47" s="2">
-        <v>-2.64</v>
+        <v>-5.38</v>
       </c>
       <c r="E47" s="2">
-        <v>-10.28</v>
+        <v>-4.03</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H47" s="2">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="I47" s="2">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,28 +2194,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>2028</v>
+        <v>266</v>
       </c>
       <c r="C48" s="2">
-        <v>-8.199999999999999</v>
+        <v>-10.07</v>
       </c>
       <c r="D48" s="2">
-        <v>-4.98</v>
+        <v>-8.67</v>
       </c>
       <c r="E48" s="2">
-        <v>-6.74</v>
+        <v>-7.32</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="H48" s="2">
         <v>24</v>
       </c>
       <c r="I48" s="2">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,28 +2226,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>269.4</v>
+        <v>319.4</v>
       </c>
       <c r="C49" s="2">
-        <v>-9.27</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="D49" s="2">
-        <v>-6.43</v>
+        <v>-11.65</v>
       </c>
       <c r="E49" s="2">
-        <v>-5.75</v>
+        <v>-8.56</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="H49" s="2">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I49" s="2">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,16 +2258,16 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>272.4</v>
+        <v>266.05</v>
       </c>
       <c r="C50" s="2">
-        <v>-14.8</v>
+        <v>-17.09</v>
       </c>
       <c r="D50" s="2">
-        <v>-4.66</v>
+        <v>-8.18</v>
       </c>
       <c r="E50" s="2">
-        <v>-5.7</v>
+        <v>-7.3</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
@@ -2276,10 +2276,10 @@
         <v>4</v>
       </c>
       <c r="H50" s="2">
+        <v>4</v>
+      </c>
+      <c r="I50" s="2">
         <v>12</v>
-      </c>
-      <c r="I50" s="2">
-        <v>26</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2290,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>317.9</v>
+        <v>330.05</v>
       </c>
       <c r="C51" s="2">
-        <v>-9.890000000000001</v>
+        <v>-19.54</v>
       </c>
       <c r="D51" s="2">
-        <v>-19.14</v>
+        <v>-10.08</v>
       </c>
       <c r="E51" s="2">
-        <v>-2.98</v>
+        <v>-5.94</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H51" s="2">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I51" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2420,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2465,13 +2465,13 @@
         <v>328</v>
       </c>
       <c r="C2" s="2">
-        <v>28.69</v>
+        <v>28.38</v>
       </c>
       <c r="D2" s="2">
-        <v>30.16</v>
+        <v>24.41</v>
       </c>
       <c r="E2" s="2">
-        <v>10.87</v>
+        <v>5.64</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2483,7 +2483,7 @@
         <v>100</v>
       </c>
       <c r="I2" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2491,28 +2491,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>11700</v>
+        <v>3168.5</v>
       </c>
       <c r="C3" s="2">
-        <v>21.03</v>
+        <v>36.53</v>
       </c>
       <c r="D3" s="2">
-        <v>17.67</v>
+        <v>3.56</v>
       </c>
       <c r="E3" s="2">
-        <v>4.62</v>
+        <v>3.28</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="I3" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2520,28 +2520,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>5086.1</v>
+        <v>11910</v>
       </c>
       <c r="C4" s="2">
-        <v>13.07</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2">
-        <v>19.13</v>
+        <v>16.87</v>
       </c>
       <c r="E4" s="2">
-        <v>7.3</v>
+        <v>0.46</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2549,90 +2549,119 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1095</v>
+        <v>5169.2</v>
       </c>
       <c r="C5" s="2">
-        <v>20.05</v>
+        <v>16.76</v>
       </c>
       <c r="D5" s="2">
-        <v>16.92</v>
+        <v>18.61</v>
       </c>
       <c r="E5" s="2">
-        <v>4.45</v>
+        <v>3.38</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
+        <v>96</v>
+      </c>
+      <c r="H5" s="2">
+        <v>94</v>
+      </c>
+      <c r="I5" s="2">
         <v>92</v>
-      </c>
-      <c r="H5" s="2">
-        <v>96</v>
-      </c>
-      <c r="I5" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>2994.9</v>
+        <v>1086.9</v>
       </c>
       <c r="C6" s="2">
-        <v>34.38</v>
+        <v>12.15</v>
       </c>
       <c r="D6" s="2">
-        <v>1.78</v>
+        <v>10.09</v>
       </c>
       <c r="E6" s="2">
-        <v>-1.37</v>
+        <v>-0.3</v>
       </c>
       <c r="F6" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G6" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H6" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I6" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1">
+        <v>8059</v>
+      </c>
+      <c r="C7" s="2">
+        <v>13.51</v>
+      </c>
+      <c r="D7" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="F7" s="2">
+        <v>84</v>
+      </c>
+      <c r="G7" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" s="2">
+        <v>86</v>
+      </c>
+      <c r="I7" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1">
-        <v>3412.2</v>
-      </c>
-      <c r="C7" s="2">
-        <v>7.03</v>
-      </c>
-      <c r="D7" s="2">
-        <v>10.01</v>
-      </c>
-      <c r="E7" s="2">
-        <v>5.36</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="B8" s="1">
+        <v>1079.9</v>
+      </c>
+      <c r="C8" s="2">
+        <v>17.87</v>
+      </c>
+      <c r="D8" s="2">
+        <v>12.21</v>
+      </c>
+      <c r="E8" s="2">
+        <v>-6.34</v>
+      </c>
+      <c r="F8" s="2">
         <v>82</v>
       </c>
-      <c r="G7" s="2">
-        <v>84</v>
-      </c>
-      <c r="H7" s="2">
-        <v>88</v>
-      </c>
-      <c r="I7" s="2">
-        <v>82</v>
+      <c r="G8" s="2">
+        <v>94</v>
+      </c>
+      <c r="H8" s="2">
+        <v>92</v>
+      </c>
+      <c r="I8" s="2">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2640,7 +2669,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D8">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2648,7 +2677,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E8">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2656,22 +2685,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G8">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H8">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I8">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -2682,7 +2711,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -2727,13 +2756,13 @@
         <v>328</v>
       </c>
       <c r="C2" s="2">
-        <v>28.69</v>
+        <v>28.38</v>
       </c>
       <c r="D2" s="2">
-        <v>30.16</v>
+        <v>24.41</v>
       </c>
       <c r="E2" s="2">
-        <v>10.87</v>
+        <v>5.64</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2745,7 +2774,7 @@
         <v>100</v>
       </c>
       <c r="I2" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2753,28 +2782,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>11700</v>
+        <v>3168.5</v>
       </c>
       <c r="C3" s="2">
-        <v>21.03</v>
+        <v>36.53</v>
       </c>
       <c r="D3" s="2">
-        <v>17.67</v>
+        <v>3.56</v>
       </c>
       <c r="E3" s="2">
-        <v>4.62</v>
+        <v>3.28</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="I3" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2782,28 +2811,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>5086.1</v>
+        <v>11910</v>
       </c>
       <c r="C4" s="2">
-        <v>13.07</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2">
-        <v>19.13</v>
+        <v>16.87</v>
       </c>
       <c r="E4" s="2">
-        <v>7.3</v>
+        <v>0.46</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2811,177 +2840,148 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1095</v>
+        <v>5169.2</v>
       </c>
       <c r="C5" s="2">
-        <v>20.05</v>
+        <v>16.76</v>
       </c>
       <c r="D5" s="2">
-        <v>16.92</v>
+        <v>18.61</v>
       </c>
       <c r="E5" s="2">
-        <v>4.45</v>
+        <v>3.38</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
+        <v>96</v>
+      </c>
+      <c r="H5" s="2">
+        <v>94</v>
+      </c>
+      <c r="I5" s="2">
         <v>92</v>
-      </c>
-      <c r="H5" s="2">
-        <v>96</v>
-      </c>
-      <c r="I5" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>1130</v>
+        <v>1086.9</v>
       </c>
       <c r="C6" s="2">
-        <v>8.73</v>
+        <v>12.15</v>
       </c>
       <c r="D6" s="2">
-        <v>13.57</v>
+        <v>10.09</v>
       </c>
       <c r="E6" s="2">
-        <v>8.84</v>
+        <v>-0.3</v>
       </c>
       <c r="F6" s="2">
+        <v>88</v>
+      </c>
+      <c r="G6" s="2">
         <v>92</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <v>96</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>94</v>
-      </c>
-      <c r="I6" s="2">
-        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1">
-        <v>2032.5</v>
+        <v>3258</v>
       </c>
       <c r="C7" s="2">
-        <v>11.12</v>
+        <v>17.64</v>
       </c>
       <c r="D7" s="2">
-        <v>16.23</v>
+        <v>2.93</v>
       </c>
       <c r="E7" s="2">
-        <v>6.25</v>
+        <v>0.25</v>
       </c>
       <c r="F7" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G7" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H7" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I7" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1">
-        <v>2994.9</v>
+        <v>8059</v>
       </c>
       <c r="C8" s="2">
-        <v>34.38</v>
+        <v>13.51</v>
       </c>
       <c r="D8" s="2">
-        <v>1.78</v>
+        <v>6.6</v>
       </c>
       <c r="E8" s="2">
-        <v>-1.37</v>
+        <v>0.11</v>
       </c>
       <c r="F8" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G8" s="2">
         <v>80</v>
       </c>
       <c r="H8" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I8" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1">
-        <v>8042</v>
+        <v>1079.9</v>
       </c>
       <c r="C9" s="2">
-        <v>12.19</v>
+        <v>17.87</v>
       </c>
       <c r="D9" s="2">
-        <v>6.58</v>
+        <v>12.21</v>
       </c>
       <c r="E9" s="2">
-        <v>4.59</v>
+        <v>-6.34</v>
       </c>
       <c r="F9" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G9" s="2">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I9" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1">
-        <v>3412.2</v>
-      </c>
-      <c r="C10" s="2">
-        <v>7.03</v>
-      </c>
-      <c r="D10" s="2">
-        <v>10.01</v>
-      </c>
-      <c r="E10" s="2">
-        <v>5.36</v>
-      </c>
-      <c r="F10" s="2">
-        <v>82</v>
-      </c>
-      <c r="G10" s="2">
-        <v>84</v>
-      </c>
-      <c r="H10" s="2">
-        <v>88</v>
-      </c>
-      <c r="I10" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C10">
+  <conditionalFormatting sqref="C2:C9">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2989,7 +2989,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D10">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2997,7 +2997,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E10">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3005,22 +3005,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F10">
+  <conditionalFormatting sqref="F2:F9">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G10">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H10">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I10">
+  <conditionalFormatting sqref="I2:I9">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -3056,13 +3056,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D2" s="2">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3070,10 +3070,10 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C3" s="2">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2">
         <v>54</v>
@@ -3084,13 +3084,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D4" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3098,13 +3098,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C5" s="2">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D5" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -3104,7 +3104,7 @@
         <v>70</v>
       </c>
       <c r="D5" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-08-28</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-08-28</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-08-28</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-08-28</t>
+    <t>Price_2026-09-04</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-09-04</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-09-04</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-09-04</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-09-04</t>
   </si>
   <si>
     <t>RS_Score_2026-08-28</t>
@@ -43,159 +46,156 @@
     <t>RS_Score_2026-08-14</t>
   </si>
   <si>
-    <t>RS_Score_2026-08-07</t>
-  </si>
-  <si>
     <t>ETERNAL</t>
   </si>
   <si>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>HCLTECH</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
     <t>ADANIENT</t>
   </si>
   <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>TITAN</t>
-  </si>
-  <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
   </si>
   <si>
     <t>SHRIRAMFIN</t>
   </si>
   <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>HCLTECH</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>SBIN</t>
   </si>
   <si>
     <t>M&amp;M</t>
   </si>
   <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>HINDALCO</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>ADANIPORTS</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
   </si>
   <si>
     <t>MARUTI</t>
   </si>
   <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
     <t>MAXHEALTH</t>
   </si>
   <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
+    <t>HINDUNILVR</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>TMPV</t>
   </si>
   <si>
     <t>TATACONSUM</t>
   </si>
   <si>
-    <t>HINDUNILVR</t>
-  </si>
-  <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>TMPV</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
     <t>2026-08-28</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>2026-08-07</t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>328</v>
+        <v>322.75</v>
       </c>
       <c r="C2" s="2">
-        <v>28.38</v>
+        <v>28.13</v>
       </c>
       <c r="D2" s="2">
-        <v>24.41</v>
+        <v>24.42</v>
       </c>
       <c r="E2" s="2">
-        <v>5.64</v>
+        <v>4.03</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -754,28 +754,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>3168.5</v>
+        <v>11919</v>
       </c>
       <c r="C3" s="2">
-        <v>36.53</v>
+        <v>19.29</v>
       </c>
       <c r="D3" s="2">
-        <v>3.56</v>
+        <v>23.77</v>
       </c>
       <c r="E3" s="2">
-        <v>3.28</v>
+        <v>2.07</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H3" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="I3" s="2">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>11910</v>
+        <v>421.15</v>
       </c>
       <c r="C4" s="2">
-        <v>25</v>
+        <v>13.51</v>
       </c>
       <c r="D4" s="2">
-        <v>16.87</v>
+        <v>6.67</v>
       </c>
       <c r="E4" s="2">
-        <v>0.46</v>
+        <v>7.03</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H4" s="2">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="I4" s="2">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,28 +818,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>5169.2</v>
+        <v>5027</v>
       </c>
       <c r="C5" s="2">
-        <v>16.76</v>
+        <v>15.6</v>
       </c>
       <c r="D5" s="2">
-        <v>18.61</v>
+        <v>17.92</v>
       </c>
       <c r="E5" s="2">
-        <v>3.38</v>
+        <v>-1.24</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
+        <v>94</v>
+      </c>
+      <c r="H5" s="2">
         <v>96</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>94</v>
-      </c>
-      <c r="I5" s="2">
-        <v>92</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>1640.9</v>
+        <v>1992.1</v>
       </c>
       <c r="C6" s="2">
-        <v>20.59</v>
+        <v>12.62</v>
       </c>
       <c r="D6" s="2">
-        <v>17.3</v>
+        <v>13.33</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.49</v>
+        <v>-1.44</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H6" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="I6" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,28 +882,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>423.7</v>
+        <v>1596.9</v>
       </c>
       <c r="C7" s="2">
-        <v>12.64</v>
+        <v>11.33</v>
       </c>
       <c r="D7" s="2">
-        <v>5.54</v>
+        <v>14.27</v>
       </c>
       <c r="E7" s="2">
-        <v>6.59</v>
+        <v>-2.63</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="H7" s="2">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="I7" s="2">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>1086.9</v>
+        <v>3310</v>
       </c>
       <c r="C8" s="2">
-        <v>12.15</v>
+        <v>16.26</v>
       </c>
       <c r="D8" s="2">
-        <v>10.09</v>
+        <v>7.8</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.3</v>
+        <v>-2.09</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H8" s="2">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I8" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>3258</v>
+        <v>1293.4</v>
       </c>
       <c r="C9" s="2">
-        <v>17.64</v>
+        <v>8.84</v>
       </c>
       <c r="D9" s="2">
-        <v>2.93</v>
+        <v>18.52</v>
       </c>
       <c r="E9" s="2">
-        <v>0.25</v>
+        <v>-4.7</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="I9" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>8059</v>
+        <v>1325</v>
       </c>
       <c r="C10" s="2">
-        <v>13.51</v>
+        <v>5.21</v>
       </c>
       <c r="D10" s="2">
-        <v>6.6</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="E10" s="2">
-        <v>0.11</v>
+        <v>1.77</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H10" s="2">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="I10" s="2">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>1079.9</v>
+        <v>1423.2</v>
       </c>
       <c r="C11" s="2">
-        <v>17.87</v>
+        <v>12.94</v>
       </c>
       <c r="D11" s="2">
-        <v>12.21</v>
+        <v>3.43</v>
       </c>
       <c r="E11" s="2">
-        <v>-6.34</v>
+        <v>-0.6</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H11" s="2">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="I11" s="2">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1316.1</v>
+        <v>1060.5</v>
       </c>
       <c r="C12" s="2">
-        <v>8.25</v>
+        <v>12.29</v>
       </c>
       <c r="D12" s="2">
-        <v>17.61</v>
+        <v>8.65</v>
       </c>
       <c r="E12" s="2">
-        <v>-4.42</v>
+        <v>-3.78</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="H12" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I12" s="2">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>1337.5</v>
+        <v>2938</v>
       </c>
       <c r="C13" s="2">
-        <v>4.87</v>
+        <v>18.25</v>
       </c>
       <c r="D13" s="2">
-        <v>4.9</v>
+        <v>-0.83</v>
       </c>
       <c r="E13" s="2">
-        <v>3.5</v>
+        <v>-2.39</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="H13" s="2">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="I13" s="2">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>2002</v>
+        <v>8650</v>
       </c>
       <c r="C14" s="2">
-        <v>13.06</v>
+        <v>11.92</v>
       </c>
       <c r="D14" s="2">
-        <v>12.43</v>
+        <v>0.06</v>
       </c>
       <c r="E14" s="2">
-        <v>-4.48</v>
+        <v>-2.83</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H14" s="2">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="I14" s="2">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>8800</v>
+        <v>1899</v>
       </c>
       <c r="C15" s="2">
-        <v>12.59</v>
+        <v>4.41</v>
       </c>
       <c r="D15" s="2">
-        <v>4.03</v>
+        <v>1.56</v>
       </c>
       <c r="E15" s="2">
-        <v>-0.11</v>
+        <v>-2.33</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H15" s="2">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I15" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,16 +1170,16 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>3334</v>
+        <v>7630.5</v>
       </c>
       <c r="C16" s="2">
-        <v>8.59</v>
+        <v>5.2</v>
       </c>
       <c r="D16" s="2">
-        <v>9.98</v>
+        <v>3.83</v>
       </c>
       <c r="E16" s="2">
-        <v>-2.76</v>
+        <v>-4.32</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
@@ -1188,10 +1188,10 @@
         <v>84</v>
       </c>
       <c r="H16" s="2">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="I16" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,28 +1202,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>1422.8</v>
+        <v>1130</v>
       </c>
       <c r="C17" s="2">
-        <v>9.18</v>
+        <v>-1.19</v>
       </c>
       <c r="D17" s="2">
-        <v>6.09</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2">
-        <v>-2.55</v>
+        <v>-4.48</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
       </c>
       <c r="G17" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H17" s="2">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="I17" s="2">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>1037.4</v>
+        <v>1273</v>
       </c>
       <c r="C18" s="2">
-        <v>-1.79</v>
+        <v>-0.09</v>
       </c>
       <c r="D18" s="2">
-        <v>2.82</v>
+        <v>-6.1</v>
       </c>
       <c r="E18" s="2">
-        <v>4.27</v>
+        <v>2.06</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="H18" s="2">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="I18" s="2">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1913.3</v>
+        <v>1707.3</v>
       </c>
       <c r="C19" s="2">
-        <v>10.66</v>
+        <v>-1.61</v>
       </c>
       <c r="D19" s="2">
-        <v>2.97</v>
+        <v>-3.87</v>
       </c>
       <c r="E19" s="2">
-        <v>-2.56</v>
+        <v>1.56</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H19" s="2">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="I19" s="2">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>5166</v>
+        <v>4977</v>
       </c>
       <c r="C20" s="2">
-        <v>13.26</v>
+        <v>16.77</v>
       </c>
       <c r="D20" s="2">
-        <v>2.89</v>
+        <v>-6.36</v>
       </c>
       <c r="E20" s="2">
-        <v>-4.33</v>
+        <v>-6.68</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
+        <v>64</v>
+      </c>
+      <c r="H20" s="2">
         <v>54</v>
       </c>
-      <c r="H20" s="2">
+      <c r="I20" s="2">
         <v>88</v>
-      </c>
-      <c r="I20" s="2">
-        <v>82</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>1423.5</v>
+        <v>2304</v>
       </c>
       <c r="C21" s="2">
-        <v>9.08</v>
+        <v>-3.42</v>
       </c>
       <c r="D21" s="2">
-        <v>0.55</v>
+        <v>10.43</v>
       </c>
       <c r="E21" s="2">
-        <v>-3.45</v>
+        <v>-5.02</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="H21" s="2">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="I21" s="2">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>1144</v>
+        <v>1010</v>
       </c>
       <c r="C22" s="2">
-        <v>-0.13</v>
+        <v>-2.63</v>
       </c>
       <c r="D22" s="2">
-        <v>7.38</v>
+        <v>5.34</v>
       </c>
       <c r="E22" s="2">
-        <v>-3.05</v>
+        <v>-4.18</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="H22" s="2">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="I22" s="2">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,28 +1394,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>411.9</v>
+        <v>1041</v>
       </c>
       <c r="C23" s="2">
-        <v>-5.31</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2">
-        <v>-4.41</v>
+        <v>1.38</v>
       </c>
       <c r="E23" s="2">
-        <v>5.18</v>
+        <v>-8.51</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
       </c>
       <c r="G23" s="2">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="H23" s="2">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="I23" s="2">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,13 +1426,13 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>1707.5</v>
+        <v>405.35</v>
       </c>
       <c r="C24" s="2">
-        <v>5.29</v>
+        <v>-6.38</v>
       </c>
       <c r="D24" s="2">
-        <v>-6.55</v>
+        <v>-1.38</v>
       </c>
       <c r="E24" s="2">
         <v>0.38</v>
@@ -1441,10 +1441,10 @@
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="H24" s="2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I24" s="2">
         <v>30</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>4045.8</v>
+        <v>1840</v>
       </c>
       <c r="C25" s="2">
-        <v>0.78</v>
+        <v>1.97</v>
       </c>
       <c r="D25" s="2">
-        <v>-3.7</v>
+        <v>1.2</v>
       </c>
       <c r="E25" s="2">
-        <v>0.52</v>
+        <v>-5.3</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="I25" s="2">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>2342</v>
+        <v>1322</v>
       </c>
       <c r="C26" s="2">
-        <v>-2.49</v>
+        <v>-9.23</v>
       </c>
       <c r="D26" s="2">
-        <v>10.67</v>
+        <v>1.61</v>
       </c>
       <c r="E26" s="2">
-        <v>-5.32</v>
+        <v>-0.4</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H26" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I26" s="2">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>1454.6</v>
+        <v>1775</v>
       </c>
       <c r="C27" s="2">
-        <v>3.13</v>
+        <v>-2.48</v>
       </c>
       <c r="D27" s="2">
-        <v>4.26</v>
+        <v>1.12</v>
       </c>
       <c r="E27" s="2">
-        <v>-4.93</v>
+        <v>-4.31</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="H27" s="2">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="I27" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>1047.5</v>
+        <v>415.35</v>
       </c>
       <c r="C28" s="2">
-        <v>-4.09</v>
+        <v>-11.19</v>
       </c>
       <c r="D28" s="2">
-        <v>0.65</v>
+        <v>-4.19</v>
       </c>
       <c r="E28" s="2">
-        <v>0.24</v>
+        <v>2.34</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="H28" s="2">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="I28" s="2">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>1882.4</v>
+        <v>546.4</v>
       </c>
       <c r="C29" s="2">
-        <v>4.72</v>
+        <v>-6.8</v>
       </c>
       <c r="D29" s="2">
-        <v>-0.55</v>
+        <v>-6.32</v>
       </c>
       <c r="E29" s="2">
-        <v>-4.47</v>
+        <v>1.19</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="H29" s="2">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="I29" s="2">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>11589</v>
+        <v>188.79</v>
       </c>
       <c r="C30" s="2">
-        <v>-1.54</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="D30" s="2">
-        <v>3.71</v>
+        <v>-0.41</v>
       </c>
       <c r="E30" s="2">
-        <v>-3.86</v>
+        <v>-0.76</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="H30" s="2">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="I30" s="2">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>13376</v>
+        <v>1385</v>
       </c>
       <c r="C31" s="2">
-        <v>2.18</v>
+        <v>4.72</v>
       </c>
       <c r="D31" s="2">
-        <v>0.67</v>
+        <v>-4.75</v>
       </c>
       <c r="E31" s="2">
-        <v>-4.52</v>
+        <v>-5.63</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="H31" s="2">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="I31" s="2">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>2608.7</v>
+        <v>3975</v>
       </c>
       <c r="C32" s="2">
-        <v>5.88</v>
+        <v>-2.12</v>
       </c>
       <c r="D32" s="2">
-        <v>-1.6</v>
+        <v>-4.57</v>
       </c>
       <c r="E32" s="2">
-        <v>-7.16</v>
+        <v>-2.57</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="H32" s="2">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="I32" s="2">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>1265</v>
+        <v>11275</v>
       </c>
       <c r="C33" s="2">
-        <v>-4.4</v>
+        <v>-2.15</v>
       </c>
       <c r="D33" s="2">
-        <v>-6.82</v>
+        <v>1.49</v>
       </c>
       <c r="E33" s="2">
-        <v>-0.55</v>
+        <v>-6.34</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="H33" s="2">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="I33" s="2">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>1287</v>
+        <v>1416</v>
       </c>
       <c r="C34" s="2">
-        <v>-5.33</v>
+        <v>-2.35</v>
       </c>
       <c r="D34" s="2">
-        <v>-2.98</v>
+        <v>2.56</v>
       </c>
       <c r="E34" s="2">
-        <v>-2.43</v>
+        <v>-7.37</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H34" s="2">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="I34" s="2">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>2898</v>
+        <v>239.5</v>
       </c>
       <c r="C35" s="2">
-        <v>2.17</v>
+        <v>-5.02</v>
       </c>
       <c r="D35" s="2">
-        <v>-8.890000000000001</v>
+        <v>1.42</v>
       </c>
       <c r="E35" s="2">
-        <v>-4.98</v>
+        <v>-5.71</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="H35" s="2">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="I35" s="2">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>180.95</v>
+        <v>1016.1</v>
       </c>
       <c r="C36" s="2">
-        <v>-10.75</v>
+        <v>-3.18</v>
       </c>
       <c r="D36" s="2">
-        <v>1.57</v>
+        <v>-1.93</v>
       </c>
       <c r="E36" s="2">
-        <v>-4.09</v>
+        <v>-5.13</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H36" s="2">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I36" s="2">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>548</v>
+        <v>3150</v>
       </c>
       <c r="C37" s="2">
-        <v>-7.93</v>
+        <v>2.47</v>
       </c>
       <c r="D37" s="2">
-        <v>-8.23</v>
+        <v>2.91</v>
       </c>
       <c r="E37" s="2">
-        <v>-0.92</v>
+        <v>-10.44</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="H37" s="2">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="I37" s="2">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>1773.2</v>
+        <v>2527.3</v>
       </c>
       <c r="C38" s="2">
-        <v>-2.32</v>
+        <v>4.13</v>
       </c>
       <c r="D38" s="2">
-        <v>-1.79</v>
+        <v>-4.88</v>
       </c>
       <c r="E38" s="2">
-        <v>-7.4</v>
+        <v>-8.1</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H38" s="2">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I38" s="2">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>1178</v>
+        <v>176.4</v>
       </c>
       <c r="C39" s="2">
-        <v>-11.17</v>
+        <v>-11.13</v>
       </c>
       <c r="D39" s="2">
-        <v>-8.15</v>
+        <v>1.67</v>
       </c>
       <c r="E39" s="2">
-        <v>-0.17</v>
+        <v>-4.91</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H39" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I39" s="2">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>186.5</v>
+        <v>234.65</v>
       </c>
       <c r="C40" s="2">
-        <v>-10.75</v>
+        <v>-19.55</v>
       </c>
       <c r="D40" s="2">
-        <v>-6.27</v>
+        <v>0.68</v>
       </c>
       <c r="E40" s="2">
-        <v>-2.36</v>
+        <v>-1.75</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H40" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I40" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1970,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>1014.1</v>
+        <v>712.1</v>
       </c>
       <c r="C41" s="2">
-        <v>0.6</v>
+        <v>-7.12</v>
       </c>
       <c r="D41" s="2">
-        <v>-7.23</v>
+        <v>-10.86</v>
       </c>
       <c r="E41" s="2">
-        <v>-7.84</v>
+        <v>-2.59</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
+        <v>20</v>
+      </c>
+      <c r="H41" s="2">
+        <v>24</v>
+      </c>
+      <c r="I41" s="2">
         <v>10</v>
-      </c>
-      <c r="H41" s="2">
-        <v>22</v>
-      </c>
-      <c r="I41" s="2">
-        <v>44</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>720.3</v>
+        <v>332.5</v>
       </c>
       <c r="C42" s="2">
-        <v>-7.29</v>
+        <v>-15.99</v>
       </c>
       <c r="D42" s="2">
-        <v>-8.41</v>
+        <v>-5.62</v>
       </c>
       <c r="E42" s="2">
-        <v>-4.34</v>
+        <v>-1.28</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="H42" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I42" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>238.4</v>
+        <v>2815.6</v>
       </c>
       <c r="C43" s="2">
-        <v>-5.79</v>
+        <v>1.71</v>
       </c>
       <c r="D43" s="2">
-        <v>-1.82</v>
+        <v>-13.59</v>
       </c>
       <c r="E43" s="2">
-        <v>-9.140000000000001</v>
+        <v>-6.92</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="H43" s="2">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="I43" s="2">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>401</v>
+        <v>1155</v>
       </c>
       <c r="C44" s="2">
-        <v>-10.2</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="D44" s="2">
-        <v>-9.5</v>
+        <v>-15.51</v>
       </c>
       <c r="E44" s="2">
-        <v>-3.61</v>
+        <v>-0.33</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H44" s="2">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="I44" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2098,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>1040.7</v>
+        <v>266</v>
       </c>
       <c r="C45" s="2">
-        <v>-9.56</v>
+        <v>-16.63</v>
       </c>
       <c r="D45" s="2">
-        <v>-6.49</v>
+        <v>-7.07</v>
       </c>
       <c r="E45" s="2">
-        <v>-6.24</v>
+        <v>-1.52</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="H45" s="2">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="I45" s="2">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,28 +2130,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>2010.4</v>
+        <v>12694</v>
       </c>
       <c r="C46" s="2">
-        <v>-12.78</v>
+        <v>-5.59</v>
       </c>
       <c r="D46" s="2">
-        <v>-7.05</v>
+        <v>-4.4</v>
       </c>
       <c r="E46" s="2">
-        <v>-5.97</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="H46" s="2">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="I46" s="2">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>232.25</v>
+        <v>984.8</v>
       </c>
       <c r="C47" s="2">
-        <v>-18.77</v>
+        <v>-2.47</v>
       </c>
       <c r="D47" s="2">
-        <v>-5.38</v>
+        <v>-14.21</v>
       </c>
       <c r="E47" s="2">
-        <v>-4.03</v>
+        <v>-7.88</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H47" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I47" s="2">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,28 +2194,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>266</v>
+        <v>1973.4</v>
       </c>
       <c r="C48" s="2">
-        <v>-10.07</v>
+        <v>-13.68</v>
       </c>
       <c r="D48" s="2">
-        <v>-8.67</v>
+        <v>-8.27</v>
       </c>
       <c r="E48" s="2">
-        <v>-7.32</v>
+        <v>-5.45</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
       </c>
       <c r="G48" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H48" s="2">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I48" s="2">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,28 +2226,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>319.4</v>
+        <v>264.1</v>
       </c>
       <c r="C49" s="2">
-        <v>-9.119999999999999</v>
+        <v>-12.79</v>
       </c>
       <c r="D49" s="2">
-        <v>-11.65</v>
+        <v>-9.15</v>
       </c>
       <c r="E49" s="2">
-        <v>-8.56</v>
+        <v>-6.56</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H49" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I49" s="2">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,28 +2258,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>266.05</v>
+        <v>311.5</v>
       </c>
       <c r="C50" s="2">
-        <v>-17.09</v>
+        <v>-8.44</v>
       </c>
       <c r="D50" s="2">
-        <v>-8.18</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="E50" s="2">
-        <v>-7.3</v>
+        <v>-10.26</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H50" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I50" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2290,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>330.05</v>
+        <v>1010</v>
       </c>
       <c r="C51" s="2">
-        <v>-19.54</v>
+        <v>-12.22</v>
       </c>
       <c r="D51" s="2">
-        <v>-10.08</v>
+        <v>-9.24</v>
       </c>
       <c r="E51" s="2">
-        <v>-5.94</v>
+        <v>-8.9</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H51" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I51" s="2">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2420,6 +2420,210 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
+    <col min="3" max="5" width="14.7109375" style="2" customWidth="1"/>
+    <col min="6" max="9" width="16.7109375" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1">
+        <v>322.75</v>
+      </c>
+      <c r="C2" s="2">
+        <v>28.13</v>
+      </c>
+      <c r="D2" s="2">
+        <v>24.42</v>
+      </c>
+      <c r="E2" s="2">
+        <v>4.03</v>
+      </c>
+      <c r="F2" s="2">
+        <v>100</v>
+      </c>
+      <c r="G2" s="2">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1">
+        <v>11919</v>
+      </c>
+      <c r="C3" s="2">
+        <v>19.29</v>
+      </c>
+      <c r="D3" s="2">
+        <v>23.77</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2.07</v>
+      </c>
+      <c r="F3" s="2">
+        <v>98</v>
+      </c>
+      <c r="G3" s="2">
+        <v>96</v>
+      </c>
+      <c r="H3" s="2">
+        <v>98</v>
+      </c>
+      <c r="I3" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1">
+        <v>5027</v>
+      </c>
+      <c r="C4" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="D4" s="2">
+        <v>17.92</v>
+      </c>
+      <c r="E4" s="2">
+        <v>-1.24</v>
+      </c>
+      <c r="F4" s="2">
+        <v>94</v>
+      </c>
+      <c r="G4" s="2">
+        <v>94</v>
+      </c>
+      <c r="H4" s="2">
+        <v>96</v>
+      </c>
+      <c r="I4" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1060.5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>12.29</v>
+      </c>
+      <c r="D5" s="2">
+        <v>8.65</v>
+      </c>
+      <c r="E5" s="2">
+        <v>-3.78</v>
+      </c>
+      <c r="F5" s="2">
+        <v>80</v>
+      </c>
+      <c r="G5" s="2">
+        <v>80</v>
+      </c>
+      <c r="H5" s="2">
+        <v>94</v>
+      </c>
+      <c r="I5" s="2">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C2:C5">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D5">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E5">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F5">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
+      <formula>80</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G5">
+    <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
+      <formula>80</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H5">
+    <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
+      <formula>80</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I5">
+    <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
+      <formula>80</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2462,16 +2666,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>328</v>
+        <v>322.75</v>
       </c>
       <c r="C2" s="2">
-        <v>28.38</v>
+        <v>28.13</v>
       </c>
       <c r="D2" s="2">
-        <v>24.41</v>
+        <v>24.42</v>
       </c>
       <c r="E2" s="2">
-        <v>5.64</v>
+        <v>4.03</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2491,28 +2695,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>3168.5</v>
+        <v>11919</v>
       </c>
       <c r="C3" s="2">
-        <v>36.53</v>
+        <v>19.29</v>
       </c>
       <c r="D3" s="2">
-        <v>3.56</v>
+        <v>23.77</v>
       </c>
       <c r="E3" s="2">
-        <v>3.28</v>
+        <v>2.07</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
       </c>
       <c r="G3" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H3" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="I3" s="2">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2520,28 +2724,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>11910</v>
+        <v>421.15</v>
       </c>
       <c r="C4" s="2">
-        <v>25</v>
+        <v>13.51</v>
       </c>
       <c r="D4" s="2">
-        <v>16.87</v>
+        <v>6.67</v>
       </c>
       <c r="E4" s="2">
-        <v>0.46</v>
+        <v>7.03</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H4" s="2">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="I4" s="2">
-        <v>98</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2549,115 +2753,115 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>5169.2</v>
+        <v>5027</v>
       </c>
       <c r="C5" s="2">
-        <v>16.76</v>
+        <v>15.6</v>
       </c>
       <c r="D5" s="2">
-        <v>18.61</v>
+        <v>17.92</v>
       </c>
       <c r="E5" s="2">
-        <v>3.38</v>
+        <v>-1.24</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
       </c>
       <c r="G5" s="2">
+        <v>94</v>
+      </c>
+      <c r="H5" s="2">
         <v>96</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>94</v>
-      </c>
-      <c r="I5" s="2">
-        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>1086.9</v>
+        <v>1596.9</v>
       </c>
       <c r="C6" s="2">
-        <v>12.15</v>
+        <v>11.33</v>
       </c>
       <c r="D6" s="2">
-        <v>10.09</v>
+        <v>14.27</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.3</v>
+        <v>-2.63</v>
       </c>
       <c r="F6" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G6" s="2">
         <v>92</v>
       </c>
       <c r="H6" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="I6" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>8059</v>
+        <v>3310</v>
       </c>
       <c r="C7" s="2">
-        <v>13.51</v>
+        <v>16.26</v>
       </c>
       <c r="D7" s="2">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="E7" s="2">
-        <v>0.11</v>
+        <v>-2.09</v>
       </c>
       <c r="F7" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G7" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H7" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I7" s="2">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1">
-        <v>1079.9</v>
+        <v>1060.5</v>
       </c>
       <c r="C8" s="2">
-        <v>17.87</v>
+        <v>12.29</v>
       </c>
       <c r="D8" s="2">
-        <v>12.21</v>
+        <v>8.65</v>
       </c>
       <c r="E8" s="2">
-        <v>-6.34</v>
+        <v>-3.78</v>
       </c>
       <c r="F8" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G8" s="2">
+        <v>80</v>
+      </c>
+      <c r="H8" s="2">
         <v>94</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <v>92</v>
-      </c>
-      <c r="I8" s="2">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2709,326 +2913,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
-    <col min="3" max="5" width="14.7109375" style="2" customWidth="1"/>
-    <col min="6" max="9" width="16.7109375" style="2" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1">
-        <v>328</v>
-      </c>
-      <c r="C2" s="2">
-        <v>28.38</v>
-      </c>
-      <c r="D2" s="2">
-        <v>24.41</v>
-      </c>
-      <c r="E2" s="2">
-        <v>5.64</v>
-      </c>
-      <c r="F2" s="2">
-        <v>100</v>
-      </c>
-      <c r="G2" s="2">
-        <v>100</v>
-      </c>
-      <c r="H2" s="2">
-        <v>100</v>
-      </c>
-      <c r="I2" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1">
-        <v>3168.5</v>
-      </c>
-      <c r="C3" s="2">
-        <v>36.53</v>
-      </c>
-      <c r="D3" s="2">
-        <v>3.56</v>
-      </c>
-      <c r="E3" s="2">
-        <v>3.28</v>
-      </c>
-      <c r="F3" s="2">
-        <v>98</v>
-      </c>
-      <c r="G3" s="2">
-        <v>86</v>
-      </c>
-      <c r="H3" s="2">
-        <v>80</v>
-      </c>
-      <c r="I3" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1">
-        <v>11910</v>
-      </c>
-      <c r="C4" s="2">
-        <v>25</v>
-      </c>
-      <c r="D4" s="2">
-        <v>16.87</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.46</v>
-      </c>
-      <c r="F4" s="2">
-        <v>96</v>
-      </c>
-      <c r="G4" s="2">
-        <v>98</v>
-      </c>
-      <c r="H4" s="2">
-        <v>98</v>
-      </c>
-      <c r="I4" s="2">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1">
-        <v>5169.2</v>
-      </c>
-      <c r="C5" s="2">
-        <v>16.76</v>
-      </c>
-      <c r="D5" s="2">
-        <v>18.61</v>
-      </c>
-      <c r="E5" s="2">
-        <v>3.38</v>
-      </c>
-      <c r="F5" s="2">
-        <v>94</v>
-      </c>
-      <c r="G5" s="2">
-        <v>96</v>
-      </c>
-      <c r="H5" s="2">
-        <v>94</v>
-      </c>
-      <c r="I5" s="2">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1086.9</v>
-      </c>
-      <c r="C6" s="2">
-        <v>12.15</v>
-      </c>
-      <c r="D6" s="2">
-        <v>10.09</v>
-      </c>
-      <c r="E6" s="2">
-        <v>-0.3</v>
-      </c>
-      <c r="F6" s="2">
-        <v>88</v>
-      </c>
-      <c r="G6" s="2">
-        <v>92</v>
-      </c>
-      <c r="H6" s="2">
-        <v>96</v>
-      </c>
-      <c r="I6" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1">
-        <v>3258</v>
-      </c>
-      <c r="C7" s="2">
-        <v>17.64</v>
-      </c>
-      <c r="D7" s="2">
-        <v>2.93</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="F7" s="2">
-        <v>86</v>
-      </c>
-      <c r="G7" s="2">
-        <v>88</v>
-      </c>
-      <c r="H7" s="2">
-        <v>74</v>
-      </c>
-      <c r="I7" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1">
-        <v>8059</v>
-      </c>
-      <c r="C8" s="2">
-        <v>13.51</v>
-      </c>
-      <c r="D8" s="2">
-        <v>6.6</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.11</v>
-      </c>
-      <c r="F8" s="2">
-        <v>84</v>
-      </c>
-      <c r="G8" s="2">
-        <v>80</v>
-      </c>
-      <c r="H8" s="2">
-        <v>86</v>
-      </c>
-      <c r="I8" s="2">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1">
-        <v>1079.9</v>
-      </c>
-      <c r="C9" s="2">
-        <v>17.87</v>
-      </c>
-      <c r="D9" s="2">
-        <v>12.21</v>
-      </c>
-      <c r="E9" s="2">
-        <v>-6.34</v>
-      </c>
-      <c r="F9" s="2">
-        <v>82</v>
-      </c>
-      <c r="G9" s="2">
-        <v>94</v>
-      </c>
-      <c r="H9" s="2">
-        <v>92</v>
-      </c>
-      <c r="I9" s="2">
-        <v>96</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="C2:C9">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
-    <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
-    <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
-    <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D5"/>
@@ -3056,13 +2940,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="2">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D2" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3070,13 +2954,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2">
+        <v>48</v>
+      </c>
+      <c r="D3" s="2">
         <v>50</v>
-      </c>
-      <c r="D3" s="2">
-        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3084,10 +2968,10 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C4" s="2">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2">
         <v>54</v>
@@ -3098,10 +2982,10 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D5" s="2">
         <v>54</v>

--- a/Report/RSReport/NSE_50_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_50_Perception_Report.xlsx
@@ -22,16 +22,19 @@
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-09-04</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-09-04</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-09-04</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-09-04</t>
+    <t>Price_2026-09-11</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-09-11</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-09-11</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-09-11</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-09-11</t>
   </si>
   <si>
     <t>RS_Score_2026-09-04</t>
@@ -43,153 +46,150 @@
     <t>RS_Score_2026-08-21</t>
   </si>
   <si>
-    <t>RS_Score_2026-08-14</t>
-  </si>
-  <si>
     <t>ETERNAL</t>
   </si>
   <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
     <t>BAJAJ-AUTO</t>
   </si>
   <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
     <t>TITAN</t>
   </si>
   <si>
+    <t>ADANIENT</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
     <t>BAJAJFINSV</t>
   </si>
   <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>TCS</t>
   </si>
   <si>
     <t>HCLTECH</t>
   </si>
   <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
-    <t>ADANIENT</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>SBILIFE</t>
+  </si>
+  <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>HDFCLIFE</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
   </si>
   <si>
     <t>INFY</t>
   </si>
   <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>ADANIPORTS</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>HINDALCO</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>SBILIFE</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>HDFCLIFE</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>M&amp;M</t>
-  </si>
-  <si>
     <t>ASIANPAINT</t>
   </si>
   <si>
+    <t>ITC</t>
+  </si>
+  <si>
     <t>WIPRO</t>
   </si>
   <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
     <t>MARUTI</t>
   </si>
   <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
     <t>HINDUNILVR</t>
   </si>
   <si>
-    <t>ITC</t>
-  </si>
-  <si>
     <t>TMPV</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
     <t>2026-09-04</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
   </si>
   <si>
     <t>2026-08-21</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>322.75</v>
+        <v>323.5</v>
       </c>
       <c r="C2" s="2">
-        <v>28.13</v>
+        <v>31.57</v>
       </c>
       <c r="D2" s="2">
-        <v>24.42</v>
+        <v>14.15</v>
       </c>
       <c r="E2" s="2">
-        <v>4.03</v>
+        <v>1.73</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -754,16 +754,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>11919</v>
+        <v>419</v>
       </c>
       <c r="C3" s="2">
-        <v>19.29</v>
+        <v>10.15</v>
       </c>
       <c r="D3" s="2">
-        <v>23.77</v>
+        <v>10.08</v>
       </c>
       <c r="E3" s="2">
-        <v>2.07</v>
+        <v>6.7</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
@@ -772,10 +772,10 @@
         <v>96</v>
       </c>
       <c r="H3" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I3" s="2">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>60</v>
@@ -786,28 +786,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>421.15</v>
+        <v>11768</v>
       </c>
       <c r="C4" s="2">
-        <v>13.51</v>
+        <v>12.63</v>
       </c>
       <c r="D4" s="2">
-        <v>6.67</v>
+        <v>17.25</v>
       </c>
       <c r="E4" s="2">
-        <v>7.03</v>
+        <v>0.9</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="I4" s="2">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>60</v>
@@ -818,16 +818,16 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>5027</v>
+        <v>5009.5</v>
       </c>
       <c r="C5" s="2">
-        <v>15.6</v>
+        <v>19.51</v>
       </c>
       <c r="D5" s="2">
-        <v>17.92</v>
+        <v>12.08</v>
       </c>
       <c r="E5" s="2">
-        <v>-1.24</v>
+        <v>-1.16</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
@@ -836,10 +836,10 @@
         <v>94</v>
       </c>
       <c r="H5" s="2">
+        <v>94</v>
+      </c>
+      <c r="I5" s="2">
         <v>96</v>
-      </c>
-      <c r="I5" s="2">
-        <v>94</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>60</v>
@@ -850,28 +850,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>1992.1</v>
+        <v>3060</v>
       </c>
       <c r="C6" s="2">
-        <v>12.62</v>
+        <v>22.44</v>
       </c>
       <c r="D6" s="2">
-        <v>13.33</v>
+        <v>-4.57</v>
       </c>
       <c r="E6" s="2">
-        <v>-1.44</v>
+        <v>1.75</v>
       </c>
       <c r="F6" s="2">
         <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="I6" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
@@ -882,16 +882,16 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>1596.9</v>
+        <v>3319</v>
       </c>
       <c r="C7" s="2">
-        <v>11.33</v>
+        <v>11.57</v>
       </c>
       <c r="D7" s="2">
-        <v>14.27</v>
+        <v>3.62</v>
       </c>
       <c r="E7" s="2">
-        <v>-2.63</v>
+        <v>2.11</v>
       </c>
       <c r="F7" s="2">
         <v>90</v>
@@ -900,10 +900,10 @@
         <v>92</v>
       </c>
       <c r="H7" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I7" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>60</v>
@@ -914,28 +914,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>3310</v>
+        <v>1304</v>
       </c>
       <c r="C8" s="2">
-        <v>16.26</v>
+        <v>3.87</v>
       </c>
       <c r="D8" s="2">
-        <v>7.8</v>
+        <v>5.49</v>
       </c>
       <c r="E8" s="2">
-        <v>-2.09</v>
+        <v>2.05</v>
       </c>
       <c r="F8" s="2">
         <v>88</v>
       </c>
       <c r="G8" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H8" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="I8" s="2">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>60</v>
@@ -946,28 +946,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>1293.4</v>
+        <v>8900</v>
       </c>
       <c r="C9" s="2">
-        <v>8.84</v>
+        <v>10.25</v>
       </c>
       <c r="D9" s="2">
-        <v>18.52</v>
+        <v>0.25</v>
       </c>
       <c r="E9" s="2">
-        <v>-4.7</v>
+        <v>0.84</v>
       </c>
       <c r="F9" s="2">
         <v>86</v>
       </c>
       <c r="G9" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H9" s="2">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="I9" s="2">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>60</v>
@@ -978,28 +978,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>1325</v>
+        <v>1541</v>
       </c>
       <c r="C10" s="2">
-        <v>5.21</v>
+        <v>8.48</v>
       </c>
       <c r="D10" s="2">
-        <v>8.130000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="E10" s="2">
-        <v>1.77</v>
+        <v>-4.29</v>
       </c>
       <c r="F10" s="2">
         <v>84</v>
       </c>
       <c r="G10" s="2">
+        <v>90</v>
+      </c>
+      <c r="H10" s="2">
+        <v>92</v>
+      </c>
+      <c r="I10" s="2">
         <v>74</v>
-      </c>
-      <c r="H10" s="2">
-        <v>56</v>
-      </c>
-      <c r="I10" s="2">
-        <v>42</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>60</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>1423.2</v>
+        <v>426.4</v>
       </c>
       <c r="C11" s="2">
-        <v>12.94</v>
+        <v>-5.79</v>
       </c>
       <c r="D11" s="2">
-        <v>3.43</v>
+        <v>1.21</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.6</v>
+        <v>5.72</v>
       </c>
       <c r="F11" s="2">
         <v>82</v>
       </c>
       <c r="G11" s="2">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="I11" s="2">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>60</v>
@@ -1042,28 +1042,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1060.5</v>
+        <v>1764.6</v>
       </c>
       <c r="C12" s="2">
-        <v>12.29</v>
+        <v>0.27</v>
       </c>
       <c r="D12" s="2">
-        <v>8.65</v>
+        <v>-5.35</v>
       </c>
       <c r="E12" s="2">
-        <v>-3.78</v>
+        <v>4.35</v>
       </c>
       <c r="F12" s="2">
         <v>80</v>
       </c>
       <c r="G12" s="2">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H12" s="2">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="I12" s="2">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>60</v>
@@ -1074,28 +1074,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>2938</v>
+        <v>1379.3</v>
       </c>
       <c r="C13" s="2">
-        <v>18.25</v>
+        <v>9.83</v>
       </c>
       <c r="D13" s="2">
-        <v>-0.83</v>
+        <v>-2.52</v>
       </c>
       <c r="E13" s="2">
-        <v>-2.39</v>
+        <v>-2.54</v>
       </c>
       <c r="F13" s="2">
         <v>78</v>
       </c>
       <c r="G13" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="H13" s="2">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="I13" s="2">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>60</v>
@@ -1106,28 +1106,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>8650</v>
+        <v>1034.5</v>
       </c>
       <c r="C14" s="2">
-        <v>11.92</v>
+        <v>11.2</v>
       </c>
       <c r="D14" s="2">
-        <v>0.06</v>
+        <v>0.52</v>
       </c>
       <c r="E14" s="2">
-        <v>-2.83</v>
+        <v>-5.03</v>
       </c>
       <c r="F14" s="2">
         <v>76</v>
       </c>
       <c r="G14" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H14" s="2">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="I14" s="2">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>60</v>
@@ -1138,28 +1138,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>1899</v>
+        <v>1913.5</v>
       </c>
       <c r="C15" s="2">
-        <v>4.41</v>
+        <v>6.74</v>
       </c>
       <c r="D15" s="2">
-        <v>1.56</v>
+        <v>2.29</v>
       </c>
       <c r="E15" s="2">
-        <v>-2.33</v>
+        <v>-4.56</v>
       </c>
       <c r="F15" s="2">
         <v>74</v>
       </c>
       <c r="G15" s="2">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H15" s="2">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="I15" s="2">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>60</v>
@@ -1170,28 +1170,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>7630.5</v>
+        <v>1038.6</v>
       </c>
       <c r="C16" s="2">
-        <v>5.2</v>
+        <v>0.24</v>
       </c>
       <c r="D16" s="2">
-        <v>3.83</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="E16" s="2">
-        <v>-4.32</v>
+        <v>3.48</v>
       </c>
       <c r="F16" s="2">
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="H16" s="2">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="I16" s="2">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -1202,16 +1202,16 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>1130</v>
+        <v>1014</v>
       </c>
       <c r="C17" s="2">
-        <v>-1.19</v>
+        <v>-0.41</v>
       </c>
       <c r="D17" s="2">
-        <v>9</v>
+        <v>3.97</v>
       </c>
       <c r="E17" s="2">
-        <v>-4.48</v>
+        <v>-3.42</v>
       </c>
       <c r="F17" s="2">
         <v>70</v>
@@ -1220,10 +1220,10 @@
         <v>60</v>
       </c>
       <c r="H17" s="2">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="I17" s="2">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -1234,28 +1234,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>1273</v>
+        <v>4973</v>
       </c>
       <c r="C18" s="2">
-        <v>-0.09</v>
+        <v>15.67</v>
       </c>
       <c r="D18" s="2">
-        <v>-6.1</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="E18" s="2">
-        <v>2.06</v>
+        <v>-5.73</v>
       </c>
       <c r="F18" s="2">
         <v>68</v>
       </c>
       <c r="G18" s="2">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="H18" s="2">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="I18" s="2">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>60</v>
@@ -1266,28 +1266,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>1707.3</v>
+        <v>1861</v>
       </c>
       <c r="C19" s="2">
-        <v>-1.61</v>
+        <v>-0.36</v>
       </c>
       <c r="D19" s="2">
-        <v>-3.87</v>
+        <v>-2.45</v>
       </c>
       <c r="E19" s="2">
-        <v>1.56</v>
+        <v>-1.12</v>
       </c>
       <c r="F19" s="2">
         <v>66</v>
       </c>
       <c r="G19" s="2">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="H19" s="2">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="I19" s="2">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>60</v>
@@ -1298,28 +1298,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>4977</v>
+        <v>7530</v>
       </c>
       <c r="C20" s="2">
-        <v>16.77</v>
+        <v>5.64</v>
       </c>
       <c r="D20" s="2">
-        <v>-6.36</v>
+        <v>1.84</v>
       </c>
       <c r="E20" s="2">
-        <v>-6.68</v>
+        <v>-6.46</v>
       </c>
       <c r="F20" s="2">
         <v>64</v>
       </c>
       <c r="G20" s="2">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="H20" s="2">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="I20" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>60</v>
@@ -1330,28 +1330,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>2304</v>
+        <v>1246</v>
       </c>
       <c r="C21" s="2">
-        <v>-3.42</v>
+        <v>-1.99</v>
       </c>
       <c r="D21" s="2">
-        <v>10.43</v>
+        <v>-6.92</v>
       </c>
       <c r="E21" s="2">
-        <v>-5.02</v>
+        <v>1.52</v>
       </c>
       <c r="F21" s="2">
         <v>62</v>
       </c>
       <c r="G21" s="2">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="H21" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I21" s="2">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>60</v>
@@ -1362,28 +1362,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>1010</v>
+        <v>2200.8</v>
       </c>
       <c r="C22" s="2">
-        <v>-2.63</v>
+        <v>-6.27</v>
       </c>
       <c r="D22" s="2">
-        <v>5.34</v>
+        <v>7.55</v>
       </c>
       <c r="E22" s="2">
-        <v>-4.18</v>
+        <v>-4.86</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
       </c>
       <c r="G22" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H22" s="2">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="I22" s="2">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>60</v>
@@ -1394,16 +1394,16 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>1041</v>
+        <v>1206.1</v>
       </c>
       <c r="C23" s="2">
-        <v>9</v>
+        <v>1.97</v>
       </c>
       <c r="D23" s="2">
-        <v>1.38</v>
+        <v>7.42</v>
       </c>
       <c r="E23" s="2">
-        <v>-8.51</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="F23" s="2">
         <v>58</v>
@@ -1412,10 +1412,10 @@
         <v>86</v>
       </c>
       <c r="H23" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I23" s="2">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>60</v>
@@ -1426,28 +1426,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>405.35</v>
+        <v>3930.7</v>
       </c>
       <c r="C24" s="2">
-        <v>-6.38</v>
+        <v>0.73</v>
       </c>
       <c r="D24" s="2">
-        <v>-1.38</v>
+        <v>-2.73</v>
       </c>
       <c r="E24" s="2">
-        <v>0.38</v>
+        <v>-3.82</v>
       </c>
       <c r="F24" s="2">
         <v>56</v>
       </c>
       <c r="G24" s="2">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H24" s="2">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="I24" s="2">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>60</v>
@@ -1458,28 +1458,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>1840</v>
+        <v>1366</v>
       </c>
       <c r="C25" s="2">
-        <v>1.97</v>
+        <v>5.66</v>
       </c>
       <c r="D25" s="2">
-        <v>1.2</v>
+        <v>-7.22</v>
       </c>
       <c r="E25" s="2">
-        <v>-5.3</v>
+        <v>-4.58</v>
       </c>
       <c r="F25" s="2">
         <v>54</v>
       </c>
       <c r="G25" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H25" s="2">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="I25" s="2">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>60</v>
@@ -1490,28 +1490,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>1322</v>
+        <v>995.7</v>
       </c>
       <c r="C26" s="2">
-        <v>-9.23</v>
+        <v>4.11</v>
       </c>
       <c r="D26" s="2">
-        <v>1.61</v>
+        <v>-4.05</v>
       </c>
       <c r="E26" s="2">
-        <v>-0.4</v>
+        <v>-6.17</v>
       </c>
       <c r="F26" s="2">
         <v>52</v>
       </c>
       <c r="G26" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H26" s="2">
         <v>48</v>
       </c>
       <c r="I26" s="2">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>60</v>
@@ -1522,28 +1522,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>1775</v>
+        <v>1831.1</v>
       </c>
       <c r="C27" s="2">
-        <v>-2.48</v>
+        <v>5.36</v>
       </c>
       <c r="D27" s="2">
-        <v>1.12</v>
+        <v>-3.72</v>
       </c>
       <c r="E27" s="2">
-        <v>-4.31</v>
+        <v>-7.02</v>
       </c>
       <c r="F27" s="2">
         <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="H27" s="2">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="I27" s="2">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>60</v>
@@ -1554,28 +1554,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>415.35</v>
+        <v>1028.6</v>
       </c>
       <c r="C28" s="2">
-        <v>-11.19</v>
+        <v>5.99</v>
       </c>
       <c r="D28" s="2">
-        <v>-4.19</v>
+        <v>-3.17</v>
       </c>
       <c r="E28" s="2">
-        <v>2.34</v>
+        <v>-8.32</v>
       </c>
       <c r="F28" s="2">
         <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="H28" s="2">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="I28" s="2">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>60</v>
@@ -1586,28 +1586,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>546.4</v>
+        <v>404.35</v>
       </c>
       <c r="C29" s="2">
-        <v>-6.8</v>
+        <v>-6.26</v>
       </c>
       <c r="D29" s="2">
-        <v>-6.32</v>
+        <v>-4.85</v>
       </c>
       <c r="E29" s="2">
-        <v>1.19</v>
+        <v>-1.96</v>
       </c>
       <c r="F29" s="2">
         <v>46</v>
       </c>
       <c r="G29" s="2">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="H29" s="2">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="I29" s="2">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>60</v>
@@ -1618,28 +1618,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>188.79</v>
+        <v>269.1</v>
       </c>
       <c r="C30" s="2">
-        <v>-9.210000000000001</v>
+        <v>-13.44</v>
       </c>
       <c r="D30" s="2">
-        <v>-0.41</v>
+        <v>-5.71</v>
       </c>
       <c r="E30" s="2">
-        <v>-0.76</v>
+        <v>1.11</v>
       </c>
       <c r="F30" s="2">
         <v>44</v>
       </c>
       <c r="G30" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H30" s="2">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I30" s="2">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>60</v>
@@ -1650,28 +1650,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>1385</v>
+        <v>183</v>
       </c>
       <c r="C31" s="2">
-        <v>4.72</v>
+        <v>-11.93</v>
       </c>
       <c r="D31" s="2">
-        <v>-4.75</v>
+        <v>-4.12</v>
       </c>
       <c r="E31" s="2">
-        <v>-5.63</v>
+        <v>-1.61</v>
       </c>
       <c r="F31" s="2">
         <v>42</v>
       </c>
       <c r="G31" s="2">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H31" s="2">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="I31" s="2">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>60</v>
@@ -1682,28 +1682,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>3975</v>
+        <v>333.4</v>
       </c>
       <c r="C32" s="2">
-        <v>-2.12</v>
+        <v>-14.24</v>
       </c>
       <c r="D32" s="2">
-        <v>-4.57</v>
+        <v>-5.4</v>
       </c>
       <c r="E32" s="2">
-        <v>-2.57</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2">
         <v>40</v>
       </c>
       <c r="G32" s="2">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="H32" s="2">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="I32" s="2">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>60</v>
@@ -1714,28 +1714,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>11275</v>
+        <v>11000</v>
       </c>
       <c r="C33" s="2">
-        <v>-2.15</v>
+        <v>-5.41</v>
       </c>
       <c r="D33" s="2">
-        <v>1.49</v>
+        <v>-3.74</v>
       </c>
       <c r="E33" s="2">
-        <v>-6.34</v>
+        <v>-5.83</v>
       </c>
       <c r="F33" s="2">
         <v>38</v>
       </c>
       <c r="G33" s="2">
+        <v>50</v>
+      </c>
+      <c r="H33" s="2">
         <v>44</v>
       </c>
-      <c r="H33" s="2">
+      <c r="I33" s="2">
         <v>46</v>
-      </c>
-      <c r="I33" s="2">
-        <v>44</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>60</v>
@@ -1746,28 +1746,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>1416</v>
+        <v>1257.5</v>
       </c>
       <c r="C34" s="2">
-        <v>-2.35</v>
+        <v>-9</v>
       </c>
       <c r="D34" s="2">
-        <v>2.56</v>
+        <v>-4.83</v>
       </c>
       <c r="E34" s="2">
-        <v>-7.37</v>
+        <v>-4.45</v>
       </c>
       <c r="F34" s="2">
         <v>36</v>
       </c>
       <c r="G34" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H34" s="2">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="I34" s="2">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>60</v>
@@ -1778,28 +1778,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>239.5</v>
+        <v>1386.2</v>
       </c>
       <c r="C35" s="2">
-        <v>-5.02</v>
+        <v>-6.01</v>
       </c>
       <c r="D35" s="2">
-        <v>1.42</v>
+        <v>-5.49</v>
       </c>
       <c r="E35" s="2">
-        <v>-5.71</v>
+        <v>-5.7</v>
       </c>
       <c r="F35" s="2">
         <v>34</v>
       </c>
       <c r="G35" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I35" s="2">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>60</v>
@@ -1810,28 +1810,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>1016.1</v>
+        <v>3107</v>
       </c>
       <c r="C36" s="2">
-        <v>-3.18</v>
+        <v>-3.27</v>
       </c>
       <c r="D36" s="2">
-        <v>-1.93</v>
+        <v>-2.94</v>
       </c>
       <c r="E36" s="2">
-        <v>-5.13</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="F36" s="2">
         <v>32</v>
       </c>
       <c r="G36" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H36" s="2">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="I36" s="2">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>60</v>
@@ -1842,28 +1842,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>3150</v>
+        <v>2818.7</v>
       </c>
       <c r="C37" s="2">
-        <v>2.47</v>
+        <v>1.27</v>
       </c>
       <c r="D37" s="2">
-        <v>2.91</v>
+        <v>-15.7</v>
       </c>
       <c r="E37" s="2">
-        <v>-10.44</v>
+        <v>-4.32</v>
       </c>
       <c r="F37" s="2">
         <v>30</v>
       </c>
       <c r="G37" s="2">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="H37" s="2">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="I37" s="2">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>60</v>
@@ -1874,28 +1874,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>2527.3</v>
+        <v>229.9</v>
       </c>
       <c r="C38" s="2">
-        <v>4.13</v>
+        <v>-4.12</v>
       </c>
       <c r="D38" s="2">
-        <v>-4.88</v>
+        <v>-3.98</v>
       </c>
       <c r="E38" s="2">
-        <v>-8.1</v>
+        <v>-7.95</v>
       </c>
       <c r="F38" s="2">
         <v>28</v>
       </c>
       <c r="G38" s="2">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H38" s="2">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I38" s="2">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>60</v>
@@ -1906,28 +1906,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>176.4</v>
+        <v>1700.6</v>
       </c>
       <c r="C39" s="2">
-        <v>-11.13</v>
+        <v>-9.75</v>
       </c>
       <c r="D39" s="2">
-        <v>1.67</v>
+        <v>-4.87</v>
       </c>
       <c r="E39" s="2">
-        <v>-4.91</v>
+        <v>-5.02</v>
       </c>
       <c r="F39" s="2">
         <v>26</v>
       </c>
       <c r="G39" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H39" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I39" s="2">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>60</v>
@@ -1938,28 +1938,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>234.65</v>
+        <v>232.5</v>
       </c>
       <c r="C40" s="2">
-        <v>-19.55</v>
+        <v>-16.91</v>
       </c>
       <c r="D40" s="2">
-        <v>0.68</v>
+        <v>-4.27</v>
       </c>
       <c r="E40" s="2">
-        <v>-1.75</v>
+        <v>-2.1</v>
       </c>
       <c r="F40" s="2">
         <v>24</v>
       </c>
       <c r="G40" s="2">
+        <v>22</v>
+      </c>
+      <c r="H40" s="2">
         <v>10</v>
       </c>
-      <c r="H40" s="2">
+      <c r="I40" s="2">
         <v>16</v>
-      </c>
-      <c r="I40" s="2">
-        <v>2</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>60</v>
@@ -1970,28 +1970,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>712.1</v>
+        <v>530</v>
       </c>
       <c r="C41" s="2">
-        <v>-7.12</v>
+        <v>-14.58</v>
       </c>
       <c r="D41" s="2">
-        <v>-10.86</v>
+        <v>-6.06</v>
       </c>
       <c r="E41" s="2">
-        <v>-2.59</v>
+        <v>-2.39</v>
       </c>
       <c r="F41" s="2">
         <v>22</v>
       </c>
       <c r="G41" s="2">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="H41" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I41" s="2">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>60</v>
@@ -2002,28 +2002,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>332.5</v>
+        <v>708.25</v>
       </c>
       <c r="C42" s="2">
-        <v>-15.99</v>
+        <v>-5.72</v>
       </c>
       <c r="D42" s="2">
-        <v>-5.62</v>
+        <v>-14.65</v>
       </c>
       <c r="E42" s="2">
-        <v>-1.28</v>
+        <v>-2.85</v>
       </c>
       <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H42" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I42" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>60</v>
@@ -2034,28 +2034,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>2815.6</v>
+        <v>1165.5</v>
       </c>
       <c r="C43" s="2">
-        <v>1.71</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="D43" s="2">
-        <v>-13.59</v>
+        <v>-14.26</v>
       </c>
       <c r="E43" s="2">
-        <v>-6.92</v>
+        <v>-2.22</v>
       </c>
       <c r="F43" s="2">
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="H43" s="2">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="I43" s="2">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>60</v>
@@ -2066,28 +2066,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>1155</v>
+        <v>1037.7</v>
       </c>
       <c r="C44" s="2">
-        <v>-9.699999999999999</v>
+        <v>-9.93</v>
       </c>
       <c r="D44" s="2">
-        <v>-15.51</v>
+        <v>-0.43</v>
       </c>
       <c r="E44" s="2">
-        <v>-0.33</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="H44" s="2">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I44" s="2">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>60</v>
@@ -2098,28 +2098,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>266</v>
+        <v>2472.5</v>
       </c>
       <c r="C45" s="2">
-        <v>-16.63</v>
+        <v>-2.81</v>
       </c>
       <c r="D45" s="2">
-        <v>-7.07</v>
+        <v>-10.25</v>
       </c>
       <c r="E45" s="2">
-        <v>-1.52</v>
+        <v>-8</v>
       </c>
       <c r="F45" s="2">
         <v>14</v>
       </c>
       <c r="G45" s="2">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H45" s="2">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="I45" s="2">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>60</v>
@@ -2130,28 +2130,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>12694</v>
+        <v>259.85</v>
       </c>
       <c r="C46" s="2">
-        <v>-5.59</v>
+        <v>-12.73</v>
       </c>
       <c r="D46" s="2">
-        <v>-4.4</v>
+        <v>-9.85</v>
       </c>
       <c r="E46" s="2">
-        <v>-9.949999999999999</v>
+        <v>-4.83</v>
       </c>
       <c r="F46" s="2">
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="H46" s="2">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="I46" s="2">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>60</v>
@@ -2162,28 +2162,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>984.8</v>
+        <v>167.4</v>
       </c>
       <c r="C47" s="2">
-        <v>-2.47</v>
+        <v>-13.92</v>
       </c>
       <c r="D47" s="2">
-        <v>-14.21</v>
+        <v>-2.87</v>
       </c>
       <c r="E47" s="2">
-        <v>-7.88</v>
+        <v>-7.97</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H47" s="2">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="I47" s="2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>60</v>
@@ -2194,16 +2194,16 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>1973.4</v>
+        <v>12590</v>
       </c>
       <c r="C48" s="2">
-        <v>-13.68</v>
+        <v>-5.69</v>
       </c>
       <c r="D48" s="2">
-        <v>-8.27</v>
+        <v>-12.03</v>
       </c>
       <c r="E48" s="2">
-        <v>-5.45</v>
+        <v>-8.5</v>
       </c>
       <c r="F48" s="2">
         <v>8</v>
@@ -2212,10 +2212,10 @@
         <v>12</v>
       </c>
       <c r="H48" s="2">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="I48" s="2">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>60</v>
@@ -2226,16 +2226,16 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>264.1</v>
+        <v>1927</v>
       </c>
       <c r="C49" s="2">
-        <v>-12.79</v>
+        <v>-15.63</v>
       </c>
       <c r="D49" s="2">
-        <v>-9.15</v>
+        <v>-12.49</v>
       </c>
       <c r="E49" s="2">
-        <v>-6.56</v>
+        <v>-6.23</v>
       </c>
       <c r="F49" s="2">
         <v>6</v>
@@ -2244,10 +2244,10 @@
         <v>8</v>
       </c>
       <c r="H49" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I49" s="2">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>60</v>
@@ -2258,28 +2258,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>311.5</v>
+        <v>301.1</v>
       </c>
       <c r="C50" s="2">
-        <v>-8.44</v>
+        <v>-12.25</v>
       </c>
       <c r="D50" s="2">
-        <v>-9.720000000000001</v>
+        <v>-13.24</v>
       </c>
       <c r="E50" s="2">
-        <v>-10.26</v>
+        <v>-8.81</v>
       </c>
       <c r="F50" s="2">
         <v>4</v>
       </c>
       <c r="G50" s="2">
+        <v>4</v>
+      </c>
+      <c r="H50" s="2">
         <v>6</v>
       </c>
-      <c r="H50" s="2">
+      <c r="I50" s="2">
         <v>2</v>
-      </c>
-      <c r="I50" s="2">
-        <v>18</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>60</v>
@@ -2290,28 +2290,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>1010</v>
+        <v>991</v>
       </c>
       <c r="C51" s="2">
-        <v>-12.22</v>
+        <v>-21.37</v>
       </c>
       <c r="D51" s="2">
-        <v>-9.24</v>
+        <v>-11.35</v>
       </c>
       <c r="E51" s="2">
-        <v>-8.9</v>
+        <v>-7.61</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
       <c r="G51" s="2">
+        <v>2</v>
+      </c>
+      <c r="H51" s="2">
         <v>14</v>
       </c>
-      <c r="H51" s="2">
+      <c r="I51" s="2">
         <v>18</v>
-      </c>
-      <c r="I51" s="2">
-        <v>34</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>60</v>
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>322.75</v>
+        <v>323.5</v>
       </c>
       <c r="C2" s="2">
-        <v>28.13</v>
+        <v>31.57</v>
       </c>
       <c r="D2" s="2">
-        <v>24.42</v>
+        <v>14.15</v>
       </c>
       <c r="E2" s="2">
-        <v>4.03</v>
+        <v>1.73</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2488,28 +2488,28 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1">
-        <v>11919</v>
+        <v>11768</v>
       </c>
       <c r="C3" s="2">
-        <v>19.29</v>
+        <v>12.63</v>
       </c>
       <c r="D3" s="2">
-        <v>23.77</v>
+        <v>17.25</v>
       </c>
       <c r="E3" s="2">
-        <v>2.07</v>
+        <v>0.9</v>
       </c>
       <c r="F3" s="2">
+        <v>96</v>
+      </c>
+      <c r="G3" s="2">
         <v>98</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
         <v>96</v>
-      </c>
-      <c r="H3" s="2">
-        <v>98</v>
       </c>
       <c r="I3" s="2">
         <v>98</v>
@@ -2520,16 +2520,16 @@
         <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>5027</v>
+        <v>5009.5</v>
       </c>
       <c r="C4" s="2">
-        <v>15.6</v>
+        <v>19.51</v>
       </c>
       <c r="D4" s="2">
-        <v>17.92</v>
+        <v>12.08</v>
       </c>
       <c r="E4" s="2">
-        <v>-1.24</v>
+        <v>-1.16</v>
       </c>
       <c r="F4" s="2">
         <v>94</v>
@@ -2538,39 +2538,39 @@
         <v>94</v>
       </c>
       <c r="H4" s="2">
+        <v>94</v>
+      </c>
+      <c r="I4" s="2">
         <v>96</v>
-      </c>
-      <c r="I4" s="2">
-        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>1060.5</v>
+        <v>3319</v>
       </c>
       <c r="C5" s="2">
-        <v>12.29</v>
+        <v>11.57</v>
       </c>
       <c r="D5" s="2">
-        <v>8.65</v>
+        <v>3.62</v>
       </c>
       <c r="E5" s="2">
-        <v>-3.78</v>
+        <v>2.11</v>
       </c>
       <c r="F5" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H5" s="2">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="I5" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2666,16 +2666,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>322.75</v>
+        <v>323.5</v>
       </c>
       <c r="C2" s="2">
-        <v>28.13</v>
+        <v>31.57</v>
       </c>
       <c r="D2" s="2">
-        <v>24.42</v>
+        <v>14.15</v>
       </c>
       <c r="E2" s="2">
-        <v>4.03</v>
+        <v>1.73</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -2695,16 +2695,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>11919</v>
+        <v>419</v>
       </c>
       <c r="C3" s="2">
-        <v>19.29</v>
+        <v>10.15</v>
       </c>
       <c r="D3" s="2">
-        <v>23.77</v>
+        <v>10.08</v>
       </c>
       <c r="E3" s="2">
-        <v>2.07</v>
+        <v>6.7</v>
       </c>
       <c r="F3" s="2">
         <v>98</v>
@@ -2713,10 +2713,10 @@
         <v>96</v>
       </c>
       <c r="H3" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I3" s="2">
-        <v>98</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2724,28 +2724,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>421.15</v>
+        <v>11768</v>
       </c>
       <c r="C4" s="2">
-        <v>13.51</v>
+        <v>12.63</v>
       </c>
       <c r="D4" s="2">
-        <v>6.67</v>
+        <v>17.25</v>
       </c>
       <c r="E4" s="2">
-        <v>7.03</v>
+        <v>0.9</v>
       </c>
       <c r="F4" s="2">
         <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="I4" s="2">
-        <v>48</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2753,16 +2753,16 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>5027</v>
+        <v>5009.5</v>
       </c>
       <c r="C5" s="2">
-        <v>15.6</v>
+        <v>19.51</v>
       </c>
       <c r="D5" s="2">
-        <v>17.92</v>
+        <v>12.08</v>
       </c>
       <c r="E5" s="2">
-        <v>-1.24</v>
+        <v>-1.16</v>
       </c>
       <c r="F5" s="2">
         <v>94</v>
@@ -2771,10 +2771,10 @@
         <v>94</v>
       </c>
       <c r="H5" s="2">
+        <v>94</v>
+      </c>
+      <c r="I5" s="2">
         <v>96</v>
-      </c>
-      <c r="I5" s="2">
-        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2782,16 +2782,16 @@
         <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>1596.9</v>
+        <v>3319</v>
       </c>
       <c r="C6" s="2">
-        <v>11.33</v>
+        <v>11.57</v>
       </c>
       <c r="D6" s="2">
-        <v>14.27</v>
+        <v>3.62</v>
       </c>
       <c r="E6" s="2">
-        <v>-2.63</v>
+        <v>2.11</v>
       </c>
       <c r="F6" s="2">
         <v>90</v>
@@ -2800,10 +2800,10 @@
         <v>92</v>
       </c>
       <c r="H6" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I6" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2811,57 +2811,57 @@
         <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>3310</v>
+        <v>1304</v>
       </c>
       <c r="C7" s="2">
-        <v>16.26</v>
+        <v>3.87</v>
       </c>
       <c r="D7" s="2">
-        <v>7.8</v>
+        <v>5.49</v>
       </c>
       <c r="E7" s="2">
-        <v>-2.09</v>
+        <v>2.05</v>
       </c>
       <c r="F7" s="2">
         <v>88</v>
       </c>
       <c r="G7" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H7" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="I7" s="2">
-        <v>74</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1">
-        <v>1060.5</v>
+        <v>1541</v>
       </c>
       <c r="C8" s="2">
-        <v>12.29</v>
+        <v>8.48</v>
       </c>
       <c r="D8" s="2">
-        <v>8.65</v>
+        <v>9.56</v>
       </c>
       <c r="E8" s="2">
-        <v>-3.78</v>
+        <v>-4.29</v>
       </c>
       <c r="F8" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G8" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H8" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I8" s="2">
-        <v>92</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2943,10 +2943,10 @@
         <v>22</v>
       </c>
       <c r="C2" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2954,13 +2954,13 @@
         <v>66</v>
       </c>
       <c r="B3" s="2">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2968,13 +2968,13 @@
         <v>67</v>
       </c>
       <c r="B4" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C4" s="2">
+        <v>48</v>
+      </c>
+      <c r="D4" s="2">
         <v>50</v>
-      </c>
-      <c r="D4" s="2">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2982,13 +2982,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="2">
+        <v>36</v>
+      </c>
+      <c r="C5" s="2">
+        <v>50</v>
+      </c>
+      <c r="D5" s="2">
         <v>52</v>
-      </c>
-      <c r="C5" s="2">
-        <v>66</v>
-      </c>
-      <c r="D5" s="2">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
